--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>645d7d7-dirty</t>
+          <t>932d1eb-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.60949299021477</v>
+        <v>0.4861186254890529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.033630367943769</v>
+        <v>4.948056657833936</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.148148880762615e-16</v>
+        <v>2.474325229812098e-16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.345341840795361</v>
+        <v>0.8836120799594211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.532946721359457e-14</v>
+        <v>-7.944965084580525e-15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09078789191347983</v>
+        <v>0.07007773737851213</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90.78789191347983</v>
+        <v>70.07773737851213</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2001530403024191</v>
+        <v>0.1544949651126453</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02500000998616425</v>
+        <v>-9.998916929839549e-09</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5813115556402076</v>
+        <v>0.4719469279513472</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.18161141661032</v>
+        <v>8.475529143122294</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.172007954129075</v>
+        <v>4.687449301023788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41821.22376080244</v>
+        <v>39550.96498477143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.04999999010101803</v>
+        <v>0.1000000098892254</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6721799329461787</v>
+        <v>0.4999999900567649</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02999999002751742</v>
+        <v>0.05000000993196219</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.295592516496379</v>
+        <v>0.9369224915798031</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>243.3298652796471</v>
+        <v>86.48660579717323</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.005324428692743563</v>
+        <v>0.01083315136423617</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01360115845257378</v>
+        <v>0.01065190338180691</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.15962593950728</v>
+        <v>1.01542662201922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09398320197010014</v>
+        <v>0.1444321744683164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1089853588824799</v>
+        <v>0.1466602750312531</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.33865111210197</v>
+        <v>7.03047382452842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.850000005846944</v>
+        <v>0.8500000084288141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1799999981912146</v>
+        <v>0.2232511737645986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04499999954780364</v>
+        <v>0.05581279344114965</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008099999837209312</v>
+        <v>0.01246027164681775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09373134698678634</v>
+        <v>0.131355066259813</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04686567349339317</v>
+        <v>0.06567753312990651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.00439278270397867</v>
+        <v>0.008627076716059934</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1118,79 +1118,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ballast</t>
+          <t>wing</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02500000998616425</v>
+        <v>0.01935915630412541</v>
       </c>
       <c r="C2" t="n">
-        <v>25.00000998616425</v>
+        <v>19.35915630412541</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02819496059103004</v>
+        <v>0.07221608723415818</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.04408174561703111</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.001613288869751387</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3.472586709721808e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.001647963112431794</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wing</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01438606737248734</v>
+        <v>0.013</v>
       </c>
       <c r="C3" t="n">
-        <v>14.38606737248734</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04699160098505007</v>
+        <v>0.03610804361707909</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05034173279268531</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001563525370303809</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09375663237814e-05</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001574424573781264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>servos</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.013</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02349580049252504</v>
+        <v>0.04332965234049491</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1211,17 +1211,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>servos</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.008640000075859326</v>
       </c>
       <c r="C5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.640000075859327</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02819496059103004</v>
+        <v>0.370000004214407</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1242,17 +1242,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>pod</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008640000052622495</v>
+        <v>0.007</v>
       </c>
       <c r="C6" t="n">
-        <v>8.640000052622495</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.370000002923472</v>
+        <v>-0.095</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1273,79 +1273,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pod</t>
+          <t>glue</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007</v>
+        <v>0.005190943509519417</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5.190943509519417</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.095</v>
+        <v>0.1008297531147197</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.01401640080971708</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.0001318557759432717</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0002106330468472504</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.0003377192267915532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>glue</t>
+          <t>receiver</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006725029030628136</v>
+        <v>0.005</v>
       </c>
       <c r="C8" t="n">
-        <v>6.725029030628136</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06507940084187656</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008857665981638807</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001277462433729217</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001736723623582004</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002964335821785161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>htail_surfaces</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005</v>
+        <v>0.001233566893034957</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>1.233566893034957</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>0.8779064051493889</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1354,13 +1354,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5.124451369081958e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.211455622892876e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5.443746581031693e-06</v>
       </c>
     </row>
     <row r="10">
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.425000002923472</v>
+        <v>0.425000004214407</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1397,63 +1397,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>htail_surfaces</t>
+          <t>vtail_surfaces</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.000801899983883722</v>
+        <v>0.0008540805948899335</v>
       </c>
       <c r="C11" t="n">
-        <v>0.801899983883722</v>
+        <v>0.8540805948899336</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8725000056208458</v>
+        <v>0.8828387749937673</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.06567753312990651</v>
       </c>
       <c r="G11" t="n">
-        <v>2.165731337960013e-06</v>
+        <v>1.228677029415095e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.35922044548669e-07</v>
+        <v>1.535045586211159e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.300450532532856e-06</v>
+        <v>3.076496776883993e-07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vtail_surfaces</t>
+          <t>ballast</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0004348854876938883</v>
+        <v>-9.998916929839549e-09</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4348854876938884</v>
+        <v>-9.998916929839549e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8734328425936406</v>
+        <v>0.04332965234049491</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04686567349339317</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.18719072207944e-07</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.97991135115217e-07</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.992439113881381e-08</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02824176748593176</v>
+        <v>0.05643440872268236</v>
       </c>
     </row>
     <row r="3">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5582584650035635</v>
+        <v>1.438220849459783</v>
       </c>
     </row>
     <row r="4">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.462885680624051e-07</v>
+        <v>8.9435818077161e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001820858179731738</v>
+        <v>0.004000000909568091</v>
       </c>
     </row>
     <row r="6">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.151993529865866</v>
+        <v>-0.2779008321205922</v>
       </c>
     </row>
     <row r="7">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001342529718818819</v>
+        <v>-0.0001888888080808782</v>
       </c>
     </row>
     <row r="8">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3157884697459488</v>
+        <v>0.4783114758039694</v>
       </c>
     </row>
     <row r="9">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.053095717966677</v>
+        <v>5.798504610333541</v>
       </c>
     </row>
     <row r="10">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.362218317472915e-05</v>
+        <v>6.878875040077161e-06</v>
       </c>
     </row>
     <row r="11">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01336292844966724</v>
+        <v>0.006383865311654358</v>
       </c>
     </row>
     <row r="12">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8972402557599345</v>
+        <v>-0.06750078826839312</v>
       </c>
     </row>
     <row r="13">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0001163375792367916</v>
+        <v>6.370983379744288e-05</v>
       </c>
     </row>
     <row r="14">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.229757316291048e-17</v>
+        <v>1.36280273604308e-17</v>
       </c>
     </row>
     <row r="15">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-9.638135169921558e-22</v>
+        <v>-1.54614635436273e-22</v>
       </c>
     </row>
     <row r="16">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2872467427726584</v>
+        <v>-0.262859136343078</v>
       </c>
     </row>
     <row r="17">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.6057466955043023</v>
+        <v>-0.4898064667341854</v>
       </c>
     </row>
     <row r="18">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.396241335171523e-17</v>
+        <v>6.886551128437982e-18</v>
       </c>
     </row>
     <row r="19">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1343180177490436</v>
+        <v>0.2193366675598729</v>
       </c>
     </row>
     <row r="20">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.725545558849204e-18</v>
+        <v>6.498174511321335e-19</v>
       </c>
     </row>
     <row r="21">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.15745950767817e-19</v>
+        <v>-5.027597466942898e-19</v>
       </c>
     </row>
     <row r="22">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3018667952492765</v>
+        <v>-0.2439029982715797</v>
       </c>
     </row>
     <row r="23">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.144754916878425</v>
+        <v>-0.9145964757529272</v>
       </c>
     </row>
     <row r="24">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.075196367056272e-18</v>
+        <v>-5.500116102087741e-18</v>
       </c>
     </row>
     <row r="25">
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02306446452892491</v>
+        <v>0.04821558204849526</v>
       </c>
     </row>
     <row r="26">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.943361263156383e-14</v>
+        <v>1.26481120295569e-13</v>
       </c>
     </row>
     <row r="27">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3526547160798665</v>
+        <v>-0.5798505183760735</v>
       </c>
     </row>
     <row r="28">
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-6.503432824197187e-06</v>
+        <v>2.581053145020834e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.004120815588269226</v>
+        <v>0.002163318530967793</v>
       </c>
     </row>
     <row r="30">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-63.14464862925413</v>
+        <v>-29.33297990530776</v>
       </c>
     </row>
     <row r="31">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001371512796438799</v>
+        <v>-0.0001530424517202103</v>
       </c>
     </row>
     <row r="32">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-3.600976924317262e-17</v>
+        <v>-9.716636602208142e-18</v>
       </c>
     </row>
     <row r="33">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.210096493883213e-20</v>
+        <v>-4.342007604553401e-20</v>
       </c>
     </row>
     <row r="34">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.04598430542773188</v>
+        <v>0.09957879373496006</v>
       </c>
     </row>
     <row r="35">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.06093555807088765</v>
+        <v>0.005594368626645732</v>
       </c>
     </row>
     <row r="36">
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.627519054399944e-17</v>
+        <v>-5.398133074725084e-18</v>
       </c>
     </row>
     <row r="37">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.09264074246226461</v>
+        <v>-0.1488566314128205</v>
       </c>
     </row>
     <row r="38">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.07965123956703249</v>
+        <v>0.08111146597243066</v>
       </c>
     </row>
     <row r="39">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.009800965861908175</v>
+        <v>0.0193538902475611</v>
       </c>
     </row>
     <row r="40">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.06985027370512431</v>
+        <v>0.06175757572486956</v>
       </c>
     </row>
     <row r="41">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.03240564863495038</v>
+        <v>-0.0215137694811276</v>
       </c>
     </row>
     <row r="42">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.03240564863495038</v>
+        <v>0.0215137694811276</v>
       </c>
     </row>
     <row r="43">
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.07965123956703249</v>
+        <v>-0.08111146597243066</v>
       </c>
     </row>
     <row r="44">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8906292096898943</v>
+        <v>0.6874625936907084</v>
       </c>
     </row>
     <row r="45">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5.643454363768099e-18</v>
+        <v>9.483708294407718e-19</v>
       </c>
     </row>
     <row r="46">
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-5.643454363768099e-18</v>
+        <v>-9.483708294407718e-19</v>
       </c>
     </row>
     <row r="47">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-5.971512479971581e-19</v>
+        <v>-2.782997315972464e-19</v>
       </c>
     </row>
     <row r="48">
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.474966653857061e-16</v>
+        <v>1.958715086302754e-17</v>
       </c>
     </row>
     <row r="49">
@@ -1961,11 +1961,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00039918417148410775,
+	L=0.0003914046783731243,
 	Y=0.0,
-	D=0.001915024915027601,
+	D=0.0008358760882080647,
 	l_b=-0.0,
-	m_b=-0.00016370490668699133,
+	m_b=-0.0001383265370471261,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5.643454363768099e-18</v>
+        <v>9.483708294407718e-19</v>
       </c>
     </row>
     <row r="51">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5.15115294169588e-15</v>
+        <v>2.625596138075559e-14</v>
       </c>
     </row>
     <row r="52">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.177711526256052e-16</v>
+        <v>-1.418086679229076e-17</v>
       </c>
     </row>
     <row r="53">
@@ -2011,29 +2011,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.844362156645189,
+	L=0.6315308867064954,
 	Y=0.0,
-	D=0.061000032511265775,
+	D=0.05421727206110085,
 	l_b=-0.0,
-	m_b=0.03675919853049462,
+	m_b=0.04270644773075434,
 	n_b=-0.0,
-	span_effective=1.1421424391871897, oswalds_efficiency=0.7631362337472126,
+	span_effective=1.0001171924296708, oswalds_efficiency=0.7929621089044373,
 ), AeroComponentResults(
-	L=0.045867868873221466,
+	L=0.0555403023058398,
 	Y=0.0,
-	D=0.00486823060563684,
+	D=0.005030575822673577,
 	l_b=-0.0,
-	m_b=-0.036587125278178444,
+	m_b=-0.0425443386386366,
 	n_b=-0.0,
-	span_effective=0.17999999819121457, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.2232511737645986, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-0.0,
-	Y=1.474966653857061e-16,
-	D=0.0020669856731941006,
-	l_b=5.643454363768099e-18,
-	m_b=-8.368345624034154e-06,
-	n_b=-1.177711526256052e-16,
-	span_effective=0.09373134698678634, oswalds_efficiency=0.8232692748986458,
+	L=2.710505431213761e-20,
+	Y=1.958715086302754e-17,
+	D=0.0016738517528870596,
+	l_b=9.483708294407718e-19,
+	m_b=-2.3782555044355553e-05,
+	n_b=-1.4180866792290764e-17,
+	span_effective=0.13135506625981302, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.06977856001004355</v>
+        <v>0.1152729719898737</v>
       </c>
     </row>
     <row r="55">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2507197770198829</v>
+        <v>0.4855033069951758</v>
       </c>
     </row>
   </sheetData>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8906292096898943</v>
+        <v>0.6874625936907084</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8906292196712372</v>
+        <v>0.687462603683204</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07965123956703249</v>
+        <v>0.08111146597243066</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.943361263156383e-14</v>
+        <v>1.26481120295569e-13</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.725545558849204e-18</v>
+        <v>6.498174511321335e-19</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.600976924317262e-17</v>
+        <v>-9.716636602208142e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3157884697459488</v>
+        <v>0.4783114758039694</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.033630367943769</v>
+        <v>4.948056657833936</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.18161141661032</v>
+        <v>8.475529143122294</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.172007954129075</v>
+        <v>4.687449301023788</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.172007954129075</v>
+        <v>4.687449301023788</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41821.22376080244</v>
+        <v>39550.96498477143</v>
       </c>
       <c r="C12" t="n">
         <v>20000</v>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04999999010101803</v>
+        <v>0.1000000098892254</v>
       </c>
       <c r="C13" t="n">
         <v>0.05</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04999999010101803</v>
+        <v>0.1000000098892254</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6721799329461787</v>
+        <v>0.4999999900567649</v>
       </c>
       <c r="C15" t="n">
         <v>0.5</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6721799329461787</v>
+        <v>0.4999999900567649</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02999999002751742</v>
+        <v>0.05000000993196219</v>
       </c>
       <c r="C17" t="n">
         <v>0.03</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02999999002751742</v>
+        <v>0.05000000993196219</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3018667952492765</v>
+        <v>-0.2439029982715797</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.04598430542773188</v>
+        <v>0.09957879373496006</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-63.14464862925413</v>
+        <v>-29.33297990530776</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.295592516496379</v>
+        <v>0.9369224915798031</v>
       </c>
       <c r="C22" t="n">
         <v>0.6</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>243.3298652796471</v>
+        <v>86.48660579717323</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.005324428692743563</v>
+        <v>0.01083315136423617</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.001088092676205903</v>
+        <v>0.0008521522705445529</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.116811316151226e-06</v>
+        <v>9.45951493738948e-06</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.746095152991352e-19</v>
+        <v>9.432178633127867e-20</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -12,6 +12,7 @@
     <sheet name="MassBreakdown" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Aerodynamics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Constraints" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DesignPoints" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a99069b-dirty</t>
+          <t>5cb9697-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,7 +491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.486118625467693</v>
+        <v>0.3829646626678594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -501,7 +502,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>design_speed_mps</t>
+          <t>v_nom_mps</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,26 +517,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>alpha_trim_deg</t>
+          <t>v_turn_mps</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.948056657649936</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m/s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>delta_a_trim_deg</t>
+          <t>turn_bank_deg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.014083662992938e-17</v>
+        <v>50</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -546,176 +547,176 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>delta_e_trim_deg</t>
+          <t>arena_width_m</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.883612080032152</v>
+        <v>4.8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>delta_r_trim_deg</t>
+          <t>wall_clearance_m</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-8.295475058712677e-15</v>
+        <v>0.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mass_total_kg</t>
+          <t>alpha_trim_deg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07007773737740047</v>
+        <v>3.265624972678735</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mass_total_g</t>
+          <t>delta_a_trim_deg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70.07773737740047</v>
+        <v>1.732786463659694e-16</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mass_total_lbm</t>
+          <t>delta_e_trim_deg</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1544949651101946</v>
+        <v>0.7295201394751571</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lbm</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ballast_mass_kg</t>
+          <t>delta_r_trim_deg</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.000074676233832e-08</v>
+        <v>1.035118855641136e-15</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sink_rate_mps</t>
+          <t>mass_total_kg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4719469279309158</v>
+        <v>0.08907177338753518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L_over_D</t>
+          <t>mass_total_g</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.475529143488501</v>
+        <v>89.07177338753517</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wing_loading_n_m2</t>
+          <t>mass_total_lbm</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.687449300794357</v>
+        <v>0.1963696465783478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>N/m^2</t>
+          <t>lbm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reynolds_wing</t>
+          <t>ballast_mass_kg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39550.96498607255</v>
+        <v>0.001248044074387546</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>static_margin</t>
+          <t>sink_rate_mps</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1000000099170008</v>
+        <v>0.3645446504338175</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MAC fraction</t>
+          <t>m/s</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tail_volume_horizontal</t>
+          <t>L_over_D</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4999999900541847</v>
+        <v>10.97259265635919</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,73 +727,178 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tail_volume_vertical</t>
+          <t>turn_radius_m</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0500000099349265</v>
+        <v>0.769816175392</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>roll_rate_ss_radps</t>
+          <t>turn_footprint_lhs_m</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9369224915803962</v>
+        <v>2.080046038462513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>roll_accel0_rad_s2</t>
+          <t>turn_CL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86.48660579196596</v>
+        <v>0.3528117324472714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rad/s^2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>roll_tau_s</t>
+          <t>wing_loading_n_m2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01083315136489528</v>
+        <v>3.467824177017998</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>N/m^2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>reynolds_wing</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>41933.23691995171</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>static_margin</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.04999999020698476</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MAC fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tail_volume_horizontal</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.7000000080815174</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tail_volume_vertical</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.02999999000825085</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>roll_rate_ss_radps</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.5999999902481539</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>roll_accel0_rad_s2</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>64.60823526290454</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rad/s^2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>roll_tau_s</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.009286741663916792</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>max_servo_utilization</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>2.958862050697145e-05</v>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B31" t="n">
+        <v>5.389712043725522e-05</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
@@ -836,7 +942,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.015426622019409</v>
+        <v>1.645457929412684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -851,7 +957,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1444321744730677</v>
+        <v>0.1531317527442298</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -866,7 +972,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.146660275036105</v>
+        <v>0.2519718567978555</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -881,7 +987,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.030473824298449</v>
+        <v>10.74537383609153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -896,7 +1002,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8500000084297308</v>
+        <v>0.8367187539795161</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,7 +1017,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2232511737712672</v>
+        <v>0.3593336687022275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -926,7 +1032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0558127934428168</v>
+        <v>0.08983341717555687</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -941,7 +1047,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01246027164756214</v>
+        <v>0.03228017136575054</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -956,7 +1062,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.131355066265821</v>
+        <v>0.1711121863070972</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -971,7 +1077,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06567753313291048</v>
+        <v>0.08555609315354862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -986,7 +1092,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.008627076716849109</v>
+        <v>0.01463969015139738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1122,28 +1228,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01935915630476586</v>
+        <v>0.03326028509731693</v>
       </c>
       <c r="C2" t="n">
-        <v>19.35915630476586</v>
+        <v>33.26028509731692</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07221608723653386</v>
+        <v>0.0765658763721149</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04408174561703931</v>
+        <v>0.07143269271752828</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001613288869805359</v>
+        <v>0.00727819775170123</v>
       </c>
       <c r="H2" t="n">
-        <v>3.472586710064994e-05</v>
+        <v>6.705939157817239e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001647963112489196</v>
+        <v>0.00734516844918581</v>
       </c>
     </row>
     <row r="3">
@@ -1159,7 +1265,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03610804361826693</v>
+        <v>0.03828293818605745</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1190,7 +1296,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04332965234192031</v>
+        <v>0.04593952582326894</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1215,13 +1321,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008640000075867576</v>
+        <v>0.008520468785815645</v>
       </c>
       <c r="C5" t="n">
-        <v>8.640000075867576</v>
+        <v>8.520468785815645</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3700000042148654</v>
+        <v>0.3633593769897581</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1277,28 +1383,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005190943509437072</v>
+        <v>0.006597909139817421</v>
       </c>
       <c r="C7" t="n">
-        <v>5.190943509437072</v>
+        <v>6.59790913981742</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1008297531191905</v>
+        <v>0.1206126412622277</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01401640081049559</v>
+        <v>0.03031106523982323</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001318557759477139</v>
+        <v>0.0005936539099383243</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002106330468548315</v>
+        <v>0.0003385489796629639</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003377192268034254</v>
+        <v>0.0009149015983556316</v>
       </c>
     </row>
     <row r="8">
@@ -1339,13 +1445,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001233566893108652</v>
+        <v>0.003195736965209304</v>
       </c>
       <c r="C9" t="n">
-        <v>1.233566893108652</v>
+        <v>3.195736965209304</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8779064051511392</v>
+        <v>0.8816354625672945</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1354,91 +1460,91 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5.124451369694181e-06</v>
+        <v>3.438870909499721e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.211455623276033e-07</v>
+        <v>2.151541320990989e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>5.443746581682121e-06</v>
+        <v>3.653545681054039e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linkages</t>
+          <t>vtail_surfaces</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001</v>
+        <v>0.00144932932498834</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>1.44932932498834</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4250000042148654</v>
+        <v>0.8794968005562904</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.08555609315354862</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3.537375704520944e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4.420360884409003e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>8.85159173875542e-07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vtail_surfaces</t>
+          <t>ballast</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0008540805949680617</v>
+        <v>0.001248044074387546</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8540805949680617</v>
+        <v>1.248044074387546</v>
       </c>
       <c r="D11" t="n">
-        <v>0.882838774996186</v>
+        <v>0.04593952582326894</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06567753313291048</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.228677029639826e-06</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.535045586492e-06</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3.076496777446261e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ballast</t>
+          <t>linkages</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.000074676233832e-08</v>
+        <v>0.001</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.000074676233832e-05</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04332965234192031</v>
+        <v>0.4183593769897581</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1467,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1485,487 +1591,487 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>nominal_CD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05643440871747699</v>
+        <v>0.03224942917054652</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDa</t>
+          <t>nominal_CDa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.438220849315466</v>
+        <v>0.6294856307726406</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDb</t>
+          <t>nominal_CDb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.943568290358704e-06</v>
+        <v>8.340197586387651e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDp</t>
+          <t>nominal_CDp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004000000916951074</v>
+        <v>-0.001820511558746352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDq</t>
+          <t>nominal_CDq</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2779008320195897</v>
+        <v>-0.07529548797726575</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDr</t>
+          <t>nominal_CDr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001888888076714834</v>
+        <v>-8.380160661236591e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>nominal_CL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4783114757805177</v>
+        <v>0.3538598496885145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CLa</t>
+          <t>nominal_CLa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.798504609986861</v>
+        <v>7.005053025496728</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CLb</t>
+          <t>nominal_CLb</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.878776442882036e-06</v>
+        <v>-2.890867534687543e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CLp</t>
+          <t>nominal_CLp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.006383865327919124</v>
+        <v>-0.01586307811807242</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CLq</t>
+          <t>nominal_CLq</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0675007877341538</v>
+        <v>0.3676832465103752</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CLr</t>
+          <t>nominal_CLr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.370983485215476e-05</v>
+        <v>-0.0001684725206008153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>nominal_CY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.771643556959456e-17</v>
+        <v>9.422363200144823e-18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CYa</t>
+          <t>nominal_CYa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.009994056630966e-22</v>
+        <v>-7.075447656711423e-23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CYb</t>
+          <t>nominal_CYb</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2628591363433991</v>
+        <v>-0.3099907511324865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CYp</t>
+          <t>nominal_CYp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.4898064667066539</v>
+        <v>-0.566406099598727</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CYq</t>
+          <t>nominal_CYq</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.952516464704019e-18</v>
+        <v>-2.441226992436795e-18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CYr</t>
+          <t>nominal_CYr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2193366675707248</v>
+        <v>0.1241092086103912</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>nominal_Cl</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.30363791679246e-19</v>
+        <v>3.087405529260732e-19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cla</t>
+          <t>nominal_Cla</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.351590182131828e-19</v>
+        <v>-1.33346092137015e-19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Clb</t>
+          <t>nominal_Clb</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2439029982603689</v>
+        <v>-0.2819421253289612</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clp</t>
+          <t>nominal_Clp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.9145964756974962</v>
+        <v>-1.064729109304657</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clq</t>
+          <t>nominal_Clq</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.338487439852477e-18</v>
+        <v>-1.711870338836074e-18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clr</t>
+          <t>nominal_Clr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04821558204955213</v>
+        <v>0.021790251455553</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cm</t>
+          <t>nominal_Cm</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.039702191125778e-14</v>
+        <v>-1.491448830018954e-10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cma</t>
+          <t>nominal_Cma</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5798505185024612</v>
+        <v>-0.3502525826742454</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cmb</t>
+          <t>nominal_Cmb</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.580938241251129e-06</v>
+        <v>-1.002744686737054e-05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cmp</t>
+          <t>nominal_Cmp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002163318540952959</v>
+        <v>-0.006396571209649135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cmq</t>
+          <t>nominal_Cmq</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-29.3329799057312</v>
+        <v>-39.52415518558014</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cmr</t>
+          <t>nominal_Cmr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001530424511486556</v>
+        <v>-0.0001389555989351931</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cn</t>
+          <t>nominal_Cn</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.362037599096439e-17</v>
+        <v>-4.05887327666648e-18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cna</t>
+          <t>nominal_Cna</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.917485264134367e-20</v>
+        <v>-7.578978318717902e-21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cnb</t>
+          <t>nominal_Cnb</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.09957879373723921</v>
+        <v>0.03795793197254786</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cnp</t>
+          <t>nominal_Cnp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.005594368619038168</v>
+        <v>-0.07056892499093069</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cnq</t>
+          <t>nominal_Cnq</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-6.557285860509823e-18</v>
+        <v>9.725461716079436e-19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cnr</t>
+          <t>nominal_Cnr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.1488566314209694</v>
+        <v>-0.05850484150544907</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>nominal_D</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.08111146596763252</v>
+        <v>0.07963424090427679</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D_induced</t>
+          <t>nominal_D_induced</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.01935389024690383</v>
+        <v>0.01223295076335761</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D_profile</t>
+          <t>nominal_D_profile</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.06175757572072869</v>
+        <v>0.06740129014091917</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F_b</t>
+          <t>nominal_F_b</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.02151376947951493</v>
+        <v>-0.02972920125926148</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F_g</t>
+          <t>nominal_F_g</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02151376947951493</v>
+        <v>0.02972920125926148</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F_w</t>
+          <t>nominal_F_w</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.08111146596763252</v>
+        <v>-0.07963424090427679</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>nominal_L</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6874625936797452</v>
+        <v>0.8737940869410059</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>M_b</t>
+          <t>nominal_M_b</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.357811919776297e-18</v>
+        <v>1.254464203857359e-18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>M_g</t>
+          <t>nominal_M_g</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.357811919776297e-18</v>
+        <v>-1.254464203857359e-18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>M_w</t>
+          <t>nominal_M_w</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-3.61789650984088e-19</v>
+        <v>3.129665040971596e-19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>nominal_Y</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.546329612426509e-17</v>
+        <v>2.326685340691906e-17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fuselage_aero_components</t>
+          <t>nominal_fuselage_aero_components</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00039140467834894514,
+	L=0.00019699568249745332,
 	Y=0.0,
-	D=0.0008358760882064288,
+	D=0.0008275962517129193,
 	l_b=-0.0,
-	m_b=-0.00013832653703869653,
+	m_b=-8.809874262680897e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -1975,65 +2081,65 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>l_b</t>
+          <t>nominal_l_b</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.357811919776297e-18</v>
+        <v>1.254464203857359e-18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>m_b</t>
+          <t>nominal_m_b</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.310056643865636e-15</v>
+        <v>-5.639640543572601e-11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>n_b</t>
+          <t>nominal_n_b</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.987814770713083e-17</v>
+        <v>-1.649187703175008e-17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>wing_aero_components</t>
+          <t>nominal_wing_aero_components</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.6315308866932998,
+	L=0.783353256168381,
 	Y=0.0,
-	D=0.054217272056737584,
+	D=0.05625018019951093,
 	l_b=-0.0,
-	m_b=0.04270644773225918,
+	m_b=0.06668583167694779,
 	n_b=-0.0,
-	span_effective=1.0001171924298569, oswalds_efficiency=0.79296210890578,
+	span_effective=1.6206496155802028, oswalds_efficiency=0.7718502781381492,
 ), AeroComponentResults(
-	L=0.05554030230809642,
+	L=0.09024383509012739,
 	Y=0.0,
-	D=0.005030575822788429,
+	D=0.007883984678618852,
 	l_b=-0.0,
-	m_b=-0.04254433864017651,
+	m_b=-0.06663054752102311,
 	n_b=-0.0,
-	span_effective=0.22325117377126721, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.3593336687022275, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=-0.0,
-	Y=2.546329612426509e-17,
-	D=0.001673851752996247,
-	l_b=1.357811919776297e-18,
-	m_b=-2.3782555037661848e-05,
-	n_b=-1.9878147707130825e-17,
-	span_effective=0.13135506626582097, oswalds_efficiency=0.8232692748986458,
+	Y=2.326685340691906e-17,
+	D=0.0024395290110764732,
+	l_b=1.2544642038573592e-18,
+	m_b=3.2814530305724925e-05,
+	n_b=-1.6491877031750078e-17,
+	span_effective=0.17111218630709724, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2041,21 +2147,277 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>x_np</t>
+          <t>nominal_x_np</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1152729719988313</v>
+        <v>0.1282692273998176</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>x_np_lateral</t>
+          <t>nominal_x_np_lateral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4855033070080527</v>
+        <v>0.3220966530276053</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>turn_CD</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.03434113097875773</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>turn_CL</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.3528117324472714</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>turn_CY</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.884426405928886e-17</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>turn_Cl</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6.402903091352355e-19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>turn_Cm</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.01094067023361572</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>turn_Cn</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>-8.517569654817715e-18</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>turn_D</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.04769962156816282</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>turn_D_induced</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.006840332530788545</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>turn_D_profile</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.04085928903737427</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>turn_F_b</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.01970625031065464</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>turn_F_g</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.01970625031065464</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>turn_F_w</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>-0.04769962156816282</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>turn_L</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.4900533454460951</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>turn_M_b</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1.463403371267119e-18</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>turn_M_g</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>-1.463403371267119e-18</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>turn_M_w</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3.520786789153028e-19</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>turn_Y</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2.617456789395252e-17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>turn_fuselage_aero_components</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>[AeroComponentResults(
+	L=0.00011968880593709713,
+	Y=0.0,
+	D=0.0004967411139152521,
+	l_b=-0.0,
+	m_b=-5.357034034996522e-05,
+	n_b=-0.0,
+	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
+)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>turn_l_b</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.463403371267119e-18</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>turn_m_b</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.00232707039471125</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>turn_n_b</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>-1.946716976662864e-17</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>turn_wing_aero_components</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>[AeroComponentResults(
+	L=0.4422075354169336,
+	Y=0.0,
+	D=0.03410682128253058,
+	l_b=-0.0,
+	m_b=0.03762132831443529,
+	n_b=-0.0,
+	span_effective=1.6206496155802028, oswalds_efficiency=0.7718502781381492,
+), AeroComponentResults(
+	L=0.04772612122322445,
+	Y=0.0,
+	D=0.0046365157976351636,
+	l_b=-0.0,
+	m_b=-0.03526246786689981,
+	n_b=-0.0,
+	span_effective=0.3593336687022275, oswalds_efficiency=0.8106853777008906,
+), AeroComponentResults(
+	L=1.3552527156068805e-20,
+	Y=2.6174567893952522e-17,
+	D=0.0016192108432932818,
+	l_b=1.4634033712671194e-18,
+	m_b=2.1780287525730196e-05,
+	n_b=-1.9467169766628638e-17,
+	span_effective=0.17111218630709724, oswalds_efficiency=0.8232692748986458,
+)]</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2069,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2111,10 +2473,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6874625936797452</v>
+        <v>0.8737940869410059</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6874626036722987</v>
+        <v>0.8737940969317202</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -2131,7 +2493,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08111146596763252</v>
+        <v>0.07963424090427679</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -2147,11 +2509,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trim Cm</t>
+          <t>Nominal Trim Cm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.039702191125778e-14</v>
+        <v>-1.491448830018954e-10</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2169,11 +2531,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trim Cl</t>
+          <t>Nominal Trim Cl</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.30363791679246e-19</v>
+        <v>3.087405529260732e-19</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2191,11 +2553,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trim Cn</t>
+          <t>Nominal Trim Cn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.362037599096439e-17</v>
+        <v>-4.05887327666648e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2217,7 +2579,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4783114757805177</v>
+        <v>0.3538598496885145</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -2233,15 +2595,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alpha &lt;= stall margin</t>
+          <t>Alpha &lt;= turn stall margin</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.948056657649936</v>
+        <v>3.265624972678735</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>1e-06</v>
@@ -2253,16 +2615,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L/D minimum</t>
+          <t>Turn CL cap</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.475529143488501</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>0.3528117324472714</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="E9" t="n">
         <v>1e-06</v>
       </c>
@@ -2273,16 +2635,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wing loading minimum</t>
+          <t>Turn footprint in width</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.687449300794357</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>2.080046038462513</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>2.4</v>
+      </c>
       <c r="E10" t="n">
         <v>1e-06</v>
       </c>
@@ -2293,16 +2655,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wing loading maximum</t>
+          <t>L/D minimum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.687449300794357</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
-        <v>20</v>
-      </c>
+        <v>10.97259265635919</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>1e-06</v>
       </c>
@@ -2313,14 +2675,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wing Reynolds</t>
+          <t>Wing loading minimum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39550.96498607255</v>
+        <v>3.467824177017998</v>
       </c>
       <c r="C12" t="n">
-        <v>20000</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
@@ -2333,16 +2695,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Static margin minimum</t>
+          <t>Wing loading maximum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1000000099170008</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>3.467824177017998</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
       <c r="E13" t="n">
         <v>1e-06</v>
       </c>
@@ -2353,16 +2715,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Static margin maximum</t>
+          <t>Wing Reynolds</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1000000099170008</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>0.1</v>
-      </c>
+        <v>41933.23691995171</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>1e-06</v>
       </c>
@@ -2373,14 +2735,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vh minimum</t>
+          <t>Static margin minimum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4999999900541847</v>
+        <v>0.04999999020698476</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
@@ -2393,15 +2755,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vh maximum</t>
+          <t>Static margin maximum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4999999900541847</v>
+        <v>0.04999999020698476</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
         <v>1e-06</v>
@@ -2413,14 +2775,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vv minimum</t>
+          <t>Vh minimum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0500000099349265</v>
+        <v>0.7000000080815174</v>
       </c>
       <c r="C17" t="n">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
@@ -2433,15 +2795,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vv maximum</t>
+          <t>Vh maximum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0500000099349265</v>
+        <v>0.7000000080815174</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.05</v>
+        <v>0.7</v>
       </c>
       <c r="E18" t="n">
         <v>1e-06</v>
@@ -2453,16 +2815,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Clb &lt;= 0</t>
+          <t>Vv minimum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.2439029982603689</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
+        <v>0.02999999000825085</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>1e-06</v>
       </c>
@@ -2473,16 +2835,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cnb &gt;= 0</t>
+          <t>Vv maximum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09957879373723921</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>0.02999999000825085</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E20" t="n">
         <v>1e-06</v>
       </c>
@@ -2493,15 +2855,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cmq &lt;= -0.01</t>
+          <t>Clb &lt;= 0</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-29.3329799057312</v>
+        <v>-0.2819421253289612</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>1e-06</v>
@@ -2513,14 +2875,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Roll rate minimum</t>
+          <t>Cnb &gt;= 0</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9369224915803962</v>
+        <v>0.03795793197254786</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
@@ -2533,16 +2895,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Roll accel minimum</t>
+          <t>Cmq &lt;= -0.01</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>86.48660579196596</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>-39.52415518558014</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>-0.01</v>
+      </c>
       <c r="E23" t="n">
         <v>1e-06</v>
       </c>
@@ -2553,16 +2915,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Roll time constant</t>
+          <t>Roll rate minimum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01083315136489528</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>0.45</v>
-      </c>
+        <v>0.5999999902481539</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>1e-06</v>
       </c>
@@ -2573,16 +2935,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aileron servo torque</t>
+          <t>Roll accel minimum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.260761353003889e-06</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
-        <v>0.144</v>
-      </c>
+        <v>64.60823526290454</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>1e-06</v>
       </c>
@@ -2593,15 +2955,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Elevator servo torque</t>
+          <t>Roll time constant</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.729757469507889e-08</v>
+        <v>0.009286741663916792</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>0.144</v>
+        <v>0.45</v>
       </c>
       <c r="E26" t="n">
         <v>1e-06</v>
@@ -2613,11 +2975,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rudder servo torque</t>
+          <t>Aileron servo torque</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.924150186828811e-22</v>
+        <v>7.761185342964752e-06</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
@@ -2628,6 +2990,542 @@
       </c>
       <c r="F27" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Elevator servo torque</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.628272149107434e-07</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Rudder servo torque</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.358258982162884e-22</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Turn aileron trim utilization</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.732786463659694e-16</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Turn elevator trim utilization</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.7295201394751571</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Turn rudder trim utilization</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.035118855641136e-15</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>24</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DesignPoint</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V_NOM_MPS</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V_TURN_MPS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TURN_BANK_DEG</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WALL_CLEARANCE_M</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARENA_LENGTH_M</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARENA_WIDTH_M</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ARENA_HEIGHT_M</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>alpha_nom_deg</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.265624972678735</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>delta_a_nom_deg</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.732786463659694e-16</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>delta_e_nom_deg</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7295201394751571</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>delta_r_nom_deg</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.035118855641136e-15</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sink_nom_mps</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3645446504338175</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CL_nom</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3538598496885145</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Manoeuvre</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>alpha_turn_deg</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3.265624972678735</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Manoeuvre</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>delta_a_turn_deg</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.732786463659694e-16</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Manoeuvre</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>delta_e_turn_deg</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7295201394751571</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Manoeuvre</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>delta_r_turn_deg</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.035118855641136e-15</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Manoeuvre</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CL_turn</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3528117324472714</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Manoeuvre</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>turn_radius_m</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.769816175392</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Manoeuvre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>turn_footprint_lhs_m</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2.080046038462513</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5cb9697-dirty</t>
+          <t>b5c9594-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3829646626678594</v>
+        <v>0.3829646626598319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>-1.086407042169356e-15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08907177338753518</v>
+        <v>0.08907177045543507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89.07177338753517</v>
+        <v>89.07177045543507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1963696465783478</v>
+        <v>0.1963696401141736</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001248044074387546</v>
+        <v>0.001248042840409447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3645446504338175</v>
+        <v>0.3645446515159374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.97259265635919</v>
+        <v>10.97259262371068</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.769816175392</v>
+        <v>1.047805349839111</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.080046038462513</v>
+        <v>2.358035212357187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.467824177017998</v>
+        <v>3.467824176548267</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>41933.23691995171</v>
+        <v>41933.23557384799</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04999999020698476</v>
+        <v>0.04999999019744358</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7000000080815174</v>
+        <v>0.7000000082067733</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02999999000825085</v>
+        <v>0.02999999000181115</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5999999902481539</v>
+        <v>0.5999999902182078</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64.60823526290454</v>
+        <v>64.60823651215563</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.009286741663916792</v>
+        <v>0.009286741483886836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.389712043725522e-05</v>
+        <v>5.389711694019127e-05</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.645457929412684</v>
+        <v>1.645457928290766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1531317527442298</v>
+        <v>0.1531317478285296</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2519718567978555</v>
+        <v>0.2519718485374762</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.74537383609153</v>
+        <v>10.74537417370354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8367187539795161</v>
+        <v>0.8367187148415608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3593336687022275</v>
+        <v>0.3593336654808725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08983341717555687</v>
+        <v>0.08983341637021813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03228017136575054</v>
+        <v>0.0322801707869799</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1711121863070972</v>
+        <v>0.1711121874275478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08555609315354862</v>
+        <v>0.0855560937137739</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01463969015139738</v>
+        <v>0.01463969034312012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1228,28 +1228,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03326028509731693</v>
+        <v>0.03326028400694686</v>
       </c>
       <c r="C2" t="n">
-        <v>33.26028509731692</v>
+        <v>33.26028400694686</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0765658763721149</v>
+        <v>0.07656587391426478</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07143269271752828</v>
+        <v>0.0714326926688235</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00727819775170123</v>
+        <v>0.007278197503175589</v>
       </c>
       <c r="H2" t="n">
-        <v>6.705939157817239e-05</v>
+        <v>6.705938507725284e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00734516844918581</v>
+        <v>0.007345168194162157</v>
       </c>
     </row>
     <row r="3">
@@ -1265,7 +1265,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03828293818605745</v>
+        <v>0.03828293695713239</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04593952582326894</v>
+        <v>0.04593952434855886</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008520468785815645</v>
+        <v>0.008520468433574046</v>
       </c>
       <c r="C5" t="n">
-        <v>8.520468785815645</v>
+        <v>8.520468433574047</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3633593769897581</v>
+        <v>0.3633593574207804</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1383,28 +1383,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006597909139817421</v>
+        <v>0.00659790892262482</v>
       </c>
       <c r="C7" t="n">
-        <v>6.59790913981742</v>
+        <v>6.59790892262482</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1206126412622277</v>
+        <v>0.1206126357324473</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03031106523982323</v>
+        <v>0.030311065303111</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005936539099383243</v>
+        <v>0.0005936538896978842</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003385489796629639</v>
+        <v>0.0003385489460493147</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009149015983556316</v>
+        <v>0.0009149015450212645</v>
       </c>
     </row>
     <row r="8">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003195736965209304</v>
+        <v>0.00319573690791101</v>
       </c>
       <c r="C9" t="n">
-        <v>3.195736965209304</v>
+        <v>3.195736907911011</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8816354625672945</v>
+        <v>0.8816354230266699</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.438870909499721e-05</v>
+        <v>3.438870786188843e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.151541320990989e-06</v>
+        <v>2.151541243881402e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>3.653545681054039e-05</v>
+        <v>3.653545550040796e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1476,28 +1476,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00144932932498834</v>
+        <v>0.001449329343968892</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44932932498834</v>
+        <v>1.449329343968892</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8794968005562904</v>
+        <v>0.8794967616984477</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08555609315354862</v>
+        <v>0.0855560937137739</v>
       </c>
       <c r="G10" t="n">
-        <v>3.537375704520944e-06</v>
+        <v>3.537375797158313e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>4.420360884409003e-06</v>
+        <v>4.42036100018792e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>8.85159173875542e-07</v>
+        <v>8.851591970455608e-07</v>
       </c>
     </row>
     <row r="11">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001248044074387546</v>
+        <v>0.001248042840409447</v>
       </c>
       <c r="C11" t="n">
-        <v>1.248044074387546</v>
+        <v>1.248042840409447</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04593952582326894</v>
+        <v>0.04593952434855886</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1544,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4183593769897581</v>
+        <v>0.4183593574207804</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03224942917054652</v>
+        <v>0.03224942926190789</v>
       </c>
     </row>
     <row r="3">
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6294856307726406</v>
+        <v>0.6294856343110077</v>
       </c>
     </row>
     <row r="4">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.340197586387651e-07</v>
+        <v>8.340161805147485e-07</v>
       </c>
     </row>
     <row r="5">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001820511558746352</v>
+        <v>-0.001820511524613933</v>
       </c>
     </row>
     <row r="6">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.07529548797726575</v>
+        <v>-0.07529549634031213</v>
       </c>
     </row>
     <row r="7">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-8.380160661236591e-05</v>
+        <v>-8.380160268495196e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3538598496885145</v>
+        <v>0.35385984963809</v>
       </c>
     </row>
     <row r="9">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.005053025496728</v>
+        <v>7.005053156532401</v>
       </c>
     </row>
     <row r="10">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.890867534687543e-05</v>
+        <v>-2.890875486074246e-05</v>
       </c>
     </row>
     <row r="11">
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01586307811807242</v>
+        <v>-0.01586307786877184</v>
       </c>
     </row>
     <row r="12">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3676832465103752</v>
+        <v>0.3676832720721501</v>
       </c>
     </row>
     <row r="13">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0001684725206008153</v>
+        <v>-0.0001684725177697466</v>
       </c>
     </row>
     <row r="14">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.422363200144823e-18</v>
+        <v>-1.14709254935964e-17</v>
       </c>
     </row>
     <row r="15">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-7.075447656711423e-23</v>
+        <v>-1.811288389569231e-13</v>
       </c>
     </row>
     <row r="16">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.3099907511324865</v>
+        <v>-0.3099907611852864</v>
       </c>
     </row>
     <row r="17">
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.566406099598727</v>
+        <v>-0.5664061109614236</v>
       </c>
     </row>
     <row r="18">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-2.441226992436795e-18</v>
+        <v>4.920359370436785e-15</v>
       </c>
     </row>
     <row r="19">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1241092086103912</v>
+        <v>0.1241092089572653</v>
       </c>
     </row>
     <row r="20">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.087405529260732e-19</v>
+        <v>-1.238244227167802e-18</v>
       </c>
     </row>
     <row r="21">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.33346092137015e-19</v>
+        <v>-1.956947532065448e-13</v>
       </c>
     </row>
     <row r="22">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2819421253289612</v>
+        <v>-0.2819421310024662</v>
       </c>
     </row>
     <row r="23">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.064729109304657</v>
+        <v>-1.064729130000453</v>
       </c>
     </row>
     <row r="24">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.711870338836074e-18</v>
+        <v>5.11993665936314e-15</v>
       </c>
     </row>
     <row r="25">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.021790251455553</v>
+        <v>0.02179025168256403</v>
       </c>
     </row>
     <row r="26">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.491448830018954e-10</v>
+        <v>-2.043139912434701e-10</v>
       </c>
     </row>
     <row r="27">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3502525826742454</v>
+        <v>-0.3502525891591913</v>
       </c>
     </row>
     <row r="28">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.002744686737054e-05</v>
+        <v>-1.002756527529876e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.006396571209649135</v>
+        <v>-0.006396570981524612</v>
       </c>
     </row>
     <row r="30">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-39.52415518558014</v>
+        <v>-39.52415465967306</v>
       </c>
     </row>
     <row r="31">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001389555989351931</v>
+        <v>-0.0001389555864853396</v>
       </c>
     </row>
     <row r="32">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-4.05887327666648e-18</v>
+        <v>5.177796536276711e-18</v>
       </c>
     </row>
     <row r="33">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-7.578978318717902e-21</v>
+        <v>-1.528864420935966e-14</v>
       </c>
     </row>
     <row r="34">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.03795793197254786</v>
+        <v>0.03795793239845403</v>
       </c>
     </row>
     <row r="35">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.07056892499093069</v>
+        <v>-0.07056892371846811</v>
       </c>
     </row>
     <row r="36">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.725461716079436e-19</v>
+        <v>3.586475024903658e-16</v>
       </c>
     </row>
     <row r="37">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.05850484150544907</v>
+        <v>-0.05850483910941145</v>
       </c>
     </row>
     <row r="38">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.07963424090427679</v>
+        <v>0.07963423851923263</v>
       </c>
     </row>
     <row r="39">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.01223295076335761</v>
+        <v>0.01223295000408741</v>
       </c>
     </row>
     <row r="40">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.06740129014091917</v>
+        <v>0.06740128851514521</v>
       </c>
     </row>
     <row r="41">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.02972920125926148</v>
+        <v>-0.02972920083507641</v>
       </c>
     </row>
     <row r="42">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02972920125926148</v>
+        <v>0.02972920083507641</v>
       </c>
     </row>
     <row r="43">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.07963424090427679</v>
+        <v>-0.07963423851923263</v>
       </c>
     </row>
     <row r="44">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8737940869410059</v>
+        <v>0.873794058170949</v>
       </c>
     </row>
     <row r="45">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.254464203857359e-18</v>
+        <v>-5.031192021622866e-18</v>
       </c>
     </row>
     <row r="46">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.254464203857359e-18</v>
+        <v>5.031192021622866e-18</v>
       </c>
     </row>
     <row r="47">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.129665040971596e-19</v>
+        <v>-3.824577332181577e-18</v>
       </c>
     </row>
     <row r="48">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.326685340691906e-17</v>
+        <v>-2.832541343211853e-17</v>
       </c>
     </row>
     <row r="49">
@@ -2067,11 +2067,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00019699568249745332,
+	L=0.00019699567303608487,
 	Y=0.0,
-	D=0.0008275962517129193,
+	D=0.0008275962274152107,
 	l_b=-0.0,
-	m_b=-8.809874262680897e-05,
+	m_b=-8.809873553677019e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.254464203857359e-18</v>
+        <v>-5.031192021622866e-18</v>
       </c>
     </row>
     <row r="51">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-5.639640543572601e-11</v>
+        <v>-7.725758810364462e-11</v>
       </c>
     </row>
     <row r="52">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.649187703175008e-17</v>
+        <v>2.103824758584693e-17</v>
       </c>
     </row>
     <row r="53">
@@ -2117,29 +2117,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.783353256168381,
+	L=0.7833532308652463,
+	Y=-1.734723475976807e-18,
+	D=0.05625017879996465,
+	l_b=-3.469446951953614e-18,
+	m_b=0.06668582602977607,
+	n_b=-5.421010862427522e-20,
+	span_effective=1.6206496144751994, oswalds_efficiency=0.7718502762705776,
+), AeroComponentResults(
+	L=0.09024383163266649,
 	Y=0.0,
-	D=0.05625018019951093,
+	D=0.007883984453949123,
 	l_b=-0.0,
-	m_b=0.06668583167694779,
+	m_b=-0.06663054190862432,
 	n_b=-0.0,
-	span_effective=1.6206496155802028, oswalds_efficiency=0.7718502781381492,
-), AeroComponentResults(
-	L=0.09024383509012739,
-	Y=0.0,
-	D=0.007883984678618852,
-	l_b=-0.0,
-	m_b=-0.06663054752102311,
-	n_b=-0.0,
-	span_effective=0.3593336687022275, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.35933366548087253, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=-0.0,
-	Y=2.326685340691906e-17,
-	D=0.0024395290110764732,
-	l_b=1.2544642038573592e-18,
-	m_b=3.2814530305724925e-05,
-	n_b=-1.6491877031750078e-17,
-	span_effective=0.17111218630709724, oswalds_efficiency=0.8232692748986458,
+	Y=-2.6590689956141722e-17,
+	D=0.0024395290338162295,
+	l_b=-1.5617450696692519e-18,
+	m_b=3.2814537127424117e-05,
+	n_b=2.10924576944712e-17,
+	span_effective=0.1711121874275478, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1282692273998176</v>
+        <v>0.1282692216227911</v>
       </c>
     </row>
     <row r="55">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3220966530276053</v>
+        <v>0.3220966430871982</v>
       </c>
     </row>
     <row r="56">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.03434113097875773</v>
+        <v>0.03329226774080776</v>
       </c>
     </row>
     <row r="57">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
     </row>
     <row r="58">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.884426405928886e-17</v>
+        <v>-2.835765446046807e-17</v>
       </c>
     </row>
     <row r="59">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6.402903091352355e-19</v>
+        <v>-6.38219382057322e-18</v>
       </c>
     </row>
     <row r="60">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.01094067023361572</v>
+        <v>0.005146727224944566</v>
       </c>
     </row>
     <row r="61">
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-8.517569654817715e-18</v>
+        <v>1.045481716114787e-17</v>
       </c>
     </row>
     <row r="62">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.04769962156816282</v>
+        <v>0.06294152819570649</v>
       </c>
     </row>
     <row r="63">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.006840332530788545</v>
+        <v>0.009382912642914253</v>
       </c>
     </row>
     <row r="64">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.04085928903737427</v>
+        <v>0.05355861555279223</v>
       </c>
     </row>
     <row r="65">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.01970625031065464</v>
+        <v>-0.02469508896185747</v>
       </c>
     </row>
     <row r="66">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.01970625031065464</v>
+        <v>0.02469508896185747</v>
       </c>
     </row>
     <row r="67">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.04769962156816282</v>
+        <v>-0.06294152819570649</v>
       </c>
     </row>
     <row r="68">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4900533454460951</v>
+        <v>0.6696076031664475</v>
       </c>
     </row>
     <row r="69">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.463403371267119e-18</v>
+        <v>-1.985412154532852e-17</v>
       </c>
     </row>
     <row r="70">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.463403371267119e-18</v>
+        <v>1.985412154532852e-17</v>
       </c>
     </row>
     <row r="71">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3.520786789153028e-19</v>
+        <v>-1.796917958637743e-17</v>
       </c>
     </row>
     <row r="72">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.617456789395252e-17</v>
+        <v>-5.361227182490354e-17</v>
       </c>
     </row>
     <row r="73">
@@ -2343,11 +2343,11 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00011968880593709713,
+	L=0.00015610787456671668,
 	Y=0.0,
-	D=0.0004967411139152521,
+	D=0.0006528172936150688,
 	l_b=-0.0,
-	m_b=-5.357034034996522e-05,
+	m_b=-6.98681858411693e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.463403371267119e-18</v>
+        <v>-1.985412154532852e-17</v>
       </c>
     </row>
     <row r="75">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.00232707039471125</v>
+        <v>0.001490013816381656</v>
       </c>
     </row>
     <row r="76">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.946716976662864e-17</v>
+        <v>3.252348902073505e-17</v>
       </c>
     </row>
     <row r="77">
@@ -2393,29 +2393,29 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.4422075354169336,
+	L=0.6021268984154694,
+	Y=-7.806255641895632e-18,
+	D=0.0447321314774594,
+	l_b=-1.734723475976807e-17,
+	m_b=0.05125661033137777,
+	n_b=-5.963111948670274e-19,
+	span_effective=1.6206496144751994, oswalds_efficiency=0.7718502762705776,
+), AeroComponentResults(
+	L=0.06732459687641117,
 	Y=0.0,
-	D=0.03410682128253058,
+	D=0.006156568354581533,
 	l_b=-0.0,
-	m_b=0.03762132831443529,
+	m_b=-0.04972386067737028,
 	n_b=-0.0,
-	span_effective=1.6206496155802028, oswalds_efficiency=0.7718502781381492,
-), AeroComponentResults(
-	L=0.04772612122322445,
-	Y=0.0,
-	D=0.0046365157976351636,
-	l_b=-0.0,
-	m_b=-0.03526246786689981,
-	n_b=-0.0,
-	span_effective=0.3593336687022275, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.35933366548087253, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=1.3552527156068805e-20,
-	Y=2.6174567893952522e-17,
-	D=0.0016192108432932818,
-	l_b=1.4634033712671194e-18,
-	m_b=2.1780287525730196e-05,
-	n_b=-1.9467169766628638e-17,
-	span_effective=0.17111218630709724, oswalds_efficiency=0.8232692748986458,
+	Y=-4.5806016183007906e-17,
+	D=0.0020170984271362254,
+	l_b=-2.5068867855604483e-18,
+	m_b=2.713234821533858e-05,
+	n_b=3.311980021560208e-17,
+	span_effective=0.1711121874275478, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8737940869410059</v>
+        <v>0.873794058170949</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8737940969317202</v>
+        <v>0.8737940681678181</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07963424090427679</v>
+        <v>0.07963423851923263</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.491448830018954e-10</v>
+        <v>-2.043139912434701e-10</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.087405529260732e-19</v>
+        <v>-1.238244227167802e-18</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4.05887327666648e-18</v>
+        <v>5.177796536276711e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3538598496885145</v>
+        <v>0.35385984963809</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.080046038462513</v>
+        <v>2.358035212357187</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.97259265635919</v>
+        <v>10.97259262371068</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.467824177017998</v>
+        <v>3.467824176548267</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.467824177017998</v>
+        <v>3.467824176548267</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41933.23691995171</v>
+        <v>41933.23557384799</v>
       </c>
       <c r="C14" t="n">
         <v>20000</v>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04999999020698476</v>
+        <v>0.04999999019744358</v>
       </c>
       <c r="C15" t="n">
         <v>0.05</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04999999020698476</v>
+        <v>0.04999999019744358</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7000000080815174</v>
+        <v>0.7000000082067733</v>
       </c>
       <c r="C17" t="n">
         <v>0.5</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7000000080815174</v>
+        <v>0.7000000082067733</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02999999000825085</v>
+        <v>0.02999999000181115</v>
       </c>
       <c r="C19" t="n">
         <v>0.03</v>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02999999000825085</v>
+        <v>0.02999999000181115</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2819421253289612</v>
+        <v>-0.2819421310024662</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03795793197254786</v>
+        <v>0.03795793239845403</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-39.52415518558014</v>
+        <v>-39.52415465967306</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5999999902481539</v>
+        <v>0.5999999902182078</v>
       </c>
       <c r="C24" t="n">
         <v>0.6</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64.60823526290454</v>
+        <v>64.60823651215563</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.009286741663916792</v>
+        <v>0.009286741483886836</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.761185342964752e-06</v>
+        <v>7.761184839387542e-06</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.628272149107434e-07</v>
+        <v>1.628272027785878e-07</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.358258982162884e-22</v>
+        <v>5.05083796544096e-22</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>1.086407042169356e-15</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>-1.086407042169356e-15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3645446504338175</v>
+        <v>0.3645446515159374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.3538598496885145</v>
+        <v>0.35385984963809</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.265624972678735</v>
+        <v>3.265624951894776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.732786463659694e-16</v>
+        <v>-1.086407042169356e-15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7295201394751571</v>
+        <v>0.7295201047390686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.035118855641136e-15</v>
+        <v>3.849205181611853e-15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3528117324472714</v>
+        <v>0.3541819883461077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.769816175392</v>
+        <v>1.047805349839111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.080046038462513</v>
+        <v>2.358035212357187</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -12,7 +12,8 @@
     <sheet name="MassBreakdown" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Aerodynamics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Constraints" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DesignPoints" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DesignVarBounds" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DesignPoints" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>b5c9594-dirty</t>
+          <t>79c29cc-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3829646626598319</v>
+        <v>0.3757800760524679</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -506,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -521,7 +522,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -581,7 +582,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.265624951894776</v>
+        <v>4.454442685290084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -596,7 +597,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.086407042169356e-15</v>
+        <v>-1.407667968928422e-17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -611,7 +612,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7295201047390686</v>
+        <v>0.7475451269562055</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -626,7 +627,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.849205181611853e-15</v>
+        <v>-7.517549736417041e-16</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -641,7 +642,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08907177045543507</v>
+        <v>0.09555066085528377</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -656,7 +657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89.07177045543507</v>
+        <v>95.55066085528377</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -671,7 +672,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1963696401141736</v>
+        <v>0.2106531484541589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -686,7 +687,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001248042840409447</v>
+        <v>-9.996466100580476e-09</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -697,101 +698,101 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sink_rate_mps</t>
+          <t>battery_slider_eta</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3645446515159374</v>
+        <v>0.6100015467829478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L_over_D</t>
+          <t>battery_x_m</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.97259262371068</v>
+        <v>0.0009573994464305569</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>turn_radius_m</t>
+          <t>sink_rate_mps</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.047805349839111</v>
+        <v>0.3565581831366305</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/s</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>turn_footprint_lhs_m</t>
+          <t>L_over_D</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.358035212357187</v>
+        <v>9.816069657612333</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>turn_CL</t>
+          <t>turn_radius_m</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3541819883461077</v>
+        <v>0.769816175392</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wing_loading_n_m2</t>
+          <t>turn_footprint_lhs_m</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.467824176548267</v>
+        <v>2.269816185298065</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>N/m^2</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>reynolds_wing</t>
+          <t>turn_CL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>41933.23557384799</v>
+        <v>0.5979462510524877</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -802,26 +803,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>static_margin</t>
+          <t>wing_loading_n_m2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04999999019744358</v>
+        <v>4.444673584361032</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MAC fraction</t>
+          <t>N/m^2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tail_volume_horizontal</t>
+          <t>reynolds_wing</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7000000082067733</v>
+        <v>24882.01095054371</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -832,75 +833,137 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tail_volume_vertical</t>
+          <t>static_margin</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02999999000181115</v>
+        <v>0.04999999021163743</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MAC fraction</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>roll_rate_ss_radps</t>
+          <t>tail_volume_horizontal</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5999999902182078</v>
+        <v>0.700000008872528</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>roll_accel0_rad_s2</t>
+          <t>tail_volume_vertical</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64.60823651215563</v>
+        <v>0.02999999000355073</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rad/s^2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>roll_tau_s</t>
+          <t>roll_rate_ss_radps</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.009286741483886836</v>
+        <v>1.32678190745631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>rad/s</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>roll_accel0_rad_s2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>95.10014421550056</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>rad/s^2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>roll_tau_s</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.01395141845894336</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>max_servo_utilization</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>5.389711694019127e-05</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B33" t="n">
+        <v>5.37734550133965e-05</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>design_var_bound_hits_count</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>design_var_bound_hits</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wing_span_m:upper; tail_arm_m:lower; ballast_mass_kg:lower</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -942,7 +1005,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.645457928290766</v>
+        <v>2.030853243889255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -957,7 +1020,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1531317478285296</v>
+        <v>0.1038446888714047</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -972,7 +1035,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2519718485374762</v>
+        <v>0.2108933232551627</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -987,7 +1050,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.74537417370354</v>
+        <v>19.55664045952458</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,7 +1065,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8367187148415608</v>
+        <v>0.4000000051175128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1017,7 +1080,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3593336654808725</v>
+        <v>0.3915367936110467</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1032,7 +1095,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08983341637021813</v>
+        <v>0.09788419840276169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1047,7 +1110,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0322801707869799</v>
+        <v>0.03832526518780485</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1062,7 +1125,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1711121874275478</v>
+        <v>0.251531261898009</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1077,7 +1140,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0855560937137739</v>
+        <v>0.1257656309490045</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1092,7 +1155,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01463969034312012</v>
+        <v>0.03163398785600238</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1122,7 +1185,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1137,7 +1200,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1152,7 +1215,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1171,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,28 +1291,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03326028400694686</v>
+        <v>0.04175687800452221</v>
       </c>
       <c r="C2" t="n">
-        <v>33.26028400694686</v>
+        <v>41.75687800452221</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07656587391426478</v>
+        <v>0.05192234443570237</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0714326926688235</v>
+        <v>0.08816349122758579</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007278197503175589</v>
+        <v>0.013919084881239</v>
       </c>
       <c r="H2" t="n">
-        <v>6.705938507725284e-05</v>
+        <v>3.881649167932292e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007345168194162157</v>
+        <v>0.01395765083165029</v>
       </c>
     </row>
     <row r="3">
@@ -1259,13 +1322,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03828293695713239</v>
+        <v>0.0009573994464305569</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1286,48 +1349,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>servos</t>
+          <t>glue</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.00707782673002102</v>
       </c>
       <c r="C4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.07782673002102</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04593952434855886</v>
+        <v>0.07725468610710508</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.05000888682295675</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.001204449409111689</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.000113368598728225</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.001286268506974585</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>flight_controller</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008520468433574046</v>
+        <v>0.005</v>
       </c>
       <c r="C5" t="n">
-        <v>8.520468433574047</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3633593574207804</v>
+        <v>0.01595739944643056</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1348,17 +1411,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pod</t>
+          <t>receiver</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.095</v>
+        <v>0.02095739944643056</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1379,48 +1442,48 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>glue</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00659790892262482</v>
+        <v>0.004590000046057616</v>
       </c>
       <c r="C7" t="n">
-        <v>6.59790892262482</v>
+        <v>4.590000046057615</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1206126357324473</v>
+        <v>0.1450000025587564</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.030311065303111</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005936538896978842</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003385489460493147</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009149015450212645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>pod</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>0.03115340666142142</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1445,13 +1508,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00319573690791101</v>
+        <v>0.00379420125359268</v>
       </c>
       <c r="C9" t="n">
-        <v>3.195736907911011</v>
+        <v>3.79420125359268</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8816354230266699</v>
+        <v>0.4489421043188936</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1460,13 +1523,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.438870786188843e-05</v>
+        <v>4.847410205755389e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.151541243881402e-06</v>
+        <v>3.032299176353551e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>3.653545550040796e-05</v>
+        <v>5.150070993202705e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1476,44 +1539,44 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001449329343968892</v>
+        <v>0.003131764797744236</v>
       </c>
       <c r="C10" t="n">
-        <v>1.449329343968892</v>
+        <v>3.131764797744236</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8794967616984477</v>
+        <v>0.4628828205920151</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0855560937137739</v>
+        <v>0.1257656309490045</v>
       </c>
       <c r="G10" t="n">
-        <v>3.537375797158313e-06</v>
+        <v>1.651405042021446e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>4.42036100018792e-06</v>
+        <v>2.063962699577019e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>8.851591970455608e-07</v>
+        <v>4.130274222752346e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ballast</t>
+          <t>servo_elevator</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001248042840409447</v>
+        <v>0.0022</v>
       </c>
       <c r="C11" t="n">
-        <v>1.248042840409447</v>
+        <v>2.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04593952434855886</v>
+        <v>0.03115340666142142</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1534,31 +1597,217 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>servo_rudder</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.03115340666142142</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>servo_aileron_R</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03115340666142142</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4500000044577295</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.07934714210482721</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>servo_aileron_L</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03115340666142142</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.4500000044577295</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.07934714210482721</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>wing_spar</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.002000000019812131</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.000000019812131</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.02596117221785118</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>linkages</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B16" t="n">
         <v>0.001</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.4183593574207804</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="D16" t="n">
+        <v>0.2000000025587564</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>regulator</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01095739944643056</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ballast</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-9.996466100580476e-09</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-9.996466100580475e-06</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.03115340666142142</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1595,7 +1844,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03224942926190789</v>
+        <v>0.06034764866659841</v>
       </c>
     </row>
     <row r="3">
@@ -1605,7 +1854,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6294856343110077</v>
+        <v>1.437729089480245</v>
       </c>
     </row>
     <row r="4">
@@ -1615,7 +1864,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.340161805147485e-07</v>
+        <v>1.268677541962251e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1625,7 +1874,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001820511524613933</v>
+        <v>-0.002349834244172455</v>
       </c>
     </row>
     <row r="6">
@@ -1635,7 +1884,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.07529549634031213</v>
+        <v>-0.3749506281527579</v>
       </c>
     </row>
     <row r="7">
@@ -1645,7 +1894,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-8.380160268495196e-05</v>
+        <v>-5.01764500990265e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1655,7 +1904,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.35385984963809</v>
+        <v>0.592376722984446</v>
       </c>
     </row>
     <row r="9">
@@ -1665,7 +1914,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.005053156532401</v>
+        <v>8.640644092522614</v>
       </c>
     </row>
     <row r="10">
@@ -1675,7 +1924,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.890875486074246e-05</v>
+        <v>-6.546555420295382e-05</v>
       </c>
     </row>
     <row r="11">
@@ -1685,7 +1934,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01586307786877184</v>
+        <v>-0.03649754052570398</v>
       </c>
     </row>
     <row r="12">
@@ -1695,7 +1944,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3676832720721501</v>
+        <v>-0.5514935474507653</v>
       </c>
     </row>
     <row r="13">
@@ -1705,7 +1954,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0001684725177697466</v>
+        <v>-0.000351288195976629</v>
       </c>
     </row>
     <row r="14">
@@ -1715,7 +1964,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.14709254935964e-17</v>
+        <v>1.268411469091419e-16</v>
       </c>
     </row>
     <row r="15">
@@ -1725,7 +1974,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.811288389569231e-13</v>
+        <v>-9.927899290575955e-22</v>
       </c>
     </row>
     <row r="16">
@@ -1735,7 +1984,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.3099907611852864</v>
+        <v>-0.5372651820009698</v>
       </c>
     </row>
     <row r="17">
@@ -1745,7 +1994,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.5664061109614236</v>
+        <v>-0.7001962711447455</v>
       </c>
     </row>
     <row r="18">
@@ -1755,7 +2004,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.920359370436785e-15</v>
+        <v>-2.314778478811373e-16</v>
       </c>
     </row>
     <row r="19">
@@ -1765,7 +2014,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1241092089572653</v>
+        <v>0.1449301782466178</v>
       </c>
     </row>
     <row r="20">
@@ -1775,7 +2024,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.238244227167802e-18</v>
+        <v>4.859129077579104e-18</v>
       </c>
     </row>
     <row r="21">
@@ -1785,7 +2034,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.956947532065448e-13</v>
+        <v>1.637725601383723e-18</v>
       </c>
     </row>
     <row r="22">
@@ -1795,7 +2044,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2819421310024662</v>
+        <v>-0.3482472358604649</v>
       </c>
     </row>
     <row r="23">
@@ -1805,7 +2054,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.064729130000453</v>
+        <v>-1.288952740205051</v>
       </c>
     </row>
     <row r="24">
@@ -1815,7 +2064,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.11993665936314e-15</v>
+        <v>-1.008301841272253e-17</v>
       </c>
     </row>
     <row r="25">
@@ -1825,7 +2074,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02179025168256403</v>
+        <v>0.06084818415651069</v>
       </c>
     </row>
     <row r="26">
@@ -1835,7 +2084,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.043139912434701e-10</v>
+        <v>5.684297594090304e-11</v>
       </c>
     </row>
     <row r="27">
@@ -1845,7 +2094,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3502525891591913</v>
+        <v>-0.4320321200483735</v>
       </c>
     </row>
     <row r="28">
@@ -1855,7 +2104,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.002756527529876e-05</v>
+        <v>-3.788732770504593e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1865,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.006396570981524612</v>
+        <v>-0.02143214387617232</v>
       </c>
     </row>
     <row r="30">
@@ -1875,7 +2124,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-39.52415465967306</v>
+        <v>-28.07197360924453</v>
       </c>
     </row>
     <row r="31">
@@ -1885,7 +2134,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001389555864853396</v>
+        <v>-0.0002150478854955052</v>
       </c>
     </row>
     <row r="32">
@@ -1895,7 +2144,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.177796536276711e-18</v>
+        <v>-2.326394685579088e-17</v>
       </c>
     </row>
     <row r="33">
@@ -1905,7 +2154,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.528864420935966e-14</v>
+        <v>1.277810489939291e-19</v>
       </c>
     </row>
     <row r="34">
@@ -1915,7 +2164,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.03795793239845403</v>
+        <v>0.05273527730867276</v>
       </c>
     </row>
     <row r="35">
@@ -1925,7 +2174,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.07056892371846811</v>
+        <v>-0.01272875567150687</v>
       </c>
     </row>
     <row r="36">
@@ -1935,7 +2184,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.586475024903658e-16</v>
+        <v>4.335473595662213e-17</v>
       </c>
     </row>
     <row r="37">
@@ -1945,7 +2194,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.05850483910941145</v>
+        <v>-0.02038937755915811</v>
       </c>
     </row>
     <row r="38">
@@ -1955,7 +2204,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.07963423851923263</v>
+        <v>0.09549157714701462</v>
       </c>
     </row>
     <row r="39">
@@ -1965,7 +2214,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.01223295000408741</v>
+        <v>0.01283254589309096</v>
       </c>
     </row>
     <row r="40">
@@ -1975,7 +2224,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.06740128851514521</v>
+        <v>0.08265903125392368</v>
       </c>
     </row>
     <row r="41">
@@ -1985,7 +2234,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.02972920083507641</v>
+        <v>-0.02240238517318356</v>
       </c>
     </row>
     <row r="42">
@@ -1995,7 +2244,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02972920083507641</v>
+        <v>0.02240238517318356</v>
       </c>
     </row>
     <row r="43">
@@ -2005,7 +2254,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.07963423851923263</v>
+        <v>-0.09549157714701462</v>
       </c>
     </row>
     <row r="44">
@@ -2015,7 +2264,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.873794058170949</v>
+        <v>0.9373519729903574</v>
       </c>
     </row>
     <row r="45">
@@ -2025,7 +2274,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-5.031192021622866e-18</v>
+        <v>1.561498925562746e-17</v>
       </c>
     </row>
     <row r="46">
@@ -2035,7 +2284,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5.031192021622866e-18</v>
+        <v>-1.561498925562746e-17</v>
       </c>
     </row>
     <row r="47">
@@ -2045,7 +2294,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-3.824577332181577e-18</v>
+        <v>9.761518152212062e-18</v>
       </c>
     </row>
     <row r="48">
@@ -2055,7 +2304,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-2.832541343211853e-17</v>
+        <v>2.00708087773337e-16</v>
       </c>
     </row>
     <row r="49">
@@ -2067,11 +2316,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00019699567303608487,
+	L=0.00015678147190471668,
 	Y=0.0,
-	D=0.0008275962274152107,
-	l_b=-0.0,
-	m_b=-8.809873553677019e-05,
+	D=0.0004462594701314906,
+	l_b=0.0,
+	m_b=-3.991760220866206e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -2085,7 +2334,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-5.031192021622866e-18</v>
+        <v>1.561498925562746e-17</v>
       </c>
     </row>
     <row r="51">
@@ -2095,7 +2344,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-7.725758810364462e-11</v>
+        <v>9.340407184407328e-12</v>
       </c>
     </row>
     <row r="52">
@@ -2105,7 +2354,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.103824758584693e-17</v>
+        <v>-7.475954525942497e-17</v>
       </c>
     </row>
     <row r="53">
@@ -2117,29 +2366,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.7833532308652463,
-	Y=-1.734723475976807e-18,
-	D=0.05625017879996465,
-	l_b=-3.469446951953614e-18,
-	m_b=0.06668582602977607,
-	n_b=-5.421010862427522e-20,
-	span_effective=1.6206496144751994, oswalds_efficiency=0.7718502762705776,
+	L=0.8190770105495178,
+	Y=0.0,
+	D=0.06895748181644042,
+	l_b=-0.0,
+	m_b=0.04077632635669387,
+	n_b=-0.0,
+	span_effective=2.0002343847124058, oswalds_efficiency=0.7260040394091332,
 ), AeroComponentResults(
-	L=0.09024383163266649,
+	L=0.11811818096893491,
 	Y=0.0,
-	D=0.007883984453949123,
+	D=0.009765739046209334,
 	l_b=-0.0,
-	m_b=-0.06663054190862432,
+	m_b=-0.040906124450364754,
 	n_b=-0.0,
-	span_effective=0.35933366548087253, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.3915367936110467, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-0.0,
-	Y=-2.6590689956141722e-17,
-	D=0.0024395290338162295,
-	l_b=-1.5617450696692519e-18,
-	m_b=3.2814537127424117e-05,
-	n_b=2.10924576944712e-17,
-	span_effective=0.1711121874275478, oswalds_efficiency=0.8232692748986458,
+	L=-5.421010862427522e-20,
+	Y=2.00708087773337e-16,
+	D=0.0034895509211424294,
+	l_b=1.5614989255627464e-17,
+	m_b=0.0001697157052199532,
+	n_b=-7.475954525942497e-17,
+	span_effective=0.25153126189800895, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2151,7 +2400,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1282692216227911</v>
+        <v>0.08244691953420585</v>
       </c>
     </row>
     <row r="55">
@@ -2161,7 +2410,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3220966430871982</v>
+        <v>0.2765931367970368</v>
       </c>
     </row>
     <row r="56">
@@ -2171,7 +2420,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.03329226774080776</v>
+        <v>0.06079264141880222</v>
       </c>
     </row>
     <row r="57">
@@ -2181,7 +2430,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3541819883461077</v>
+        <v>0.5979462510524877</v>
       </c>
     </row>
     <row r="58">
@@ -2191,7 +2440,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-2.835765446046807e-17</v>
+        <v>-1.390024184358077e-17</v>
       </c>
     </row>
     <row r="59">
@@ -2201,7 +2450,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-6.38219382057322e-18</v>
+        <v>-3.909370778916788e-19</v>
       </c>
     </row>
     <row r="60">
@@ -2211,7 +2460,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.005146727224944566</v>
+        <v>0.0009755464962518065</v>
       </c>
     </row>
     <row r="61">
@@ -2221,7 +2470,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.045481716114787e-17</v>
+        <v>7.322293911674736e-19</v>
       </c>
     </row>
     <row r="62">
@@ -2231,7 +2480,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.06294152819570649</v>
+        <v>0.07067440280798423</v>
       </c>
     </row>
     <row r="63">
@@ -2241,7 +2490,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.009382912642914253</v>
+        <v>0.009606110359610167</v>
       </c>
     </row>
     <row r="64">
@@ -2251,7 +2500,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.05355861555279223</v>
+        <v>0.06106829244837406</v>
       </c>
     </row>
     <row r="65">
@@ -2261,7 +2510,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.02469508896185747</v>
+        <v>-0.01647178025661227</v>
       </c>
     </row>
     <row r="66">
@@ -2271,7 +2520,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.02469508896185747</v>
+        <v>0.01647178025661227</v>
       </c>
     </row>
     <row r="67">
@@ -2281,7 +2530,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.06294152819570649</v>
+        <v>-0.07067440280798423</v>
       </c>
     </row>
     <row r="68">
@@ -2291,7 +2540,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6696076031664475</v>
+        <v>0.6951416029660685</v>
       </c>
     </row>
     <row r="69">
@@ -2301,7 +2550,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.985412154532852e-17</v>
+        <v>-9.229890253319994e-19</v>
       </c>
     </row>
     <row r="70">
@@ -2311,7 +2560,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.985412154532852e-17</v>
+        <v>9.229890253319994e-19</v>
       </c>
     </row>
     <row r="71">
@@ -2321,7 +2570,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.796917958637743e-17</v>
+        <v>-7.85933829926345e-19</v>
       </c>
     </row>
     <row r="72">
@@ -2331,7 +2580,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-5.361227182490354e-17</v>
+        <v>-1.615970729769585e-17</v>
       </c>
     </row>
     <row r="73">
@@ -2343,11 +2592,11 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.00015610787456671668,
+	L=0.00011937629023782458,
 	Y=0.0,
-	D=0.0006528172936150688,
-	l_b=-0.0,
-	m_b=-6.98681858411693e-05,
+	D=0.0003401772681419904,
+	l_b=0.0,
+	m_b=-3.053643707906197e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -2361,7 +2610,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.985412154532852e-17</v>
+        <v>-9.229890253319994e-19</v>
       </c>
     </row>
     <row r="75">
@@ -2371,7 +2620,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.001490013816381656</v>
+        <v>0.0001177723651018134</v>
       </c>
     </row>
     <row r="76">
@@ -2381,7 +2630,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3.252348902073505e-17</v>
+        <v>1.72876846503767e-18</v>
       </c>
     </row>
     <row r="77">
@@ -2393,29 +2642,29 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.6021268984154694,
-	Y=-7.806255641895632e-18,
-	D=0.0447321314774594,
-	l_b=-1.734723475976807e-17,
-	m_b=0.05125661033137777,
-	n_b=-5.963111948670274e-19,
-	span_effective=1.6206496144751994, oswalds_efficiency=0.7718502762705776,
+	L=0.608866044905681,
+	Y=0.0,
+	D=0.05071731058422466,
+	l_b=-0.0,
+	m_b=0.0298878579987019,
+	n_b=-0.0,
+	span_effective=2.0002343847124058, oswalds_efficiency=0.7260040394091332,
 ), AeroComponentResults(
-	L=0.06732459687641117,
+	L=0.08615618177014973,
 	Y=0.0,
-	D=0.006156568354581533,
+	D=0.007207914076889615,
 	l_b=-0.0,
-	m_b=-0.04972386067737028,
+	m_b=-0.02987586889835551,
 	n_b=-0.0,
-	span_effective=0.35933366548087253, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.3915367936110467, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=1.3552527156068805e-20,
-	Y=-4.5806016183007906e-17,
-	D=0.0020170984271362254,
-	l_b=-2.5068867855604483e-18,
-	m_b=2.713234821533858e-05,
-	n_b=3.311980021560208e-17,
-	span_effective=0.1711121874275478, oswalds_efficiency=0.8232692748986458,
+	L=5.421010862427522e-20,
+	Y=-1.6159707297695848e-17,
+	D=0.002802890519117794,
+	l_b=-9.229890253319994e-19,
+	m_b=0.00013631970183448745,
+	n_b=1.7287684650376704e-18,
+	span_effective=0.25153126189800895, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2473,10 +2722,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.873794058170949</v>
+        <v>0.9373519729903574</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8737940681678181</v>
+        <v>0.9373519829903338</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -2493,7 +2742,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07963423851923263</v>
+        <v>0.09549157714701462</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -2513,7 +2762,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.043139912434701e-10</v>
+        <v>5.684297594090304e-11</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2535,7 +2784,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.238244227167802e-18</v>
+        <v>4.859129077579104e-18</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2557,7 +2806,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.177796536276711e-18</v>
+        <v>-2.326394685579088e-17</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2579,7 +2828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.35385984963809</v>
+        <v>0.592376722984446</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -2599,7 +2848,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.265624951894776</v>
+        <v>4.454442685290084</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
@@ -2619,7 +2868,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3541819883461077</v>
+        <v>0.5979462510524877</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
@@ -2639,7 +2888,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.358035212357187</v>
+        <v>2.269816185298065</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -2659,7 +2908,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.97259262371068</v>
+        <v>9.816069657612333</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
@@ -2679,7 +2928,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.467824176548267</v>
+        <v>4.444673584361032</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -2699,7 +2948,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.467824176548267</v>
+        <v>4.444673584361032</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
@@ -2719,7 +2968,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41933.23557384799</v>
+        <v>24882.01095054371</v>
       </c>
       <c r="C14" t="n">
         <v>20000</v>
@@ -2739,7 +2988,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04999999019744358</v>
+        <v>0.04999999021163743</v>
       </c>
       <c r="C15" t="n">
         <v>0.05</v>
@@ -2759,7 +3008,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04999999019744358</v>
+        <v>0.04999999021163743</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
@@ -2779,7 +3028,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7000000082067733</v>
+        <v>0.700000008872528</v>
       </c>
       <c r="C17" t="n">
         <v>0.5</v>
@@ -2799,7 +3048,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7000000082067733</v>
+        <v>0.700000008872528</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -2819,7 +3068,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02999999000181115</v>
+        <v>0.02999999000355073</v>
       </c>
       <c r="C19" t="n">
         <v>0.03</v>
@@ -2839,7 +3088,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02999999000181115</v>
+        <v>0.02999999000355073</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -2859,7 +3108,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2819421310024662</v>
+        <v>-0.3482472358604649</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
@@ -2879,7 +3128,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03795793239845403</v>
+        <v>0.05273527730867276</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2899,7 +3148,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-39.52415465967306</v>
+        <v>-28.07197360924453</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
@@ -2919,7 +3168,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5999999902182078</v>
+        <v>1.32678190745631</v>
       </c>
       <c r="C24" t="n">
         <v>0.6</v>
@@ -2939,7 +3188,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64.60823651215563</v>
+        <v>95.10014421550056</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -2959,7 +3208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.009286741483886836</v>
+        <v>0.01395141845894336</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -2979,7 +3228,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.761184839387542e-06</v>
+        <v>7.743377521929095e-06</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
@@ -2999,7 +3248,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.628272027785878e-07</v>
+        <v>1.652598046741634e-07</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
@@ -3019,7 +3268,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5.05083796544096e-22</v>
+        <v>2.398931626149465e-22</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
@@ -3039,7 +3288,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.086407042169356e-15</v>
+        <v>1.407667968928422e-17</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
@@ -3059,7 +3308,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7295201047390686</v>
+        <v>0.7475451269562055</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
@@ -3079,7 +3328,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.849205181611853e-15</v>
+        <v>7.517549736417041e-16</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
@@ -3103,6 +3352,442 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>BoundHit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IsAtBoundary</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>alpha_deg</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4.454442685290084</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>delta_a_deg</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-1.407667968928422e-17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>delta_e_deg</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7475451269562055</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>delta_r_deg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-7.517549736417041e-16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-30</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>wing_span_m</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.000000019812131</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[WARN] wing_span_m hit upper bound (value=2, upper=2, tol=0.002).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>wing_chord_m</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1038446888714047</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tail_arm_m</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.4000000051175128</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.00085</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[WARN] tail_arm_m hit lower bound (value=0.4, lower=0.4, tol=0.00085).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>htail_span_m</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3915367936110467</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vtail_height_m</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.251531261898009</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ballast_mass_kg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-9.996466100580476e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.5e-05</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[WARN] ballast_mass_kg hit lower bound (value=-9.99647e-09, lower=0, tol=2.5e-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>battery_slider_eta</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6100015467829478</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3140,7 +3825,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3160,7 +3845,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3280,7 +3965,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.265624951894776</v>
+        <v>4.454442685290084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3300,7 +3985,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1.086407042169356e-15</v>
+        <v>-1.407667968928422e-17</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3320,7 +4005,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7295201047390686</v>
+        <v>0.7475451269562055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3340,7 +4025,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.849205181611853e-15</v>
+        <v>-7.517549736417041e-16</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3360,7 +4045,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3645446515159374</v>
+        <v>0.3565581831366305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3380,7 +4065,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.35385984963809</v>
+        <v>0.592376722984446</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3400,7 +4085,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.265624951894776</v>
+        <v>4.454442685290084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3420,7 +4105,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1.086407042169356e-15</v>
+        <v>-1.407667968928422e-17</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3440,7 +4125,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7295201047390686</v>
+        <v>0.7475451269562055</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3460,7 +4145,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.849205181611853e-15</v>
+        <v>-7.517549736417041e-16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3480,7 +4165,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3541819883461077</v>
+        <v>0.5979462510524877</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3500,7 +4185,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.047805349839111</v>
+        <v>0.769816175392</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3520,7 +4205,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.358035212357187</v>
+        <v>2.269816185298065</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fb0dd39-dirty</t>
+          <t>bdcac3f-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>147.4547270755265</v>
+        <v>225.7690647637066</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6766844357244848</v>
+        <v>0.6440573443182428</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -608,41 +608,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>alpha_trim_deg</t>
+          <t>fuselage_tail_x_m</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.244685672697495</v>
+        <v>0.5340573443182428</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>delta_a_trim_deg</t>
+          <t>fuselage_length_m</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.310889154646248e-16</v>
+        <v>0.6440573443182428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>delta_e_trim_deg</t>
+          <t>alpha_trim_deg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1730216997764102</v>
+        <v>4.995818923191007</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -653,11 +653,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>delta_r_trim_deg</t>
+          <t>delta_a_trim_deg</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.329118856354705e-16</v>
+        <v>2.318821944480995e-16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -668,11 +668,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>alpha_turn_deg</t>
+          <t>delta_e_trim_deg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.000000079981351</v>
+        <v>1.248382770292376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>delta_a_turn_deg</t>
+          <t>delta_r_trim_deg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.403263081402325e-17</v>
+        <v>3.758299667982743e-15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -698,11 +698,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>delta_e_turn_deg</t>
+          <t>alpha_turn_deg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1196032005122943</v>
+        <v>8.000000079995392</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -713,11 +713,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>delta_r_turn_deg</t>
+          <t>delta_a_turn_deg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.754992318227725e-16</v>
+        <v>-2.809137900571732e-18</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -728,191 +728,191 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mass_total_kg</t>
+          <t>delta_e_turn_deg</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08673341084853904</v>
+        <v>4.149054262853123</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mass_total_g</t>
+          <t>delta_r_turn_deg</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86.73341084853904</v>
+        <v>7.814204555748593e-17</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mass_total_lbm</t>
+          <t>mass_total_kg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1912144396267932</v>
+        <v>0.1070485325235647</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lbm</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ballast_mass_kg</t>
+          <t>mass_total_g</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>107.0485325235647</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>battery_slider_eta</t>
+          <t>mass_total_lbm</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7072709585758128</v>
+        <v>0.2360016164371651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lbm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>battery_x_m</t>
+          <t>ballast_mass_kg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.05950317774457095</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sink_rate_mps</t>
+          <t>battery_slider_eta</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4871003372485448</v>
+        <v>0.6766792150473272</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L_over_D</t>
+          <t>battery_x_m</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.238342910150571</v>
+        <v>0.05787929025254737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>turn_radius_m</t>
+          <t>sink_rate_mps</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.368562089585778</v>
+        <v>0.617381854787086</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/s</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>turn_footprint_lhs_m</t>
+          <t>L_over_D</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.310600117228323</v>
+        <v>7.999999920130635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>turn_CL</t>
+          <t>turn_radius_m</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6581539076316473</v>
+        <v>1.437845545371058</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>wing_loading_n_m2</t>
+          <t>turn_footprint_lhs_m</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.606575903852786</v>
+        <v>2.393570521135981</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>N/m^2</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>reynolds_wing</t>
+          <t>turn_CL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63384.73648907142</v>
+        <v>0.7071245061333374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -923,26 +923,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>static_margin</t>
+          <t>wing_loading_n_m2</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1000000100104355</v>
+        <v>5.199892746342704</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MAC fraction</t>
+          <t>N/m^2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tail_volume_horizontal</t>
+          <t>reynolds_wing</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4999999900095295</v>
+        <v>67223.26919679661</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -953,56 +953,56 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tail_volume_vertical</t>
+          <t>static_margin</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.02999999000155204</v>
+        <v>0.04999998999434588</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MAC fraction</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>roll_rate_ss_radps</t>
+          <t>tail_volume_horizontal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.097055405350419</v>
+        <v>0.4999999900064669</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>roll_rate_ss_turn_radps</t>
+          <t>tail_volume_vertical</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.64182702697815</v>
+        <v>0.02999999000058427</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>min_roll_rate_turn_radps</t>
+          <t>roll_rate_ss_radps</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5817764173314431</v>
+        <v>4.065798068775985</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1013,240 +1013,420 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>roll_accel0_rad_s2</t>
+          <t>roll_rate_ss_turn_radps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>199.6538351644555</v>
+        <v>3.704393795995896</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rad/s^2</t>
+          <t>rad/s</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>roll_tau_s</t>
+          <t>min_roll_rate_turn_radps</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0205207949147366</v>
+        <v>0.5817764173314431</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>rad/s</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_m</t>
+          <t>roll_accel0_rad_s2</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.286305286222613</v>
+        <v>162.8965872304802</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>rad/s^2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_allow_m</t>
+          <t>roll_tau_s</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.03536304221140358</v>
+        <v>0.02495938151867688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_semispan_fraction</t>
+          <t>wing_tip_deflection_m</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.909942597207468</v>
+        <v>1.640336697806695</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_over_allow</t>
+          <t>wing_tip_deflection_allow_m</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>36.37428246509334</v>
+        <v>0.03645799806119386</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_m</t>
+          <t>wing_tip_deflection_semispan_fraction</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6164535879086877</v>
+        <v>3.599400482831624</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_allow_m</t>
+          <t>wing_tip_deflection_over_allow</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.01464915112656194</v>
+        <v>44.9925060353953</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_semispan_fraction</t>
+          <t>wing_struct_semispan_m</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.366494522899308</v>
+        <v>0.4627552680926893</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_over_allow</t>
+          <t>wing_struct_half_load_n</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>42.08118153624135</v>
+        <v>0.8168686578824084</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>objective_struct_deflection_penalty</t>
+          <t>wing_struct_line_load_n_m</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>62.56699299601062</v>
+        <v>1.765228219333401</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>objective_htail_deflection_penalty</t>
+          <t>wing_struct_E_pa</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>84.38317710074055</v>
+        <v>1500000</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>objective_roll_tau_penalty</t>
+          <t>wing_struct_thickness_m</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0001039760552920197</v>
+        <v>0.006</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>max_servo_utilization</t>
+          <t>htail_tip_deflection_m</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0001542502917221551</v>
+        <v>0.8605320307455027</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>design_var_bound_hits_count</t>
+          <t>htail_tip_deflection_allow_m</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>0.01665499913439414</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>htail_tip_deflection_semispan_fraction</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4.133447375417382</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>htail_tip_deflection_over_allow</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>51.66809219271727</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>htail_struct_semispan_m</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.2081874891799267</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>htail_struct_half_load_n</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.2042171644706021</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>htail_struct_line_load_n_m</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.9809290907683061</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>N/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>htail_struct_E_pa</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>htail_struct_thickness_m</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>objective_struct_deflection_penalty</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>96.7670293637146</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>objective_htail_deflection_penalty</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>128.3627783308596</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>objective_roll_tau_penalty</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.0001538199322950294</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>max_servo_utilization</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.003577412893454938</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>design_var_bound_hits_count</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>design_var_bound_hits</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>alpha_turn_deg:upper; ballast_mass_kg:lower</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1263,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.897714353467453</v>
+        <v>0.9255105361853786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1305,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2057496155261446</v>
+        <v>0.2182096598924276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1320,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1847043830782299</v>
+        <v>0.2019553393278698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1335,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.363139883259615</v>
+        <v>4.241382057245469</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1350,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6766844357244848</v>
+        <v>0.6440573443182428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1361,11 +1541,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>htail_span_m</t>
+          <t>fuselage_tail_x_m</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3662287781640486</v>
+        <v>0.5340573443182428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,11 +1556,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>htail_chord_m</t>
+          <t>fuselage_length_m</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09155719454101215</v>
+        <v>0.6440573443182428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,26 +1571,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>htail_area_m2</t>
+          <t>htail_span_m</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03353087948888298</v>
+        <v>0.4163749783598534</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>m^2</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vtail_height_m</t>
+          <t>htail_chord_m</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1314886677990685</v>
+        <v>0.1189642795313867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1421,88 +1601,118 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vtail_chord_m</t>
+          <t>htail_area_m2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06574433389953427</v>
+        <v>0.04953374931547669</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m^2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vtail_area_m2</t>
+          <t>vtail_height_m</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.008644634879786901</v>
+        <v>0.1575689288959599</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>m^2</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dihedral_deg</t>
+          <t>vtail_chord_m</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>0.07878446444797996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aileron_semispan_start</t>
+          <t>vtail_area_m2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3</v>
+        <v>0.01241398367671004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>m^2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>aileron_semispan_end</t>
+          <t>dihedral_deg</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aileron_chord_fraction</t>
+          <t>aileron_semispan_start</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.3</v>
       </c>
       <c r="C16" t="inlineStr">
+        <is>
+          <t>eta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aileron_semispan_end</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>eta</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aileron_chord_fraction</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1519,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1576,28 +1786,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03657146784948952</v>
+        <v>0.03998715718691821</v>
       </c>
       <c r="C2" t="n">
-        <v>36.57146784948952</v>
+        <v>39.98715718691821</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1028748077630723</v>
+        <v>0.1091048299462138</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03897161538626745</v>
+        <v>0.04017830450503364</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002382102281151037</v>
+        <v>0.002768367587653758</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001331356409168534</v>
+        <v>0.0001637203424472442</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002515018493260794</v>
+        <v>0.00293184800715788</v>
       </c>
     </row>
     <row r="3">
@@ -1613,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05950317774457095</v>
+        <v>0.05787929025254737</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1634,79 +1844,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>glue</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006424697099891781</v>
+        <v>0.008498136449883124</v>
       </c>
       <c r="C4" t="n">
-        <v>6.42469709989178</v>
+        <v>8.498136449883123</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1330200348926835</v>
+        <v>0.2120286721591214</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02051803584683956</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002107443677363908</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001534755354339675</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003589016344926982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flight_controller</t>
+          <t>glue</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005</v>
+        <v>0.007929520927671456</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.929520927671456</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07450317774457095</v>
+        <v>0.1469015240633527</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.01899822970330011</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.0002468923347374914</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.0001552806533449748</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0003946558443010751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>htail_surfaces</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005</v>
+        <v>0.005944049917857202</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>5.944049917857202</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07950317774457095</v>
+        <v>0.5043162744353962</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1715,29 +1925,29 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>8.588018928113547e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7.014721812434071e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>9.288599501869274e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>htail_surfaces</t>
+          <t>flight_controller</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004023705538665957</v>
+        <v>0.005</v>
       </c>
       <c r="C7" t="n">
-        <v>4.023705538665957</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6124630329949908</v>
+        <v>0.07287929025254737</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1746,29 +1956,29 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.497581295107372e-05</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.813817477398982e-06</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4.778359487016471e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pod</t>
+          <t>receiver</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06172488465784337</v>
+        <v>0.07787929025254738</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1789,17 +1999,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>servo_elevator</t>
+          <t>tail mount module 1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0022</v>
+        <v>0.004</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06172488465784337</v>
+        <v>0.4805234185291188</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1820,17 +2030,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>servo_rudder</t>
+          <t>avionics tray</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0022</v>
+        <v>0.004</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06172488465784337</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1851,23 +2061,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>servo_aileron_R</t>
+          <t>wing root module 1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0022</v>
+        <v>0.003</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06172488465784337</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1989171124391451</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03507445384764071</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1882,23 +2092,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>servo_aileron_L</t>
+          <t>wing root module 2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0022</v>
+        <v>0.003</v>
       </c>
       <c r="C12" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06172488465784337</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1989171124391451</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03507445384764071</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1913,17 +2123,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>wing_attach_1</t>
+          <t>servo_elevator</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0015</v>
+        <v>0.0022</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06172488465784337</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1944,17 +2154,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wing_attach_2</t>
+          <t>servo_rudder</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0015</v>
+        <v>0.0022</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06172488465784337</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1975,54 +2185,54 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vtail_surfaces</t>
+          <t>servo_aileron_R</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001037356185574428</v>
+        <v>0.0022</v>
       </c>
       <c r="C15" t="n">
-        <v>1.037356185574428</v>
+        <v>2.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5995566026742519</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.2050762390942155</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06574433389953427</v>
+        <v>0.03616047405453028</v>
       </c>
       <c r="G15" t="n">
-        <v>1.495372261235747e-06</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.868242805120707e-06</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3.744265781633223e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>linkages</t>
+          <t>servo_aileron_L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.001</v>
+        <v>0.0022</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2833422178622424</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.2050762390942155</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.03616047405453028</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2037,38 +2247,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tail_attach_1</t>
+          <t>vtail_surfaces</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001</v>
+        <v>0.001489678041205204</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>1.489678041205204</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5666844357244848</v>
+        <v>0.4842263668936928</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.07878446444797996</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3.083257073043368e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3.85267476814058e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>7.7165221215902e-07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tail_attach_2</t>
+          <t>linkages</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2078,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5666844357244848</v>
+        <v>0.2224170673348514</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2099,17 +2309,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>regulator</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0004761941748638135</v>
+        <v>0.0004</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4761941748638135</v>
+        <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2283422178622424</v>
+        <v>0.06787929025254737</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2130,17 +2340,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>regulator</t>
+          <t>ballast</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0004</v>
+        <v>-9.999970538854929e-09</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4</v>
+        <v>-9.999970538854929e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06950317774457095</v>
+        <v>0.06546289796772828</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2155,68 +2365,6 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>wing_spar</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.05143740388153614</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ballast</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>-9.99994642977062e-09</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-9.999946429770621e-06</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.06172488465784337</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2253,7 +2401,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04020252463277364</v>
+        <v>0.05751815038676538</v>
       </c>
     </row>
     <row r="3">
@@ -2263,7 +2411,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7089406967563069</v>
+        <v>1.152405761619146</v>
       </c>
     </row>
     <row r="4">
@@ -2273,7 +2421,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.248769998485446e-07</v>
+        <v>1.073697533394615e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2283,7 +2431,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001080003796651019</v>
+        <v>0.005419148698872222</v>
       </c>
     </row>
     <row r="6">
@@ -2293,7 +2441,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1096479884250615</v>
+        <v>0.1337423730331383</v>
       </c>
     </row>
     <row r="7">
@@ -2303,7 +2451,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-8.76458508131117e-05</v>
+        <v>7.472239453576446e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2313,7 +2461,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.371404708411338</v>
+        <v>0.4601451985001849</v>
       </c>
     </row>
     <row r="9">
@@ -2323,7 +2471,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.959604829420631</v>
+        <v>4.205442473775639</v>
       </c>
     </row>
     <row r="10">
@@ -2333,7 +2481,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.903854905942078e-05</v>
+        <v>-8.942361667426424e-06</v>
       </c>
     </row>
     <row r="11">
@@ -2343,7 +2491,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01024442269270676</v>
+        <v>-0.004376802865635465</v>
       </c>
     </row>
     <row r="12">
@@ -2353,7 +2501,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9326837301397717</v>
+        <v>0.1663165750367956</v>
       </c>
     </row>
     <row r="13">
@@ -2363,7 +2511,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0002030157178478653</v>
+        <v>-8.509891452623819e-05</v>
       </c>
     </row>
     <row r="14">
@@ -2373,7 +2521,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.301184975741987e-17</v>
+        <v>-1.424111831562682e-17</v>
       </c>
     </row>
     <row r="15">
@@ -2383,7 +2531,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.604963421346768e-22</v>
+        <v>2.064475784849059e-22</v>
       </c>
     </row>
     <row r="16">
@@ -2393,7 +2541,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2055912480839551</v>
+        <v>-0.2011796791725537</v>
       </c>
     </row>
     <row r="17">
@@ -2403,7 +2551,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3645967476365859</v>
+        <v>-0.3023435725556479</v>
       </c>
     </row>
     <row r="18">
@@ -2413,7 +2561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.811435116695395e-18</v>
+        <v>8.317272200571798e-18</v>
       </c>
     </row>
     <row r="19">
@@ -2423,7 +2571,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1121070171897</v>
+        <v>0.1129973019841508</v>
       </c>
     </row>
     <row r="20">
@@ -2433,7 +2581,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-6.330959906980324e-19</v>
+        <v>-9.400956093217906e-19</v>
       </c>
     </row>
     <row r="21">
@@ -2443,7 +2591,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.022595901599515e-19</v>
+        <v>-2.304523668986025e-19</v>
       </c>
     </row>
     <row r="22">
@@ -2453,7 +2601,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1805289653271583</v>
+        <v>-0.1497243077168116</v>
       </c>
     </row>
     <row r="23">
@@ -2463,7 +2611,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6968679583191469</v>
+        <v>-0.5775611233947082</v>
       </c>
     </row>
     <row r="24">
@@ -2473,7 +2621,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.846373641638289e-18</v>
+        <v>4.453099110204681e-19</v>
       </c>
     </row>
     <row r="25">
@@ -2483,7 +2631,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02588508737936159</v>
+        <v>0.04978841957870687</v>
       </c>
     </row>
     <row r="26">
@@ -2493,7 +2641,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.886347016376049e-15</v>
+        <v>4.321499743788634e-15</v>
       </c>
     </row>
     <row r="27">
@@ -2503,7 +2651,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4959605325898676</v>
+        <v>-0.2102720816105791</v>
       </c>
     </row>
     <row r="28">
@@ -2513,7 +2661,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-5.351519495242641e-06</v>
+        <v>-5.239409296253893e-06</v>
       </c>
     </row>
     <row r="29">
@@ -2523,7 +2671,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.00309803815056864</v>
+        <v>-0.0020621132823843</v>
       </c>
     </row>
     <row r="30">
@@ -2533,7 +2681,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-11.38360583922604</v>
+        <v>-6.231079381770853</v>
       </c>
     </row>
     <row r="31">
@@ -2543,7 +2691,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001367525901532949</v>
+        <v>-0.0001217899959902428</v>
       </c>
     </row>
     <row r="32">
@@ -2553,7 +2701,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6.16160842751699e-18</v>
+        <v>5.041479338892034e-18</v>
       </c>
     </row>
     <row r="33">
@@ -2563,7 +2711,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.235964898824341e-20</v>
+        <v>-2.02213262557967e-20</v>
       </c>
     </row>
     <row r="34">
@@ -2573,7 +2721,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02796323743347748</v>
+        <v>0.03505599997496323</v>
       </c>
     </row>
     <row r="35">
@@ -2583,7 +2731,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.08336113527733333</v>
+        <v>-0.03421589833381396</v>
       </c>
     </row>
     <row r="36">
@@ -2593,7 +2741,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.230756929329205e-18</v>
+        <v>-3.003814999326735e-18</v>
       </c>
     </row>
     <row r="37">
@@ -2603,7 +2751,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.05902241211571213</v>
+        <v>-0.03028335527322533</v>
       </c>
     </row>
     <row r="38">
@@ -2613,7 +2761,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.09210036461158713</v>
+        <v>0.1440758110043622</v>
       </c>
     </row>
     <row r="39">
@@ -2623,7 +2771,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.02938208727305527</v>
+        <v>0.05068158451746413</v>
       </c>
     </row>
     <row r="40">
@@ -2633,7 +2781,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.06271827733853186</v>
+        <v>0.0933942264868981</v>
       </c>
     </row>
     <row r="41">
@@ -2643,7 +2791,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.02887087957778729</v>
+        <v>-0.04315599143577227</v>
       </c>
     </row>
     <row r="42">
@@ -2653,7 +2801,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02887087957778729</v>
+        <v>0.04315599143577227</v>
       </c>
     </row>
     <row r="43">
@@ -2663,7 +2811,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.09210036461158713</v>
+        <v>-0.1440758110043622</v>
       </c>
     </row>
     <row r="44">
@@ -2673,7 +2821,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8508547504317385</v>
+        <v>1.152606476527654</v>
       </c>
     </row>
     <row r="45">
@@ -2683,7 +2831,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-1.302014303094148e-18</v>
+        <v>-2.179413077165105e-18</v>
       </c>
     </row>
     <row r="46">
@@ -2693,7 +2841,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.302014303094148e-18</v>
+        <v>2.179413077165105e-18</v>
       </c>
     </row>
     <row r="47">
@@ -2703,7 +2851,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-3.605228256444694e-19</v>
+        <v>-1.15334136985157e-18</v>
       </c>
     </row>
     <row r="48">
@@ -2713,7 +2861,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-2.980897637340449e-17</v>
+        <v>-3.567222967248125e-17</v>
       </c>
     </row>
     <row r="49">
@@ -2725,11 +2873,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.000283349485019138,
+	L=0.000314036243216673,
 	Y=0.0,
-	D=0.00082498590818047,
+	D=0.0007289501622465802,
 	l_b=0.0,
-	m_b=-5.6832971519495305e-05,
+	m_b=-2.9076860385309108e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -2743,7 +2891,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.302014303094148e-18</v>
+        <v>-2.179413077165105e-18</v>
       </c>
     </row>
     <row r="51">
@@ -2753,7 +2901,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.360490767352701e-15</v>
+        <v>2.362080122426599e-15</v>
       </c>
     </row>
     <row r="52">
@@ -2763,7 +2911,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.267185769704085e-17</v>
+        <v>1.168760484624072e-17</v>
       </c>
     </row>
     <row r="53">
@@ -2775,29 +2923,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.710480830323665,
+	L=0.8780379151087044,
 	Y=0.0,
-	D=0.04857241318121182,
+	D=0.06442041737847674,
 	l_b=-0.0,
-	m_b=0.06377135239350398,
+	m_b=0.08900825386796501,
 	n_b=-0.0,
-	span_effective=0.8841796534823293, oswalds_efficiency=0.8088471951475533,
+	span_effective=0.9115567574672864, oswalds_efficiency=0.8095875167779147,
 ), AeroComponentResults(
-	L=0.14009057062305444,
+	L=0.2742545251757332,
 	Y=0.0,
-	D=0.0113382046591498,
+	D=0.02567952455426785,
 	l_b=-0.0,
-	m_b=-0.06373849874539635,
+	m_b=-0.08906211845275344,
 	n_b=-0.0,
-	span_effective=0.3662287781640486, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.41637497835985343, oswalds_efficiency=0.8137951483430786,
 ), AeroComponentResults(
 	L=-0.0,
-	Y=-2.980897637340449e-17,
-	D=0.0019826735899897644,
-	l_b=-1.302014303094148e-18,
-	m_b=2.3979323410498457e-05,
-	n_b=1.2671857697040849e-17,
-	span_effective=0.13148866779906854, oswalds_efficiency=0.8232692748986458,
+	Y=-3.567222967248125e-17,
+	D=0.0025653343919069247,
+	l_b=-2.1794130771651045e-18,
+	m_b=8.29414451760979e-05,
+	n_b=1.1687604846240722e-17,
+	span_effective=0.15756892889595991, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2809,7 +2957,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1535949985049412</v>
+        <v>0.1578120048746437</v>
       </c>
     </row>
     <row r="55">
@@ -2819,7 +2967,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2551215340926887</v>
+        <v>0.3081737632218351</v>
       </c>
     </row>
     <row r="56">
@@ -2829,7 +2977,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1209035842538319</v>
+        <v>0.1418633642512787</v>
       </c>
     </row>
     <row r="57">
@@ -2839,7 +2987,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6581539076316473</v>
+        <v>0.7071245061333374</v>
       </c>
     </row>
     <row r="58">
@@ -2849,7 +2997,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.30116445069763e-17</v>
+        <v>2.990596526940585e-17</v>
       </c>
     </row>
     <row r="59">
@@ -2859,7 +3007,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-6.976991376381678e-19</v>
+        <v>1.931869213079225e-18</v>
       </c>
     </row>
     <row r="60">
@@ -2869,7 +3017,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.127166801250863e-14</v>
+        <v>5.914511041849252e-15</v>
       </c>
     </row>
     <row r="61">
@@ -2879,7 +3027,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6.763888112789971e-18</v>
+        <v>-1.010300013270307e-17</v>
       </c>
     </row>
     <row r="62">
@@ -2889,7 +3037,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.2188477842253777</v>
+        <v>0.2949844355523568</v>
       </c>
     </row>
     <row r="63">
@@ -2899,7 +3047,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.07290171037039068</v>
+        <v>0.09935617363132208</v>
       </c>
     </row>
     <row r="64">
@@ -2909,7 +3057,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1459460738549869</v>
+        <v>0.1956282619210346</v>
       </c>
     </row>
     <row r="65">
@@ -2919,7 +3067,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.0509175052428418</v>
+        <v>-0.08747860705441396</v>
       </c>
     </row>
     <row r="66">
@@ -2929,7 +3077,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0509175052428418</v>
+        <v>0.08747860705441396</v>
       </c>
     </row>
     <row r="67">
@@ -2939,7 +3087,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.2188477842253777</v>
+        <v>-0.2949844355523568</v>
       </c>
     </row>
     <row r="68">
@@ -2949,7 +3097,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.191325511591645</v>
+        <v>1.470363574188967</v>
       </c>
     </row>
     <row r="69">
@@ -2959,7 +3107,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.133729202298832e-18</v>
+        <v>3.717816371450392e-18</v>
       </c>
     </row>
     <row r="70">
@@ -2969,7 +3117,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.133729202298832e-18</v>
+        <v>-3.717816371450392e-18</v>
       </c>
     </row>
     <row r="71">
@@ -2979,7 +3127,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4.069569876969691e-19</v>
+        <v>9.757090527598963e-19</v>
       </c>
     </row>
     <row r="72">
@@ -2989,7 +3137,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-2.355239993135123e-17</v>
+        <v>6.218514787946424e-17</v>
       </c>
     </row>
     <row r="73">
@@ -3001,11 +3149,11 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.000689572759702006,
+	L=0.0006015902157105119,
 	Y=0.0,
-	D=0.0007458171196977457,
+	D=0.0006763829236288282,
 	l_b=0.0,
-	m_b=-0.00011286693376903223,
+	m_b=-4.457904735356192e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -3019,7 +3167,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.133729202298832e-18</v>
+        <v>3.717816371450392e-18</v>
       </c>
     </row>
     <row r="75">
@@ -3029,7 +3177,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4.197881734065156e-15</v>
+        <v>2.683623993599699e-15</v>
       </c>
     </row>
     <row r="76">
@@ -3039,7 +3187,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.099100896198732e-17</v>
+        <v>-1.94428789691513e-17</v>
       </c>
     </row>
     <row r="77">
@@ -3051,29 +3199,29 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=1.0095045644429477,
+	L=1.1470933682913842,
 	Y=0.0,
-	D=0.12083101191454017,
+	D=0.13452808441524672,
 	l_b=-0.0,
-	m_b=0.08389166944227885,
+	m_b=0.10912158150324003,
 	n_b=-0.0,
-	span_effective=0.8841796534823293, oswalds_efficiency=0.8088471951475533,
+	span_effective=0.9115567574672864, oswalds_efficiency=0.8095875167779147,
 ), AeroComponentResults(
-	L=0.18113137438899507,
+	L=0.3226686156818727,
 	Y=0.0,
-	D=0.022692964501242467,
+	D=0.05817686423775249,
 	l_b=-0.0,
-	m_b=-0.08374983841179572,
+	m_b=-0.10911225766315945,
 	n_b=-0.0,
-	span_effective=0.3662287781640486, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.41637497835985343, oswalds_efficiency=0.8137951483430786,
 ), AeroComponentResults(
 	L=-5.421010862427522e-20,
-	Y=-2.355239993135123e-17,
-	D=0.001676280319506566,
-	l_b=-1.1337292022988325e-18,
-	m_b=-2.8964096709908716e-05,
-	n_b=1.0991008961987324e-17,
-	span_effective=0.13148866779906854, oswalds_efficiency=0.8232692748986458,
+	Y=6.218514787946424e-17,
+	D=0.0022469303444065903,
+	l_b=3.7178163714503916e-18,
+	m_b=3.525520727566548e-05,
+	n_b=-1.9442878969151304e-17,
+	span_effective=0.15756892889595991, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -3131,10 +3279,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8508547504317385</v>
+        <v>1.152606476527654</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8508547604241681</v>
+        <v>1.050146104056169</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -3151,7 +3299,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09210036461158713</v>
+        <v>0.1440758110043622</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -3171,7 +3319,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.886347016376049e-15</v>
+        <v>4.321499743788634e-15</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -3193,7 +3341,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-6.330959906980324e-19</v>
+        <v>-9.400956093217906e-19</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -3215,7 +3363,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.16160842751699e-18</v>
+        <v>5.041479338892034e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3237,7 +3385,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.371404708411338</v>
+        <v>0.4601451985001849</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -3257,7 +3405,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.000000079981351</v>
+        <v>8.000000079995392</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
@@ -3277,7 +3425,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6581539076316473</v>
+        <v>0.7071245061333374</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
@@ -3293,21 +3441,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turn Lift &gt;= n*Weight</t>
+          <t>Turn Lift &gt;= K_LEVEL_TURN*n*Weight</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.191325511591645</v>
+        <v>1.470363574188967</v>
       </c>
       <c r="C10" t="n">
-        <v>1.323695023989486</v>
+        <v>1.470363584188335</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>1e-06</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3317,7 +3465,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.127166801250863e-14</v>
+        <v>5.914511041849252e-15</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -3339,7 +3487,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.310600117228323</v>
+        <v>2.393570521135981</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
@@ -3359,7 +3507,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.64182702697815</v>
+        <v>3.704393795995896</v>
       </c>
       <c r="C13" t="n">
         <v>0.5817764173314431</v>
@@ -3379,7 +3527,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6164535879086877</v>
+        <v>0.8605320307455027</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -3397,7 +3545,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01464915112656194</v>
+        <v>0.01665499913439414</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -3415,7 +3563,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84.38317710074055</v>
+        <v>128.3627783308596</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -3433,7 +3581,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9.238342910150571</v>
+        <v>7.999999920130635</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
@@ -3453,7 +3601,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.606575903852786</v>
+        <v>5.199892746342704</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
@@ -3473,7 +3621,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.606575903852786</v>
+        <v>5.199892746342704</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
@@ -3493,7 +3641,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63384.73648907142</v>
+        <v>67223.26919679661</v>
       </c>
       <c r="C20" t="n">
         <v>20000</v>
@@ -3513,7 +3661,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1000000100104355</v>
+        <v>0.04999998999434588</v>
       </c>
       <c r="C21" t="n">
         <v>0.05</v>
@@ -3533,7 +3681,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1000000100104355</v>
+        <v>0.04999998999434588</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
@@ -3553,7 +3701,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4999999900095295</v>
+        <v>0.4999999900064669</v>
       </c>
       <c r="C23" t="n">
         <v>0.5</v>
@@ -3573,7 +3721,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4999999900095295</v>
+        <v>0.4999999900064669</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -3593,7 +3741,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02999999000155204</v>
+        <v>0.02999999000058427</v>
       </c>
       <c r="C25" t="n">
         <v>0.03</v>
@@ -3613,7 +3761,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02999999000155204</v>
+        <v>0.02999999000058427</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -3633,7 +3781,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1805289653271583</v>
+        <v>-0.1497243077168116</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
@@ -3653,7 +3801,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02796323743347748</v>
+        <v>0.03505599997496323</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3673,7 +3821,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-11.38360583922604</v>
+        <v>-6.231079381770853</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
@@ -3693,7 +3841,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.097055405350419</v>
+        <v>4.065798068775985</v>
       </c>
       <c r="C30" t="n">
         <v>0.6</v>
@@ -3713,7 +3861,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>199.6538351644555</v>
+        <v>162.8965872304802</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
@@ -3733,7 +3881,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0205207949147366</v>
+        <v>0.02495938151867688</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
@@ -3753,11 +3901,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.221204200799033e-05</v>
+        <v>2.575737283287555e-05</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>0.144</v>
+        <v>0.0072</v>
       </c>
       <c r="E33" t="n">
         <v>1e-06</v>
@@ -3773,11 +3921,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8.971801952016054e-06</v>
+        <v>1.72210662448098e-05</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>0.144</v>
+        <v>0.0072</v>
       </c>
       <c r="E34" t="n">
         <v>1e-06</v>
@@ -3793,11 +3941,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.260688996155473e-06</v>
+        <v>3.890340309234259e-06</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>0.144</v>
+        <v>0.0072</v>
       </c>
       <c r="E35" t="n">
         <v>1e-06</v>
@@ -3813,7 +3961,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.403263081402325e-17</v>
+        <v>2.809137900571732e-18</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
@@ -3833,7 +3981,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1196032005122943</v>
+        <v>4.149054262853123</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
@@ -3853,7 +4001,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.754992318227725e-16</v>
+        <v>7.814204555748593e-17</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
@@ -3934,7 +4082,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.244685672697495</v>
+        <v>4.995818923191007</v>
       </c>
       <c r="C2" t="n">
         <v>-4</v>
@@ -3967,7 +4115,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.310889154646248e-16</v>
+        <v>2.318821944480995e-16</v>
       </c>
       <c r="C3" t="n">
         <v>-30</v>
@@ -4000,7 +4148,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1730216997764102</v>
+        <v>1.248382770292376</v>
       </c>
       <c r="C4" t="n">
         <v>-30</v>
@@ -4033,7 +4181,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.329118856354705e-16</v>
+        <v>3.758299667982743e-15</v>
       </c>
       <c r="C5" t="n">
         <v>-30</v>
@@ -4066,7 +4214,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.000000079981351</v>
+        <v>8.000000079995392</v>
       </c>
       <c r="C6" t="n">
         <v>-4</v>
@@ -4103,7 +4251,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.403263081402325e-17</v>
+        <v>-2.809137900571732e-18</v>
       </c>
       <c r="C7" t="n">
         <v>-30</v>
@@ -4136,7 +4284,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1196032005122943</v>
+        <v>4.149054262853123</v>
       </c>
       <c r="C8" t="n">
         <v>-30</v>
@@ -4169,7 +4317,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.754992318227725e-16</v>
+        <v>7.814204555748593e-17</v>
       </c>
       <c r="C9" t="n">
         <v>-30</v>
@@ -4202,7 +4350,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8840760552850895</v>
+        <v>0.9114499515298465</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
@@ -4235,7 +4383,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2057496155261446</v>
+        <v>0.2182096598924276</v>
       </c>
       <c r="C11" t="n">
         <v>0.1</v>
@@ -4268,10 +4416,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6766844357244848</v>
+        <v>0.6440573443182428</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D12" t="n">
         <v>0.8</v>
@@ -4301,13 +4449,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3662287781640486</v>
+        <v>0.4163749783598534</v>
       </c>
       <c r="C13" t="n">
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4315,7 +4463,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -4334,7 +4482,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1314886677990685</v>
+        <v>0.1575689288959599</v>
       </c>
       <c r="C14" t="n">
         <v>0.1</v>
@@ -4404,7 +4552,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7072709585758128</v>
+        <v>0.6766792150473272</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -4498,7 +4646,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4638,7 +4786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.244685672697495</v>
+        <v>4.995818923191007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4658,7 +4806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.310889154646248e-16</v>
+        <v>2.318821944480995e-16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4678,7 +4826,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1730216997764102</v>
+        <v>1.248382770292376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4698,7 +4846,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.329118856354705e-16</v>
+        <v>3.758299667982743e-15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4718,7 +4866,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4871003372485448</v>
+        <v>0.617381854787086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4738,7 +4886,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.371404708411338</v>
+        <v>0.4601451985001849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4758,7 +4906,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.000000079981351</v>
+        <v>8.000000079995392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4778,7 +4926,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.403263081402325e-17</v>
+        <v>-2.809137900571732e-18</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4798,7 +4946,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.1196032005122943</v>
+        <v>4.149054262853123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4818,7 +4966,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.754992318227725e-16</v>
+        <v>7.814204555748593e-17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4838,7 +4986,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6581539076316473</v>
+        <v>0.7071245061333374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4858,7 +5006,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.368562089585778</v>
+        <v>1.437845545371058</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4878,7 +5026,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.310600117228323</v>
+        <v>2.393570521135981</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bdcac3f-dirty</t>
+          <t>3f20d9c-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>225.7690647637066</v>
+        <v>126.7317013672611</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6440573443182428</v>
+        <v>0.6399411649061671</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5340573443182428</v>
+        <v>0.5299411649061672</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6440573443182428</v>
+        <v>0.6399411649061671</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.995818923191007</v>
+        <v>5.121658855088541</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.318821944480995e-16</v>
+        <v>-1.003039419388021e-16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.248382770292376</v>
+        <v>1.07084831044651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.758299667982743e-15</v>
+        <v>7.417831106112554e-15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.000000079995392</v>
+        <v>7.608325391688213</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.809137900571732e-18</v>
+        <v>5.377062767205443e-18</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.149054262853123</v>
+        <v>8.219893660890538</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.814204555748593e-17</v>
+        <v>1.454124360923813e-15</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1070485325235647</v>
+        <v>0.08976216479594404</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>107.0485325235647</v>
+        <v>89.76216479594405</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2360016164371651</v>
+        <v>0.197891699095256</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6766792150473272</v>
+        <v>0.739374410448861</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.05787929025254737</v>
+        <v>0.05287817641095208</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.617381854787086</v>
+        <v>0.5874999992029738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7.999999920130635</v>
+        <v>7.999999920010524</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.437845545371058</v>
+        <v>1.50883970376832</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.393570521135981</v>
+        <v>2.400000023994921</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7071245061333374</v>
+        <v>0.6677777267646771</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.199892746342704</v>
+        <v>6.333919194811074</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>67223.26919679661</v>
+        <v>56310.25292766299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.04999998999434588</v>
+        <v>0.04999999007341833</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4999999900064669</v>
+        <v>0.4999999900054579</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.02999999000058427</v>
+        <v>0.02999999000124711</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.065798068775985</v>
+        <v>4.778401783804584</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.704393795995896</v>
+        <v>4.270061168506224</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>162.8965872304802</v>
+        <v>206.9382837941339</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02495938151867688</v>
+        <v>0.02309095106132333</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_m</t>
+          <t>wing_tip_deflection_proxy_m</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.640336697806695</v>
+        <v>1.084473598671871</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1088,11 +1088,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_allow_m</t>
+          <t>wing_tip_deflection_proxy_allow_m</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.03645799806119386</v>
+        <v>0.03129282561812807</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_semispan_fraction</t>
+          <t>wing_tip_deflection_proxy_semispan_fraction</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.599400482831624</v>
+        <v>2.772452988185589</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1118,11 +1118,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_over_allow</t>
+          <t>wing_tip_deflection_proxy_over_allow</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>44.9925060353953</v>
+        <v>34.65566235231987</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4627552680926893</v>
+        <v>0.3971945986718404</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8168686578824084</v>
+        <v>0.6849594044583612</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.765228219333401</v>
+        <v>1.724493250282767</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1208,11 +1208,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_m</t>
+          <t>htail_tip_deflection_proxy_m</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8605320307455027</v>
+        <v>0.4929079927997522</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1223,11 +1223,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_allow_m</t>
+          <t>htail_tip_deflection_proxy_allow_m</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01665499913439414</v>
+        <v>0.01287631970508052</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1238,11 +1238,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_semispan_fraction</t>
+          <t>htail_tip_deflection_proxy_semispan_fraction</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4.133447375417382</v>
+        <v>3.062415373891464</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_over_allow</t>
+          <t>htail_tip_deflection_proxy_over_allow</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>51.66809219271727</v>
+        <v>38.28019217364329</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2081874891799267</v>
+        <v>0.1609539963135065</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2042171644706021</v>
+        <v>0.1712398511145903</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9809290907683061</v>
+        <v>1.063905557095016</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1343,11 +1343,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>objective_struct_deflection_penalty</t>
+          <t>objective_struct_deflection_proxy_penalty</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>96.7670293637146</v>
+        <v>56.63518041868387</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1358,11 +1358,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>objective_htail_deflection_penalty</t>
+          <t>objective_htail_deflection_proxy_penalty</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>128.3627783308596</v>
+        <v>69.49070752484344</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0001538199322950294</v>
+        <v>0.0001316523508435627</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.003577412893454938</v>
+        <v>0.002154550749008229</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>alpha_turn_deg:upper; ballast_mass_kg:lower</t>
+          <t>ballast_mass_kg:lower</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9255105361853786</v>
+        <v>0.7943891973436807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2182096598924276</v>
+        <v>0.1750074259201051</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2019553393278698</v>
+        <v>0.139024008605856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.241382057245469</v>
+        <v>4.539174227420141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6440573443182428</v>
+        <v>0.6399411649061671</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5340573443182428</v>
+        <v>0.5299411649061672</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6440573443182428</v>
+        <v>0.6399411649061671</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4163749783598534</v>
+        <v>0.321907992627013</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1189642795313867</v>
+        <v>0.08047699815675324</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04953374931547669</v>
+        <v>0.02590618892928826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1575689288959599</v>
+        <v>0.1178844373525108</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07878446444797996</v>
+        <v>0.05894221867625538</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01241398367671004</v>
+        <v>0.006948370284959018</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03998715718691821</v>
+        <v>0.02752675370395948</v>
       </c>
       <c r="C2" t="n">
-        <v>39.98715718691821</v>
+        <v>27.52675370395948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1091048299462138</v>
+        <v>0.08750371296005256</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04017830450503364</v>
+        <v>0.03448605911925642</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002768367587653758</v>
+        <v>0.001404005707300966</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001637203424472442</v>
+        <v>7.252347189887447e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00293184800715788</v>
+        <v>0.001476364018677616</v>
       </c>
     </row>
     <row r="3">
@@ -1823,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05787929025254737</v>
+        <v>0.05287817641095208</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008498136449883124</v>
+        <v>0.008443824742075418</v>
       </c>
       <c r="C4" t="n">
-        <v>8.498136449883123</v>
+        <v>8.443824742075417</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2120286721591214</v>
+        <v>0.2099705824530836</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1879,44 +1879,44 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007929520927671456</v>
+        <v>0.006649049244144003</v>
       </c>
       <c r="C5" t="n">
-        <v>7.929520927671456</v>
+        <v>6.649049244144003</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1469015240633527</v>
+        <v>0.127347442746731</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01899822970330011</v>
+        <v>0.0136560917668209</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002468923347374914</v>
+        <v>0.0001274016940968726</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001552806533449748</v>
+        <v>0.0001207184376797192</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003946558443010751</v>
+        <v>0.0002440523717955666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>htail_surfaces</t>
+          <t>flight_controller</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005944049917857202</v>
+        <v>0.005</v>
       </c>
       <c r="C6" t="n">
-        <v>5.944049917857202</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5043162744353962</v>
+        <v>0.06787817641095208</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1925,19 +1925,19 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>8.588018928113547e-05</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.014721812434071e-06</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>9.288599501869274e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flight_controller</t>
+          <t>receiver</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07287929025254737</v>
+        <v>0.07287817641095208</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1968,17 +1968,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>tail mount module 1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07787929025254738</v>
+        <v>0.4937265157356281</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tail mount module 1</t>
+          <t>avionics tray</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2009,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4805234185291188</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2030,17 +2030,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>avionics tray</t>
+          <t>htail_surfaces</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004</v>
+        <v>0.003108742671514591</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3.108742671514591</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.5098219153669787</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2049,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.684755655060274e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.68015811910358e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.852305155569905e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2071,7 +2071,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>2.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
         <v>2.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         <v>2.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2050762390942155</v>
+        <v>0.1760221441019704</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03616047405453028</v>
+        <v>0.03103745320733078</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -2226,13 +2226,13 @@
         <v>2.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2050762390942155</v>
+        <v>-0.1760221441019704</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03616047405453028</v>
+        <v>0.03103745320733078</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2247,63 +2247,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vtail_surfaces</t>
+          <t>linkages</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001489678041205204</v>
+        <v>0.001</v>
       </c>
       <c r="C17" t="n">
-        <v>1.489678041205204</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4842263668936928</v>
+        <v>0.2347917081443011</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07878446444797996</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.083257073043368e-06</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.85267476814058e-06</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>7.7165221215902e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>linkages</t>
+          <t>vtail_surfaces</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.001</v>
+        <v>0.0008338044341950822</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.8338044341950822</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2224170673348514</v>
+        <v>0.4990545256267299</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.05894221867625538</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>9.662223456636757e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.206996240422537e-06</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.420246014101536e-07</v>
       </c>
     </row>
     <row r="19">
@@ -2319,7 +2319,7 @@
         <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06787929025254737</v>
+        <v>0.06287817641095207</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.999970538854929e-09</v>
+        <v>-9.99994450676177e-09</v>
       </c>
       <c r="C20" t="n">
-        <v>-9.999970538854929e-06</v>
+        <v>-9.99994450676177e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06546289796772828</v>
+        <v>0.05250222777603154</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05751815038676538</v>
+        <v>0.0585168609929957</v>
       </c>
     </row>
     <row r="3">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.152405761619146</v>
+        <v>1.201985309532947</v>
       </c>
     </row>
     <row r="4">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.073697533394615e-05</v>
+        <v>1.328843061191225e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005419148698872222</v>
+        <v>0.007000042905977444</v>
       </c>
     </row>
     <row r="6">
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1337423730331383</v>
+        <v>-0.1004116753205303</v>
       </c>
     </row>
     <row r="7">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.472239453576446e-05</v>
+        <v>9.356877442301405e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4601451985001849</v>
+        <v>0.4681348832632325</v>
       </c>
     </row>
     <row r="9">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.205442473775639</v>
+        <v>4.277116033625902</v>
       </c>
     </row>
     <row r="10">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-8.942361667426424e-06</v>
+        <v>-3.594293956647017e-06</v>
       </c>
     </row>
     <row r="11">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.004376802865635465</v>
+        <v>-0.001640654347379034</v>
       </c>
     </row>
     <row r="12">
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1663165750367956</v>
+        <v>-0.1829936964112822</v>
       </c>
     </row>
     <row r="13">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-8.509891452623819e-05</v>
+        <v>-1.599603727253651e-05</v>
       </c>
     </row>
     <row r="14">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.424111831562682e-17</v>
+        <v>-4.515946520211539e-17</v>
       </c>
     </row>
     <row r="15">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.064475784849059e-22</v>
+        <v>7.319503129305733e-22</v>
       </c>
     </row>
     <row r="16">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2011796791725537</v>
+        <v>-0.1817904219295661</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3023435725556479</v>
+        <v>-0.3205136839584692</v>
       </c>
     </row>
     <row r="18">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.317272200571798e-18</v>
+        <v>1.325508940677575e-17</v>
       </c>
     </row>
     <row r="19">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1129973019841508</v>
+        <v>0.1187186584023332</v>
       </c>
     </row>
     <row r="20">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.400956093217906e-19</v>
+        <v>-2.574427574422738e-18</v>
       </c>
     </row>
     <row r="21">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.304523668986025e-19</v>
+        <v>3.916820998576346e-23</v>
       </c>
     </row>
     <row r="22">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1497243077168116</v>
+        <v>-0.1588441682609945</v>
       </c>
     </row>
     <row r="23">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5775611233947082</v>
+        <v>-0.6081823484123782</v>
       </c>
     </row>
     <row r="24">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.453099110204681e-19</v>
+        <v>2.159926378475337e-18</v>
       </c>
     </row>
     <row r="25">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04978841957870687</v>
+        <v>0.0469233778768687</v>
       </c>
     </row>
     <row r="26">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.321499743788634e-15</v>
+        <v>5.47347271698509e-14</v>
       </c>
     </row>
     <row r="27">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2102720816105791</v>
+        <v>-0.2138557592241535</v>
       </c>
     </row>
     <row r="28">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-5.239409296253893e-06</v>
+        <v>-2.744099530098935e-06</v>
       </c>
     </row>
     <row r="29">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0020621132823843</v>
+        <v>0.0007723394382532205</v>
       </c>
     </row>
     <row r="30">
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-6.231079381770853</v>
+        <v>-9.078162866799115</v>
       </c>
     </row>
     <row r="31">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001217899959902428</v>
+        <v>-0.0001277220925384723</v>
       </c>
     </row>
     <row r="32">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.041479338892034e-18</v>
+        <v>2.008185553909865e-17</v>
       </c>
     </row>
     <row r="33">
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.02213262557967e-20</v>
+        <v>-3.257187420208019e-22</v>
       </c>
     </row>
     <row r="34">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.03505599997496323</v>
+        <v>0.0407860197448539</v>
       </c>
     </row>
     <row r="35">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.03421589833381396</v>
+        <v>-0.02682529655707725</v>
       </c>
     </row>
     <row r="36">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.003814999326735e-18</v>
+        <v>-5.89437524336239e-18</v>
       </c>
     </row>
     <row r="37">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.03028335527322533</v>
+        <v>-0.04198303977746306</v>
       </c>
     </row>
     <row r="38">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1440758110043622</v>
+        <v>0.1100708544316998</v>
       </c>
     </row>
     <row r="39">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.05068158451746413</v>
+        <v>0.03689004728669686</v>
       </c>
     </row>
     <row r="40">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0933942264868981</v>
+        <v>0.07318080714500298</v>
       </c>
     </row>
     <row r="41">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.04315599143577227</v>
+        <v>-0.03102246861014932</v>
       </c>
     </row>
     <row r="42">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.04315599143577227</v>
+        <v>0.03102246861014932</v>
       </c>
     </row>
     <row r="43">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1440758110043622</v>
+        <v>-0.1100708544316998</v>
       </c>
     </row>
     <row r="44">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.152606476527654</v>
+        <v>0.8805668266490886</v>
       </c>
     </row>
     <row r="45">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-2.179413077165105e-18</v>
+        <v>-3.846850640809567e-18</v>
       </c>
     </row>
     <row r="46">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.179413077165105e-18</v>
+        <v>3.846850640809567e-18</v>
       </c>
     </row>
     <row r="47">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.15334136985157e-18</v>
+        <v>-1.15270597288779e-18</v>
       </c>
     </row>
     <row r="48">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-3.567222967248125e-17</v>
+        <v>-8.494544710917492e-17</v>
       </c>
     </row>
     <row r="49">
@@ -2873,11 +2873,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.000314036243216673,
+	L=0.000352616649762903,
 	Y=0.0,
-	D=0.0007289501622465802,
+	D=0.0007855778511405799,
 	l_b=0.0,
-	m_b=-2.9076860385309108e-05,
+	m_b=-3.539309727233035e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-2.179413077165105e-18</v>
+        <v>-3.846850640809567e-18</v>
       </c>
     </row>
     <row r="51">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.362080122426599e-15</v>
+        <v>1.801817294541999e-14</v>
       </c>
     </row>
     <row r="52">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.168760484624072e-17</v>
+        <v>3.00074080998565e-17</v>
       </c>
     </row>
     <row r="53">
@@ -2923,29 +2923,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.8780379151087044,
+	L=0.7045648921134826,
 	Y=0.0,
-	D=0.06442041737847674,
+	D=0.05434495647015744,
 	l_b=-0.0,
-	m_b=0.08900825386796501,
+	m_b=0.0636749406098028,
 	n_b=-0.0,
-	span_effective=0.9115567574672864, oswalds_efficiency=0.8095875167779147,
+	span_effective=0.7824123147017349, oswalds_efficiency=0.8077792477821385,
 ), AeroComponentResults(
-	L=0.2742545251757332,
+	L=0.17564931788584298,
 	Y=0.0,
-	D=0.02567952455426785,
+	D=0.016244862020259498,
 	l_b=-0.0,
-	m_b=-0.08906211845275344,
+	m_b=-0.06366404685753295,
 	n_b=-0.0,
-	span_effective=0.41637497835985343, oswalds_efficiency=0.8137951483430786,
+	span_effective=0.321907992627013, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-0.0,
-	Y=-3.567222967248125e-17,
-	D=0.0025653343919069247,
-	l_b=-2.1794130771651045e-18,
-	m_b=8.29414451760979e-05,
-	n_b=1.1687604846240722e-17,
-	span_effective=0.15756892889595991, oswalds_efficiency=0.8232692748986458,
+	L=2.710505431213761e-20,
+	Y=-8.494544710917492e-17,
+	D=0.0018054108034454568,
+	l_b=-3.846850640809567e-18,
+	m_b=2.4499345020493072e-05,
+	n_b=3.00074080998565e-17,
+	span_effective=0.11788443735251077, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1578120048746437</v>
+        <v>0.1360978123055108</v>
       </c>
     </row>
     <row r="55">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3081737632218351</v>
+        <v>0.3055745085297195</v>
       </c>
     </row>
     <row r="56">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1418633642512787</v>
+        <v>0.1393928527511432</v>
       </c>
     </row>
     <row r="57">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7071245061333374</v>
+        <v>0.6677777267646771</v>
       </c>
     </row>
     <row r="58">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.990596526940585e-17</v>
+        <v>5.789581195068685e-18</v>
       </c>
     </row>
     <row r="59">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.931869213079225e-18</v>
+        <v>3.734649104488625e-19</v>
       </c>
     </row>
     <row r="60">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5.914511041849252e-15</v>
+        <v>-2.261620206498122e-11</v>
       </c>
     </row>
     <row r="61">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.010300013270307e-17</v>
+        <v>-2.899578372353855e-18</v>
       </c>
     </row>
     <row r="62">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.2949844355523568</v>
+        <v>0.2093797551446262</v>
       </c>
     </row>
     <row r="63">
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.09935617363132208</v>
+        <v>0.05994237243079437</v>
       </c>
     </row>
     <row r="64">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1956282619210346</v>
+        <v>0.1494373827138319</v>
       </c>
     </row>
     <row r="65">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.08747860705441396</v>
+        <v>-0.07473112296409837</v>
       </c>
     </row>
     <row r="66">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.08747860705441396</v>
+        <v>0.07473112296409837</v>
       </c>
     </row>
     <row r="67">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.2949844355523568</v>
+        <v>-0.2093797551446262</v>
       </c>
     </row>
     <row r="68">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.470363574188967</v>
+        <v>1.003058149406276</v>
       </c>
     </row>
     <row r="69">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3.717816371450392e-18</v>
+        <v>4.456329697044344e-19</v>
       </c>
     </row>
     <row r="70">
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-3.717816371450392e-18</v>
+        <v>-4.456329697044344e-19</v>
       </c>
     </row>
     <row r="71">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9.757090527598963e-19</v>
+        <v>-1.638120095141176e-20</v>
       </c>
     </row>
     <row r="72">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6.218514787946424e-17</v>
+        <v>8.696436503653317e-18</v>
       </c>
     </row>
     <row r="73">
@@ -3149,11 +3149,11 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0006015902157105119,
+	L=0.0005721440772656707,
 	Y=0.0,
-	D=0.0006763829236288282,
+	D=0.000691597035098835,
 	l_b=0.0,
-	m_b=-4.457904735356192e-05,
+	m_b=-5.134608615884502e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3.717816371450392e-18</v>
+        <v>4.456329697044344e-19</v>
       </c>
     </row>
     <row r="75">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.683623993599699e-15</v>
+        <v>-5.945252909498721e-12</v>
       </c>
     </row>
     <row r="76">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.94428789691513e-17</v>
+        <v>-3.459890567522886e-18</v>
       </c>
     </row>
     <row r="77">
@@ -3199,29 +3199,29 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=1.1470933682913842,
+	L=0.819339492848226,
 	Y=0.0,
-	D=0.13452808441524672,
+	D=0.09613428532860471,
 	l_b=-0.0,
-	m_b=0.10912158150324003,
+	m_b=0.06966064861102046,
 	n_b=-0.0,
-	span_effective=0.9115567574672864, oswalds_efficiency=0.8095875167779147,
+	span_effective=0.7824123147017349, oswalds_efficiency=0.8077792477821385,
 ), AeroComponentResults(
-	L=0.3226686156818727,
+	L=0.18314651248078412,
 	Y=0.0,
-	D=0.05817686423775249,
+	D=0.051073690743135086,
 	l_b=-0.0,
-	m_b=-0.10911225766315945,
+	m_b=-0.06960640580774259,
 	n_b=-0.0,
-	span_effective=0.41637497835985343, oswalds_efficiency=0.8137951483430786,
+	span_effective=0.321907992627013, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-5.421010862427522e-20,
-	Y=6.218514787946424e-17,
-	D=0.0022469303444065903,
-	l_b=3.7178163714503916e-18,
-	m_b=3.525520727566548e-05,
-	n_b=-1.9442878969151304e-17,
-	span_effective=0.15756892889595991, oswalds_efficiency=0.8232692748986458,
+	L=-0.0,
+	Y=8.696436503653317e-18,
+	D=0.0015378096069932246,
+	l_b=4.456329697044344e-19,
+	m_b=-2.8967230642786827e-06,
+	n_b=-3.4598905675228862e-18,
+	span_effective=0.11788443735251077, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.152606476527654</v>
+        <v>0.8805668266490886</v>
       </c>
       <c r="C2" t="n">
-        <v>1.050146104056169</v>
+        <v>0.8805668366482111</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1440758110043622</v>
+        <v>0.1100708544316998</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.321499743788634e-15</v>
+        <v>5.47347271698509e-14</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-9.400956093217906e-19</v>
+        <v>-2.574427574422738e-18</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.041479338892034e-18</v>
+        <v>2.008185553909865e-17</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4601451985001849</v>
+        <v>0.4681348832632325</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.000000079995392</v>
+        <v>7.608325391688213</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7071245061333374</v>
+        <v>0.6677777267646771</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.470363574188967</v>
+        <v>1.003058149406276</v>
       </c>
       <c r="C10" t="n">
-        <v>1.470363584188335</v>
+        <v>0.9589431662417057</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.914511041849252e-15</v>
+        <v>-2.261620206498122e-11</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.393570521135981</v>
+        <v>2.400000023994921</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.704393795995896</v>
+        <v>4.270061168506224</v>
       </c>
       <c r="C13" t="n">
         <v>0.5817764173314431</v>
@@ -3523,11 +3523,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H-tail tip deflection (diag)</t>
+          <t>H-tail tip deflection proxy (diag)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8605320307455027</v>
+        <v>0.4929079927997522</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -3541,11 +3541,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H-tail tip deflection allow (diag)</t>
+          <t>H-tail tip deflection proxy allow (diag)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01665499913439414</v>
+        <v>0.01287631970508052</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -3559,11 +3559,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H-tail deflection penalty (diag)</t>
+          <t>H-tail deflection proxy penalty (diag)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>128.3627783308596</v>
+        <v>69.49070752484344</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.999999920130635</v>
+        <v>7.999999920010524</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.199892746342704</v>
+        <v>6.333919194811074</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.199892746342704</v>
+        <v>6.333919194811074</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>67223.26919679661</v>
+        <v>56310.25292766299</v>
       </c>
       <c r="C20" t="n">
         <v>20000</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.04999998999434588</v>
+        <v>0.04999999007341833</v>
       </c>
       <c r="C21" t="n">
         <v>0.05</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04999998999434588</v>
+        <v>0.04999999007341833</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4999999900064669</v>
+        <v>0.4999999900054579</v>
       </c>
       <c r="C23" t="n">
         <v>0.5</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4999999900064669</v>
+        <v>0.4999999900054579</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02999999000058427</v>
+        <v>0.02999999000124711</v>
       </c>
       <c r="C25" t="n">
         <v>0.03</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02999999000058427</v>
+        <v>0.02999999000124711</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1497243077168116</v>
+        <v>-0.1588441682609945</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03505599997496323</v>
+        <v>0.0407860197448539</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-6.231079381770853</v>
+        <v>-9.078162866799115</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.065798068775985</v>
+        <v>4.778401783804584</v>
       </c>
       <c r="C30" t="n">
         <v>0.6</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>162.8965872304802</v>
+        <v>206.9382837941339</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.02495938151867688</v>
+        <v>0.02309095106132333</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.575737283287555e-05</v>
+        <v>1.551276539285925e-05</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.72210662448098e-05</v>
+        <v>6.646427043993081e-06</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.890340309234259e-06</v>
+        <v>1.777116740371975e-06</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.809137900571732e-18</v>
+        <v>5.377062767205443e-18</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.149054262853123</v>
+        <v>8.219893660890538</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7.814204555748593e-17</v>
+        <v>1.454124360923813e-15</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.995818923191007</v>
+        <v>5.121658855088541</v>
       </c>
       <c r="C2" t="n">
         <v>-4</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.318821944480995e-16</v>
+        <v>-1.003039419388021e-16</v>
       </c>
       <c r="C3" t="n">
         <v>-30</v>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.248382770292376</v>
+        <v>1.07084831044651</v>
       </c>
       <c r="C4" t="n">
         <v>-30</v>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.758299667982743e-15</v>
+        <v>7.417831106112554e-15</v>
       </c>
       <c r="C5" t="n">
         <v>-30</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.000000079995392</v>
+        <v>7.608325391688213</v>
       </c>
       <c r="C6" t="n">
         <v>-4</v>
@@ -4232,17 +4232,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>upper</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[WARN] alpha_turn_deg hit upper bound (value=8, upper=8, tol=0.012).</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4251,7 +4247,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2.809137900571732e-18</v>
+        <v>5.377062767205443e-18</v>
       </c>
       <c r="C7" t="n">
         <v>-30</v>
@@ -4284,7 +4280,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.149054262853123</v>
+        <v>8.219893660890538</v>
       </c>
       <c r="C8" t="n">
         <v>-30</v>
@@ -4317,7 +4313,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.814204555748593e-17</v>
+        <v>1.454124360923813e-15</v>
       </c>
       <c r="C9" t="n">
         <v>-30</v>
@@ -4350,7 +4346,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9114499515298465</v>
+        <v>0.7823206404532017</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
@@ -4383,7 +4379,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2182096598924276</v>
+        <v>0.1750074259201051</v>
       </c>
       <c r="C11" t="n">
         <v>0.1</v>
@@ -4416,7 +4412,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6440573443182428</v>
+        <v>0.6399411649061671</v>
       </c>
       <c r="C12" t="n">
         <v>0.35</v>
@@ -4449,7 +4445,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4163749783598534</v>
+        <v>0.321907992627013</v>
       </c>
       <c r="C13" t="n">
         <v>0.2</v>
@@ -4482,7 +4478,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1575689288959599</v>
+        <v>0.1178844373525108</v>
       </c>
       <c r="C14" t="n">
         <v>0.1</v>
@@ -4552,7 +4548,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6766792150473272</v>
+        <v>0.739374410448861</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -4626,7 +4622,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4646,7 +4642,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,7 +4782,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.995818923191007</v>
+        <v>5.121658855088541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4806,7 +4802,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.318821944480995e-16</v>
+        <v>-1.003039419388021e-16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4826,7 +4822,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.248382770292376</v>
+        <v>1.07084831044651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4846,7 +4842,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.758299667982743e-15</v>
+        <v>7.417831106112554e-15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4866,7 +4862,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.617381854787086</v>
+        <v>0.5874999992029738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4886,7 +4882,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4601451985001849</v>
+        <v>0.4681348832632325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4906,7 +4902,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.000000079995392</v>
+        <v>7.608325391688213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4926,7 +4922,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-2.809137900571732e-18</v>
+        <v>5.377062767205443e-18</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4946,7 +4942,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.149054262853123</v>
+        <v>8.219893660890538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4966,7 +4962,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.814204555748593e-17</v>
+        <v>1.454124360923813e-15</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4986,7 +4982,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7071245061333374</v>
+        <v>0.6677777267646771</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5006,7 +5002,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.437845545371058</v>
+        <v>1.50883970376832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5026,7 +5022,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.393570521135981</v>
+        <v>2.400000023994921</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3f20d9c-dirty</t>
+          <t>60dcbd7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126.7317013672611</v>
+        <v>126.7317013666007</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6399411649061671</v>
+        <v>0.6399411649201149</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5299411649061672</v>
+        <v>0.5299411649201149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6399411649061671</v>
+        <v>0.6399411649201149</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.121658855088541</v>
+        <v>5.121658855102545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.003039419388021e-16</v>
+        <v>-3.74449204844204e-15</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.07084831044651</v>
+        <v>1.070848310464889</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.417831106112554e-15</v>
+        <v>-3.437330567014082e-15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.608325391688213</v>
+        <v>7.532504735482284</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.377062767205443e-18</v>
+        <v>-1.705533569452131</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.219893660890538</v>
+        <v>7.905314283524218</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.454124360923813e-15</v>
+        <v>-0.003744755182158211</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08976216479594404</v>
+        <v>0.08976216479617943</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>89.76216479594405</v>
+        <v>89.76216479617943</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.197891699095256</v>
+        <v>0.197891699095775</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.739374410448861</v>
+        <v>0.7393744104303894</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.05287817641095208</v>
+        <v>0.05287817640743128</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5874999992029738</v>
+        <v>0.587499999203023</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7.999999920010524</v>
+        <v>7.999999920008439</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.400000023994921</v>
+        <v>2.400000023996182</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6677777267646771</v>
+        <v>0.6459553469363073</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.333919194811074</v>
+        <v>6.333919194793097</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>56310.25292766299</v>
+        <v>56310.25292778893</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.04999999007341833</v>
+        <v>0.04999999006819524</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4999999900054579</v>
+        <v>0.4999999900044497</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.02999999000124711</v>
+        <v>0.02999999000100435</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.778401783804584</v>
+        <v>4.778401783574358</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4.270061168506224</v>
+        <v>4.270061168300489</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>206.9382837941339</v>
+        <v>206.9382837836613</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02309095106132333</v>
+        <v>0.02309095106137936</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.084473598671871</v>
+        <v>1.084473598682779</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.03129282561812807</v>
+        <v>0.03129282561822896</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.772452988185589</v>
+        <v>2.772452988204536</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>34.65566235231987</v>
+        <v>34.6556623525567</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3971945986718404</v>
+        <v>0.397194598673121</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6849594044583612</v>
+        <v>0.6849594044601575</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.724493250282767</v>
+        <v>1.724493250281729</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4929079927997522</v>
+        <v>0.492907992788391</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01287631970508052</v>
+        <v>0.01287631970491524</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.062415373891464</v>
+        <v>3.062415373860185</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>38.28019217364329</v>
+        <v>38.28019217325232</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1609539963135065</v>
+        <v>0.1609539963114405</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1712398511145903</v>
+        <v>0.1712398511150394</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.063905557095016</v>
+        <v>1.063905557111462</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>56.63518041868387</v>
+        <v>56.63518041948094</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>69.49070752484344</v>
+        <v>69.49070752338585</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0001316523508435627</v>
+        <v>0.0001316523508442016</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.002154550749008229</v>
+        <v>0.002154550749024812</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7943891973436807</v>
+        <v>0.7943891973462419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1750074259201051</v>
+        <v>0.1750074259204965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.139024008605856</v>
+        <v>0.1390240086066151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.539174227420141</v>
+        <v>4.539174227424624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6399411649061671</v>
+        <v>0.6399411649201149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5299411649061672</v>
+        <v>0.5299411649201149</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6399411649061671</v>
+        <v>0.6399411649201149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.321907992627013</v>
+        <v>0.3219079926228811</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08047699815675324</v>
+        <v>0.08047699815572026</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02590618892928826</v>
+        <v>0.02590618892862321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1178844373525108</v>
+        <v>0.1178844373506977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05894221867625538</v>
+        <v>0.05894221867534886</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.006948370284959018</v>
+        <v>0.006948370284745287</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02752675370395948</v>
+        <v>0.0275267537041098</v>
       </c>
       <c r="C2" t="n">
-        <v>27.52675370395948</v>
+        <v>27.5267537041098</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08750371296005256</v>
+        <v>0.08750371296024825</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03448605911925642</v>
+        <v>0.03448605911936761</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001404005707300966</v>
+        <v>0.001404005707317685</v>
       </c>
       <c r="H2" t="n">
-        <v>7.252347189887447e-05</v>
+        <v>7.25234718995945e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001476364018677616</v>
+        <v>0.001476364018695055</v>
       </c>
     </row>
     <row r="3">
@@ -1823,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05287817641095208</v>
+        <v>0.05287817640743128</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008443824742075418</v>
+        <v>0.008443824742259454</v>
       </c>
       <c r="C4" t="n">
-        <v>8.443824742075417</v>
+        <v>8.443824742259455</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2099705824530836</v>
+        <v>0.2099705824600575</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1879,28 +1879,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006649049244144003</v>
+        <v>0.006649049244161439</v>
       </c>
       <c r="C5" t="n">
-        <v>6.649049244144003</v>
+        <v>6.649049244161439</v>
       </c>
       <c r="D5" t="n">
-        <v>0.127347442746731</v>
+        <v>0.1273474427478046</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0136560917668209</v>
+        <v>0.0136560917668623</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001274016940968726</v>
+        <v>0.0001274016940981738</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001207184376797192</v>
+        <v>0.0001207184376870165</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002440523717955666</v>
+        <v>0.0002440523718041577</v>
       </c>
     </row>
     <row r="6">
@@ -1916,7 +1916,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06787817641095208</v>
+        <v>0.06787817640743128</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07287817641095208</v>
+        <v>0.07287817640743129</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4937265157356281</v>
+        <v>0.4937265157500407</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003108742671514591</v>
+        <v>0.003108742671434785</v>
       </c>
       <c r="C10" t="n">
-        <v>3.108742671514591</v>
+        <v>3.108742671434785</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5098219153669787</v>
+        <v>0.5098219153811848</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2049,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.684755655060274e-05</v>
+        <v>2.684755654922437e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.68015811910358e-06</v>
+        <v>1.680158119017376e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>2.852305155569905e-05</v>
+        <v>2.852305155423459e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2071,7 +2071,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>2.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
         <v>2.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         <v>2.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1760221441019704</v>
+        <v>0.1760221441025379</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03103745320733078</v>
+        <v>0.03103745320743085</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -2226,13 +2226,13 @@
         <v>2.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1760221441019704</v>
+        <v>-0.1760221441025379</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03103745320733078</v>
+        <v>0.03103745320743085</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2257,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2347917081443011</v>
+        <v>0.2347917081516623</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2282,28 +2282,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0008338044341950822</v>
+        <v>0.0008338044341694344</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8338044341950822</v>
+        <v>0.8338044341694344</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4990545256267299</v>
+        <v>0.4990545256409991</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05894221867625538</v>
+        <v>0.05894221867534886</v>
       </c>
       <c r="G18" t="n">
-        <v>9.662223456636757e-07</v>
+        <v>9.662223456042532e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>1.206996240422537e-06</v>
+        <v>1.206996240348283e-06</v>
       </c>
       <c r="I18" t="n">
-        <v>2.420246014101536e-07</v>
+        <v>2.420246013952836e-07</v>
       </c>
     </row>
     <row r="19">
@@ -2319,7 +2319,7 @@
         <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06287817641095207</v>
+        <v>0.06287817640743128</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.99994450676177e-09</v>
+        <v>-9.999955459419767e-09</v>
       </c>
       <c r="C20" t="n">
-        <v>-9.99994450676177e-06</v>
+        <v>-9.999955459419767e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>0.05250222777603154</v>
+        <v>0.05250222777614895</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0585168609929957</v>
+        <v>0.05851686099283452</v>
       </c>
     </row>
     <row r="3">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.201985309532947</v>
+        <v>1.201985309517442</v>
       </c>
     </row>
     <row r="4">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.328843061191225e-05</v>
+        <v>1.328846082718172e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007000042905977444</v>
+        <v>0.007000042906282755</v>
       </c>
     </row>
     <row r="6">
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1004116753205303</v>
+        <v>-0.1004116753517414</v>
       </c>
     </row>
     <row r="7">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.356877442301405e-05</v>
+        <v>9.356877454097522e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4681348832632325</v>
+        <v>0.4681348832618211</v>
       </c>
     </row>
     <row r="9">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.277116033625902</v>
+        <v>4.277116033415986</v>
       </c>
     </row>
     <row r="10">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.594293956647017e-06</v>
+        <v>-3.594246248326795e-06</v>
       </c>
     </row>
     <row r="11">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.001640654347379034</v>
+        <v>-0.0016406543467129</v>
       </c>
     </row>
     <row r="12">
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1829936964112822</v>
+        <v>-0.1829936965180301</v>
       </c>
     </row>
     <row r="13">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.599603727253651e-05</v>
+        <v>-1.599603749458112e-05</v>
       </c>
     </row>
     <row r="14">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-4.515946520211539e-17</v>
+        <v>4.200373892855655e-17</v>
       </c>
     </row>
     <row r="15">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.319503129305733e-22</v>
+        <v>-2.324953378177332e-12</v>
       </c>
     </row>
     <row r="16">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1817904219295661</v>
+        <v>-0.1817904219270933</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3205136839584692</v>
+        <v>-0.3205136839573485</v>
       </c>
     </row>
     <row r="18">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.325508940677575e-17</v>
+        <v>2.857109651435494e-14</v>
       </c>
     </row>
     <row r="19">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1187186584023332</v>
+        <v>0.118718658402095</v>
       </c>
     </row>
     <row r="20">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-2.574427574422738e-18</v>
+        <v>-2.899279049879472e-17</v>
       </c>
     </row>
     <row r="21">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.916820998576346e-23</v>
+        <v>-3.591881349651887e-12</v>
       </c>
     </row>
     <row r="22">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1588441682609945</v>
+        <v>-0.1588441682550804</v>
       </c>
     </row>
     <row r="23">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6081823484123782</v>
+        <v>-0.6081823484098711</v>
       </c>
     </row>
     <row r="24">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.159926378475337e-18</v>
+        <v>4.6434878995595e-14</v>
       </c>
     </row>
     <row r="25">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0469233778768687</v>
+        <v>0.04692337787657939</v>
       </c>
     </row>
     <row r="26">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.47347271698509e-14</v>
+        <v>3.993145396211353e-15</v>
       </c>
     </row>
     <row r="27">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2138557592241535</v>
+        <v>-0.2138557591913179</v>
       </c>
     </row>
     <row r="28">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.744099530098935e-06</v>
+        <v>-2.744034293323864e-06</v>
       </c>
     </row>
     <row r="29">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0007723394382532205</v>
+        <v>0.0007723394385426648</v>
       </c>
     </row>
     <row r="30">
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-9.078162866799115</v>
+        <v>-9.078162866910734</v>
       </c>
     </row>
     <row r="31">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001277220925384723</v>
+        <v>-0.0001277220929158548</v>
       </c>
     </row>
     <row r="32">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.008185553909865e-17</v>
+        <v>-3.848285448722548e-17</v>
       </c>
     </row>
     <row r="33">
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-3.257187420208019e-22</v>
+        <v>-8.397685793681886e-13</v>
       </c>
     </row>
     <row r="34">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0407860197448539</v>
+        <v>0.04078601974986889</v>
       </c>
     </row>
     <row r="35">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.02682529655707725</v>
+        <v>-0.02682529655510784</v>
       </c>
     </row>
     <row r="36">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-5.89437524336239e-18</v>
+        <v>8.424853383526709e-15</v>
       </c>
     </row>
     <row r="37">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.04198303977746306</v>
+        <v>-0.04198303977863586</v>
       </c>
     </row>
     <row r="38">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1100708544316998</v>
+        <v>0.1100708544319977</v>
       </c>
     </row>
     <row r="39">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.03689004728669686</v>
+        <v>0.03689004728664066</v>
       </c>
     </row>
     <row r="40">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.07318080714500298</v>
+        <v>0.07318080714535705</v>
       </c>
     </row>
     <row r="41">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.03102246861014932</v>
+        <v>-0.031022468610037</v>
       </c>
     </row>
     <row r="42">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.03102246861014932</v>
+        <v>0.031022468610037</v>
       </c>
     </row>
     <row r="43">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1100708544316998</v>
+        <v>-0.1100708544319977</v>
       </c>
     </row>
     <row r="44">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8805668266490886</v>
+        <v>0.8805668266512421</v>
       </c>
     </row>
     <row r="45">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-3.846850640809567e-18</v>
+        <v>-4.332261502253491e-17</v>
       </c>
     </row>
     <row r="46">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.846850640809567e-18</v>
+        <v>4.332261502253491e-17</v>
       </c>
     </row>
     <row r="47">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.15270597288779e-18</v>
+        <v>-4.828300106558769e-17</v>
       </c>
     </row>
     <row r="48">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-8.494544710917492e-17</v>
+        <v>7.900949153391744e-17</v>
       </c>
     </row>
     <row r="49">
@@ -2873,11 +2873,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.000352616649762903,
+	L=0.00035261664977201217,
 	Y=0.0,
-	D=0.0007855778511405799,
+	D=0.0007855778511536321,
 	l_b=0.0,
-	m_b=-3.539309727233035e-05,
+	m_b=-3.5393097275636525e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-3.846850640809567e-18</v>
+        <v>-4.332261502253491e-17</v>
       </c>
     </row>
     <row r="51">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.801817294541999e-14</v>
+        <v>1.31450704271216e-15</v>
       </c>
     </row>
     <row r="52">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3.00074080998565e-17</v>
+        <v>-5.750318824907891e-17</v>
       </c>
     </row>
     <row r="53">
@@ -2923,29 +2923,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.7045648921134826,
+	L=0.7045648921189102,
+	Y=-3.642919299551295e-17,
+	D=0.05434495647078885,
+	l_b=-4.85722573273506e-17,
+	m_b=0.06367494061098433,
+	n_b=-1.6479873021779667e-17,
+	span_effective=0.7824123147042575, oswalds_efficiency=0.8077792477821114,
+), AeroComponentResults(
+	L=0.17564931788256002,
 	Y=0.0,
-	D=0.05434495647015744,
+	D=0.01624486202000868,
 	l_b=-0.0,
-	m_b=0.0636749406098028,
+	m_b=-0.0636640468587233,
 	n_b=-0.0,
-	span_effective=0.7824123147017349, oswalds_efficiency=0.8077792477821385,
+	span_effective=0.32190799262288106, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=0.17564931788584298,
-	Y=0.0,
-	D=0.016244862020259498,
-	l_b=-0.0,
-	m_b=-0.06366404685753295,
-	n_b=-0.0,
-	span_effective=0.321907992627013, oswalds_efficiency=0.8106853777008906,
-), AeroComponentResults(
-	L=2.710505431213761e-20,
-	Y=-8.494544710917492e-17,
-	D=0.0018054108034454568,
-	l_b=-3.846850640809567e-18,
-	m_b=2.4499345020493072e-05,
-	n_b=3.00074080998565e-17,
-	span_effective=0.11788443735251077, oswalds_efficiency=0.8232692748986458,
+	L=-2.710505431213761e-20,
+	Y=1.154386845294304e-16,
+	D=0.0018054108034058734,
+	l_b=5.24964230481569e-18,
+	m_b=2.4499345015921855e-05,
+	n_b=-4.1023315227299244e-17,
+	span_effective=0.11788443735069772, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1360978123055108</v>
+        <v>0.1360978123056898</v>
       </c>
     </row>
     <row r="55">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3055745085297195</v>
+        <v>0.3055745085557066</v>
       </c>
     </row>
     <row r="56">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1393928527511432</v>
+        <v>0.135062116442991</v>
       </c>
     </row>
     <row r="57">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6677777267646771</v>
+        <v>0.6459553469363073</v>
       </c>
     </row>
     <row r="58">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5.789581195068685e-18</v>
+        <v>0.006835607173014744</v>
       </c>
     </row>
     <row r="59">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.734649104488625e-19</v>
+        <v>0.01159311023408533</v>
       </c>
     </row>
     <row r="60">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.261620206498122e-11</v>
+        <v>-6.245385560558712e-10</v>
       </c>
     </row>
     <row r="61">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.899578372353855e-18</v>
+        <v>-0.001099912204178762</v>
       </c>
     </row>
     <row r="62">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.2093797551446262</v>
+        <v>0.2028746260096247</v>
       </c>
     </row>
     <row r="63">
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.05994237243079437</v>
+        <v>0.05609494085320976</v>
       </c>
     </row>
     <row r="64">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1494373827138319</v>
+        <v>0.146779685156415</v>
       </c>
     </row>
     <row r="65">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.07473112296409837</v>
+        <v>-0.07393138946914127</v>
       </c>
     </row>
     <row r="66">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.07473112296409837</v>
+        <v>0.07393138946914127</v>
       </c>
     </row>
     <row r="67">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.2093797551446262</v>
+        <v>-0.2028746260096247</v>
       </c>
     </row>
     <row r="68">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.003058149406276</v>
+        <v>0.970279104754999</v>
       </c>
     </row>
     <row r="69">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4.456329697044344e-19</v>
+        <v>0.01383335354200187</v>
       </c>
     </row>
     <row r="70">
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-4.456329697044344e-19</v>
+        <v>-0.01383335354200187</v>
       </c>
     </row>
     <row r="71">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.638120095141176e-20</v>
+        <v>0.01354193235514438</v>
       </c>
     </row>
     <row r="72">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>8.696436503653317e-18</v>
+        <v>0.01026765524853465</v>
       </c>
     </row>
     <row r="73">
@@ -3149,11 +3149,11 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0005721440772656707,
+	L=0.0005621476020800174,
 	Y=0.0,
-	D=0.000691597035098835,
+	D=0.0006896002202767209,
 	l_b=0.0,
-	m_b=-5.134608615884502e-05,
+	m_b=-5.055267504813792e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4.456329697044344e-19</v>
+        <v>0.01383335354200187</v>
       </c>
     </row>
     <row r="75">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-5.945252909498721e-12</v>
+        <v>-1.641760918497949e-10</v>
       </c>
     </row>
     <row r="76">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-3.459890567522886e-18</v>
+        <v>-0.00131245835486251</v>
       </c>
     </row>
     <row r="77">
@@ -3199,29 +3199,29 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.819339492848226,
+	L=0.7921758189286069,
+	Y=0.010251774318121298,
+	D=0.09660885495119134,
+	l_b=0.013832638081993733,
+	m_b=0.06740793789633955,
+	n_b=-0.0013068765136166741,
+	span_effective=0.7824123147042575, oswalds_efficiency=0.8077792477821114,
+), AeroComponentResults(
+	L=0.177541138224312,
 	Y=0.0,
-	D=0.09613428532860471,
+	D=0.0479434200255805,
 	l_b=-0.0,
-	m_b=0.06966064861102046,
+	m_b=-0.06735521341618966,
 	n_b=-0.0,
-	span_effective=0.7824123147017349, oswalds_efficiency=0.8077792477821385,
+	span_effective=0.32190799262288106, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=0.18314651248078412,
-	Y=0.0,
-	D=0.051073690743135086,
-	l_b=-0.0,
-	m_b=-0.06960640580774259,
-	n_b=-0.0,
-	span_effective=0.321907992627013, oswalds_efficiency=0.8106853777008906,
-), AeroComponentResults(
-	L=-0.0,
-	Y=8.696436503653317e-18,
-	D=0.0015378096069932246,
-	l_b=4.456329697044344e-19,
-	m_b=-2.8967230642786827e-06,
-	n_b=-3.4598905675228862e-18,
-	span_effective=0.11788443735251077, oswalds_efficiency=0.8232692748986458,
+	L=2.710505431213761e-20,
+	Y=1.588093041334959e-05,
+	D=0.0015378099593664216,
+	l_b=7.154600081401185e-07,
+	m_b=-2.1719692778361147e-06,
+	n_b=-5.581841245835802e-06,
+	span_effective=0.11788443735069772, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8805668266490886</v>
+        <v>0.8805668266512421</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8805668366482111</v>
+        <v>0.8805668366505203</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1100708544316998</v>
+        <v>0.1100708544319977</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.47347271698509e-14</v>
+        <v>3.993145396211353e-15</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.574427574422738e-18</v>
+        <v>-2.899279049879472e-17</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.008185553909865e-17</v>
+        <v>-3.848285448722548e-17</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4681348832632325</v>
+        <v>0.4681348832618211</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.608325391688213</v>
+        <v>7.532504735482284</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6677777267646771</v>
+        <v>0.6459553469363073</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.003058149406276</v>
+        <v>0.970279104754999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9589431662417057</v>
+        <v>0.9589431662442204</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-2.261620206498122e-11</v>
+        <v>-6.245385560558712e-10</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.400000023994921</v>
+        <v>2.400000023996182</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.270061168506224</v>
+        <v>4.270061168300489</v>
       </c>
       <c r="C13" t="n">
         <v>0.5817764173314431</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4929079927997522</v>
+        <v>0.492907992788391</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01287631970508052</v>
+        <v>0.01287631970491524</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>69.49070752484344</v>
+        <v>69.49070752338585</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.999999920010524</v>
+        <v>7.999999920008439</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.333919194811074</v>
+        <v>6.333919194793097</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.333919194811074</v>
+        <v>6.333919194793097</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>56310.25292766299</v>
+        <v>56310.25292778893</v>
       </c>
       <c r="C20" t="n">
         <v>20000</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.04999999007341833</v>
+        <v>0.04999999006819524</v>
       </c>
       <c r="C21" t="n">
         <v>0.05</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04999999007341833</v>
+        <v>0.04999999006819524</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4999999900054579</v>
+        <v>0.4999999900044497</v>
       </c>
       <c r="C23" t="n">
         <v>0.5</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4999999900054579</v>
+        <v>0.4999999900044497</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02999999000124711</v>
+        <v>0.02999999000100435</v>
       </c>
       <c r="C25" t="n">
         <v>0.03</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02999999000124711</v>
+        <v>0.02999999000100435</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1588441682609945</v>
+        <v>-0.1588441682550804</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0407860197448539</v>
+        <v>0.04078601974986889</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-9.078162866799115</v>
+        <v>-9.078162866910734</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.778401783804584</v>
+        <v>4.778401783574358</v>
       </c>
       <c r="C30" t="n">
         <v>0.6</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>206.9382837941339</v>
+        <v>206.9382837836613</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.02309095106132333</v>
+        <v>0.02309095106137936</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.551276539285925e-05</v>
+        <v>1.551276539297865e-05</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6.646427043993081e-06</v>
+        <v>6.646427043737145e-06</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.777116740371975e-06</v>
+        <v>1.777116740289979e-06</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5.377062767205443e-18</v>
+        <v>1.705533569452131</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.219893660890538</v>
+        <v>7.905314283524218</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.454124360923813e-15</v>
+        <v>0.003744755182158211</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.121658855088541</v>
+        <v>5.121658855102545</v>
       </c>
       <c r="C2" t="n">
         <v>-4</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.003039419388021e-16</v>
+        <v>-3.74449204844204e-15</v>
       </c>
       <c r="C3" t="n">
         <v>-30</v>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.07084831044651</v>
+        <v>1.070848310464889</v>
       </c>
       <c r="C4" t="n">
         <v>-30</v>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.417831106112554e-15</v>
+        <v>-3.437330567014082e-15</v>
       </c>
       <c r="C5" t="n">
         <v>-30</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.608325391688213</v>
+        <v>7.532504735482284</v>
       </c>
       <c r="C6" t="n">
         <v>-4</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.377062767205443e-18</v>
+        <v>-1.705533569452131</v>
       </c>
       <c r="C7" t="n">
         <v>-30</v>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.219893660890538</v>
+        <v>7.905314283524218</v>
       </c>
       <c r="C8" t="n">
         <v>-30</v>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.454124360923813e-15</v>
+        <v>-0.003744755182158211</v>
       </c>
       <c r="C9" t="n">
         <v>-30</v>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7823206404532017</v>
+        <v>0.782320640455724</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1750074259201051</v>
+        <v>0.1750074259204965</v>
       </c>
       <c r="C11" t="n">
         <v>0.1</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6399411649061671</v>
+        <v>0.6399411649201149</v>
       </c>
       <c r="C12" t="n">
         <v>0.35</v>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.321907992627013</v>
+        <v>0.3219079926228811</v>
       </c>
       <c r="C13" t="n">
         <v>0.2</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1178844373525108</v>
+        <v>0.1178844373506977</v>
       </c>
       <c r="C14" t="n">
         <v>0.1</v>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.739374410448861</v>
+        <v>0.7393744104303894</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.121658855088541</v>
+        <v>5.121658855102545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1.003039419388021e-16</v>
+        <v>-3.74449204844204e-15</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.07084831044651</v>
+        <v>1.070848310464889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.417831106112554e-15</v>
+        <v>-3.437330567014082e-15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5874999992029738</v>
+        <v>0.587499999203023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4681348832632325</v>
+        <v>0.4681348832618211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.608325391688213</v>
+        <v>7.532504735482284</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.377062767205443e-18</v>
+        <v>-1.705533569452131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.219893660890538</v>
+        <v>7.905314283524218</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.454124360923813e-15</v>
+        <v>-0.003744755182158211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6677777267646771</v>
+        <v>0.6459553469363073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.400000023994921</v>
+        <v>2.400000023996182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60dcbd7</t>
+          <t>7228918-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hl3422_ic_ac_uk/Documents/Year 4/Final Year Project/01 - Github/Nausicaa/02_Glider_Design/C_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_8671AC497A61C26F136E40BAAA6F9BEED5AACA69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A8B10FF-1985-4B63-9186-5906156919B8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_A8110C474001FACCD2568C65D25FA35CF9D1E27E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CEC7CAA-04BD-47D7-BC83-B92A84BE4B34}"/>
   <bookViews>
-    <workbookView xWindow="24171" yWindow="1834" windowWidth="19200" windowHeight="9969" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21840" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <t>code_version</t>
   </si>
   <si>
-    <t>7228918-dirty</t>
+    <t>bc62cee-dirty</t>
   </si>
   <si>
     <t>-</t>
@@ -572,11 +572,11 @@
   </si>
   <si>
     <t>[AeroComponentResults(
-	L=0.00035261664977201217,
+	L=0.00035261664582293803,
 	Y=0.0,
-	D=0.0007855778511536321,
+	D=0.0007855778455927358,
 	l_b=0.0,
-	m_b=-3.5393097275636525e-05,
+	m_b=-3.5393095810291366e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -595,29 +595,29 @@
   </si>
   <si>
     <t>[AeroComponentResults(
-	L=0.7045648921189102,
-	Y=-3.642919299551295e-17,
-	D=0.05434495647078885,
-	l_b=-4.85722573273506e-17,
-	m_b=0.06367494061098433,
-	n_b=-1.6479873021779667e-17,
-	span_effective=0.7824123147042575, oswalds_efficiency=0.8077792477821114,
+	L=0.7045648894914193,
+	Y=0.0,
+	D=0.05434495615617649,
+	l_b=-0.0,
+	m_b=0.06367494015619117,
+	n_b=-0.0,
+	span_effective=0.7824123133415943, oswalds_efficiency=0.8077792478113651,
 ), AeroComponentResults(
-	L=0.17564931788256002,
+	L=0.17564931938955264,
 	Y=0.0,
-	D=0.01624486202000868,
+	D=0.016244862160157553,
 	l_b=-0.0,
-	m_b=-0.0636640468587233,
+	m_b=-0.06366404637955274,
 	n_b=-0.0,
-	span_effective=0.32190799262288106, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.3219079942067673, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-2.710505431213761e-20,
-	Y=1.154386845294304e-16,
-	D=0.0018054108034058734,
-	l_b=5.24964230481569e-18,
-	m_b=2.4499345015921855e-05,
-	n_b=-4.1023315227299244e-17,
-	span_effective=0.11788443735069772, oswalds_efficiency=0.8232692748986458,
+	L=5.421010862427522e-20,
+	Y=1.9602795658765795e-17,
+	D=0.0018054108147366474,
+	l_b=8.439929332489222e-19,
+	m_b=2.449934669606339e-05,
+	n_b=-6.4367523447094324e-18,
+	span_effective=0.11788443786978452, oswalds_efficiency=0.8232692748986458,
 )]</t>
   </si>
   <si>
@@ -679,11 +679,11 @@
   </si>
   <si>
     <t>[AeroComponentResults(
-	L=0.0005621476020800174,
+	L=0.0005800206369382567,
 	Y=0.0,
-	D=0.0006896002202767209,
+	D=0.0006931850057774216,
 	l_b=0.0,
-	m_b=-5.055267504813792e-05,
+	m_b=-5.1971737181715635e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -702,29 +702,29 @@
   </si>
   <si>
     <t>[AeroComponentResults(
-	L=0.7921758189286069,
-	Y=0.010251774318121298,
-	D=0.09660885495119134,
-	l_b=0.013832638081993733,
-	m_b=0.06740793789633955,
-	n_b=-0.0013068765136166741,
-	span_effective=0.7824123147042575, oswalds_efficiency=0.8077792477821114,
+	L=0.8248647378679281,
+	Y=0.0,
+	D=0.09730794151890333,
+	l_b=-0.0,
+	m_b=0.06992279164942262,
+	n_b=-0.0,
+	span_effective=0.7824123133415943, oswalds_efficiency=0.8077792478113651,
 ), AeroComponentResults(
-	L=0.177541138224312,
+	L=0.18380315430952476,
 	Y=0.0,
-	D=0.0479434200255805,
+	D=0.05129563647122002,
 	l_b=-0.0,
-	m_b=-0.06735521341618966,
+	m_b=-0.06986735620068013,
 	n_b=-0.0,
-	span_effective=0.32190799262288106, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.3219079942067673, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=2.710505431213761e-20,
-	Y=1.588093041334959e-05,
-	D=0.0015378099593664216,
-	l_b=7.154600081401185e-07,
-	m_b=-2.1719692778361147e-06,
-	n_b=-5.581841245835802e-06,
-	span_effective=0.11788443735069772, oswalds_efficiency=0.8232692748986458,
+	L=-5.421010862427522e-20,
+	Y=4.522146931825082e-17,
+	D=0.0015378096166264418,
+	l_b=2.126215166677926e-18,
+	m_b=-3.4636900840585787e-06,
+	n_b=-1.655637703233244e-17,
+	span_effective=0.11788443786978452, oswalds_efficiency=0.8232692748986458,
 )]</t>
   </si>
   <si>
@@ -951,7 +951,6 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1307,7 +1306,8 @@
   <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>126.7317013666007</v>
+        <v>126.7317014079503</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -1425,7 +1425,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0.63994116492011488</v>
+        <v>0.63994115898851145</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -1436,7 +1436,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0.52994116492011489</v>
+        <v>0.52994115898851146</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1447,7 +1447,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0.63994116492011488</v>
+        <v>0.63994115898851145</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -1458,7 +1458,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>5.1216588551025453</v>
+        <v>5.1216588485150671</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -1469,7 +1469,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-3.7444920484420398E-15</v>
+        <v>-5.5536956088661469E-17</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
@@ -1480,7 +1480,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>1.0708483104648889</v>
+        <v>1.0708483140055509</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -1491,7 +1491,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-3.4373305670140819E-15</v>
+        <v>-1.453058710546046E-15</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -1502,7 +1502,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>7.5325047354822843</v>
+        <v>7.6676395581233496</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
@@ -1513,7 +1513,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1.705533569452131</v>
+        <v>-7.361633920078792E-19</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -1524,7 +1524,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>7.9053142835242181</v>
+        <v>8.2024026613530392</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -1535,7 +1535,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-3.744755182158211E-3</v>
+        <v>1.5398283992121381E-15</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
@@ -1546,7 +1546,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>8.9762164796179433E-2</v>
+        <v>8.9762164680708731E-2</v>
       </c>
       <c r="C22" t="s">
         <v>31</v>
@@ -1557,7 +1557,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>89.762164796179434</v>
+        <v>89.762164680708736</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -1568,7 +1568,7 @@
         <v>34</v>
       </c>
       <c r="B24">
-        <v>0.197891699095775</v>
+        <v>0.19789169884120569</v>
       </c>
       <c r="C24" t="s">
         <v>35</v>
@@ -1590,7 +1590,7 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>0.73937441043038943</v>
+        <v>0.73937442090976735</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -1601,7 +1601,7 @@
         <v>38</v>
       </c>
       <c r="B27">
-        <v>5.2878176407431282E-2</v>
+        <v>5.287817845072279E-2</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
@@ -1612,7 +1612,7 @@
         <v>39</v>
       </c>
       <c r="B28">
-        <v>0.58749999920302298</v>
+        <v>0.58749999923424179</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -1623,7 +1623,7 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>7.9999999200084391</v>
+        <v>7.999999919658924</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -1645,7 +1645,7 @@
         <v>42</v>
       </c>
       <c r="B31">
-        <v>2.4000000239961818</v>
+        <v>2.4000000233149299</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
@@ -1656,7 +1656,7 @@
         <v>43</v>
       </c>
       <c r="B32">
-        <v>0.6459553469363073</v>
+        <v>0.67189851255091793</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1667,7 +1667,7 @@
         <v>44</v>
       </c>
       <c r="B33">
-        <v>6.3339191947930971</v>
+        <v>6.3339192019701471</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
@@ -1678,7 +1678,7 @@
         <v>46</v>
       </c>
       <c r="B34">
-        <v>56310.252927788933</v>
+        <v>56310.252889616051</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1689,7 +1689,7 @@
         <v>47</v>
       </c>
       <c r="B35">
-        <v>4.9999990068195242E-2</v>
+        <v>4.9999989866858163E-2</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
@@ -1700,7 +1700,7 @@
         <v>49</v>
       </c>
       <c r="B36">
-        <v>0.49999999000444972</v>
+        <v>0.4999999898414394</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="B37">
-        <v>2.999999000100435E-2</v>
+        <v>2.999998999211792E-2</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1722,7 +1722,7 @@
         <v>51</v>
       </c>
       <c r="B38">
-        <v>4.778401783574358</v>
+        <v>7.5558478472500559</v>
       </c>
       <c r="C38" t="s">
         <v>52</v>
@@ -1733,7 +1733,7 @@
         <v>53</v>
       </c>
       <c r="B39">
-        <v>4.2700611683004892</v>
+        <v>6.7520342464787726</v>
       </c>
       <c r="C39" t="s">
         <v>52</v>
@@ -1755,7 +1755,7 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>206.93828378366129</v>
+        <v>327.22116252168502</v>
       </c>
       <c r="C41" t="s">
         <v>56</v>
@@ -1766,7 +1766,7 @@
         <v>57</v>
       </c>
       <c r="B42">
-        <v>2.3090951061379358E-2</v>
+        <v>2.3090951052865748E-2</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
@@ -1777,7 +1777,7 @@
         <v>58</v>
       </c>
       <c r="B43">
-        <v>1.0844735986827789</v>
+        <v>1.084473592356658</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -1788,7 +1788,7 @@
         <v>59</v>
       </c>
       <c r="B44">
-        <v>3.1292825618228957E-2</v>
+        <v>3.1292825563728817E-2</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
@@ -1799,7 +1799,7 @@
         <v>60</v>
       </c>
       <c r="B45">
-        <v>2.7724529882045359</v>
+        <v>2.7724529768603809</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1810,7 +1810,7 @@
         <v>61</v>
       </c>
       <c r="B46">
-        <v>34.655662352556703</v>
+        <v>34.655662210754762</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -1821,7 +1821,7 @@
         <v>62</v>
       </c>
       <c r="B47">
-        <v>0.39719459867312101</v>
+        <v>0.39719459798135981</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
@@ -1832,7 +1832,7 @@
         <v>63</v>
       </c>
       <c r="B48">
-        <v>0.68495940446015746</v>
+        <v>0.68495940357902074</v>
       </c>
       <c r="C48" t="s">
         <v>64</v>
@@ -1843,7 +1843,7 @@
         <v>65</v>
       </c>
       <c r="B49">
-        <v>1.724493250281729</v>
+        <v>1.724493251066737</v>
       </c>
       <c r="C49" t="s">
         <v>66</v>
@@ -1876,7 +1876,7 @@
         <v>70</v>
       </c>
       <c r="B52">
-        <v>0.49290799278839098</v>
+        <v>0.49290799700482812</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
@@ -1887,7 +1887,7 @@
         <v>71</v>
       </c>
       <c r="B53">
-        <v>1.287631970491524E-2</v>
+        <v>1.2876319768270691E-2</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
@@ -1898,7 +1898,7 @@
         <v>72</v>
       </c>
       <c r="B54">
-        <v>3.0624153738601851</v>
+        <v>3.0624153849886961</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -1909,7 +1909,7 @@
         <v>73</v>
       </c>
       <c r="B55">
-        <v>38.280192173252317</v>
+        <v>38.2801923123587</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -1920,7 +1920,7 @@
         <v>74</v>
       </c>
       <c r="B56">
-        <v>0.1609539963114405</v>
+        <v>0.16095399710338371</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
@@ -1931,7 +1931,7 @@
         <v>75</v>
       </c>
       <c r="B57">
-        <v>0.17123985111503939</v>
+        <v>0.17123985089475521</v>
       </c>
       <c r="C57" t="s">
         <v>64</v>
@@ -1942,7 +1942,7 @@
         <v>76</v>
       </c>
       <c r="B58">
-        <v>1.063905557111462</v>
+        <v>1.0639055505081041</v>
       </c>
       <c r="C58" t="s">
         <v>66</v>
@@ -1975,7 +1975,7 @@
         <v>79</v>
       </c>
       <c r="B61">
-        <v>56.635180419480939</v>
+        <v>56.635179942237123</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -1986,7 +1986,7 @@
         <v>80</v>
       </c>
       <c r="B62">
-        <v>69.490707523385851</v>
+        <v>69.490708041969668</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -1997,7 +1997,7 @@
         <v>81</v>
       </c>
       <c r="B63">
-        <v>1.316523508442016E-4</v>
+        <v>1.3165235074712151E-4</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -2008,7 +2008,7 @@
         <v>82</v>
       </c>
       <c r="B64">
-        <v>2.1545507490248121E-3</v>
+        <v>2.9625072707329769E-3</v>
       </c>
       <c r="C64" t="s">
         <v>83</v>
@@ -2046,9 +2046,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.08984375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2066,7 +2063,7 @@
         <v>88</v>
       </c>
       <c r="B2">
-        <v>0.79438919734624192</v>
+        <v>0.79438919596271962</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -2077,7 +2074,7 @@
         <v>89</v>
       </c>
       <c r="B3">
-        <v>0.17500742592049651</v>
+        <v>0.17500742580185841</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -2088,7 +2085,7 @@
         <v>90</v>
       </c>
       <c r="B4">
-        <v>0.1390240086066151</v>
+        <v>0.13902400827024361</v>
       </c>
       <c r="C4" t="s">
         <v>91</v>
@@ -2099,7 +2096,7 @@
         <v>92</v>
       </c>
       <c r="B5">
-        <v>4.5391742274246241</v>
+        <v>4.5391742225962384</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -2110,7 +2107,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.63994116492011488</v>
+        <v>0.63994115898851145</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -2121,7 +2118,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>0.52994116492011489</v>
+        <v>0.52994115898851146</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -2132,7 +2129,7 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>0.63994116492011488</v>
+        <v>0.63994115898851145</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -2143,7 +2140,7 @@
         <v>93</v>
       </c>
       <c r="B9">
-        <v>0.32190799262288111</v>
+        <v>0.3219079942067673</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -2154,7 +2151,7 @@
         <v>94</v>
       </c>
       <c r="B10">
-        <v>8.0476998155720264E-2</v>
+        <v>8.0476998551691825E-2</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -2165,7 +2162,7 @@
         <v>95</v>
       </c>
       <c r="B11">
-        <v>2.590618892862321E-2</v>
+        <v>2.5906189183556031E-2</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -2176,7 +2173,7 @@
         <v>96</v>
       </c>
       <c r="B12">
-        <v>0.1178844373506977</v>
+        <v>0.1178844378697845</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -2187,7 +2184,7 @@
         <v>97</v>
       </c>
       <c r="B13">
-        <v>5.8942218675348858E-2</v>
+        <v>5.8942218934892258E-2</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -2198,7 +2195,7 @@
         <v>98</v>
       </c>
       <c r="B14">
-        <v>6.948370284745287E-3</v>
+        <v>6.9483703459375431E-3</v>
       </c>
       <c r="C14" t="s">
         <v>91</v>
@@ -2231,7 +2228,7 @@
         <v>102</v>
       </c>
       <c r="B17">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="C17" t="s">
         <v>101</v>
@@ -2258,9 +2255,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="21.08984375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2296,28 +2290,28 @@
         <v>113</v>
       </c>
       <c r="B2">
-        <v>2.7526753704109799E-2</v>
+        <v>2.7526753637508249E-2</v>
       </c>
       <c r="C2">
-        <v>27.526753704109801</v>
+        <v>27.52675363750825</v>
       </c>
       <c r="D2">
-        <v>8.7503712960248253E-2</v>
+        <v>8.7503712900929217E-2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.4486059119367612E-2</v>
+        <v>3.4486059059306073E-2</v>
       </c>
       <c r="G2">
-        <v>1.4040057073176849E-3</v>
+        <v>1.4040056990304701E-3</v>
       </c>
       <c r="H2">
-        <v>7.2523471899594498E-5</v>
+        <v>7.2523471625906619E-5</v>
       </c>
       <c r="I2">
-        <v>1.476364018695055E-3</v>
+        <v>1.4763640101345509E-3</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -2331,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>5.2878176407431282E-2</v>
+        <v>5.287817845072279E-2</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2354,13 +2348,13 @@
         <v>115</v>
       </c>
       <c r="B4">
-        <v>8.4438247422594544E-3</v>
+        <v>8.4438246639937913E-3</v>
       </c>
       <c r="C4">
-        <v>8.443824742259455</v>
+        <v>8.4438246639937908</v>
       </c>
       <c r="D4">
-        <v>0.20997058246005751</v>
+        <v>0.20997057949425571</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -2383,28 +2377,28 @@
         <v>116</v>
       </c>
       <c r="B5">
-        <v>6.6490492441614391E-3</v>
+        <v>6.6490492356080554E-3</v>
       </c>
       <c r="C5">
-        <v>6.6490492441614393</v>
+        <v>6.6490492356080546</v>
       </c>
       <c r="D5">
-        <v>0.1273474427478046</v>
+        <v>0.12734744240519949</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.36560917668623E-2</v>
+        <v>1.365609174185217E-2</v>
       </c>
       <c r="G5">
-        <v>1.2740169409817379E-4</v>
+        <v>1.2740169343441649E-4</v>
       </c>
       <c r="H5">
-        <v>1.207184376870165E-4</v>
+        <v>1.207184343887168E-4</v>
       </c>
       <c r="I5">
-        <v>2.4405237180415769E-4</v>
+        <v>2.4405236785225091E-4</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -2418,7 +2412,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>6.7878176407431282E-2</v>
+        <v>6.787817845072279E-2</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2447,7 +2441,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>7.2878176407431286E-2</v>
+        <v>7.2878178450722794E-2</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2476,7 +2470,7 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>0.49372651575004067</v>
+        <v>0.49372650964025011</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2505,7 +2499,7 @@
         <v>4</v>
       </c>
       <c r="D9">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2528,13 +2522,13 @@
         <v>121</v>
       </c>
       <c r="B10">
-        <v>3.1087426714347848E-3</v>
+        <v>3.1087427020267239E-3</v>
       </c>
       <c r="C10">
-        <v>3.108742671434785</v>
+        <v>3.1087427020267242</v>
       </c>
       <c r="D10">
-        <v>0.50982191538118482</v>
+        <v>0.50982190935058846</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -2543,13 +2537,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>2.6847556549224369E-5</v>
+        <v>2.684755707759434E-5</v>
       </c>
       <c r="H10">
-        <v>1.6801581190173761E-6</v>
+        <v>1.680158152062009E-6</v>
       </c>
       <c r="I10">
-        <v>2.852305155423459E-5</v>
+        <v>2.8523052115603311E-5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2563,7 +2557,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -2592,7 +2586,7 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2621,7 +2615,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D13">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2650,7 +2644,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D14">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2679,13 +2673,13 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D15">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E15">
-        <v>0.17602214410253789</v>
+        <v>0.17602214379597461</v>
       </c>
       <c r="F15">
-        <v>3.103745320743085E-2</v>
+        <v>3.1037453153375472E-2</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2708,13 +2702,13 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D16">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E16">
-        <v>-0.17602214410253789</v>
+        <v>-0.17602214379597461</v>
       </c>
       <c r="F16">
-        <v>3.103745320743085E-2</v>
+        <v>3.1037453153375472E-2</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2737,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.23479170815166231</v>
+        <v>0.23479170503737129</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2760,28 +2754,28 @@
         <v>129</v>
       </c>
       <c r="B18">
-        <v>8.338044341694344E-4</v>
+        <v>8.3380444151250521E-4</v>
       </c>
       <c r="C18">
-        <v>0.83380443416943439</v>
+        <v>0.83380444151250521</v>
       </c>
       <c r="D18">
-        <v>0.49905452564099911</v>
+        <v>0.49905451954218871</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>5.8942218675348858E-2</v>
+        <v>5.8942218934892258E-2</v>
       </c>
       <c r="G18">
-        <v>9.662223456042532E-7</v>
+        <v>9.6622236261721869E-7</v>
       </c>
       <c r="H18">
-        <v>1.206996240348283E-6</v>
+        <v>1.206996261607605E-6</v>
       </c>
       <c r="I18">
-        <v>2.420246013952836E-7</v>
+        <v>2.4202460565265548E-7</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2795,7 +2789,7 @@
         <v>0.4</v>
       </c>
       <c r="D19">
-        <v>6.2878176407431277E-2</v>
+        <v>6.2878178450722785E-2</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2818,13 +2812,13 @@
         <v>131</v>
       </c>
       <c r="B20">
-        <v>-9.9999554594197674E-9</v>
+        <v>-9.9999405653052107E-9</v>
       </c>
       <c r="C20">
-        <v>-9.9999554594197669E-6</v>
+        <v>-9.9999405653052099E-6</v>
       </c>
       <c r="D20">
-        <v>5.2502227776148949E-2</v>
+        <v>5.250222774055753E-2</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2866,7 +2860,7 @@
         <v>133</v>
       </c>
       <c r="B2">
-        <v>5.851686099283452E-2</v>
+        <v>5.851686106225025E-2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2874,7 +2868,7 @@
         <v>134</v>
       </c>
       <c r="B3">
-        <v>1.201985309517442</v>
+        <v>1.2019853054554761</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2882,7 +2876,7 @@
         <v>135</v>
       </c>
       <c r="B4">
-        <v>1.3288460827181719E-5</v>
+        <v>1.328840993830682E-5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2890,7 +2884,7 @@
         <v>136</v>
       </c>
       <c r="B5">
-        <v>7.0000429062827552E-3</v>
+        <v>7.0000428328900743E-3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2898,7 +2892,7 @@
         <v>137</v>
       </c>
       <c r="B6">
-        <v>-0.10041167535174141</v>
+        <v>-0.1004116662717963</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2906,7 +2900,7 @@
         <v>138</v>
       </c>
       <c r="B7">
-        <v>9.3568774540975217E-5</v>
+        <v>9.356877340299663E-5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2914,7 +2908,7 @@
         <v>139</v>
       </c>
       <c r="B8">
-        <v>0.46813488326182112</v>
+        <v>0.46813488379669438</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2922,7 +2916,7 @@
         <v>140</v>
       </c>
       <c r="B9">
-        <v>4.2771160334159859</v>
+        <v>4.277116045775621</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2930,7 +2924,7 @@
         <v>141</v>
       </c>
       <c r="B10">
-        <v>-3.5942462483267949E-6</v>
+        <v>-3.5944116371702312E-6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2938,7 +2932,7 @@
         <v>142</v>
       </c>
       <c r="B11">
-        <v>-1.6406543467129E-3</v>
+        <v>-1.6406546796687851E-3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2946,7 +2940,7 @@
         <v>143</v>
       </c>
       <c r="B12">
-        <v>-0.1829936965180301</v>
+        <v>-0.182993687658839</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2954,7 +2948,7 @@
         <v>144</v>
       </c>
       <c r="B13">
-        <v>-1.599603749458112E-5</v>
+        <v>-1.5996047486588338E-5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2962,7 +2956,7 @@
         <v>145</v>
       </c>
       <c r="B14">
-        <v>4.2003738928556549E-17</v>
+        <v>1.0421415163257741E-17</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2970,7 +2964,7 @@
         <v>146</v>
       </c>
       <c r="B15">
-        <v>-2.324953378177332E-12</v>
+        <v>-1.6891145449190939E-22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2978,7 +2972,7 @@
         <v>147</v>
       </c>
       <c r="B16">
-        <v>-0.1817904219270933</v>
+        <v>-0.1817904232124426</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2986,7 +2980,7 @@
         <v>148</v>
       </c>
       <c r="B17">
-        <v>-0.32051368395734853</v>
+        <v>-0.32051368424311599</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2994,7 +2988,7 @@
         <v>149</v>
       </c>
       <c r="B18">
-        <v>2.857109651435494E-14</v>
+        <v>-3.0588670287472291E-18</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3002,7 +2996,7 @@
         <v>150</v>
       </c>
       <c r="B19">
-        <v>0.118718658402095</v>
+        <v>0.11871865801791549</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3010,7 +3004,7 @@
         <v>151</v>
       </c>
       <c r="B20">
-        <v>-2.8992790498794717E-17</v>
+        <v>5.6482533164821213E-19</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3018,7 +3012,7 @@
         <v>152</v>
       </c>
       <c r="B21">
-        <v>-3.5918813496518868E-12</v>
+        <v>-3.2661532632680472E-19</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3026,7 +3020,7 @@
         <v>153</v>
       </c>
       <c r="B22">
-        <v>-0.15884416825508041</v>
+        <v>-0.15884416838197951</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3034,7 +3028,7 @@
         <v>154</v>
       </c>
       <c r="B23">
-        <v>-0.60818234840987107</v>
+        <v>-0.60818234905545576</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3042,7 +3036,7 @@
         <v>155</v>
       </c>
       <c r="B24">
-        <v>4.6434878995594997E-14</v>
+        <v>-1.8177580022587212E-18</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3050,7 +3044,7 @@
         <v>156</v>
       </c>
       <c r="B25">
-        <v>4.6923377876579388E-2</v>
+        <v>4.6923377936140369E-2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3058,7 +3052,7 @@
         <v>157</v>
       </c>
       <c r="B26">
-        <v>3.9931453962113534E-15</v>
+        <v>8.3611685254905366E-11</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -3066,7 +3060,7 @@
         <v>158</v>
       </c>
       <c r="B27">
-        <v>-0.21385575919131791</v>
+        <v>-0.2138557589481575</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -3074,7 +3068,7 @@
         <v>159</v>
       </c>
       <c r="B28">
-        <v>-2.744034293323864E-6</v>
+        <v>-2.7442637703634519E-6</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3082,7 +3076,7 @@
         <v>160</v>
       </c>
       <c r="B29">
-        <v>7.7233943854266478E-4</v>
+        <v>7.7233925660336739E-4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3090,7 +3084,7 @@
         <v>161</v>
       </c>
       <c r="B30">
-        <v>-9.0781628669107342</v>
+        <v>-9.0781627481001106</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -3098,7 +3092,7 @@
         <v>162</v>
       </c>
       <c r="B31">
-        <v>-1.2772209291585479E-4</v>
+        <v>-1.2772209677933171E-4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3106,7 +3100,7 @@
         <v>163</v>
       </c>
       <c r="B32">
-        <v>-3.8482854487225481E-17</v>
+        <v>-4.3076673211499966E-18</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3114,7 +3108,7 @@
         <v>164</v>
       </c>
       <c r="B33">
-        <v>-8.397685793681886E-13</v>
+        <v>-2.9206328780962878E-20</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -3122,7 +3116,7 @@
         <v>165</v>
       </c>
       <c r="B34">
-        <v>4.0786019749868889E-2</v>
+        <v>4.0786019250300502E-2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3130,7 +3124,7 @@
         <v>166</v>
       </c>
       <c r="B35">
-        <v>-2.682529655510784E-2</v>
+        <v>-2.6825297658322009E-2</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -3138,7 +3132,7 @@
         <v>167</v>
       </c>
       <c r="B36">
-        <v>8.424853383526709E-15</v>
+        <v>1.142634098853538E-18</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -3146,7 +3140,7 @@
         <v>168</v>
       </c>
       <c r="B37">
-        <v>-4.1983039778635857E-2</v>
+        <v>-4.1983039114655493E-2</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -3154,7 +3148,7 @@
         <v>169</v>
       </c>
       <c r="B38">
-        <v>0.1100708544319977</v>
+        <v>0.1100708542962507</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -3162,7 +3156,7 @@
         <v>170</v>
       </c>
       <c r="B39">
-        <v>3.6890047286640658E-2</v>
+        <v>3.6890047319587289E-2</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -3170,7 +3164,7 @@
         <v>171</v>
       </c>
       <c r="B40">
-        <v>7.3180807145357046E-2</v>
+        <v>7.3180806976663418E-2</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -3178,7 +3172,7 @@
         <v>172</v>
       </c>
       <c r="B41">
-        <v>-3.1022468610037001E-2</v>
+        <v>-3.10224686771794E-2</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -3186,7 +3180,7 @@
         <v>173</v>
       </c>
       <c r="B42">
-        <v>3.1022468610037001E-2</v>
+        <v>3.10224686771794E-2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -3194,7 +3188,7 @@
         <v>174</v>
       </c>
       <c r="B43">
-        <v>-0.1100708544319977</v>
+        <v>-0.1100708542962507</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -3202,7 +3196,7 @@
         <v>175</v>
       </c>
       <c r="B44">
-        <v>0.88056682665124208</v>
+        <v>0.88056682552679499</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -3210,7 +3204,7 @@
         <v>176</v>
       </c>
       <c r="B45">
-        <v>-4.3322615022534907E-17</v>
+        <v>8.4399293324892216E-19</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -3218,7 +3212,7 @@
         <v>177</v>
       </c>
       <c r="B46">
-        <v>4.3322615022534907E-17</v>
+        <v>-8.4399293324892216E-19</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -3226,7 +3220,7 @@
         <v>178</v>
       </c>
       <c r="B47">
-        <v>-4.8283001065587691E-17</v>
+        <v>2.6600908953026521E-19</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -3234,7 +3228,7 @@
         <v>179</v>
       </c>
       <c r="B48">
-        <v>7.9009491533917443E-17</v>
+        <v>1.9602795658765791E-17</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -3250,7 +3244,7 @@
         <v>182</v>
       </c>
       <c r="B50">
-        <v>-4.3322615022534907E-17</v>
+        <v>8.4399293324892216E-19</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -3258,7 +3252,7 @@
         <v>183</v>
       </c>
       <c r="B51">
-        <v>1.3145070427121601E-15</v>
+        <v>2.7524204073423649E-11</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -3266,7 +3260,7 @@
         <v>184</v>
       </c>
       <c r="B52">
-        <v>-5.7503188249078912E-17</v>
+        <v>-6.4367523447094317E-18</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -3282,7 +3276,7 @@
         <v>187</v>
       </c>
       <c r="B54">
-        <v>0.13609781230568979</v>
+        <v>0.13609781192191731</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -3290,7 +3284,7 @@
         <v>188</v>
       </c>
       <c r="B55">
-        <v>0.30557450855570661</v>
+        <v>0.30557450445952561</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -3298,7 +3292,7 @@
         <v>189</v>
       </c>
       <c r="B56">
-        <v>0.13506211644299099</v>
+        <v>0.1408170535347481</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -3306,7 +3300,7 @@
         <v>43</v>
       </c>
       <c r="B57">
-        <v>0.6459553469363073</v>
+        <v>0.67189851255091793</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -3314,7 +3308,7 @@
         <v>190</v>
       </c>
       <c r="B58">
-        <v>6.8356071730147436E-3</v>
+        <v>3.0105821953666613E-17</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -3322,7 +3316,7 @@
         <v>191</v>
       </c>
       <c r="B59">
-        <v>1.1593110234085329E-2</v>
+        <v>1.7818851254259181E-18</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -3330,7 +3324,7 @@
         <v>192</v>
       </c>
       <c r="B60">
-        <v>-6.2453855605587121E-10</v>
+        <v>8.1699104264630406E-11</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -3338,7 +3332,7 @@
         <v>193</v>
       </c>
       <c r="B61">
-        <v>-1.099912204178762E-3</v>
+        <v>-1.387515357203983E-17</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -3346,7 +3340,7 @@
         <v>194</v>
       </c>
       <c r="B62">
-        <v>0.20287462600962469</v>
+        <v>0.2115190236529163</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -3354,7 +3348,7 @@
         <v>195</v>
       </c>
       <c r="B63">
-        <v>5.6094940853209763E-2</v>
+        <v>6.0684451040389102E-2</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -3362,7 +3356,7 @@
         <v>196</v>
       </c>
       <c r="B64">
-        <v>0.14677968515641501</v>
+        <v>0.1508345726125272</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -3370,7 +3364,7 @@
         <v>197</v>
       </c>
       <c r="B65">
-        <v>-7.3931389469141268E-2</v>
+        <v>-7.4967395358773697E-2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -3378,7 +3372,7 @@
         <v>198</v>
       </c>
       <c r="B66">
-        <v>7.3931389469141268E-2</v>
+        <v>7.4967395358773697E-2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -3386,7 +3380,7 @@
         <v>199</v>
       </c>
       <c r="B67">
-        <v>-0.20287462600962469</v>
+        <v>-0.2115190236529163</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -3394,7 +3388,7 @@
         <v>200</v>
       </c>
       <c r="B68">
-        <v>0.97027910475499901</v>
+        <v>1.009247912814391</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -3402,7 +3396,7 @@
         <v>201</v>
       </c>
       <c r="B69">
-        <v>1.383335354200187E-2</v>
+        <v>2.126215166677926E-18</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -3410,7 +3404,7 @@
         <v>202</v>
       </c>
       <c r="B70">
-        <v>-1.383335354200187E-2</v>
+        <v>-2.126215166677926E-18</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -3418,7 +3412,7 @@
         <v>203</v>
       </c>
       <c r="B71">
-        <v>1.354193235514438E-2</v>
+        <v>-1.018547115135082E-19</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -3426,7 +3420,7 @@
         <v>204</v>
       </c>
       <c r="B72">
-        <v>1.026765524853465E-2</v>
+        <v>4.5221469318250818E-17</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -3442,7 +3436,7 @@
         <v>207</v>
       </c>
       <c r="B74">
-        <v>1.383335354200187E-2</v>
+        <v>2.126215166677926E-18</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -3450,7 +3444,7 @@
         <v>208</v>
       </c>
       <c r="B75">
-        <v>-1.641760918497949E-10</v>
+        <v>2.1476719850503728E-11</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -3458,7 +3452,7 @@
         <v>209</v>
       </c>
       <c r="B76">
-        <v>-1.3124583548625101E-3</v>
+        <v>-1.6556377032332441E-17</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -3505,10 +3499,10 @@
         <v>217</v>
       </c>
       <c r="B2">
-        <v>0.88056682665124208</v>
+        <v>0.88056682552679499</v>
       </c>
       <c r="C2">
-        <v>0.88056683665052027</v>
+        <v>0.88056683551775272</v>
       </c>
       <c r="E2">
         <v>9.9999999999999995E-7</v>
@@ -3522,7 +3516,7 @@
         <v>218</v>
       </c>
       <c r="B3">
-        <v>0.1100708544319977</v>
+        <v>0.1100708542962507</v>
       </c>
       <c r="C3">
         <v>1E-3</v>
@@ -3539,7 +3533,7 @@
         <v>219</v>
       </c>
       <c r="B4">
-        <v>3.9931453962113534E-15</v>
+        <v>8.3611685254905366E-11</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3559,7 +3553,7 @@
         <v>220</v>
       </c>
       <c r="B5">
-        <v>-2.8992790498794717E-17</v>
+        <v>5.6482533164821213E-19</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3579,7 +3573,7 @@
         <v>221</v>
       </c>
       <c r="B6">
-        <v>-3.8482854487225481E-17</v>
+        <v>-4.3076673211499966E-18</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3599,7 +3593,7 @@
         <v>222</v>
       </c>
       <c r="B7">
-        <v>0.46813488326182112</v>
+        <v>0.46813488379669438</v>
       </c>
       <c r="D7">
         <v>1.2</v>
@@ -3616,7 +3610,7 @@
         <v>223</v>
       </c>
       <c r="B8">
-        <v>7.5325047354822843</v>
+        <v>7.6676395581233496</v>
       </c>
       <c r="D8">
         <v>12</v>
@@ -3633,7 +3627,7 @@
         <v>224</v>
       </c>
       <c r="B9">
-        <v>0.6459553469363073</v>
+        <v>0.67189851255091793</v>
       </c>
       <c r="D9">
         <v>0.9</v>
@@ -3650,10 +3644,10 @@
         <v>225</v>
       </c>
       <c r="B10">
-        <v>0.97027910475499901</v>
+        <v>1.009247912814391</v>
       </c>
       <c r="C10">
-        <v>0.95894316624422038</v>
+        <v>0.95894316501062893</v>
       </c>
       <c r="E10">
         <v>9.9999999999999995E-7</v>
@@ -3667,7 +3661,7 @@
         <v>226</v>
       </c>
       <c r="B11">
-        <v>-6.2453855605587121E-10</v>
+        <v>8.1699104264630406E-11</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -3687,7 +3681,7 @@
         <v>227</v>
       </c>
       <c r="B12">
-        <v>2.4000000239961818</v>
+        <v>2.4000000233149299</v>
       </c>
       <c r="D12">
         <v>2.4</v>
@@ -3704,7 +3698,7 @@
         <v>228</v>
       </c>
       <c r="B13">
-        <v>4.2700611683004892</v>
+        <v>6.7520342464787726</v>
       </c>
       <c r="C13">
         <v>0.58177641733144314</v>
@@ -3721,7 +3715,7 @@
         <v>229</v>
       </c>
       <c r="B14">
-        <v>0.49290799278839098</v>
+        <v>0.49290799700482812</v>
       </c>
       <c r="E14">
         <v>9.9999999999999995E-7</v>
@@ -3735,7 +3729,7 @@
         <v>230</v>
       </c>
       <c r="B15">
-        <v>1.287631970491524E-2</v>
+        <v>1.2876319768270691E-2</v>
       </c>
       <c r="E15">
         <v>9.9999999999999995E-7</v>
@@ -3749,7 +3743,7 @@
         <v>231</v>
       </c>
       <c r="B16">
-        <v>69.490707523385851</v>
+        <v>69.490708041969668</v>
       </c>
       <c r="E16">
         <v>9.9999999999999995E-7</v>
@@ -3763,7 +3757,7 @@
         <v>232</v>
       </c>
       <c r="B17">
-        <v>7.9999999200084391</v>
+        <v>7.999999919658924</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -3780,7 +3774,7 @@
         <v>233</v>
       </c>
       <c r="B18">
-        <v>6.3339191947930971</v>
+        <v>6.3339192019701471</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -3797,7 +3791,7 @@
         <v>234</v>
       </c>
       <c r="B19">
-        <v>6.3339191947930971</v>
+        <v>6.3339192019701471</v>
       </c>
       <c r="D19">
         <v>20</v>
@@ -3814,7 +3808,7 @@
         <v>235</v>
       </c>
       <c r="B20">
-        <v>56310.252927788933</v>
+        <v>56310.252889616051</v>
       </c>
       <c r="C20">
         <v>20000</v>
@@ -3831,7 +3825,7 @@
         <v>236</v>
       </c>
       <c r="B21">
-        <v>4.9999990068195242E-2</v>
+        <v>4.9999989866858163E-2</v>
       </c>
       <c r="C21">
         <v>0.05</v>
@@ -3848,7 +3842,7 @@
         <v>237</v>
       </c>
       <c r="B22">
-        <v>4.9999990068195242E-2</v>
+        <v>4.9999989866858163E-2</v>
       </c>
       <c r="D22">
         <v>0.1</v>
@@ -3865,7 +3859,7 @@
         <v>238</v>
       </c>
       <c r="B23">
-        <v>0.49999999000444972</v>
+        <v>0.4999999898414394</v>
       </c>
       <c r="C23">
         <v>0.5</v>
@@ -3882,7 +3876,7 @@
         <v>239</v>
       </c>
       <c r="B24">
-        <v>0.49999999000444972</v>
+        <v>0.4999999898414394</v>
       </c>
       <c r="D24">
         <v>0.7</v>
@@ -3899,7 +3893,7 @@
         <v>240</v>
       </c>
       <c r="B25">
-        <v>2.999999000100435E-2</v>
+        <v>2.999998999211792E-2</v>
       </c>
       <c r="C25">
         <v>0.03</v>
@@ -3916,7 +3910,7 @@
         <v>241</v>
       </c>
       <c r="B26">
-        <v>2.999999000100435E-2</v>
+        <v>2.999998999211792E-2</v>
       </c>
       <c r="D26">
         <v>0.05</v>
@@ -3933,7 +3927,7 @@
         <v>242</v>
       </c>
       <c r="B27">
-        <v>-0.15884416825508041</v>
+        <v>-0.15884416838197951</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3950,7 +3944,7 @@
         <v>243</v>
       </c>
       <c r="B28">
-        <v>4.0786019749868889E-2</v>
+        <v>4.0786019250300502E-2</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3967,7 +3961,7 @@
         <v>244</v>
       </c>
       <c r="B29">
-        <v>-9.0781628669107342</v>
+        <v>-9.0781627481001106</v>
       </c>
       <c r="D29">
         <v>-0.01</v>
@@ -3984,7 +3978,7 @@
         <v>245</v>
       </c>
       <c r="B30">
-        <v>4.778401783574358</v>
+        <v>7.5558478472500559</v>
       </c>
       <c r="C30">
         <v>0.6</v>
@@ -4001,7 +3995,7 @@
         <v>246</v>
       </c>
       <c r="B31">
-        <v>206.93828378366129</v>
+        <v>327.22116252168502</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -4018,7 +4012,7 @@
         <v>247</v>
       </c>
       <c r="B32">
-        <v>2.3090951061379358E-2</v>
+        <v>2.3090951052865748E-2</v>
       </c>
       <c r="D32">
         <v>0.45</v>
@@ -4035,7 +4029,7 @@
         <v>248</v>
       </c>
       <c r="B33">
-        <v>1.5512765392978651E-5</v>
+        <v>2.133005234927743E-5</v>
       </c>
       <c r="D33">
         <v>7.1999999999999998E-3</v>
@@ -4052,7 +4046,7 @@
         <v>249</v>
       </c>
       <c r="B34">
-        <v>6.6464270437371452E-6</v>
+        <v>6.6464271418445364E-6</v>
       </c>
       <c r="D34">
         <v>7.1999999999999998E-3</v>
@@ -4069,7 +4063,7 @@
         <v>250</v>
       </c>
       <c r="B35">
-        <v>1.777116740289979E-6</v>
+        <v>1.777116763765797E-6</v>
       </c>
       <c r="D35">
         <v>7.1999999999999998E-3</v>
@@ -4086,7 +4080,7 @@
         <v>251</v>
       </c>
       <c r="B36">
-        <v>1.705533569452131</v>
+        <v>7.361633920078792E-19</v>
       </c>
       <c r="D36">
         <v>24</v>
@@ -4103,7 +4097,7 @@
         <v>252</v>
       </c>
       <c r="B37">
-        <v>7.9053142835242181</v>
+        <v>8.2024026613530392</v>
       </c>
       <c r="D37">
         <v>24</v>
@@ -4120,7 +4114,7 @@
         <v>253</v>
       </c>
       <c r="B38">
-        <v>3.744755182158211E-3</v>
+        <v>1.5398283992121381E-15</v>
       </c>
       <c r="D38">
         <v>24</v>
@@ -4177,7 +4171,7 @@
         <v>258</v>
       </c>
       <c r="B2">
-        <v>5.1216588551025453</v>
+        <v>5.1216588485150671</v>
       </c>
       <c r="C2">
         <v>-4</v>
@@ -4203,7 +4197,7 @@
         <v>260</v>
       </c>
       <c r="B3">
-        <v>-3.7444920484420398E-15</v>
+        <v>-5.5536956088661469E-17</v>
       </c>
       <c r="C3">
         <v>-30</v>
@@ -4229,7 +4223,7 @@
         <v>261</v>
       </c>
       <c r="B4">
-        <v>1.0708483104648889</v>
+        <v>1.0708483140055509</v>
       </c>
       <c r="C4">
         <v>-30</v>
@@ -4255,7 +4249,7 @@
         <v>262</v>
       </c>
       <c r="B5">
-        <v>-3.4373305670140819E-15</v>
+        <v>-1.453058710546046E-15</v>
       </c>
       <c r="C5">
         <v>-30</v>
@@ -4281,7 +4275,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>7.5325047354822843</v>
+        <v>7.6676395581233496</v>
       </c>
       <c r="C6">
         <v>-4</v>
@@ -4307,7 +4301,7 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-1.705533569452131</v>
+        <v>-7.361633920078792E-19</v>
       </c>
       <c r="C7">
         <v>-30</v>
@@ -4333,7 +4327,7 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>7.9053142835242181</v>
+        <v>8.2024026613530392</v>
       </c>
       <c r="C8">
         <v>-30</v>
@@ -4359,7 +4353,7 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>-3.744755182158211E-3</v>
+        <v>1.5398283992121381E-15</v>
       </c>
       <c r="C9">
         <v>-30</v>
@@ -4385,7 +4379,7 @@
         <v>88</v>
       </c>
       <c r="B10">
-        <v>0.78232064045572403</v>
+        <v>0.78232063909322058</v>
       </c>
       <c r="C10">
         <v>0.3</v>
@@ -4411,7 +4405,7 @@
         <v>89</v>
       </c>
       <c r="B11">
-        <v>0.17500742592049651</v>
+        <v>0.17500742580185841</v>
       </c>
       <c r="C11">
         <v>0.1</v>
@@ -4437,7 +4431,7 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>0.63994116492011488</v>
+        <v>0.63994115898851145</v>
       </c>
       <c r="C12">
         <v>0.35</v>
@@ -4463,7 +4457,7 @@
         <v>93</v>
       </c>
       <c r="B13">
-        <v>0.32190799262288111</v>
+        <v>0.3219079942067673</v>
       </c>
       <c r="C13">
         <v>0.2</v>
@@ -4489,7 +4483,7 @@
         <v>96</v>
       </c>
       <c r="B14">
-        <v>0.1178844373506977</v>
+        <v>0.1178844378697845</v>
       </c>
       <c r="C14">
         <v>0.1</v>
@@ -4544,7 +4538,7 @@
         <v>37</v>
       </c>
       <c r="B16">
-        <v>0.73937441043038943</v>
+        <v>0.73937442090976735</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -4710,7 +4704,7 @@
         <v>258</v>
       </c>
       <c r="C10">
-        <v>5.1216588551025453</v>
+        <v>5.1216588485150671</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -4724,7 +4718,7 @@
         <v>260</v>
       </c>
       <c r="C11">
-        <v>-3.7444920484420398E-15</v>
+        <v>-5.5536956088661469E-17</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -4738,7 +4732,7 @@
         <v>261</v>
       </c>
       <c r="C12">
-        <v>1.0708483104648889</v>
+        <v>1.0708483140055509</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -4752,7 +4746,7 @@
         <v>262</v>
       </c>
       <c r="C13">
-        <v>-3.4373305670140819E-15</v>
+        <v>-1.453058710546046E-15</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -4766,7 +4760,7 @@
         <v>277</v>
       </c>
       <c r="C14">
-        <v>0.58749999920302298</v>
+        <v>0.58749999923424179</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -4780,7 +4774,7 @@
         <v>278</v>
       </c>
       <c r="C15">
-        <v>0.46813488326182112</v>
+        <v>0.46813488379669438</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -4794,7 +4788,7 @@
         <v>26</v>
       </c>
       <c r="C16">
-        <v>7.5325047354822843</v>
+        <v>7.6676395581233496</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -4808,7 +4802,7 @@
         <v>27</v>
       </c>
       <c r="C17">
-        <v>-1.705533569452131</v>
+        <v>-7.361633920078792E-19</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -4822,7 +4816,7 @@
         <v>28</v>
       </c>
       <c r="C18">
-        <v>7.9053142835242181</v>
+        <v>8.2024026613530392</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -4836,7 +4830,7 @@
         <v>29</v>
       </c>
       <c r="C19">
-        <v>-3.744755182158211E-3</v>
+        <v>1.5398283992121381E-15</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -4850,7 +4844,7 @@
         <v>280</v>
       </c>
       <c r="C20">
-        <v>0.6459553469363073</v>
+        <v>0.67189851255091793</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
@@ -4878,7 +4872,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>2.4000000239961818</v>
+        <v>2.4000000233149299</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12d7bf0-dirty</t>
+          <t>6d31dd0-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.7380000000000003</v>
+        <v>0.6450000000000004</v>
       </c>
     </row>
     <row r="295">
@@ -10640,7 +10640,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>2.55</v>
+        <v>2.202</v>
       </c>
     </row>
     <row r="296">
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>1.461</v>
+        <v>1.322</v>
       </c>
     </row>
     <row r="298">
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>37.15700000000001</v>
+        <v>34.784</v>
       </c>
     </row>
     <row r="299">
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>12.501</v>
+        <v>11.175</v>
       </c>
     </row>
     <row r="300">
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>54.508</v>
+        <v>50.198</v>
       </c>
     </row>
     <row r="301">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.7350840000000001</v>
+        <v>0.6466690000000002</v>
       </c>
     </row>
     <row r="303">
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>2.561095</v>
+        <v>2.192599</v>
       </c>
     </row>
     <row r="304">
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1.465695</v>
+        <v>1.319143</v>
       </c>
     </row>
     <row r="306">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>37.155953</v>
+        <v>34.783258</v>
       </c>
     </row>
     <row r="307">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>12.497404</v>
+        <v>11.177236</v>
       </c>
     </row>
     <row r="308">
@@ -10770,7 +10770,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>54.507566</v>
+        <v>50.197163</v>
       </c>
     </row>
     <row r="309">

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62106cf-dirty</t>
+          <t>5510482-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.58581107273481</v>
+        <v>1.79185260855713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7831813144429484</v>
+        <v>0.6712501614845966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6731813144429484</v>
+        <v>0.5712501614845966</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7831813144429484</v>
+        <v>0.6712501614845966</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.35539781503875</v>
+        <v>5.181709548775771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.747393628933218e-16</v>
+        <v>6.677006654063078e-17</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.228921909584063</v>
+        <v>-1.112396518263171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-5.009559374285092e-15</v>
+        <v>-1.305569024969542e-15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.35539781503875</v>
+        <v>5.181709548775771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.747393628933218e-16</v>
+        <v>6.677006654063078e-17</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.228921909584063</v>
+        <v>-1.112396518263171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-5.009559374285092e-15</v>
+        <v>-1.305569024969542e-15</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1606667490162134</v>
+        <v>0.140866002900824</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1606667490162134</v>
+        <v>0.140866002900824</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.474970827815581e-09</v>
+        <v>7.084625203967024e-09</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>160.6667490162135</v>
+        <v>140.866002900824</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3542095494600437</v>
+        <v>0.3105563766445718</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.13133115592258</v>
+        <v>0.1441175773158246</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.02683218145776771</v>
+        <v>0.01502644652070806</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.13133115592258</v>
+        <v>0.1441175773158246</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.02683218145776771</v>
+        <v>0.01502644652070806</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1606667490162134</v>
+        <v>0.140866002900824</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2039745787048131</v>
+        <v>0.02358254083198405</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0497490786629821</v>
+        <v>-0.08417021565831362</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.01795706339148154</v>
+        <v>0.04225210446311809</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6073597679157974</v>
+        <v>0.7484904106847665</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9.878823522672636</v>
+        <v>8.016134703895203</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.333072680333501</v>
+        <v>1.749999996503405</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.333072680333501</v>
+        <v>1.749999996503405</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27.00527925528691</v>
+        <v>20.5714286125314</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7.514895939417326</v>
+        <v>7.514895932668145</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4.790485495770057</v>
+        <v>4.790485500072426</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.857412815436557</v>
+        <v>5.440485503569021</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1183,11 +1183,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>turn_curvature_margin_mps2</t>
+          <t>agility_lateral_margin_mps2</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-19.49038331586958</v>
+        <v>-13.05653267986326</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4709472823739185</v>
+        <v>0.385007216173159</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10.38438048650968</v>
+        <v>8.489403328184636</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>54149.30565142133</v>
+        <v>94066.68509676102</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.04999999003231618</v>
+        <v>0.2000000098107236</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8708157105346108</v>
+        <v>0.5558482021720921</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.02999999001463034</v>
+        <v>0.02999999002463568</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.285495423909251</v>
+        <v>5.605487237063405</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.628396339127401</v>
+        <v>4.484389789650724</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0333204982427328</v>
+        <v>0.03437008016121631</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>100.3992550618949</v>
+        <v>171.0246568338559</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>50.39925506566945</v>
+        <v>121.0246568464731</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>100.3992550656695</v>
+        <v>171.0246568464731</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>100.3992550656695</v>
+        <v>171.0246568464731</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.795441978686092</v>
+        <v>-0.7261221598264442</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.795441978686092</v>
+        <v>-0.7261221598264442</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>98.60283000497498</v>
+        <v>163.0920617807786</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0333204982427328</v>
+        <v>0.03437008016121631</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0119474760896612</v>
+        <v>0.006735401206332104</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.04535418557331994</v>
+        <v>0.0280000002797276</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.02107408776258908</v>
+        <v>0.01924400325441034</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2634260970323635</v>
+        <v>0.2405500406801292</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.57567308739442</v>
+        <v>0.3553993177105463</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7880703989349344</v>
+        <v>0.6909477392333268</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.368954735233247</v>
+        <v>1.944144810643859</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.502384226145168</v>
+        <v>0.5497888006219521</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0004389233015415032</v>
+        <v>0.003385495155179471</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0134740525633578</v>
+        <v>0.01628575244430116</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.002606035857304814</v>
+        <v>0.01663046355031217</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.03257544821631017</v>
+        <v>0.2078807943789021</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.1684256570419725</v>
+        <v>0.2035719055537644</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.1970175997337336</v>
+        <v>0.1727369348083317</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.169760018716364</v>
+        <v>0.8485303231722755</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.2680718121975056</v>
+        <v>0.05380548506041465</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.1588957892195114</v>
+        <v>0.3301844120382679</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.1613246836757413</v>
+        <v>0.1338198671999475</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.01480911033010347</v>
+        <v>0.0152755911827628</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.003970478485063968</v>
+        <v>0.007397234821551284</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6073597679157974</v>
+        <v>0.7484904106847665</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6426669960648538</v>
+        <v>0.563464011603296</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-3.990011252770125e-07</v>
+        <v>-3.971588330453208e-07</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0007551245299278695</v>
+        <v>0.0006187130069220122</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.1588957892195114</v>
+        <v>0.3301844120382679</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.1613246836757413</v>
+        <v>0.1338198671999475</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.01480911033010347</v>
+        <v>0.0152755911827628</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.58581107273481</v>
+        <v>1.79185260855713</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6073597679157974</v>
+        <v>0.7484904106847665</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>38.2996296569159</v>
+        <v>41.77187381988302</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6426669960648538</v>
+        <v>0.563464011603296</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>40.52607571698579</v>
+        <v>31.44589063366207</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-3.990011252770125e-07</v>
+        <v>-3.971588330453208e-07</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-2.516069739561821e-05</v>
+        <v>-2.216470434837432e-05</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0007551245299278695</v>
+        <v>0.0006187130069220122</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.04761755942500892</v>
+        <v>0.03452923549444306</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.1588957892195114</v>
+        <v>0.3301844120382679</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>10.01984359621652</v>
+        <v>18.4269850355686</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.1613246836757413</v>
+        <v>0.1338198671999475</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>10.17300777182296</v>
+        <v>7.46824077833637</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.01480911033010347</v>
+        <v>0.0152755911827628</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.9338508593312078</v>
+        <v>0.8525026617598482</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.58581107273481</v>
+        <v>1.79185260855713</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ballast_mass_kg:lower</t>
+          <t>wing_span_m:upper; tail_arm_m:lower; ballast_mass_kg:lower</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.35539781503875</v>
+        <v>5.181709548775771</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1.747393628933218e-16</v>
+        <v>6.677006654063078e-17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.228921909584063</v>
+        <v>-1.112396518263171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-5.009559374285092e-15</v>
+        <v>-1.305569024969542e-15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6073597679157974</v>
+        <v>0.7484904106847665</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4709472823739185</v>
+        <v>0.385007216173159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.795441978686092</v>
+        <v>-0.7261221598264442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.35539781503875</v>
+        <v>5.181709548775771</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-1.747393628933218e-16</v>
+        <v>6.677006654063078e-17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.228921909584063</v>
+        <v>-1.112396518263171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-5.009559374285092e-15</v>
+        <v>-1.305569024969542e-15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4709472823739185</v>
+        <v>0.385007216173159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.333072680333501</v>
+        <v>1.749999996503405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.333072680333501</v>
+        <v>1.749999996503405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.00527925528691</v>
+        <v>20.5714286125314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.514895939417326</v>
+        <v>7.514895932668145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.790485495770057</v>
+        <v>4.790485500072426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.857412815436557</v>
+        <v>5.440485503569021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3079,11 +3079,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>turn_curvature_margin_mps2</t>
+          <t>agility_lateral_margin_mps2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-19.49038331586958</v>
+        <v>-13.05653267986326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.795441978686092</v>
+        <v>-0.7261221598264442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0333204982427328</v>
+        <v>0.03437008016121631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100.3992550618949</v>
+        <v>171.0246568338559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50.39925506566945</v>
+        <v>121.0246568464731</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100.3992550656695</v>
+        <v>171.0246568464731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>100.3992550656695</v>
+        <v>171.0246568464731</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.15134617478884</v>
+        <v>0.7107986354210927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1318282535659262</v>
+        <v>0.2290084178524724</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1517799554722224</v>
+        <v>0.1627788709094808</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.733682982556253</v>
+        <v>3.103810078627723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7831813144429484</v>
+        <v>0.6712501614845966</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6731813144429484</v>
+        <v>0.5712501614845966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7831813144429484</v>
+        <v>0.6712501614845966</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3368513140839449</v>
+        <v>0.4071438111075289</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08421282852098623</v>
+        <v>0.1017859527768822</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02836720195002013</v>
+        <v>0.04144152073079079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1296567456435643</v>
+        <v>0.1169334036779487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06482837282178215</v>
+        <v>0.05846670183897434</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.008405435845439966</v>
+        <v>0.006836710447855052</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3585,168 +3585,168 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03005243118350003</v>
+        <v>0.03223021644007719</v>
       </c>
       <c r="C2" t="n">
-        <v>30.05243118350003</v>
+        <v>32.23021644007719</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06591412678296309</v>
+        <v>0.1145042089262362</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05698229127896829</v>
+        <v>0.0378572219322534</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003219773257695084</v>
+        <v>0.001316163888248209</v>
       </c>
       <c r="H2" t="n">
-        <v>4.496598218396961e-05</v>
+        <v>0.0001453352561245325</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003264558925291953</v>
+        <v>0.001461305763074101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wing_spar_tube</t>
+          <t>centre module core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01496085950170246</v>
+        <v>0.0131864418212479</v>
       </c>
       <c r="C3" t="n">
-        <v>14.96085950170246</v>
+        <v>13.1864418212479</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03295706339148154</v>
+        <v>0.0828521044631181</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05598229127896828</v>
+        <v>-0.00727</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001602858292021014</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.740214875425615e-08</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001602858292021014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>centre module core</t>
+          <t>glue</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0131864418212479</v>
+        <v>0.01043451873339437</v>
       </c>
       <c r="C4" t="n">
-        <v>13.1864418212479</v>
+        <v>10.43451873339437</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05855706339148155</v>
+        <v>0.1441175773158247</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00727</v>
+        <v>0.01502644652070806</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.0002013291726779135</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.0002444997845013802</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.000435303264902527</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>glue</t>
+          <t>receiver</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01190124066786766</v>
+        <v>0.01</v>
       </c>
       <c r="C5" t="n">
-        <v>11.90124066786766</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.13133115592258</v>
+        <v>0.1172521044631181</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02683218145776771</v>
+        <v>-0.008</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006499521011378489</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004609552060408431</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001085279544289125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>boom</t>
+          <t>wing_spar_tube</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01033383398830761</v>
+        <v>0.00923628249382696</v>
       </c>
       <c r="C6" t="n">
-        <v>10.33383398830761</v>
+        <v>9.236282493826961</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2815906572214742</v>
+        <v>0.05725210446311809</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.03685722193225339</v>
       </c>
       <c r="G6" t="n">
-        <v>2.583458497076902e-08</v>
+        <v>0.0003771597547200107</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00052822078881353</v>
+        <v>2.30907062345674e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00052822078881353</v>
+        <v>0.0003771597547200107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09295706339148155</v>
+        <v>0.04225210446311809</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3755,143 +3755,143 @@
         <v>-0.008</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.355e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.6755e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.8735e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>boom</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008856937219372078</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>8.856937219372078</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01795706339148154</v>
+        <v>0.2356250807422983</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.008</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.355e-07</v>
+        <v>2.214234304843019e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6755e-06</v>
+        <v>0.0003325719250636766</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8735e-06</v>
+        <v>0.0003325719250636766</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wing_tape_bottom</t>
+          <t>htail_surfaces</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00680312783599799</v>
+        <v>0.004972982487694896</v>
       </c>
       <c r="C9" t="n">
-        <v>6.803127835997991</v>
+        <v>4.972982487694896</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03295706339148154</v>
+        <v>0.5508929709292202</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05404729127896828</v>
+        <v>-0.0025</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0007288567063883537</v>
+        <v>6.86997153560883e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.417327880237951e-06</v>
+        <v>4.29722883806718e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007302740151064483</v>
+        <v>7.298948472042393e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wing_tape_top</t>
+          <t>servo_elevator</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00680312783599799</v>
+        <v>0.004</v>
       </c>
       <c r="C10" t="n">
-        <v>6.803127835997991</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03295706339148154</v>
+        <v>0.05725210446311809</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05991729127896828</v>
+        <v>-0.0065</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0007288567063883537</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.417327880237951e-06</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007302740151064483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>htail_tape</t>
+          <t>servo_rudder</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004042215769007339</v>
+        <v>0.004</v>
       </c>
       <c r="C11" t="n">
-        <v>4.042215769007338</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.639232334478258</v>
+        <v>0.05725210446311809</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0025</v>
+        <v>-0.0065</v>
       </c>
       <c r="G11" t="n">
-        <v>3.823044653954983e-05</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8.504578097640044e-07</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3.906424530020555e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>servo_elevator</t>
+          <t>servo_aileron_R</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3901,13 +3901,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03295706339148154</v>
+        <v>0.0687025253557417</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.280000002797276</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0065</v>
+        <v>0.05637155509160542</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3922,7 +3922,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>servo_rudder</t>
+          <t>servo_aileron_L</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -3932,13 +3932,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03295706339148154</v>
+        <v>0.0687025253557417</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.280000002797276</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0065</v>
+        <v>0.05637155509160542</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3953,69 +3953,69 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>servo_aileron_R</t>
+          <t>wing mount R fwd</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.004</v>
+        <v>0.003953389544688026</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3.953389544688026</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03954847606977785</v>
+        <v>0.0833711044631181</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4535418557331994</v>
+        <v>0.03743439716312056</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08697166604634926</v>
+        <v>0.009600694226414574</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.315463615237264e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.353146406408094e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.448142662848282e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>servo_aileron_L</t>
+          <t>wing mount R aft</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004</v>
+        <v>0.003953389544688026</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3.953389544688026</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03954847606977785</v>
+        <v>0.1260021044631181</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4535418557331994</v>
+        <v>0.03743439716312056</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08697166604634926</v>
+        <v>0.009600694226414574</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.315463615237264e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.353146406408094e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.448142662848282e-06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wing mount R fwd</t>
+          <t>wing mount L fwd</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -4025,10 +4025,10 @@
         <v>3.953389544688026</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05907606339148155</v>
+        <v>0.0833711044631181</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03743439716312056</v>
+        <v>-0.03743439716312056</v>
       </c>
       <c r="F16" t="n">
         <v>0.009600694226414574</v>
@@ -4046,7 +4046,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wing mount R aft</t>
+          <t>wing mount L aft</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4056,10 +4056,10 @@
         <v>3.953389544688026</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1017070633914816</v>
+        <v>0.1260021044631181</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03743439716312056</v>
+        <v>-0.03743439716312056</v>
       </c>
       <c r="F17" t="n">
         <v>0.009600694226414574</v>
@@ -4077,116 +4077,116 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wing mount L fwd</t>
+          <t>tail module core</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.003953389544688026</v>
+        <v>0.001795290858725762</v>
       </c>
       <c r="C18" t="n">
-        <v>3.953389544688026</v>
+        <v>1.795290858725762</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05907606339148155</v>
+        <v>0.5481501614845966</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.03743439716312056</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.009600694226414574</v>
+        <v>-0.0005</v>
       </c>
       <c r="G18" t="n">
-        <v>2.315463615237264e-06</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.353146406408094e-07</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.448142662848282e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>wing mount L aft</t>
+          <t>wing_tape_bottom</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.003953389544688026</v>
+        <v>0.001225000012238082</v>
       </c>
       <c r="C19" t="n">
-        <v>3.953389544688026</v>
+        <v>1.225000012238082</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1017070633914816</v>
+        <v>0.03112605223155904</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.03743439716312056</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.009600694226414574</v>
+        <v>0.01949361096612669</v>
       </c>
       <c r="G19" t="n">
-        <v>2.315463615237264e-06</v>
+        <v>1.250521043333296e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.353146406408094e-07</v>
+        <v>8.463590583745587e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>2.448142662848282e-06</v>
+        <v>1.335156604129082e-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>htail_surfaces</t>
+          <t>wing_tape_top</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.003404064234002415</v>
+        <v>0.001225000012238082</v>
       </c>
       <c r="C20" t="n">
-        <v>3.404064234002415</v>
+        <v>1.225000012238082</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6563387487387511</v>
+        <v>0.03112605223155904</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0025</v>
+        <v>0.02536361096612669</v>
       </c>
       <c r="G20" t="n">
-        <v>3.219047890710453e-05</v>
+        <v>1.250521043333296e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>2.014298414358566e-06</v>
+        <v>8.463590583745587e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>3.419967122511209e-05</v>
+        <v>1.335156604129082e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tail module core</t>
+          <t>linkages</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.001795290858725762</v>
+        <v>0.001</v>
       </c>
       <c r="C21" t="n">
-        <v>1.795290858725762</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6500813144429484</v>
+        <v>0.2499999972703895</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -4201,32 +4201,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vtail_tape</t>
+          <t>tail support</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001555880947722772</v>
+        <v>0.001</v>
       </c>
       <c r="C22" t="n">
-        <v>1.555880947722772</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6392323344782579</v>
+        <v>0.491059994540779</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06882837282178215</v>
+        <v>-0.00587</v>
       </c>
       <c r="G22" t="n">
-        <v>2.183455808584203e-06</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.503784778979926e-06</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3.279547578220985e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4236,152 +4236,152 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.001008652301452796</v>
+        <v>0.0008204052537426062</v>
       </c>
       <c r="C23" t="n">
-        <v>1.008652301452796</v>
+        <v>0.8204052537426062</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6524618575989103</v>
+        <v>0.5422291207416386</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06882837282178215</v>
+        <v>0.06246670183897435</v>
       </c>
       <c r="G23" t="n">
-        <v>1.413783524262231e-06</v>
+        <v>9.354274988965154e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>1.766283793795177e-06</v>
+        <v>1.168515243695261e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>3.54013247985125e-07</v>
+        <v>2.343183526793591e-07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>linkages</t>
+          <t>htail mount R</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.001</v>
+        <v>0.0007628808864265929</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.7628808864265929</v>
       </c>
       <c r="D24" t="n">
-        <v>0.307116167239129</v>
+        <v>0.5530501614845966</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.01469135802469136</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0.00325</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>6.956787515816837e-08</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.36523891966759e-08</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>8.29341840224343e-08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tail support</t>
+          <t>htail mount L</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.001</v>
+        <v>0.0007628808864265929</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0.7628808864265929</v>
       </c>
       <c r="D25" t="n">
-        <v>0.605292334478258</v>
+        <v>0.5530501614845966</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0.01469135802469136</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.00587</v>
+        <v>-0.00325</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>6.956787515816837e-08</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1.36523891966759e-08</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>8.29341840224343e-08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>htail mount R</t>
+          <t>htail_tape_bottom</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0007628808864265929</v>
+        <v>0.0007125016694381755</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7628808864265929</v>
+        <v>0.7125016694381755</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6549813144429484</v>
+        <v>0.5305357803738437</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01469135802469136</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.00325</v>
+        <v>-0.003935</v>
       </c>
       <c r="G26" t="n">
-        <v>6.956787515816837e-08</v>
+        <v>9.842385238354917e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>1.36523891966759e-08</v>
+        <v>5.938517351835922e-09</v>
       </c>
       <c r="I26" t="n">
-        <v>8.29341840224343e-08</v>
+        <v>9.848321748827051e-06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>htail mount L</t>
+          <t>htail_tape_top</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0007628808864265929</v>
+        <v>0.0007125016694381755</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7628808864265929</v>
+        <v>0.7125016694381755</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6549813144429484</v>
+        <v>0.5305357803738437</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.01469135802469136</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.00325</v>
+        <v>-0.001065</v>
       </c>
       <c r="G27" t="n">
-        <v>6.956787515816837e-08</v>
+        <v>9.842385238354917e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>1.36523891966759e-08</v>
+        <v>5.938517351835922e-09</v>
       </c>
       <c r="I27" t="n">
-        <v>8.29341840224343e-08</v>
+        <v>9.848321748827051e-06</v>
       </c>
     </row>
     <row r="28">
@@ -4397,7 +4397,7 @@
         <v>0.6789473684210525</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6443813144429483</v>
+        <v>0.5424501614845966</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>0.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05795706339148154</v>
+        <v>0.08225210446311809</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4449,63 +4449,125 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ballast</t>
+          <t>vtail_tape_side_a</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-9.999777840203466e-09</v>
+        <v>0.0002046334564364102</v>
       </c>
       <c r="C30" t="n">
-        <v>-9.999777840203467e-06</v>
+        <v>0.2046334564364102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0497490786629821</v>
+        <v>0.5305357803738437</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.001565</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.06246670183897435</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.331702364587007e-07</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.348752270702196e-07</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.705566995754566e-09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>vtail_tape_side_b</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0002046334564364102</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.2046334564364102</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.5305357803738437</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.001565</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.06246670183897435</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.331702364587007e-07</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.348752270702196e-07</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.705566995754566e-09</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ballast</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-9.999817078172689e-09</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-9.999817078172688e-06</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.08417021565831362</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>wing_spar_slot_void</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>-0.0005986752495678232</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.5986752495678233</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.03295706339148154</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.05598229127896828</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-6.414018755270692e-05</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-1.596467332180862e-09</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-6.414018755270692e-05</v>
+      <c r="B33" t="n">
+        <v>-0.0003696000036924043</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.3696000036924043</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.05725210446311809</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.03685722193225339</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-1.509249325232445e-05</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-9.856000098464112e-10</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-1.509249325232445e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4541,7 +4603,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04767240565569973</v>
+        <v>0.04802903523890088</v>
       </c>
     </row>
     <row r="3">
@@ -4551,7 +4613,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.160229094102044</v>
+        <v>0.9052593767455703</v>
       </c>
     </row>
     <row r="4">
@@ -4561,7 +4623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.838897085946809e-05</v>
+        <v>6.988755252935022e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4571,7 +4633,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009877598291727076</v>
+        <v>0.003220249934487996</v>
       </c>
     </row>
     <row r="6">
@@ -4581,7 +4643,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0450745529961341</v>
+        <v>0.0490958063780883</v>
       </c>
     </row>
     <row r="7">
@@ -4591,7 +4653,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.033785203753753e-05</v>
+        <v>2.242047255490709e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4601,7 +4663,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4709472823739185</v>
+        <v>0.385007216173159</v>
       </c>
     </row>
     <row r="9">
@@ -4611,7 +4673,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.099542122905522</v>
+        <v>3.946169266351761</v>
       </c>
     </row>
     <row r="10">
@@ -4621,7 +4683,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-5.232680367490593e-06</v>
+        <v>1.413635694832638e-06</v>
       </c>
     </row>
     <row r="11">
@@ -4631,7 +4693,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.001771554759333327</v>
+        <v>0.001138272616552083</v>
       </c>
     </row>
     <row r="12">
@@ -4641,7 +4703,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3588580574469535</v>
+        <v>1.498776004896007</v>
       </c>
     </row>
     <row r="13">
@@ -4651,7 +4713,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-3.159417150122579e-05</v>
+        <v>3.462100883755426e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4661,7 +4723,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-8.340102897045682e-18</v>
+        <v>-3.892433734384674e-18</v>
       </c>
     </row>
     <row r="15">
@@ -4671,7 +4733,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.876373636832613e-22</v>
+        <v>1.040183806542279e-22</v>
       </c>
     </row>
     <row r="16">
@@ -4681,7 +4743,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2257387672433209</v>
+        <v>-0.1499341988688302</v>
       </c>
     </row>
     <row r="17">
@@ -4691,7 +4753,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3894082049153679</v>
+        <v>-0.26322800055028</v>
       </c>
     </row>
     <row r="18">
@@ -4701,7 +4763,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.858358546548576e-19</v>
+        <v>8.365823057123388e-19</v>
       </c>
     </row>
     <row r="19">
@@ -4711,7 +4773,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1290898860430167</v>
+        <v>0.1114463936623395</v>
       </c>
     </row>
     <row r="20">
@@ -4721,7 +4783,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
     </row>
     <row r="21">
@@ -4731,7 +4793,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-4.124145170162167e-19</v>
+        <v>-4.563704725340319e-19</v>
       </c>
     </row>
     <row r="22">
@@ -4741,7 +4803,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.193544057494299</v>
+        <v>-0.1301655956246374</v>
       </c>
     </row>
     <row r="23">
@@ -4751,7 +4813,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7344244084966796</v>
+        <v>-0.5395584074505652</v>
       </c>
     </row>
     <row r="24">
@@ -4761,7 +4823,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-2.836402722342722e-18</v>
+        <v>-1.3578453863819e-18</v>
       </c>
     </row>
     <row r="25">
@@ -4771,7 +4833,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04795201441572707</v>
+        <v>0.03502875234481945</v>
       </c>
     </row>
     <row r="26">
@@ -4781,7 +4843,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.001000009991657225</v>
+        <v>-1.009987835178577e-06</v>
       </c>
     </row>
     <row r="27">
@@ -4791,7 +4853,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2549770553146526</v>
+        <v>-0.7892338919851279</v>
       </c>
     </row>
     <row r="28">
@@ -4801,7 +4863,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-3.297409304079991e-06</v>
+        <v>1.940823624861621e-06</v>
       </c>
     </row>
     <row r="29">
@@ -4811,7 +4873,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.001220852054790783</v>
+        <v>0.002189207205635887</v>
       </c>
     </row>
     <row r="30">
@@ -4821,7 +4883,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-32.3166852935431</v>
+        <v>-7.533849191345507</v>
       </c>
     </row>
     <row r="31">
@@ -4831,7 +4893,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001812386630471469</v>
+        <v>-3.16190110333429e-05</v>
       </c>
     </row>
     <row r="32">
@@ -4841,7 +4903,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
     </row>
     <row r="33">
@@ -4851,7 +4913,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-3.150573600855849e-20</v>
+        <v>-4.14586001324609e-20</v>
       </c>
     </row>
     <row r="34">
@@ -4861,7 +4923,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.04784035854620862</v>
+        <v>0.03416412908632467</v>
       </c>
     </row>
     <row r="35">
@@ -4871,7 +4933,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.01686495428073289</v>
+        <v>-0.05499141773995983</v>
       </c>
     </row>
     <row r="36">
@@ -4881,7 +4943,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-4.868477354018845e-19</v>
+        <v>-6.859057942205118e-19</v>
       </c>
     </row>
     <row r="37">
@@ -4891,7 +4953,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.04522999113009531</v>
+        <v>-0.05513066451968678</v>
       </c>
     </row>
     <row r="38">
@@ -4901,7 +4963,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1595474192096365</v>
+        <v>0.1723892536131114</v>
       </c>
     </row>
     <row r="39">
@@ -4911,7 +4973,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.03561027008343283</v>
+        <v>0.0688812103927496</v>
       </c>
     </row>
     <row r="40">
@@ -4921,7 +4983,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1239371491262036</v>
+        <v>0.1035080432203617</v>
       </c>
     </row>
     <row r="41">
@@ -4931,7 +4993,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0393900586001623</v>
+        <v>-0.04687932565982794</v>
       </c>
     </row>
     <row r="42">
@@ -4941,7 +5003,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0393900586001623</v>
+        <v>0.04687932565982794</v>
       </c>
     </row>
     <row r="43">
@@ -4951,7 +5013,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1595474192096365</v>
+        <v>-0.1723892536131114</v>
       </c>
     </row>
     <row r="44">
@@ -4961,7 +5023,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.576140797869869</v>
+        <v>1.381895478466654</v>
       </c>
     </row>
     <row r="45">
@@ -4971,7 +5033,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-1.293241993411458e-18</v>
+        <v>-7.683760514855735e-19</v>
       </c>
     </row>
     <row r="46">
@@ -4981,7 +5043,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.293241993411458e-18</v>
+        <v>7.683760514855735e-19</v>
       </c>
     </row>
     <row r="47">
@@ -4991,7 +5053,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.071830780402675e-19</v>
+        <v>-1.808423270124363e-19</v>
       </c>
     </row>
     <row r="48">
@@ -5001,7 +5063,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-2.791220360844868e-17</v>
+        <v>-1.397100197560465e-17</v>
       </c>
     </row>
     <row r="49">
@@ -5013,11 +5075,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0005059730682710907,
+	L=0.0005904382621664052,
 	Y=0.0,
-	D=0.0013932562610853177,
+	D=0.0012589771690821355,
 	l_b=0.0,
-	m_b=-0.00011151866774732061,
+	m_b=-6.552338160818865e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -5031,7 +5093,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.293241993411458e-18</v>
+        <v>-7.683760514855735e-19</v>
       </c>
     </row>
     <row r="51">
@@ -5041,7 +5103,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0004412000506197723</v>
+        <v>-8.301831523082378e-07</v>
       </c>
     </row>
     <row r="52">
@@ -5051,7 +5113,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.556860645294556e-17</v>
+        <v>6.470639226974886e-18</v>
       </c>
     </row>
     <row r="53">
@@ -5063,29 +5125,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=1.3114409056669936,
+	L=1.0956757227437843,
 	Y=0.0,
-	D=0.0971406265853706,
+	D=0.07825480540132544,
 	l_b=-0.0,
-	m_b=0.13258212937614866,
+	m_b=0.1079741847549681,
 	n_b=-0.0,
-	span_effective=1.133987507196419, oswalds_efficiency=0.7831411536571873,
+	span_effective=0.700082034708293, oswalds_efficiency=0.8165703158185763,
 ), AeroComponentResults(
-	L=0.26419391913460405,
+	L=0.28562931746070264,
 	Y=0.0,
-	D=0.022476225442635032,
+	D=0.021467253789769394,
 	l_b=-0.0,
-	m_b=-0.13292305061850596,
+	m_b=-0.10794220143671768,
 	n_b=-0.0,
-	span_effective=0.3368513140839449, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.4071438111075289, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-2.710505431213761e-20,
-	Y=-2.7912203608448677e-17,
-	D=0.0029270408371126775,
-	l_b=-1.293241993411458e-18,
-	m_b=1.123985948484327e-05,
-	n_b=1.5568606452945562e-17,
-	span_effective=0.1296567456435643, oswalds_efficiency=0.8232692748986458,
+	L=2.710505431213761e-20,
+	Y=-1.3971001975604652e-17,
+	D=0.002527006860184775,
+	l_b=-7.6837605148557345e-19,
+	m_b=3.270988020545509e-05,
+	n_b=6.4706392269748856e-18,
+	span_effective=0.11693340367794869, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5097,7 +5159,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1379225672868539</v>
+        <v>0.1899192631330574</v>
       </c>
     </row>
     <row r="55">
@@ -5107,7 +5169,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3753336127683418</v>
+        <v>0.3060807352752326</v>
       </c>
     </row>
     <row r="56">
@@ -5117,7 +5179,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.04767240565569973</v>
+        <v>0.04802903523890088</v>
       </c>
     </row>
     <row r="57">
@@ -5127,7 +5189,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.160229094102044</v>
+        <v>0.9052593767455703</v>
       </c>
     </row>
     <row r="58">
@@ -5137,7 +5199,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.838897085946809e-05</v>
+        <v>6.988755252935022e-06</v>
       </c>
     </row>
     <row r="59">
@@ -5147,7 +5209,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.009877598291727076</v>
+        <v>0.003220249934487996</v>
       </c>
     </row>
     <row r="60">
@@ -5157,7 +5219,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0450745529961341</v>
+        <v>0.0490958063780883</v>
       </c>
     </row>
     <row r="61">
@@ -5167,7 +5229,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>8.033785203753753e-05</v>
+        <v>2.242047255490709e-05</v>
       </c>
     </row>
     <row r="62">
@@ -5177,7 +5239,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4709472823739185</v>
+        <v>0.385007216173159</v>
       </c>
     </row>
     <row r="63">
@@ -5187,7 +5249,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5.099542122905522</v>
+        <v>3.946169266351761</v>
       </c>
     </row>
     <row r="64">
@@ -5197,7 +5259,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-5.232680367490593e-06</v>
+        <v>1.413635694832638e-06</v>
       </c>
     </row>
     <row r="65">
@@ -5207,7 +5269,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.001771554759333327</v>
+        <v>0.001138272616552083</v>
       </c>
     </row>
     <row r="66">
@@ -5217,7 +5279,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3588580574469535</v>
+        <v>1.498776004896007</v>
       </c>
     </row>
     <row r="67">
@@ -5227,7 +5289,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-3.159417150122579e-05</v>
+        <v>3.462100883755426e-05</v>
       </c>
     </row>
     <row r="68">
@@ -5237,7 +5299,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-8.340102897045682e-18</v>
+        <v>-3.892433734384674e-18</v>
       </c>
     </row>
     <row r="69">
@@ -5247,7 +5309,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.876373636832613e-22</v>
+        <v>1.040183806542279e-22</v>
       </c>
     </row>
     <row r="70">
@@ -5257,7 +5319,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.2257387672433209</v>
+        <v>-0.1499341988688302</v>
       </c>
     </row>
     <row r="71">
@@ -5267,7 +5329,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.3894082049153679</v>
+        <v>-0.26322800055028</v>
       </c>
     </row>
     <row r="72">
@@ -5277,7 +5339,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4.858358546548576e-19</v>
+        <v>8.365823057123388e-19</v>
       </c>
     </row>
     <row r="73">
@@ -5287,7 +5349,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1290898860430167</v>
+        <v>0.1114463936623395</v>
       </c>
     </row>
     <row r="74">
@@ -5297,7 +5359,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
     </row>
     <row r="75">
@@ -5307,7 +5369,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-4.124145170162167e-19</v>
+        <v>-4.563704725340319e-19</v>
       </c>
     </row>
     <row r="76">
@@ -5317,7 +5379,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.193544057494299</v>
+        <v>-0.1301655956246374</v>
       </c>
     </row>
     <row r="77">
@@ -5327,7 +5389,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7344244084966796</v>
+        <v>-0.5395584074505652</v>
       </c>
     </row>
     <row r="78">
@@ -5337,7 +5399,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.836402722342722e-18</v>
+        <v>-1.3578453863819e-18</v>
       </c>
     </row>
     <row r="79">
@@ -5347,7 +5409,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.04795201441572707</v>
+        <v>0.03502875234481945</v>
       </c>
     </row>
     <row r="80">
@@ -5357,7 +5419,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.001000009991657225</v>
+        <v>-1.009987835178577e-06</v>
       </c>
     </row>
     <row r="81">
@@ -5367,7 +5429,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.2549770553146526</v>
+        <v>-0.7892338919851279</v>
       </c>
     </row>
     <row r="82">
@@ -5377,7 +5439,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.297409304079991e-06</v>
+        <v>1.940823624861621e-06</v>
       </c>
     </row>
     <row r="83">
@@ -5387,7 +5449,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.001220852054790783</v>
+        <v>0.002189207205635887</v>
       </c>
     </row>
     <row r="84">
@@ -5397,7 +5459,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-32.3166852935431</v>
+        <v>-7.533849191345507</v>
       </c>
     </row>
     <row r="85">
@@ -5407,7 +5469,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.0001812386630471469</v>
+        <v>-3.16190110333429e-05</v>
       </c>
     </row>
     <row r="86">
@@ -5417,7 +5479,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
     </row>
     <row r="87">
@@ -5427,7 +5489,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-3.150573600855849e-20</v>
+        <v>-4.14586001324609e-20</v>
       </c>
     </row>
     <row r="88">
@@ -5437,7 +5499,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.04784035854620862</v>
+        <v>0.03416412908632467</v>
       </c>
     </row>
     <row r="89">
@@ -5447,7 +5509,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.01686495428073289</v>
+        <v>-0.05499141773995983</v>
       </c>
     </row>
     <row r="90">
@@ -5457,7 +5519,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-4.868477354018845e-19</v>
+        <v>-6.859057942205118e-19</v>
       </c>
     </row>
     <row r="91">
@@ -5467,7 +5529,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.04522999113009531</v>
+        <v>-0.05513066451968678</v>
       </c>
     </row>
     <row r="92">
@@ -5477,7 +5539,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1595474192096365</v>
+        <v>0.1723892536131114</v>
       </c>
     </row>
     <row r="93">
@@ -5487,7 +5549,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.03561027008343283</v>
+        <v>0.0688812103927496</v>
       </c>
     </row>
     <row r="94">
@@ -5497,7 +5559,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.1239371491262036</v>
+        <v>0.1035080432203617</v>
       </c>
     </row>
     <row r="95">
@@ -5507,7 +5569,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.0393900586001623</v>
+        <v>-0.04687932565982794</v>
       </c>
     </row>
     <row r="96">
@@ -5517,7 +5579,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0393900586001623</v>
+        <v>0.04687932565982794</v>
       </c>
     </row>
     <row r="97">
@@ -5527,7 +5589,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.1595474192096365</v>
+        <v>-0.1723892536131114</v>
       </c>
     </row>
     <row r="98">
@@ -5537,7 +5599,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.576140797869869</v>
+        <v>1.381895478466654</v>
       </c>
     </row>
     <row r="99">
@@ -5547,7 +5609,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.293241993411458e-18</v>
+        <v>-7.683760514855735e-19</v>
       </c>
     </row>
     <row r="100">
@@ -5557,7 +5619,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.293241993411458e-18</v>
+        <v>7.683760514855735e-19</v>
       </c>
     </row>
     <row r="101">
@@ -5567,7 +5629,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-1.071830780402675e-19</v>
+        <v>-1.808423270124363e-19</v>
       </c>
     </row>
     <row r="102">
@@ -5577,7 +5639,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-2.791220360844868e-17</v>
+        <v>-1.397100197560465e-17</v>
       </c>
     </row>
     <row r="103">
@@ -5589,11 +5651,11 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0005059730682710907,
+	L=0.0005904382621664052,
 	Y=0.0,
-	D=0.0013932562610853177,
+	D=0.0012589771690821355,
 	l_b=0.0,
-	m_b=-0.00011151866774732061,
+	m_b=-6.552338160818865e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -5607,7 +5669,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-1.293241993411458e-18</v>
+        <v>-7.683760514855735e-19</v>
       </c>
     </row>
     <row r="105">
@@ -5617,7 +5679,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0004412000506197723</v>
+        <v>-8.301831523082378e-07</v>
       </c>
     </row>
     <row r="106">
@@ -5627,7 +5689,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.556860645294556e-17</v>
+        <v>6.470639226974886e-18</v>
       </c>
     </row>
     <row r="107">
@@ -5639,29 +5701,29 @@
       <c r="B107" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=1.3114409056669936,
+	L=1.0956757227437843,
 	Y=0.0,
-	D=0.0971406265853706,
+	D=0.07825480540132544,
 	l_b=-0.0,
-	m_b=0.13258212937614866,
+	m_b=0.1079741847549681,
 	n_b=-0.0,
-	span_effective=1.133987507196419, oswalds_efficiency=0.7831411536571873,
+	span_effective=0.700082034708293, oswalds_efficiency=0.8165703158185763,
 ), AeroComponentResults(
-	L=0.26419391913460405,
+	L=0.28562931746070264,
 	Y=0.0,
-	D=0.022476225442635032,
+	D=0.021467253789769394,
 	l_b=-0.0,
-	m_b=-0.13292305061850596,
+	m_b=-0.10794220143671768,
 	n_b=-0.0,
-	span_effective=0.3368513140839449, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.4071438111075289, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-2.710505431213761e-20,
-	Y=-2.7912203608448677e-17,
-	D=0.0029270408371126775,
-	l_b=-1.293241993411458e-18,
-	m_b=1.123985948484327e-05,
-	n_b=1.5568606452945562e-17,
-	span_effective=0.1296567456435643, oswalds_efficiency=0.8232692748986458,
+	L=2.710505431213761e-20,
+	Y=-1.3971001975604652e-17,
+	D=0.002527006860184775,
+	l_b=-7.6837605148557345e-19,
+	m_b=3.270988020545509e-05,
+	n_b=6.4706392269748856e-18,
+	span_effective=0.11693340367794869, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5673,7 +5735,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.1379225672868539</v>
+        <v>0.1899192631330574</v>
       </c>
     </row>
     <row r="109">
@@ -5683,7 +5745,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.3753336127683418</v>
+        <v>0.3060807352752326</v>
       </c>
     </row>
   </sheetData>
@@ -5779,10 +5841,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.576140797869869</v>
+        <v>1.381895478466654</v>
       </c>
       <c r="C2" t="n">
-        <v>1.576140807849054</v>
+        <v>1.381895488457083</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -5797,16 +5859,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.979185255915013e-09</v>
+        <v>-9.990429816753021e-09</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.979185255915013e-09</v>
+        <v>-9.990429816753021e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.331404660179773e-09</v>
+        <v>-7.229511855420815e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -5819,7 +5881,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1595474192096365</v>
+        <v>0.1723892536131114</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -5837,16 +5899,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.1585474192096365</v>
+        <v>0.1713892536131114</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.1585474192096365</v>
+        <v>0.1713892536131114</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1585474192096365</v>
+        <v>0.1713892536131114</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -5859,13 +5921,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.001000009991657225</v>
+        <v>-1.009987835178577e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.001</v>
+        <v>-1e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001</v>
+        <v>1e-06</v>
       </c>
       <c r="E4" t="n">
         <v>1e-06</v>
@@ -5879,18 +5941,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-9.991657225335779e-09</v>
+        <v>-9.987835178576707e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002000009991657226</v>
+        <v>2.009987835178577e-06</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.991657225335779e-09</v>
+        <v>-9.987835178576707e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.991657225335779e-09</v>
+        <v>-9.987835178576707e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -5903,7 +5965,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -5923,22 +5985,22 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
       <c r="I5" t="n">
-        <v>3.356225712756503e-19</v>
+        <v>3.011763798644184e-19</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
       <c r="K5" t="n">
-        <v>3.356225712756503e-19</v>
+        <v>3.011763798644184e-19</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009999999999999996</v>
+        <v>0.0009999999999999998</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0009999999999999996</v>
+        <v>0.0009999999999999998</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -5951,7 +6013,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -5971,22 +6033,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.040369672139024e-18</v>
+        <v>-2.536262932741319e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009999999999999959</v>
+        <v>0.0009999999999999974</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009999999999999959</v>
+        <v>0.0009999999999999974</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -5999,7 +6061,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4709472823739185</v>
+        <v>0.385007216173159</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -6018,15 +6080,15 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.7290527176260815</v>
+        <v>0.8149927838268409</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.7290527176260815</v>
+        <v>0.8149927838268409</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6075439313550679</v>
+        <v>0.6791606531890342</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -6039,10 +6101,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.878823522672636</v>
+        <v>8.016134703895203</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
@@ -6057,16 +6119,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.878823522672636</v>
+        <v>2.016134703895203</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>1.878823522672636</v>
+        <v>2.016134703895203</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1901869709850162</v>
+        <v>0.2515095839040132</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -6079,7 +6141,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.38438048650968</v>
+        <v>8.489403328184636</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -6097,16 +6159,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8.384380486509679</v>
+        <v>6.489403328184636</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>8.384380486509679</v>
+        <v>6.489403328184636</v>
       </c>
       <c r="M9" t="n">
-        <v>0.807403050899551</v>
+        <v>0.7644121827313772</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -6119,7 +6181,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.38438048650968</v>
+        <v>8.489403328184636</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -6138,15 +6200,15 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>9.615619513490321</v>
+        <v>11.51059667181536</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>9.615619513490321</v>
+        <v>11.51059667181536</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4807809756745161</v>
+        <v>0.5755298335907681</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -6159,7 +6221,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54149.30565142133</v>
+        <v>94066.68509676102</v>
       </c>
       <c r="C11" t="n">
         <v>20000</v>
@@ -6177,16 +6239,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>34149.30565142133</v>
+        <v>74066.68509676102</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>34149.30565142133</v>
+        <v>74066.68509676102</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6306508502851867</v>
+        <v>0.7873848751082582</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -6199,7 +6261,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04999999003231618</v>
+        <v>0.2000000098107236</v>
       </c>
       <c r="C12" t="n">
         <v>0.05</v>
@@ -6217,19 +6279,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-9.967683824163576e-09</v>
+        <v>0.1500000098107235</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-9.967683824163576e-09</v>
+        <v>0.1500000098107235</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.967683824163576e-09</v>
+        <v>0.1500000098107235</v>
       </c>
       <c r="N12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6239,7 +6301,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04999999003231618</v>
+        <v>0.2000000098107236</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
@@ -6258,18 +6320,18 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.1500000099676838</v>
+        <v>-9.810723539116495e-09</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.1500000099676838</v>
+        <v>-9.810723539116495e-09</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1500000099676838</v>
+        <v>-9.810723539116495e-09</v>
       </c>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6279,7 +6341,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8708157105346108</v>
+        <v>0.5558482021720921</v>
       </c>
       <c r="C14" t="n">
         <v>0.5</v>
@@ -6297,16 +6359,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.3708157105346108</v>
+        <v>0.05584820217209208</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.3708157105346108</v>
+        <v>0.05584820217209208</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3708157105346108</v>
+        <v>0.05584820217209208</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -6319,7 +6381,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8708157105346108</v>
+        <v>0.5558482021720921</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
@@ -6338,15 +6400,15 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.1291842894653892</v>
+        <v>0.4441517978279079</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.1291842894653892</v>
+        <v>0.4441517978279079</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1291842894653892</v>
+        <v>0.4441517978279079</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -6359,7 +6421,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02999999001463034</v>
+        <v>0.02999999002463568</v>
       </c>
       <c r="C16" t="n">
         <v>0.03</v>
@@ -6377,16 +6439,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.98536965959862e-09</v>
+        <v>-9.975364319292357e-09</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-9.98536965959862e-09</v>
+        <v>-9.975364319292357e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.98536965959862e-09</v>
+        <v>-9.975364319292357e-09</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -6399,7 +6461,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02999999001463034</v>
+        <v>0.02999999002463568</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
@@ -6418,15 +6480,15 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.05000000998536966</v>
+        <v>0.05000000997536432</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.05000000998536966</v>
+        <v>0.05000000997536432</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05000000998536966</v>
+        <v>0.05000000997536432</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -6439,7 +6501,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.193544057494299</v>
+        <v>-0.1301655956246374</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -6458,15 +6520,15 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.193544057494299</v>
+        <v>0.1301655956246374</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.193544057494299</v>
+        <v>0.1301655956246374</v>
       </c>
       <c r="M18" t="n">
-        <v>0.193544057494299</v>
+        <v>0.1301655956246374</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -6479,7 +6541,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.04784035854620862</v>
+        <v>0.03416412908632467</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -6497,16 +6559,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.04784035854620862</v>
+        <v>0.03416412908632467</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0.04784035854620862</v>
+        <v>0.03416412908632467</v>
       </c>
       <c r="M19" t="n">
-        <v>0.04784035854620862</v>
+        <v>0.03416412908632467</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -6519,7 +6581,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.7344244084966796</v>
+        <v>-0.5395584074505652</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -6538,15 +6600,15 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.7343244084966796</v>
+        <v>0.5394584074505652</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.7343244084966796</v>
+        <v>0.5394584074505652</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7343244084966796</v>
+        <v>0.5394584074505652</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -6559,7 +6621,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.285495423909251</v>
+        <v>5.605487237063405</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -6591,7 +6653,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>98.60283000497498</v>
+        <v>163.0920617807786</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -6623,7 +6685,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0333204982427328</v>
+        <v>0.03437008016121631</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -6655,7 +6717,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.858744509246056e-05</v>
+        <v>5.326009071516924e-05</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -6674,15 +6736,15 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.007171412554907539</v>
+        <v>0.007146739909284831</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.007171412554907539</v>
+        <v>0.007146739909284831</v>
       </c>
       <c r="M24" t="n">
-        <v>0.007171412554907539</v>
+        <v>0.007146739909284831</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -6695,7 +6757,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.241122031492843e-05</v>
+        <v>2.191509007190641e-05</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
@@ -6714,15 +6776,15 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.007187588779685072</v>
+        <v>0.007178084909928093</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.007187588779685072</v>
+        <v>0.007178084909928093</v>
       </c>
       <c r="M25" t="n">
-        <v>0.007187588779685072</v>
+        <v>0.007178084909928093</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -6735,7 +6797,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.853351864525215e-06</v>
+        <v>2.826630830291486e-06</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -6754,15 +6816,15 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.007196146648135475</v>
+        <v>0.007197173369169708</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0.007196146648135475</v>
+        <v>0.007197173369169708</v>
       </c>
       <c r="M26" t="n">
-        <v>0.007196146648135475</v>
+        <v>0.007197173369169708</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -6775,7 +6837,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.35539781503875</v>
+        <v>5.181709548775771</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -6807,7 +6869,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4709472823739185</v>
+        <v>0.385007216173159</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -6835,11 +6897,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Turn curvature margin (diag)</t>
+          <t>Agility lateral margin (diag)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-19.49038331586958</v>
+        <v>-13.05653267986326</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -6871,7 +6933,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5.857412815436557</v>
+        <v>5.440485503569021</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -6903,7 +6965,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.001000009991657225</v>
+        <v>-1.009987835178577e-06</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -6935,7 +6997,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7344244084966796</v>
+        <v>-0.5395584074505652</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -6967,7 +7029,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100.3992550618949</v>
+        <v>171.0246568338559</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -6999,7 +7061,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>50.39925506566945</v>
+        <v>121.0246568464731</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -7031,7 +7093,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>100.3992550656695</v>
+        <v>171.0246568464731</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -7063,7 +7125,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.747393628933218e-16</v>
+        <v>6.677006654063078e-17</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -7095,7 +7157,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.228921909584063</v>
+        <v>1.112396518263171</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -7127,7 +7189,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.009559374285092e-15</v>
+        <v>1.305569024969542e-15</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -7159,7 +7221,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0004389233015415032</v>
+        <v>0.003385495155179471</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -7191,7 +7253,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0134740525633578</v>
+        <v>0.01628575244430116</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
@@ -7223,7 +7285,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1613246836757413</v>
+        <v>0.1338198671999475</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -7341,13 +7403,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.001000009991657225</v>
+        <v>-1.009987835178577e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.001</v>
+        <v>-1e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001</v>
+        <v>1e-06</v>
       </c>
       <c r="E2" t="n">
         <v>1e-06</v>
@@ -7361,18 +7423,18 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.991657225335779e-09</v>
+        <v>-9.987835178576707e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002000009991657226</v>
+        <v>2.009987835178577e-06</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.991657225335779e-09</v>
+        <v>-9.987835178576707e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.991657225335779e-09</v>
+        <v>-9.987835178576707e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -7385,7 +7447,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02999999001463034</v>
+        <v>0.02999999002463568</v>
       </c>
       <c r="C3" t="n">
         <v>0.03</v>
@@ -7403,16 +7465,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-9.98536965959862e-09</v>
+        <v>-9.975364319292357e-09</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-9.98536965959862e-09</v>
+        <v>-9.975364319292357e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.98536965959862e-09</v>
+        <v>-9.975364319292357e-09</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -7421,16 +7483,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Static margin minimum</t>
+          <t>Static margin maximum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04999999003231618</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>0.2000000098107236</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="E4" t="n">
         <v>1e-06</v>
       </c>
@@ -7442,17 +7504,17 @@
           <t>ineq</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>-9.967683824163576e-09</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>-9.810723539116495e-09</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.967683824163576e-09</v>
+        <v>-9.810723539116495e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.967683824163576e-09</v>
+        <v>-9.810723539116495e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -7465,10 +7527,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.576140797869869</v>
+        <v>1.381895478466654</v>
       </c>
       <c r="C5" t="n">
-        <v>1.576140807849054</v>
+        <v>1.381895488457083</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -7483,16 +7545,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-9.979185255915013e-09</v>
+        <v>-9.990429816753021e-09</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-9.979185255915013e-09</v>
+        <v>-9.990429816753021e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.331404660179773e-09</v>
+        <v>-7.229511855420815e-09</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -7505,7 +7567,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -7525,22 +7587,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.040369672139024e-18</v>
+        <v>-2.536262932741319e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>4.040369672139024e-18</v>
+        <v>2.536262932741319e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009999999999999959</v>
+        <v>0.0009999999999999974</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009999999999999959</v>
+        <v>0.0009999999999999974</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -7553,7 +7615,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -7573,22 +7635,22 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
       <c r="I7" t="n">
-        <v>3.356225712756503e-19</v>
+        <v>3.011763798644184e-19</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.356225712756503e-19</v>
+        <v>-3.011763798644184e-19</v>
       </c>
       <c r="K7" t="n">
-        <v>3.356225712756503e-19</v>
+        <v>3.011763798644184e-19</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009999999999999996</v>
+        <v>0.0009999999999999998</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009999999999999996</v>
+        <v>0.0009999999999999998</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -7605,7 +7667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7627,7 +7689,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -7647,7 +7709,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9996437460017515</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7657,7 +7719,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.9973159716987698</v>
       </c>
     </row>
     <row r="6">
@@ -7703,27 +7765,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[16]</t>
+          <t>iterations.alpha_du[1]</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.8695588035970125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[17]</t>
+          <t>iterations.alpha_du[2]</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.7453311880063755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[18]</t>
+          <t>iterations.alpha_du[3]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -7733,7 +7795,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[19]</t>
+          <t>iterations.alpha_du[4]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7743,47 +7805,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[1]</t>
+          <t>iterations.alpha_du[5]</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8539190474422188</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[2]</t>
+          <t>iterations.alpha_du[6]</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7534833341271718</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[3]</t>
+          <t>iterations.alpha_du[7]</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2140142787733328</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[4]</t>
+          <t>iterations.alpha_du[8]</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6978355822711707</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[5]</t>
+          <t>iterations.alpha_du[9]</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7793,17 +7855,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[6]</t>
+          <t>iterations.alpha_pr[0]</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6710454346374727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[7]</t>
+          <t>iterations.alpha_pr[10]</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -7813,7 +7875,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[8]</t>
+          <t>iterations.alpha_pr[11]</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7823,27 +7885,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[9]</t>
+          <t>iterations.alpha_pr[12]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0.990561915582554</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[0]</t>
+          <t>iterations.alpha_pr[13]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[10]</t>
+          <t>iterations.alpha_pr[14]</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -7853,7 +7915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[11]</t>
+          <t>iterations.alpha_pr[15]</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7863,1187 +7925,1189 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[12]</t>
+          <t>iterations.alpha_pr[1]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8219101484370761</v>
+        <v>0.1841698804006667</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[13]</t>
+          <t>iterations.alpha_pr[2]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0.1744191010923265</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[14]</t>
+          <t>iterations.alpha_pr[3]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.2747435512240049</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[15]</t>
+          <t>iterations.alpha_pr[4]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0.8138735300488935</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[16]</t>
+          <t>iterations.alpha_pr[5]</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0.9073522984905922</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[17]</t>
+          <t>iterations.alpha_pr[6]</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0.8195713998759652</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[18]</t>
+          <t>iterations.alpha_pr[7]</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0.756715670987304</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[19]</t>
+          <t>iterations.alpha_pr[8]</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0.8497056588344294</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[1]</t>
+          <t>iterations.alpha_pr[9]</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.2460284001538794</v>
+        <v>0.9762557900019193</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[2]</t>
+          <t>iterations.d_norm[0]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2036117121924281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[3]</t>
+          <t>iterations.d_norm[10]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.342399093149569</v>
+        <v>0.04433152731960267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[4]</t>
+          <t>iterations.d_norm[11]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.830821421419331</v>
+        <v>0.005889165940314859</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[5]</t>
+          <t>iterations.d_norm[12]</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.03599633996243668</v>
+        <v>0.04385908849175971</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[6]</t>
+          <t>iterations.d_norm[13]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0.2112783470201302</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[7]</t>
+          <t>iterations.d_norm[14]</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0.1135833105427513</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[8]</t>
+          <t>iterations.d_norm[15]</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0.05281005041817935</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[9]</t>
+          <t>iterations.d_norm[1]</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2.078634897574489</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iterations.d_norm[0]</t>
+          <t>iterations.d_norm[2]</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>4.193052402585394</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iterations.d_norm[10]</t>
+          <t>iterations.d_norm[3]</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.777820999575859</v>
+        <v>16.19596884554542</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iterations.d_norm[11]</t>
+          <t>iterations.d_norm[4]</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.958774445982449</v>
+        <v>1.882658903545234</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iterations.d_norm[12]</t>
+          <t>iterations.d_norm[5]</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.421341908808847</v>
+        <v>0.6450909206167239</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iterations.d_norm[13]</t>
+          <t>iterations.d_norm[6]</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3747503708840588</v>
+        <v>2.34780476720436</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iterations.d_norm[14]</t>
+          <t>iterations.d_norm[7]</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.02699634286897754</v>
+        <v>3.327814778762712</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iterations.d_norm[15]</t>
+          <t>iterations.d_norm[8]</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.01115063726234203</v>
+        <v>1.236876107552781</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iterations.d_norm[16]</t>
+          <t>iterations.d_norm[9]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1551844463137139</v>
+        <v>0.3071213350370104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iterations.d_norm[17]</t>
+          <t>iterations.inf_du[0]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0945296469733071</v>
+        <v>0.9545759034129052</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iterations.d_norm[18]</t>
+          <t>iterations.inf_du[10]</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.03356459456066948</v>
+        <v>0.0001452643769042083</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iterations.d_norm[19]</t>
+          <t>iterations.inf_du[11]</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.005315569397794031</v>
+        <v>0.01061171300692143</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iterations.d_norm[1]</t>
+          <t>iterations.inf_du[12]</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.046219236545849</v>
+        <v>0.003653837950373884</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iterations.d_norm[2]</t>
+          <t>iterations.inf_du[13]</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.349341328959048</v>
+        <v>6.430315565353339e-06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iterations.d_norm[3]</t>
+          <t>iterations.inf_du[14]</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11.70538093003743</v>
+        <v>2.114267019237559e-07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>iterations.d_norm[4]</t>
+          <t>iterations.inf_du[15]</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23.23479789684333</v>
+        <v>4.674262754633673e-09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iterations.d_norm[5]</t>
+          <t>iterations.inf_du[1]</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>26.44872849336223</v>
+        <v>16.5271815113038</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iterations.d_norm[6]</t>
+          <t>iterations.inf_du[2]</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6.707828192528886</v>
+        <v>38.43302884143124</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iterations.d_norm[7]</t>
+          <t>iterations.inf_du[3]</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4.319355787330189</v>
+        <v>60.40652897372787</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>iterations.d_norm[8]</t>
+          <t>iterations.inf_du[4]</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.942009852974985</v>
+        <v>6.273314933237373</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iterations.d_norm[9]</t>
+          <t>iterations.inf_du[5]</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5.020389371940222</v>
+        <v>1.275006790258558</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iterations.inf_du[0]</t>
+          <t>iterations.inf_du[6]</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9503702043616177</v>
+        <v>1.290709283206298</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iterations.inf_du[10]</t>
+          <t>iterations.inf_du[7]</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3204346597257484</v>
+        <v>2.956557412044539</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iterations.inf_du[11]</t>
+          <t>iterations.inf_du[8]</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.2019148614787909</v>
+        <v>2.706440096871027</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iterations.inf_du[12]</t>
+          <t>iterations.inf_du[9]</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3508788475118894</v>
+        <v>0.0417606889005171</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iterations.inf_du[13]</t>
+          <t>iterations.inf_pr[0]</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.006854985734676688</v>
+        <v>0.09696628842104291</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iterations.inf_du[14]</t>
+          <t>iterations.inf_pr[10]</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.001267627981903274</v>
+        <v>1.857549047912244e-06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iterations.inf_du[15]</t>
+          <t>iterations.inf_pr[11]</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0001118062608678194</v>
+        <v>4.727152697059367e-09</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iterations.inf_du[16]</t>
+          <t>iterations.inf_pr[12]</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.001653326513569198</v>
+        <v>7.644981564469688e-09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iterations.inf_du[17]</t>
+          <t>iterations.inf_pr[13]</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9.940567864674676e-05</v>
+        <v>3.96880836528446e-09</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iterations.inf_du[18]</t>
+          <t>iterations.inf_pr[14]</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3.417687040041528e-07</v>
+        <v>6.317296815869233e-11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iterations.inf_du[19]</t>
+          <t>iterations.inf_pr[15]</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2.497486661923176e-10</v>
+        <v>3.61002061577409e-11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>iterations.inf_du[1]</t>
+          <t>iterations.inf_pr[1]</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9.260404910173037</v>
+        <v>0.08056408675789051</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>iterations.inf_du[2]</t>
+          <t>iterations.inf_pr[2]</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.55300224853946</v>
+        <v>0.06724205920869081</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>iterations.inf_du[3]</t>
+          <t>iterations.inf_pr[3]</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15.57613339624941</v>
+        <v>0.04725390342973679</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iterations.inf_du[4]</t>
+          <t>iterations.inf_pr[4]</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2.82853663554399</v>
+        <v>0.04365719331379392</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iterations.inf_du[5]</t>
+          <t>iterations.inf_pr[5]</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>413.2066106562972</v>
+        <v>0.001928854673058922</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iterations.inf_du[6]</t>
+          <t>iterations.inf_pr[6]</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>126.9980968656988</v>
+        <v>0.008694077208617479</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iterations.inf_du[7]</t>
+          <t>iterations.inf_pr[7]</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5.245434923090848</v>
+        <v>0.01270562742753967</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iterations.inf_du[8]</t>
+          <t>iterations.inf_pr[8]</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3.424508335815212</v>
+        <v>0.002809957848590727</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iterations.inf_du[9]</t>
+          <t>iterations.inf_pr[9]</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.39258621832183</v>
+        <v>0.000184637957667988</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[0]</t>
+          <t>iterations.mu[0]</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6547093457608195</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[10]</t>
+          <t>iterations.mu[10]</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.02301975969031567</v>
+        <v>1.90217338042289e-06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[11]</t>
+          <t>iterations.mu[11]</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0167144181232679</v>
+        <v>4.21420113508245e-07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[12]</t>
+          <t>iterations.mu[12]</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.007316246659314629</v>
+        <v>4.13890221288537e-08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[13]</t>
+          <t>iterations.mu[13]</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0006385213413580004</v>
+        <v>2.658123934185443e-09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[14]</t>
+          <t>iterations.mu[14]</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0001170308175108478</v>
+        <v>7.155658304627041e-11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[15]</t>
+          <t>iterations.mu[15]</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1.786981766863788e-05</v>
+        <v>9.999999999999999e-12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[16]</t>
+          <t>iterations.mu[1]</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.334539981606708e-06</v>
+        <v>0.1980754861799579</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[17]</t>
+          <t>iterations.mu[2]</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.289377429131155e-08</v>
+        <v>9.529436303557169e-07</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[18]</t>
+          <t>iterations.mu[3]</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.824988771215175e-11</v>
+        <v>0.06531265460594078</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[19]</t>
+          <t>iterations.mu[4]</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1.661901172234082e-11</v>
+        <v>0.07239469536400245</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[1]</t>
+          <t>iterations.mu[5]</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4866984663242357</v>
+        <v>0.00815004317151272</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[2]</t>
+          <t>iterations.mu[6]</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.3943300441792879</v>
+        <v>0.002634337937762354</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[3]</t>
+          <t>iterations.mu[7]</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.2782183815030352</v>
+        <v>0.0008211406080667111</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[4]</t>
+          <t>iterations.mu[8]</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.3679595835812766</v>
+        <v>0.0003185986999670291</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[5]</t>
+          <t>iterations.mu[9]</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.3582163905394466</v>
+        <v>4.224445327306245e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[6]</t>
+          <t>iterations.obj[0]</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5173753928316316</v>
+        <v>1.891556931836755</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[7]</t>
+          <t>iterations.obj[10]</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.1599567494131211</v>
+        <v>1.791866130647261</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[8]</t>
+          <t>iterations.obj[11]</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.2136015980957993</v>
+        <v>1.791856049859151</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[9]</t>
+          <t>iterations.obj[12]</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.07793451949355479</v>
+        <v>1.791852928964671</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iterations.mu[0]</t>
+          <t>iterations.obj[13]</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>1.791852639517245</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iterations.mu[10]</t>
+          <t>iterations.obj[14]</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.008292547098657869</v>
+        <v>1.791852611769461</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iterations.mu[11]</t>
+          <t>iterations.obj[15]</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.002563628880309917</v>
+        <v>1.79185260855713</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iterations.mu[12]</t>
+          <t>iterations.obj[1]</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0004669361547809767</v>
+        <v>1.555382562575581</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iterations.mu[13]</t>
+          <t>iterations.obj[2]</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4.783259180348711e-05</v>
+        <v>1.601570595398571</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iterations.mu[14]</t>
+          <t>iterations.obj[3]</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2.387335062517728e-06</v>
+        <v>1.634083941494519</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iterations.mu[15]</t>
+          <t>iterations.obj[4]</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5.181795580830154e-08</v>
+        <v>1.887549754148789</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>iterations.mu[16]</t>
+          <t>iterations.obj[5]</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5.715481324004851e-09</v>
+        <v>1.873910259886061</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>iterations.mu[17]</t>
+          <t>iterations.obj[6]</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.897939439435423e-10</v>
+        <v>1.826779056485769</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>iterations.mu[18]</t>
+          <t>iterations.obj[7]</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>9.999999999999999e-12</v>
+        <v>1.801915776259836</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iterations.mu[19]</t>
+          <t>iterations.obj[8]</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9.999999999999999e-12</v>
+        <v>1.795358394615814</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iterations.mu[1]</t>
+          <t>iterations.obj[9]</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.1229093134056774</v>
+        <v>1.79215914772873</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iterations.mu[2]</t>
+          <t>iterations.regularization_size[0]</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>9.807649349355954e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iterations.mu[3]</t>
+          <t>iterations.regularization_size[10]</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2.560067371146684e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iterations.mu[4]</t>
+          <t>iterations.regularization_size[11]</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.004204093422568634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iterations.mu[5]</t>
+          <t>iterations.regularization_size[12]</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.05393002725074752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iterations.mu[6]</t>
+          <t>iterations.regularization_size[13]</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.05393002725074752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iterations.mu[7]</t>
+          <t>iterations.regularization_size[14]</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.05393002725074752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iterations.mu[8]</t>
+          <t>iterations.regularization_size[15]</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.05393002725074752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>iterations.mu[9]</t>
+          <t>iterations.regularization_size[1]</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.05393002725074752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>iterations.obj[0]</t>
+          <t>iterations.regularization_size[2]</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.842293983200966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>iterations.obj[10]</t>
+          <t>iterations.regularization_size[3]</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.640547874183544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iterations.obj[11]</t>
+          <t>iterations.regularization_size[4]</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.603099111252822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iterations.obj[12]</t>
+          <t>iterations.regularization_size[5]</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1.590034150629177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iterations.obj[13]</t>
+          <t>iterations.regularization_size[6]</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1.58602806172487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iterations.obj[14]</t>
+          <t>iterations.regularization_size[7]</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1.585806410843659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iterations.obj[15]</t>
+          <t>iterations.regularization_size[8]</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.58580747061704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iterations.obj[16]</t>
+          <t>iterations.regularization_size[9]</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.585810781098408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>iterations.obj[17]</t>
+          <t>n_call_callback_fun</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.585811070935787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>iterations.obj[18]</t>
+          <t>n_call_nlp_f</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.585811072735297</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>iterations.obj[19]</t>
+          <t>n_call_nlp_g</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1.58581107273481</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iterations.obj[1]</t>
+          <t>n_call_nlp_grad</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1.515552050055352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iterations.obj[2]</t>
+          <t>n_call_nlp_grad_f</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.571187904431847</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iterations.obj[3]</t>
+          <t>n_call_nlp_hess_l</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.625148346719672</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iterations.obj[4]</t>
+          <t>n_call_nlp_jac_g</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1.605329992205122</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iterations.obj[5]</t>
+          <t>n_call_total</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.605553651460532</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iterations.obj[6]</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1.834293086742371</v>
+          <t>return_status</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Solve_Succeeded</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>iterations.obj[7]</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1.663625926070912</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="B140" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>iterations.obj[8]</t>
+          <t>t_proc_callback_fun</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1.726015512659463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>iterations.obj[9]</t>
+          <t>t_proc_nlp_f</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1.678473303539289</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[0]</t>
+          <t>t_proc_nlp_g</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.5750000000000002</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[10]</t>
+          <t>t_proc_nlp_grad</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -9053,47 +9117,47 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[11]</t>
+          <t>t_proc_nlp_grad_f</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[12]</t>
+          <t>t_proc_nlp_hess_l</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>7.518000000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[13]</t>
+          <t>t_proc_nlp_jac_g</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>2.427</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[14]</t>
+          <t>t_proc_total</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>11.442</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[15]</t>
+          <t>t_wall_callback_fun</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -9103,27 +9167,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[16]</t>
+          <t>t_wall_nlp_f</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>0.279849</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[17]</t>
+          <t>t_wall_nlp_g</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>0.5752290000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[18]</t>
+          <t>t_wall_nlp_grad</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -9133,372 +9197,50 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[19]</t>
+          <t>t_wall_nlp_grad_f</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>0.608633</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[1]</t>
+          <t>t_wall_nlp_hess_l</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>7.518521999999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[2]</t>
+          <t>t_wall_nlp_jac_g</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>2.427948</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[3]</t>
+          <t>t_wall_total</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>11.441171</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[4]</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[5]</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[6]</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[7]</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[8]</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[9]</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>n_call_callback_fun</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>n_call_nlp_f</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>n_call_nlp_g</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>n_call_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>n_call_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>n_call_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>n_call_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>n_call_total</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>return_status</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Solve_Succeeded</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="B172" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>t_proc_callback_fun</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_f</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0.368</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_g</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0.7110000000000002</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>0.8430000000000002</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>10.156</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>3.252</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>t_proc_total</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>15.377</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>t_wall_callback_fun</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_f</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0.36441</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_g</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>0.7179180000000001</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>0.8466069999999999</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>10.158953</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>3.251212</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>t_wall_total</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>15.375886</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
           <t>unified_return_status</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>SOLVER_RET_SUCCESS</t>
         </is>
@@ -9560,10 +9302,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6073597679157974</v>
+        <v>0.7484904106847665</v>
       </c>
       <c r="E2" t="n">
-        <v>38.2996296569159</v>
+        <v>41.77187381988302</v>
       </c>
     </row>
     <row r="3">
@@ -9581,10 +9323,10 @@
         <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6426669960648538</v>
+        <v>0.563464011603296</v>
       </c>
       <c r="E3" t="n">
-        <v>40.52607571698579</v>
+        <v>31.44589063366207</v>
       </c>
     </row>
     <row r="4">
@@ -9602,10 +9344,10 @@
         <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.990011252770125e-07</v>
+        <v>-3.971588330453208e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.516069739561821e-05</v>
+        <v>-2.216470434837432e-05</v>
       </c>
     </row>
     <row r="5">
@@ -9623,10 +9365,10 @@
         <v>0.05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007551245299278695</v>
+        <v>0.0006187130069220122</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04761755942500892</v>
+        <v>0.03452923549444306</v>
       </c>
     </row>
     <row r="6">
@@ -9644,10 +9386,10 @@
         <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1588957892195114</v>
+        <v>0.3301844120382679</v>
       </c>
       <c r="E6" t="n">
-        <v>10.01984359621652</v>
+        <v>18.4269850355686</v>
       </c>
     </row>
     <row r="7">
@@ -9665,10 +9407,10 @@
         <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1613246836757413</v>
+        <v>0.1338198671999475</v>
       </c>
       <c r="E7" t="n">
-        <v>10.17300777182296</v>
+        <v>7.46824077833637</v>
       </c>
     </row>
     <row r="8">
@@ -9686,10 +9428,10 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01480911033010347</v>
+        <v>0.0152755911827628</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9338508593312078</v>
+        <v>0.8525026617598482</v>
       </c>
     </row>
     <row r="9">
@@ -9705,7 +9447,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1.58581107273481</v>
+        <v>1.79185260855713</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -9779,7 +9521,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.35539781503875</v>
+        <v>5.181709548775771</v>
       </c>
       <c r="C2" t="n">
         <v>-4</v>
@@ -9812,7 +9554,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.747393628933218e-16</v>
+        <v>6.677006654063078e-17</v>
       </c>
       <c r="C3" t="n">
         <v>-30</v>
@@ -9845,7 +9587,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.228921909584063</v>
+        <v>-1.112396518263171</v>
       </c>
       <c r="C4" t="n">
         <v>-30</v>
@@ -9878,7 +9620,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5.009559374285092e-15</v>
+        <v>-1.305569024969542e-15</v>
       </c>
       <c r="C5" t="n">
         <v>-30</v>
@@ -9911,13 +9653,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.133854639332998</v>
+        <v>0.70000000699319</v>
       </c>
       <c r="C6" t="n">
         <v>0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -9925,17 +9667,21 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.002</v>
+        <v>0.0007</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>upper</t>
         </is>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[WARN] wing_span_m hit upper bound (value=0.7, upper=0.7, tol=0.0007).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9944,7 +9690,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1318282535659262</v>
+        <v>0.2290084178524724</v>
       </c>
       <c r="C7" t="n">
         <v>0.1</v>
@@ -9977,10 +9723,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.614232334478258</v>
+        <v>0.499999994540779</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="n">
         <v>0.8</v>
@@ -9995,13 +9741,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>lower</t>
         </is>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[WARN] tail_arm_m hit lower bound (value=0.5, lower=0.5, tol=0.0008).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10010,13 +9760,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7831813144429484</v>
+        <v>0.6712501614845966</v>
       </c>
       <c r="C9" t="n">
         <v>0.35</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10024,7 +9774,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.0008</v>
+        <v>0.0007</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -10043,7 +9793,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3368513140839449</v>
+        <v>0.4071438111075289</v>
       </c>
       <c r="C10" t="n">
         <v>0.2</v>
@@ -10076,7 +9826,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1296567456435643</v>
+        <v>0.1169334036779487</v>
       </c>
       <c r="C11" t="n">
         <v>0.1</v>
@@ -10146,7 +9896,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2039745787048131</v>
+        <v>0.02358254083198405</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5510482-dirty</t>
+          <t>41c01f7-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.79185260855713</v>
+        <v>1.772375861260131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6712501614845966</v>
+        <v>0.6588701626881606</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5712501614845966</v>
+        <v>0.5588701626881606</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6712501614845966</v>
+        <v>0.6588701626881606</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.181709548775771</v>
+        <v>4.522872254052008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.677006654063078e-17</v>
+        <v>1.060388543299999e-16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.112396518263171</v>
+        <v>-0.1472207713764126</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.305569024969542e-15</v>
+        <v>3.030457717975491e-15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.181709548775771</v>
+        <v>4.522872254052008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.677006654063078e-17</v>
+        <v>1.060388543299999e-16</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.112396518263171</v>
+        <v>-0.1472207713764126</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.305569024969542e-15</v>
+        <v>3.030457717975491e-15</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.140866002900824</v>
+        <v>0.1339518263149601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.140866002900824</v>
+        <v>0.1339518263149601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -808,56 +808,56 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ballast_penalty_feather_term</t>
+          <t>mass_total_g</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.084625203967024e-09</v>
+        <v>133.9518263149601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mass_total_g</t>
+          <t>mass_total_lbm</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>140.866002900824</v>
+        <v>0.2953132265319191</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>lbm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mass_total_lbm</t>
+          <t>total_cg_x_m</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3105563766445718</v>
+        <v>0.1293733909091868</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lbm</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>total_cg_x_m</t>
+          <t>total_cg_y_m</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1441175773158246</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -868,11 +868,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>total_cg_y_m</t>
+          <t>total_cg_z_m</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.01442931460082879</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -883,11 +883,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>total_cg_z_m</t>
+          <t>total_cg_x_weighted_m</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01502644652070806</v>
+        <v>0.1293733909091868</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -898,11 +898,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>total_cg_x_weighted_m</t>
+          <t>total_cg_y_weighted_m</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1441175773158246</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -913,11 +913,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>total_cg_y_weighted_m</t>
+          <t>total_cg_z_weighted_m</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>0.01442931460082879</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -928,11 +928,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>total_cg_z_weighted_m</t>
+          <t>total_cg_x_error_m</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01502644652070806</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>total_cg_x_error_m</t>
+          <t>total_cg_y_error_m</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -958,7 +958,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>total_cg_y_error_m</t>
+          <t>total_cg_z_error_m</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -973,56 +973,56 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>total_cg_z_error_m</t>
+          <t>mass_component_sum_kg</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>0.1339518263149601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mass_component_sum_kg</t>
+          <t>battery_x_m</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.140866002900824</v>
+        <v>0.03465626254971951</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ballast_mass_kg</t>
+          <t>sink_rate_mps</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.7287422796956008</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m/s</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ballast_slider_eta</t>
+          <t>L_over_D</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.02358254083198405</v>
+        <v>8.919476944056441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1033,11 +1033,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ballast_x_m</t>
+          <t>turn_radius_allow_raw_m</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.08417021565831362</v>
+        <v>1.749999997303377</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1048,11 +1048,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>battery_x_m</t>
+          <t>turn_radius_allow_m</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.04225210446311809</v>
+        <v>1.749999997303377</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1063,41 +1063,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sink_rate_mps</t>
+          <t>a_lat_req_mps2</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7484904106847665</v>
+        <v>8.251428584143424</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m/s^2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L_over_D</t>
+          <t>a_lat_ach_mps2</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.016134703895203</v>
+        <v>7.514895942952997</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m/s^2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>turn_radius_allow_raw_m</t>
+          <t>turn_radius_ach_m</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.749999996503405</v>
+        <v>1.921516959065938</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1108,11 +1108,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>turn_radius_allow_m</t>
+          <t>turn_footprint_lhs_m</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.749999996503405</v>
+        <v>2.571516961762562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a_lat_req_mps2</t>
+          <t>agility_lateral_margin_mps2</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20.5714286125314</v>
+        <v>-0.7365326411904274</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1138,71 +1138,71 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>a_lat_ach_mps2</t>
+          <t>turn_CL</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7.514895932668145</v>
+        <v>0.3596702631069514</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>m/s^2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>turn_radius_ach_m</t>
+          <t>wing_loading_n_m2</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4.790485500072426</v>
+        <v>9.307585668421478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m^2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>turn_footprint_lhs_m</t>
+          <t>reynolds_wing</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.440485503569021</v>
+        <v>88385.39754700637</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>agility_lateral_margin_mps2</t>
+          <t>static_margin</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-13.05653267986326</v>
+        <v>0.09999999438017741</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>m/s^2</t>
+          <t>MAC fraction</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>turn_CL</t>
+          <t>tail_volume_horizontal</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.385007216173159</v>
+        <v>0.5044402178041257</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1213,131 +1213,131 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>wing_loading_n_m2</t>
+          <t>tail_volume_vertical</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.489403328184636</v>
+        <v>0.02999999591331827</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>N/m^2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>reynolds_wing</t>
+          <t>roll_rate_ss_radps</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>94066.68509676102</v>
+        <v>5.905933264278247</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rad/s</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>static_margin</t>
+          <t>roll_rate_ss_turn_radps</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2000000098107236</v>
+        <v>2.762159557447057</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MAC fraction</t>
+          <t>rad/s</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tail_volume_horizontal</t>
+          <t>roll_tau_turn_s</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5558482021720921</v>
+        <v>0.05309394686325974</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>s</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tail_volume_vertical</t>
+          <t>delta_a_turn_eff_deg</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.02999999002463568</v>
+        <v>24</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>roll_rate_ss_radps</t>
+          <t>bank_entry_phi_capture_proxy_deg</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5.605487237063405</v>
+        <v>102.3793920419568</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>roll_rate_ss_turn_radps</t>
+          <t>bank_entry_margin_deg</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4.484389789650724</v>
+        <v>52.37940784031489</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>roll_tau_turn_s</t>
+          <t>bank_entry_phi_raw_deg</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.03437008016121631</v>
+        <v>102.3794078403149</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>deg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>delta_a_turn_eff_deg</t>
+          <t>bank_entry_phi_achieved_deg</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24</v>
+        <v>102.3794078403149</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1348,131 +1348,131 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bank_entry_phi_capture_proxy_deg</t>
+          <t>nominal_Cl_delta_a_fd</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>171.0246568338559</v>
+        <v>-0.7735620812668736</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>1/rad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bank_entry_margin_deg</t>
+          <t>turn_Cl_delta_a_fd</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>121.0246568464731</v>
+        <v>-0.7735620812668736</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>1/rad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bank_entry_phi_raw_deg</t>
+          <t>roll_accel0_rad_s2</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>171.0246568464731</v>
+        <v>190.2712995487436</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>rad/s^2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bank_entry_phi_achieved_deg</t>
+          <t>roll_tau_s</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>171.0246568464731</v>
+        <v>0.03103953816621339</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>s</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nominal_Cl_delta_a_fd</t>
+          <t>wing_tip_deflection_proxy_m</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7261221598264442</v>
+        <v>0.006416930983084015</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1/rad</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>turn_Cl_delta_a_fd</t>
+          <t>wing_tip_deflection_proxy_allow_m</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7261221598264442</v>
+        <v>0.02800000021572985</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1/rad</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>roll_accel0_rad_s2</t>
+          <t>wing_tip_deflection_proxy_semispan_fraction</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>163.0920617807786</v>
+        <v>0.01833408838183968</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>rad/s^2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>roll_tau_s</t>
+          <t>wing_tip_deflection_proxy_over_allow</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.03437008016121631</v>
+        <v>0.229176104772996</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_proxy_m</t>
+          <t>wing_struct_semispan_m</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.006735401206332104</v>
+        <v>0.3553993168982336</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1483,146 +1483,146 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_proxy_allow_m</t>
+          <t>wing_struct_half_load_n</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0280000002797276</v>
+        <v>0.6570337042240595</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_proxy_semispan_fraction</t>
+          <t>wing_struct_line_load_n_m</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.01924400325441034</v>
+        <v>1.848719659785382</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/m</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>wing_tip_deflection_proxy_over_allow</t>
+          <t>wing_struct_E_pa</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2405500406801292</v>
+        <v>1500000</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>wing_struct_semispan_m</t>
+          <t>wing_struct_EI_Nm2</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3553993177105463</v>
+        <v>0.5487498773555851</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N*m^2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>wing_struct_half_load_n</t>
+          <t>wing_struct_thickness_m</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6909477392333268</v>
+        <v>0.006</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>wing_struct_line_load_n_m</t>
+          <t>htail_tip_deflection_proxy_m</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.944144810643859</v>
+        <v>0.001817246788802192</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>wing_struct_E_pa</t>
+          <t>htail_tip_deflection_proxy_allow_m</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1500000</v>
+        <v>0.01345603621896405</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>wing_struct_EI_Nm2</t>
+          <t>htail_tip_deflection_proxy_semispan_fraction</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5497888006219521</v>
+        <v>0.01080405408684073</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>N*m^2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>wing_struct_thickness_m</t>
+          <t>htail_tip_deflection_proxy_over_allow</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.006</v>
+        <v>0.1350506760855091</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_proxy_m</t>
+          <t>htail_struct_semispan_m</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.003385495155179471</v>
+        <v>0.1682004527370506</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1633,146 +1633,146 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_proxy_allow_m</t>
+          <t>htail_struct_half_load_n</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.01628575244430116</v>
+        <v>0.1642584260560149</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_proxy_semispan_fraction</t>
+          <t>htail_struct_line_load_n_m</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.01663046355031217</v>
+        <v>0.9765635192005199</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/m</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>htail_tip_deflection_proxy_over_allow</t>
+          <t>htail_struct_E_pa</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.2078807943789021</v>
+        <v>1000000</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>htail_struct_semispan_m</t>
+          <t>htail_struct_EI_Nm2</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.2035719055537644</v>
+        <v>0.05376569217599583</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N*m^2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>htail_struct_half_load_n</t>
+          <t>htail_struct_thickness_m</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.1727369348083317</v>
+        <v>0.003</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>htail_struct_line_load_n_m</t>
+          <t>objective_struct_deflection_proxy_penalty</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8485303231722755</v>
+        <v>0.3280847114488961</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>htail_struct_E_pa</t>
+          <t>objective_htail_deflection_proxy_penalty</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1000000</v>
+        <v>0.1659353775819366</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>htail_struct_EI_Nm2</t>
+          <t>objective_roll_tau_penalty</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.05380548506041465</v>
+        <v>0.01379535029609484</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>N*m^2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>htail_struct_thickness_m</t>
+          <t>max_servo_utilization</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.003</v>
+        <v>0.006530685414614465</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>fraction</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>objective_struct_deflection_proxy_penalty</t>
+          <t>J_sink</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.3301844120382679</v>
+        <v>0.7287422796956008</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1783,11 +1783,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>objective_htail_deflection_proxy_penalty</t>
+          <t>J_mass</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.1338198671999475</v>
+        <v>0.5358073052598403</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1798,11 +1798,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>objective_roll_tau_penalty</t>
+          <t>J_trim</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0152755911827628</v>
+        <v>1.083697776233297e-05</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1813,26 +1813,26 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>max_servo_utilization</t>
+          <t>J_wing_deflection</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.007397234821551284</v>
+        <v>0.3280847114488961</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>J_sink</t>
+          <t>J_htail_deflection</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7484904106847665</v>
+        <v>0.1659353775819366</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1843,11 +1843,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>J_mass</t>
+          <t>J_roll_tau</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.563464011603296</v>
+        <v>0.01379535029609484</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1858,11 +1858,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>J_ballast</t>
+          <t>J_total</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-3.971588330453208e-07</v>
+        <v>1.772375861260131</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1873,11 +1873,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>J_trim</t>
+          <t>objective_term_J_sink_value</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0006187130069220122</v>
+        <v>0.7287422796956008</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1888,11 +1888,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>J_wing_deflection</t>
+          <t>objective_term_J_sink_weight</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.3301844120382679</v>
+        <v>1</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1903,26 +1903,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>J_htail_deflection</t>
+          <t>objective_term_J_sink_pct_total</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.1338198671999475</v>
+        <v>41.1166895027264</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>J_roll_tau</t>
+          <t>objective_term_J_mass_value</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0152755911827628</v>
+        <v>0.5358073052598403</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1933,11 +1933,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>J_total</t>
+          <t>objective_term_J_mass_weight</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.79185260855713</v>
+        <v>0.4</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1948,26 +1948,26 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>objective_term_J_sink_value</t>
+          <t>objective_term_J_mass_pct_total</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7484904106847665</v>
+        <v>30.2310202351148</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>objective_term_J_sink_weight</t>
+          <t>objective_term_J_trim_value</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>1.083697776233297e-05</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1978,41 +1978,41 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>objective_term_J_sink_pct_total</t>
+          <t>objective_term_J_trim_weight</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>41.77187381988302</v>
+        <v>0.05</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>objective_term_J_mass_value</t>
+          <t>objective_term_J_trim_pct_total</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.563464011603296</v>
+        <v>0.0006114379009104792</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>objective_term_J_mass_weight</t>
+          <t>objective_term_J_wing_deflection_value</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4</v>
+        <v>0.3280847114488961</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2023,41 +2023,41 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>objective_term_J_mass_pct_total</t>
+          <t>objective_term_J_wing_deflection_weight</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>31.44589063366207</v>
+        <v>0.5</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>objective_term_J_ballast_value</t>
+          <t>objective_term_J_wing_deflection_pct_total</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-3.971588330453208e-07</v>
+        <v>18.51101217411261</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>objective_term_J_ballast_weight</t>
+          <t>objective_term_J_htail_deflection_value</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4</v>
+        <v>0.1659353775819366</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2068,41 +2068,41 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>objective_term_J_ballast_pct_total</t>
+          <t>objective_term_J_htail_deflection_weight</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-2.216470434837432e-05</v>
+        <v>0.1</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>objective_term_J_trim_value</t>
+          <t>objective_term_J_htail_deflection_pct_total</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0006187130069220122</v>
+        <v>9.362313108008546</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>objective_term_J_trim_weight</t>
+          <t>objective_term_J_roll_tau_value</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.05</v>
+        <v>0.01379535029609484</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2113,41 +2113,41 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>objective_term_J_trim_pct_total</t>
+          <t>objective_term_J_roll_tau_weight</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.03452923549444306</v>
+        <v>0.2</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>objective_term_J_wing_deflection_value</t>
+          <t>objective_term_J_roll_tau_pct_total</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.3301844120382679</v>
+        <v>0.7783535421367435</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>objective_term_J_wing_deflection_weight</t>
+          <t>objective_term_J_total_value</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5</v>
+        <v>1.772375861260131</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2158,41 +2158,39 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>objective_term_J_wing_deflection_pct_total</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>18.4269850355686</v>
-      </c>
+          <t>objective_term_J_total_weight</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>objective_term_J_htail_deflection_value</t>
+          <t>objective_term_J_total_pct_total</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.1338198671999475</v>
+        <v>100</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>objective_term_J_htail_deflection_weight</t>
+          <t>objective_weight_w_sink</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2203,26 +2201,26 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>objective_term_J_htail_deflection_pct_total</t>
+          <t>objective_weight_w_mass</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>7.46824077833637</v>
+        <v>0.4</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>objective_term_J_roll_tau_value</t>
+          <t>objective_weight_w_trim_effort</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0152755911827628</v>
+        <v>0.05</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2233,11 +2231,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>objective_term_J_roll_tau_weight</t>
+          <t>objective_weight_w_wing_deflection</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2248,26 +2246,26 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>objective_term_J_roll_tau_pct_total</t>
+          <t>objective_weight_w_htail_deflection</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.8525026617598482</v>
+        <v>0.1</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>objective_term_J_total_value</t>
+          <t>objective_weight_w_roll_tau</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.79185260855713</v>
+        <v>0.2</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2278,10 +2276,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>objective_term_J_total_weight</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>objective_scale_sink_mps</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
           <t>-</t>
@@ -2291,26 +2291,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>objective_term_J_total_pct_total</t>
+          <t>objective_scale_mass_kg</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>objective_weight_w_sink</t>
+          <t>objective_scale_trim_deg</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2321,11 +2321,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>objective_weight_w_mass</t>
+          <t>objective_scale_roll_tau_s</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>objective_weight_w_ballast</t>
+          <t>design_var_bound_hits_count</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2351,165 +2351,15 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>objective_weight_w_trim_effort</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0.05</v>
+          <t>design_var_bound_hits</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>wing_span_m:upper; tail_arm_m:lower</t>
+        </is>
       </c>
       <c r="C128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>objective_weight_w_wing_deflection</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>objective_weight_w_htail_deflection</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>objective_weight_w_roll_tau</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>objective_scale_sink_mps</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>1</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>objective_scale_mass_kg</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>objective_scale_ballast_kg</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>objective_scale_trim_deg</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>10</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>objective_scale_roll_tau_s</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>design_var_bound_hits_count</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>3</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>design_var_bound_hits</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>wing_span_m:upper; tail_arm_m:lower; ballast_mass_kg:lower</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2563,7 +2413,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2583,7 +2433,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2723,7 +2573,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.181709548775771</v>
+        <v>4.522872254052008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2743,7 +2593,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.677006654063078e-17</v>
+        <v>1.060388543299999e-16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2763,7 +2613,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-1.112396518263171</v>
+        <v>-0.1472207713764126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2783,7 +2633,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.305569024969542e-15</v>
+        <v>3.030457717975491e-15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2803,7 +2653,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7484904106847665</v>
+        <v>0.7287422796956008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2823,7 +2673,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.385007216173159</v>
+        <v>0.3596702631069514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2843,7 +2693,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.7261221598264442</v>
+        <v>-0.7735620812668736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2863,7 +2713,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.181709548775771</v>
+        <v>4.522872254052008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2883,7 +2733,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.677006654063078e-17</v>
+        <v>1.060388543299999e-16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2903,7 +2753,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1.112396518263171</v>
+        <v>-0.1472207713764126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2923,7 +2773,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1.305569024969542e-15</v>
+        <v>3.030457717975491e-15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2793,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.385007216173159</v>
+        <v>0.3596702631069514</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2813,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.749999996503405</v>
+        <v>1.749999997303377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,7 +2833,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.749999996503405</v>
+        <v>1.749999997303377</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,7 +2853,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20.5714286125314</v>
+        <v>8.251428584143424</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,7 +2873,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.514895932668145</v>
+        <v>7.514895942952997</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3043,7 +2893,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.790485500072426</v>
+        <v>1.921516959065938</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3063,7 +2913,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.440485503569021</v>
+        <v>2.571516961762562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3083,7 +2933,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-13.05653267986326</v>
+        <v>-0.7365326411904274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3103,7 +2953,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.7261221598264442</v>
+        <v>-0.7735620812668736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3123,7 +2973,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.03437008016121631</v>
+        <v>0.05309394686325974</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3163,7 +3013,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>171.0246568338559</v>
+        <v>102.3793920419568</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3183,7 +3033,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>121.0246568464731</v>
+        <v>52.37940784031489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3203,7 +3053,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>171.0246568464731</v>
+        <v>102.3794078403149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3223,7 +3073,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>171.0246568464731</v>
+        <v>102.3794078403149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3269,7 +3119,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7107986354210927</v>
+        <v>0.7107986337964672</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3284,7 +3134,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2290084178524724</v>
+        <v>0.198625050198878</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3299,7 +3149,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1627788709094808</v>
+        <v>0.1411824143191172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3314,7 +3164,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.103810078627723</v>
+        <v>3.578595112171216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3329,7 +3179,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6712501614845966</v>
+        <v>0.6588701626881606</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3344,7 +3194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5712501614845966</v>
+        <v>0.5588701626881606</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3359,7 +3209,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6712501614845966</v>
+        <v>0.6588701626881606</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3374,7 +3224,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4071438111075289</v>
+        <v>0.3364009054741012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3389,7 +3239,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1017859527768822</v>
+        <v>0.08410022636852531</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3404,7 +3254,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04144152073079079</v>
+        <v>0.0282913923009488</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3419,7 +3269,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1169334036779487</v>
+        <v>0.1089005104594736</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3434,7 +3284,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05846670183897434</v>
+        <v>0.05445025522973681</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3449,7 +3299,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.006836710447855052</v>
+        <v>0.005929660589166962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3528,7 +3378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3585,28 +3435,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03223021644007719</v>
+        <v>0.02795411803518521</v>
       </c>
       <c r="C2" t="n">
-        <v>32.23021644007719</v>
+        <v>27.95411803518521</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1145042089262362</v>
+        <v>0.09931252509943901</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0378572219322534</v>
+        <v>0.03785722186172508</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001316163888248209</v>
+        <v>0.001141543699713236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001453352561245325</v>
+        <v>9.484487009244002e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001461305763074101</v>
+        <v>0.001236220845097465</v>
       </c>
     </row>
     <row r="3">
@@ -3622,7 +3472,7 @@
         <v>13.1864418212479</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0828521044631181</v>
+        <v>0.07525626254971951</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3643,63 +3493,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>glue</t>
+          <t>receiver</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01043451873339437</v>
+        <v>0.01</v>
       </c>
       <c r="C4" t="n">
-        <v>10.43451873339437</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1441175773158247</v>
+        <v>0.1096562625497195</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01502644652070806</v>
+        <v>-0.008</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002013291726779135</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0002444997845013802</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000435303264902527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>glue</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01</v>
+        <v>0.009922357504811859</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9.922357504811858</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1172521044631181</v>
+        <v>0.1293733909091868</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008</v>
+        <v>0.01442931460082879</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.0001834265574949846</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.0002126393334283085</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0003861664048330671</v>
       </c>
     </row>
     <row r="6">
@@ -3709,28 +3559,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00923628249382696</v>
+        <v>0.009236282472716198</v>
       </c>
       <c r="C6" t="n">
-        <v>9.236282493826961</v>
+        <v>9.236282472716198</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05725210446311809</v>
+        <v>0.04965626254971951</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03685722193225339</v>
+        <v>0.03685722186172508</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003771597547200107</v>
+        <v>0.0003771597521339159</v>
       </c>
       <c r="H6" t="n">
-        <v>2.30907062345674e-08</v>
+        <v>2.309070618179049e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003771597547200107</v>
+        <v>0.0003771597521339159</v>
       </c>
     </row>
     <row r="7">
@@ -3746,7 +3596,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04225210446311809</v>
+        <v>0.03465626254971951</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3771,13 +3621,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008856937219372078</v>
+        <v>0.008693586983636675</v>
       </c>
       <c r="C8" t="n">
-        <v>8.856937219372078</v>
+        <v>8.693586983636676</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2356250807422983</v>
+        <v>0.2294350813440803</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3786,50 +3636,50 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.214234304843019e-08</v>
+        <v>2.173396745909169e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003325719250636766</v>
+        <v>0.0003145085420092318</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003325719250636766</v>
+        <v>0.0003145085420092318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>htail_surfaces</t>
+          <t>servo_elevator</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004972982487694896</v>
+        <v>0.004</v>
       </c>
       <c r="C9" t="n">
-        <v>4.972982487694896</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5508929709292202</v>
+        <v>0.04965626254971951</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0025</v>
+        <v>-0.0065</v>
       </c>
       <c r="G9" t="n">
-        <v>6.86997153560883e-05</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.29722883806718e-06</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.298948472042393e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>servo_elevator</t>
+          <t>servo_rudder</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3839,7 +3689,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05725210446311809</v>
+        <v>0.04965626254971951</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3860,7 +3710,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>servo_rudder</t>
+          <t>servo_aileron_R</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3870,13 +3720,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05725210446311809</v>
+        <v>0.05958751505966341</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.2800000021572985</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0065</v>
+        <v>0.05637155497876012</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3891,7 +3741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>servo_aileron_R</t>
+          <t>servo_aileron_L</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3901,13 +3751,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0687025253557417</v>
+        <v>0.05958751505966341</v>
       </c>
       <c r="E12" t="n">
-        <v>0.280000002797276</v>
+        <v>-0.2800000021572985</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05637155509160542</v>
+        <v>0.05637155497876012</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3922,38 +3772,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>servo_aileron_L</t>
+          <t>wing mount R fwd</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.004</v>
+        <v>0.003953389544688026</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3.953389544688026</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0687025253557417</v>
+        <v>0.07577526254971952</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.280000002797276</v>
+        <v>0.03743439716312056</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05637155509160542</v>
+        <v>0.009600694226414574</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.315463615237264e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.353146406408094e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2.448142662848282e-06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wing mount R fwd</t>
+          <t>wing mount R aft</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3963,7 +3813,7 @@
         <v>3.953389544688026</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0833711044631181</v>
+        <v>0.1184062625497195</v>
       </c>
       <c r="E14" t="n">
         <v>0.03743439716312056</v>
@@ -3984,7 +3834,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>wing mount R aft</t>
+          <t>wing mount L fwd</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3994,10 +3844,10 @@
         <v>3.953389544688026</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1260021044631181</v>
+        <v>0.07577526254971952</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03743439716312056</v>
+        <v>-0.03743439716312056</v>
       </c>
       <c r="F15" t="n">
         <v>0.009600694226414574</v>
@@ -4015,7 +3865,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wing mount L fwd</t>
+          <t>wing mount L aft</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -4025,7 +3875,7 @@
         <v>3.953389544688026</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0833711044631181</v>
+        <v>0.1184062625497195</v>
       </c>
       <c r="E16" t="n">
         <v>-0.03743439716312056</v>
@@ -4046,32 +3896,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wing mount L aft</t>
+          <t>htail_surfaces</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.003953389544688026</v>
+        <v>0.003394967076113856</v>
       </c>
       <c r="C17" t="n">
-        <v>3.953389544688026</v>
+        <v>3.394967076113856</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1260021044631181</v>
+        <v>0.5420501174144555</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.03743439716312056</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.009600694226414574</v>
+        <v>-0.0025</v>
       </c>
       <c r="G17" t="n">
-        <v>2.315463615237264e-06</v>
+        <v>3.201866135835449e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.353146406408094e-07</v>
+        <v>2.003553421122548e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.448142662848282e-06</v>
+        <v>3.401712232886286e-05</v>
       </c>
     </row>
     <row r="18">
@@ -4087,7 +3937,7 @@
         <v>1.795290858725762</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5481501614845966</v>
+        <v>0.5357701626881606</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -4112,28 +3962,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001225000012238082</v>
+        <v>0.001225000009438181</v>
       </c>
       <c r="C19" t="n">
-        <v>1.225000012238082</v>
+        <v>1.225000009438181</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03112605223155904</v>
+        <v>0.02732813127485976</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01949361096612669</v>
+        <v>0.01949361093086254</v>
       </c>
       <c r="G19" t="n">
-        <v>1.250521043333296e-05</v>
+        <v>1.250521034758597e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>8.463590583745587e-07</v>
+        <v>6.20928234954222e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>1.335156604129082e-05</v>
+        <v>1.312613513212349e-05</v>
       </c>
     </row>
     <row r="20">
@@ -4143,28 +3993,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.001225000012238082</v>
+        <v>0.001225000009438181</v>
       </c>
       <c r="C20" t="n">
-        <v>1.225000012238082</v>
+        <v>1.225000009438181</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03112605223155904</v>
+        <v>0.02732813127485976</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02536361096612669</v>
+        <v>0.02536361093086253</v>
       </c>
       <c r="G20" t="n">
-        <v>1.250521043333296e-05</v>
+        <v>1.250521034758597e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>8.463590583745587e-07</v>
+        <v>6.20928234954222e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>1.335156604129082e-05</v>
+        <v>1.312613513212349e-05</v>
       </c>
     </row>
     <row r="21">
@@ -4180,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2499999972703895</v>
+        <v>0.2500000021150964</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4211,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.491059994540779</v>
+        <v>0.4910600042301929</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4232,38 +4082,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vtail_surfaces</t>
+          <t>htail mount R</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0008204052537426062</v>
+        <v>0.0007628808864265929</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8204052537426062</v>
+        <v>0.7628808864265929</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5422291207416386</v>
+        <v>0.5406701626881606</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.01469135802469136</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06246670183897435</v>
+        <v>-0.00325</v>
       </c>
       <c r="G23" t="n">
-        <v>9.354274988965154e-07</v>
+        <v>6.956787515816837e-08</v>
       </c>
       <c r="H23" t="n">
-        <v>1.168515243695261e-06</v>
+        <v>1.36523891966759e-08</v>
       </c>
       <c r="I23" t="n">
-        <v>2.343183526793591e-07</v>
+        <v>8.29341840224343e-08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>htail mount R</t>
+          <t>htail mount L</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4273,10 +4123,10 @@
         <v>0.7628808864265929</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5530501614845966</v>
+        <v>0.5406701626881606</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01469135802469136</v>
+        <v>-0.01469135802469136</v>
       </c>
       <c r="F24" t="n">
         <v>-0.00325</v>
@@ -4294,125 +4144,125 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>htail mount L</t>
+          <t>vtail_surfaces</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0007628808864265929</v>
+        <v>0.0007115592707000354</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7628808864265929</v>
+        <v>0.7115592707000353</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5530501614845966</v>
+        <v>0.5361201231866978</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.01469135802469136</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.00325</v>
+        <v>0.05845025522973681</v>
       </c>
       <c r="G25" t="n">
-        <v>6.956787515816837e-08</v>
+        <v>7.037511635074226e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>1.36523891966759e-08</v>
+        <v>8.79021867567997e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>8.29341840224343e-08</v>
+        <v>1.763380429666244e-07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>htail_tape_bottom</t>
+          <t>vtail mount</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0007125016694381755</v>
+        <v>0.0006789473684210525</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7125016694381755</v>
+        <v>0.6789473684210525</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5305357803738437</v>
+        <v>0.5300701626881605</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.003935</v>
+        <v>0.01355555555555556</v>
       </c>
       <c r="G26" t="n">
-        <v>9.842385238354917e-06</v>
+        <v>2.541128167641326e-08</v>
       </c>
       <c r="H26" t="n">
-        <v>5.938517351835922e-09</v>
+        <v>3.795059088693956e-08</v>
       </c>
       <c r="I26" t="n">
-        <v>9.848321748827051e-06</v>
+        <v>1.299194078947368e-08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>htail_tape_top</t>
+          <t>htail_tape_bottom</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0007125016694381755</v>
+        <v>0.0005887015845796772</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7125016694381755</v>
+        <v>0.5887015845796771</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5305357803738437</v>
+        <v>0.5252300721407505</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.001065</v>
+        <v>-0.003935</v>
       </c>
       <c r="G27" t="n">
-        <v>9.842385238354917e-06</v>
+        <v>5.55172998826601e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>5.938517351835922e-09</v>
+        <v>4.906675626228927e-09</v>
       </c>
       <c r="I27" t="n">
-        <v>9.848321748827051e-06</v>
+        <v>5.55663500571611e-06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vtail mount</t>
+          <t>htail_tape_top</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0006789473684210525</v>
+        <v>0.0005887015845796772</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6789473684210525</v>
+        <v>0.5887015845796771</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5424501614845966</v>
+        <v>0.5252300721407505</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01355555555555556</v>
+        <v>-0.001065</v>
       </c>
       <c r="G28" t="n">
-        <v>2.541128167641326e-08</v>
+        <v>5.55172998826601e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>3.795059088693956e-08</v>
+        <v>4.906675626228927e-09</v>
       </c>
       <c r="I28" t="n">
-        <v>1.299194078947368e-08</v>
+        <v>5.55663500571611e-06</v>
       </c>
     </row>
     <row r="29">
@@ -4428,7 +4278,7 @@
         <v>0.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08225210446311809</v>
+        <v>0.07465626254971951</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4453,28 +4303,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0002046334564364102</v>
+        <v>0.0001905758933040788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2046334564364102</v>
+        <v>0.1905758933040788</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5305357803738437</v>
+        <v>0.5252300721407505</v>
       </c>
       <c r="E30" t="n">
         <v>0.001565</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06246670183897435</v>
+        <v>0.05845025522973681</v>
       </c>
       <c r="G30" t="n">
-        <v>2.331702364587007e-07</v>
+        <v>1.883419956894637e-07</v>
       </c>
       <c r="H30" t="n">
-        <v>2.348752270702196e-07</v>
+        <v>1.899298597392813e-07</v>
       </c>
       <c r="I30" t="n">
-        <v>1.705566995754566e-09</v>
+        <v>1.588400838583727e-09</v>
       </c>
     </row>
     <row r="31">
@@ -4484,90 +4334,59 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002046334564364102</v>
+        <v>0.0001905758933040788</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2046334564364102</v>
+        <v>0.1905758933040788</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5305357803738437</v>
+        <v>0.5252300721407505</v>
       </c>
       <c r="E31" t="n">
         <v>-0.001565</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06246670183897435</v>
+        <v>0.05845025522973681</v>
       </c>
       <c r="G31" t="n">
-        <v>2.331702364587007e-07</v>
+        <v>1.883419956894637e-07</v>
       </c>
       <c r="H31" t="n">
-        <v>2.348752270702196e-07</v>
+        <v>1.899298597392813e-07</v>
       </c>
       <c r="I31" t="n">
-        <v>1.705566995754566e-09</v>
+        <v>1.588400838583727e-09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ballast</t>
+          <t>wing_spar_slot_void</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-9.999817078172689e-09</v>
+        <v>-0.000369600002847634</v>
       </c>
       <c r="C32" t="n">
-        <v>-9.999817078172688e-06</v>
+        <v>-0.3696000028476339</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.08417021565831362</v>
+        <v>0.04965626254971951</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.03685722186172508</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1.509249314883896e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-9.856000075936905e-10</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>wing_spar_slot_void</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>-0.0003696000036924043</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.3696000036924043</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.05725210446311809</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.03685722193225339</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-1.509249325232445e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-9.856000098464112e-10</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-1.509249325232445e-05</v>
+        <v>-1.509249314883896e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4603,7 +4422,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04802903523890088</v>
+        <v>0.04032414292484048</v>
       </c>
     </row>
     <row r="3">
@@ -4613,7 +4432,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9052593767455703</v>
+        <v>0.706821319036679</v>
       </c>
     </row>
     <row r="4">
@@ -4623,7 +4442,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.988755252935022e-06</v>
+        <v>2.48227145496557e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4633,7 +4452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003220249934487996</v>
+        <v>0.0002991990472531181</v>
       </c>
     </row>
     <row r="6">
@@ -4643,7 +4462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0490958063780883</v>
+        <v>0.06028571002997252</v>
       </c>
     </row>
     <row r="7">
@@ -4653,7 +4472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.242047255490709e-05</v>
+        <v>-6.308359872669866e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4663,7 +4482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.385007216173159</v>
+        <v>0.3596702631069514</v>
       </c>
     </row>
     <row r="9">
@@ -4673,7 +4492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.946169266351761</v>
+        <v>4.120642083537414</v>
       </c>
     </row>
     <row r="10">
@@ -4683,7 +4502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.413635694832638e-06</v>
+        <v>-1.659296967596858e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4693,7 +4512,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001138272616552083</v>
+        <v>-0.009732654147442954</v>
       </c>
     </row>
     <row r="12">
@@ -4703,7 +4522,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.498776004896007</v>
+        <v>0.7309491100831456</v>
       </c>
     </row>
     <row r="13">
@@ -4713,7 +4532,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.462100883755426e-05</v>
+        <v>-0.0002183347423412307</v>
       </c>
     </row>
     <row r="14">
@@ -4723,7 +4542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-3.892433734384674e-18</v>
+        <v>1.070443142643919e-17</v>
       </c>
     </row>
     <row r="15">
@@ -4733,7 +4552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.040183806542279e-22</v>
+        <v>-2.934323416224544e-22</v>
       </c>
     </row>
     <row r="16">
@@ -4743,7 +4562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1499341988688302</v>
+        <v>-0.1696621847927534</v>
       </c>
     </row>
     <row r="17">
@@ -4753,7 +4572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.26322800055028</v>
+        <v>-0.2997746495015723</v>
       </c>
     </row>
     <row r="18">
@@ -4763,7 +4582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.365823057123388e-19</v>
+        <v>-2.668696566238722e-18</v>
       </c>
     </row>
     <row r="19">
@@ -4773,7 +4592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1114463936623395</v>
+        <v>0.1113100136966325</v>
       </c>
     </row>
     <row r="20">
@@ -4783,7 +4602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
     </row>
     <row r="21">
@@ -4793,7 +4612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-4.563704725340319e-19</v>
+        <v>-4.2546964124101e-19</v>
       </c>
     </row>
     <row r="22">
@@ -4803,7 +4622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1301655956246374</v>
+        <v>-0.1482161274128829</v>
       </c>
     </row>
     <row r="23">
@@ -4813,7 +4632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5395584074505652</v>
+        <v>-0.57931475229415</v>
       </c>
     </row>
     <row r="24">
@@ -4823,7 +4642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.3578453863819e-18</v>
+        <v>-2.115546118917234e-18</v>
       </c>
     </row>
     <row r="25">
@@ -4833,7 +4652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03502875234481945</v>
+        <v>0.02860661663172016</v>
       </c>
     </row>
     <row r="26">
@@ -4843,7 +4662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.009987835178577e-06</v>
+        <v>-1.004551826244132e-06</v>
       </c>
     </row>
     <row r="27">
@@ -4853,7 +4672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.7892338919851279</v>
+        <v>-0.4120641851964639</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.940823624861621e-06</v>
+        <v>-5.903426930099402e-06</v>
       </c>
     </row>
     <row r="29">
@@ -4873,7 +4692,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002189207205635887</v>
+        <v>-0.003055762525274423</v>
       </c>
     </row>
     <row r="30">
@@ -4883,7 +4702,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-7.533849191345507</v>
+        <v>-8.507266713995831</v>
       </c>
     </row>
     <row r="31">
@@ -4893,7 +4712,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.16190110333429e-05</v>
+        <v>-0.0001752827143098739</v>
       </c>
     </row>
     <row r="32">
@@ -4903,7 +4722,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
     </row>
     <row r="33">
@@ -4913,7 +4732,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-4.14586001324609e-20</v>
+        <v>-3.350924762584389e-20</v>
       </c>
     </row>
     <row r="34">
@@ -4923,7 +4742,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.03416412908632467</v>
+        <v>0.0299962223873968</v>
       </c>
     </row>
     <row r="35">
@@ -4933,7 +4752,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.05499141773995983</v>
+        <v>-0.07322030889983785</v>
       </c>
     </row>
     <row r="36">
@@ -4943,7 +4762,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-6.859057942205118e-19</v>
+        <v>1.220942317636456e-18</v>
       </c>
     </row>
     <row r="37">
@@ -4953,7 +4772,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.05513066451968678</v>
+        <v>-0.06226673402358746</v>
       </c>
     </row>
     <row r="38">
@@ -4963,7 +4782,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1723892536131114</v>
+        <v>0.1473256130028743</v>
       </c>
     </row>
     <row r="39">
@@ -4973,7 +4792,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0688812103927496</v>
+        <v>0.05326256064932234</v>
       </c>
     </row>
     <row r="40">
@@ -4983,7 +4802,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1035080432203617</v>
+        <v>0.09406305235355195</v>
       </c>
     </row>
     <row r="41">
@@ -4993,7 +4812,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.04687932565982794</v>
+        <v>-0.04324334535596183</v>
       </c>
     </row>
     <row r="42">
@@ -5003,7 +4822,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.04687932565982794</v>
+        <v>0.04324334535596183</v>
       </c>
     </row>
     <row r="43">
@@ -5013,7 +4832,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1723892536131114</v>
+        <v>-0.1473256130028743</v>
       </c>
     </row>
     <row r="44">
@@ -5023,7 +4842,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.381895478466654</v>
+        <v>1.314067408448119</v>
       </c>
     </row>
     <row r="45">
@@ -5033,7 +4852,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-7.683760514855735e-19</v>
+        <v>1.634216067761712e-18</v>
       </c>
     </row>
     <row r="46">
@@ -5043,7 +4862,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7.683760514855735e-19</v>
+        <v>-1.634216067761712e-18</v>
       </c>
     </row>
     <row r="47">
@@ -5053,7 +4872,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.808423270124363e-19</v>
+        <v>5.144082233155528e-19</v>
       </c>
     </row>
     <row r="48">
@@ -5063,7 +4882,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-1.397100197560465e-17</v>
+        <v>3.910900039925955e-17</v>
       </c>
     </row>
     <row r="49">
@@ -5075,11 +4894,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0005904382621664052,
+	L=0.0005302005204882881,
 	Y=0.0,
-	D=0.0012589771690821355,
+	D=0.0014141311605339448,
 	l_b=0.0,
-	m_b=-6.552338160818865e-05,
+	m_b=-6.694062172613041e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -5093,7 +4912,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-7.683760514855735e-19</v>
+        <v>1.634216067761712e-18</v>
       </c>
     </row>
     <row r="51">
@@ -5103,7 +4922,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-8.301831523082378e-07</v>
+        <v>-7.289864885474766e-07</v>
       </c>
     </row>
     <row r="52">
@@ -5113,7 +4932,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6.470639226974886e-18</v>
+        <v>-1.413594239683177e-17</v>
       </c>
     </row>
     <row r="53">
@@ -5125,29 +4944,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=1.0956757227437843,
+	L=1.0698722785012416,
 	Y=0.0,
-	D=0.07825480540132544,
+	D=0.07143399869162918,
 	l_b=-0.0,
-	m_b=0.1079741847549681,
+	m_b=0.09492504160609908,
 	n_b=-0.0,
-	span_effective=0.700082034708293, oswalds_efficiency=0.8165703158185763,
+	span_effective=0.7000820331081617, oswalds_efficiency=0.8136413326387908,
 ), AeroComponentResults(
-	L=0.28562931746070264,
+	L=0.24366492942638923,
 	Y=0.0,
-	D=0.021467253789769394,
+	D=0.018655800310761445,
 	l_b=-0.0,
-	m_b=-0.10794220143671768,
+	m_b=-0.09489249059848912,
 	n_b=-0.0,
-	span_effective=0.4071438111075289, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.33640090547410123, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=2.710505431213761e-20,
-	Y=-1.3971001975604652e-17,
-	D=0.002527006860184775,
-	l_b=-7.6837605148557345e-19,
-	m_b=3.270988020545509e-05,
-	n_b=6.4706392269748856e-18,
-	span_effective=0.11693340367794869, oswalds_efficiency=0.8232692748986458,
+	Y=3.9109000399259554e-17,
+	D=0.002559122190627374,
+	l_b=1.6342160677617116e-18,
+	m_b=3.366062762762295e-05,
+	n_b=-1.4135942396831773e-17,
+	span_effective=0.10890051045947362, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5159,7 +4978,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1899192631330574</v>
+        <v>0.1492358948128371</v>
       </c>
     </row>
     <row r="55">
@@ -5169,7 +4988,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3060807352752326</v>
+        <v>0.2550423719968766</v>
       </c>
     </row>
     <row r="56">
@@ -5179,7 +4998,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.04802903523890088</v>
+        <v>0.04032414292484048</v>
       </c>
     </row>
     <row r="57">
@@ -5189,7 +5008,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9052593767455703</v>
+        <v>0.706821319036679</v>
       </c>
     </row>
     <row r="58">
@@ -5199,7 +5018,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6.988755252935022e-06</v>
+        <v>2.48227145496557e-06</v>
       </c>
     </row>
     <row r="59">
@@ -5209,7 +5028,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.003220249934487996</v>
+        <v>0.0002991990472531181</v>
       </c>
     </row>
     <row r="60">
@@ -5219,7 +5038,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0490958063780883</v>
+        <v>0.06028571002997252</v>
       </c>
     </row>
     <row r="61">
@@ -5229,7 +5048,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.242047255490709e-05</v>
+        <v>-6.308359872669866e-05</v>
       </c>
     </row>
     <row r="62">
@@ -5239,7 +5058,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.385007216173159</v>
+        <v>0.3596702631069514</v>
       </c>
     </row>
     <row r="63">
@@ -5249,7 +5068,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3.946169266351761</v>
+        <v>4.120642083537414</v>
       </c>
     </row>
     <row r="64">
@@ -5259,7 +5078,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.413635694832638e-06</v>
+        <v>-1.659296967596858e-05</v>
       </c>
     </row>
     <row r="65">
@@ -5269,7 +5088,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.001138272616552083</v>
+        <v>-0.009732654147442954</v>
       </c>
     </row>
     <row r="66">
@@ -5279,7 +5098,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.498776004896007</v>
+        <v>0.7309491100831456</v>
       </c>
     </row>
     <row r="67">
@@ -5289,7 +5108,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.462100883755426e-05</v>
+        <v>-0.0002183347423412307</v>
       </c>
     </row>
     <row r="68">
@@ -5299,7 +5118,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-3.892433734384674e-18</v>
+        <v>1.070443142643919e-17</v>
       </c>
     </row>
     <row r="69">
@@ -5309,7 +5128,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.040183806542279e-22</v>
+        <v>-2.934323416224544e-22</v>
       </c>
     </row>
     <row r="70">
@@ -5319,7 +5138,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.1499341988688302</v>
+        <v>-0.1696621847927534</v>
       </c>
     </row>
     <row r="71">
@@ -5329,7 +5148,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.26322800055028</v>
+        <v>-0.2997746495015723</v>
       </c>
     </row>
     <row r="72">
@@ -5339,7 +5158,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>8.365823057123388e-19</v>
+        <v>-2.668696566238722e-18</v>
       </c>
     </row>
     <row r="73">
@@ -5349,7 +5168,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1114463936623395</v>
+        <v>0.1113100136966325</v>
       </c>
     </row>
     <row r="74">
@@ -5359,7 +5178,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
     </row>
     <row r="75">
@@ -5369,7 +5188,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-4.563704725340319e-19</v>
+        <v>-4.2546964124101e-19</v>
       </c>
     </row>
     <row r="76">
@@ -5379,7 +5198,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1301655956246374</v>
+        <v>-0.1482161274128829</v>
       </c>
     </row>
     <row r="77">
@@ -5389,7 +5208,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.5395584074505652</v>
+        <v>-0.57931475229415</v>
       </c>
     </row>
     <row r="78">
@@ -5399,7 +5218,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.3578453863819e-18</v>
+        <v>-2.115546118917234e-18</v>
       </c>
     </row>
     <row r="79">
@@ -5409,7 +5228,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.03502875234481945</v>
+        <v>0.02860661663172016</v>
       </c>
     </row>
     <row r="80">
@@ -5419,7 +5238,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.009987835178577e-06</v>
+        <v>-1.004551826244132e-06</v>
       </c>
     </row>
     <row r="81">
@@ -5429,7 +5248,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.7892338919851279</v>
+        <v>-0.4120641851964639</v>
       </c>
     </row>
     <row r="82">
@@ -5439,7 +5258,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.940823624861621e-06</v>
+        <v>-5.903426930099402e-06</v>
       </c>
     </row>
     <row r="83">
@@ -5449,7 +5268,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.002189207205635887</v>
+        <v>-0.003055762525274423</v>
       </c>
     </row>
     <row r="84">
@@ -5459,7 +5278,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-7.533849191345507</v>
+        <v>-8.507266713995831</v>
       </c>
     </row>
     <row r="85">
@@ -5469,7 +5288,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-3.16190110333429e-05</v>
+        <v>-0.0001752827143098739</v>
       </c>
     </row>
     <row r="86">
@@ -5479,7 +5298,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
     </row>
     <row r="87">
@@ -5489,7 +5308,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-4.14586001324609e-20</v>
+        <v>-3.350924762584389e-20</v>
       </c>
     </row>
     <row r="88">
@@ -5499,7 +5318,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.03416412908632467</v>
+        <v>0.0299962223873968</v>
       </c>
     </row>
     <row r="89">
@@ -5509,7 +5328,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.05499141773995983</v>
+        <v>-0.07322030889983785</v>
       </c>
     </row>
     <row r="90">
@@ -5519,7 +5338,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-6.859057942205118e-19</v>
+        <v>1.220942317636456e-18</v>
       </c>
     </row>
     <row r="91">
@@ -5529,7 +5348,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.05513066451968678</v>
+        <v>-0.06226673402358746</v>
       </c>
     </row>
     <row r="92">
@@ -5539,7 +5358,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1723892536131114</v>
+        <v>0.1473256130028743</v>
       </c>
     </row>
     <row r="93">
@@ -5549,7 +5368,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0688812103927496</v>
+        <v>0.05326256064932234</v>
       </c>
     </row>
     <row r="94">
@@ -5559,7 +5378,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.1035080432203617</v>
+        <v>0.09406305235355195</v>
       </c>
     </row>
     <row r="95">
@@ -5569,7 +5388,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.04687932565982794</v>
+        <v>-0.04324334535596183</v>
       </c>
     </row>
     <row r="96">
@@ -5579,7 +5398,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.04687932565982794</v>
+        <v>0.04324334535596183</v>
       </c>
     </row>
     <row r="97">
@@ -5589,7 +5408,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.1723892536131114</v>
+        <v>-0.1473256130028743</v>
       </c>
     </row>
     <row r="98">
@@ -5599,7 +5418,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.381895478466654</v>
+        <v>1.314067408448119</v>
       </c>
     </row>
     <row r="99">
@@ -5609,7 +5428,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-7.683760514855735e-19</v>
+        <v>1.634216067761712e-18</v>
       </c>
     </row>
     <row r="100">
@@ -5619,7 +5438,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>7.683760514855735e-19</v>
+        <v>-1.634216067761712e-18</v>
       </c>
     </row>
     <row r="101">
@@ -5629,7 +5448,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-1.808423270124363e-19</v>
+        <v>5.144082233155528e-19</v>
       </c>
     </row>
     <row r="102">
@@ -5639,7 +5458,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-1.397100197560465e-17</v>
+        <v>3.910900039925955e-17</v>
       </c>
     </row>
     <row r="103">
@@ -5651,11 +5470,11 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0005904382621664052,
+	L=0.0005302005204882881,
 	Y=0.0,
-	D=0.0012589771690821355,
+	D=0.0014141311605339448,
 	l_b=0.0,
-	m_b=-6.552338160818865e-05,
+	m_b=-6.694062172613041e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -5669,7 +5488,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-7.683760514855735e-19</v>
+        <v>1.634216067761712e-18</v>
       </c>
     </row>
     <row r="105">
@@ -5679,7 +5498,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-8.301831523082378e-07</v>
+        <v>-7.289864885474766e-07</v>
       </c>
     </row>
     <row r="106">
@@ -5689,7 +5508,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>6.470639226974886e-18</v>
+        <v>-1.413594239683177e-17</v>
       </c>
     </row>
     <row r="107">
@@ -5701,29 +5520,29 @@
       <c r="B107" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=1.0956757227437843,
+	L=1.0698722785012416,
 	Y=0.0,
-	D=0.07825480540132544,
+	D=0.07143399869162918,
 	l_b=-0.0,
-	m_b=0.1079741847549681,
+	m_b=0.09492504160609908,
 	n_b=-0.0,
-	span_effective=0.700082034708293, oswalds_efficiency=0.8165703158185763,
+	span_effective=0.7000820331081617, oswalds_efficiency=0.8136413326387908,
 ), AeroComponentResults(
-	L=0.28562931746070264,
+	L=0.24366492942638923,
 	Y=0.0,
-	D=0.021467253789769394,
+	D=0.018655800310761445,
 	l_b=-0.0,
-	m_b=-0.10794220143671768,
+	m_b=-0.09489249059848912,
 	n_b=-0.0,
-	span_effective=0.4071438111075289, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.33640090547410123, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=2.710505431213761e-20,
-	Y=-1.3971001975604652e-17,
-	D=0.002527006860184775,
-	l_b=-7.6837605148557345e-19,
-	m_b=3.270988020545509e-05,
-	n_b=6.4706392269748856e-18,
-	span_effective=0.11693340367794869, oswalds_efficiency=0.8232692748986458,
+	Y=3.9109000399259554e-17,
+	D=0.002559122190627374,
+	l_b=1.6342160677617116e-18,
+	m_b=3.366062762762295e-05,
+	n_b=-1.4135942396831773e-17,
+	span_effective=0.10890051045947362, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5735,7 +5554,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.1899192631330574</v>
+        <v>0.1492358948128371</v>
       </c>
     </row>
     <row r="109">
@@ -5745,7 +5564,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.3060807352752326</v>
+        <v>0.2550423719968766</v>
       </c>
     </row>
   </sheetData>
@@ -5841,10 +5660,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.381895478466654</v>
+        <v>1.314067408448119</v>
       </c>
       <c r="C2" t="n">
-        <v>1.381895488457083</v>
+        <v>1.314067416149759</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -5859,16 +5678,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.990429816753021e-09</v>
+        <v>-7.701639548329808e-09</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.990429816753021e-09</v>
+        <v>-7.701639548329808e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-7.229511855420815e-09</v>
+        <v>-5.860916611794357e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -5881,7 +5700,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1723892536131114</v>
+        <v>0.1473256130028743</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -5899,16 +5718,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.1713892536131114</v>
+        <v>0.1463256130028743</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.1713892536131114</v>
+        <v>0.1463256130028743</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1713892536131114</v>
+        <v>0.1463256130028743</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -5921,7 +5740,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.009987835178577e-06</v>
+        <v>-1.004551826244132e-06</v>
       </c>
       <c r="C4" t="n">
         <v>-1e-06</v>
@@ -5941,18 +5760,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-9.987835178576707e-09</v>
+        <v>-4.551826244131708e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.009987835178577e-06</v>
+        <v>2.004551826244132e-06</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.987835178576707e-09</v>
+        <v>-4.551826244131708e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.987835178576707e-09</v>
+        <v>-4.551826244131708e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -5965,7 +5784,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -5985,22 +5804,22 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="I5" t="n">
-        <v>3.011763798644184e-19</v>
+        <v>-6.292884784522545e-19</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="K5" t="n">
-        <v>3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009999999999999998</v>
+        <v>0.0009999999999999994</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0009999999999999998</v>
+        <v>0.0009999999999999994</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -6013,7 +5832,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -6033,22 +5852,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.536262932741319e-18</v>
+        <v>5.443335099852945e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>5.443335099852945e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009999999999999974</v>
+        <v>0.0009999999999999946</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009999999999999974</v>
+        <v>0.0009999999999999946</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -6061,7 +5880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.385007216173159</v>
+        <v>0.3596702631069514</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -6080,15 +5899,15 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.8149927838268409</v>
+        <v>0.8403297368930486</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.8149927838268409</v>
+        <v>0.8403297368930486</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6791606531890342</v>
+        <v>0.7002747807442071</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -6101,7 +5920,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.016134703895203</v>
+        <v>8.919476944056441</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -6119,16 +5938,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.016134703895203</v>
+        <v>2.919476944056441</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>2.016134703895203</v>
+        <v>2.919476944056441</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2515095839040132</v>
+        <v>0.3273148147999705</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -6141,7 +5960,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.489403328184636</v>
+        <v>9.307585668421478</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -6159,16 +5978,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.489403328184636</v>
+        <v>7.307585668421478</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>6.489403328184636</v>
+        <v>7.307585668421478</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7644121827313772</v>
+        <v>0.7851215050552212</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -6181,7 +6000,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.489403328184636</v>
+        <v>9.307585668421478</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -6200,15 +6019,15 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>11.51059667181536</v>
+        <v>10.69241433157852</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>11.51059667181536</v>
+        <v>10.69241433157852</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5755298335907681</v>
+        <v>0.5346207165789261</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -6221,7 +6040,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>94066.68509676102</v>
+        <v>88385.39754700637</v>
       </c>
       <c r="C11" t="n">
         <v>20000</v>
@@ -6239,16 +6058,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>74066.68509676102</v>
+        <v>68385.39754700637</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>74066.68509676102</v>
+        <v>68385.39754700637</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7873848751082582</v>
+        <v>0.7737182775088689</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -6261,7 +6080,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2000000098107236</v>
+        <v>0.09999999438017741</v>
       </c>
       <c r="C12" t="n">
         <v>0.05</v>
@@ -6279,16 +6098,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.1500000098107235</v>
+        <v>0.04999999438017741</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.1500000098107235</v>
+        <v>0.04999999438017741</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1500000098107235</v>
+        <v>0.04999999438017741</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -6301,11 +6120,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2000000098107236</v>
+        <v>0.09999999438017741</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
         <v>1e-06</v>
@@ -6320,15 +6139,15 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>-9.810723539116495e-09</v>
+        <v>5.619822593394552e-09</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-9.810723539116495e-09</v>
+        <v>5.619822593394552e-09</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.810723539116495e-09</v>
+        <v>5.619822593394552e-09</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -6341,7 +6160,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5558482021720921</v>
+        <v>0.5044402178041257</v>
       </c>
       <c r="C14" t="n">
         <v>0.5</v>
@@ -6359,16 +6178,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.05584820217209208</v>
+        <v>0.004440217804125735</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.05584820217209208</v>
+        <v>0.004440217804125735</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05584820217209208</v>
+        <v>0.004440217804125735</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -6381,7 +6200,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5558482021720921</v>
+        <v>0.5044402178041257</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
@@ -6400,15 +6219,15 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.4441517978279079</v>
+        <v>0.4955597821958743</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.4441517978279079</v>
+        <v>0.4955597821958743</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4441517978279079</v>
+        <v>0.4955597821958743</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -6421,7 +6240,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02999999002463568</v>
+        <v>0.02999999591331827</v>
       </c>
       <c r="C16" t="n">
         <v>0.03</v>
@@ -6439,16 +6258,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.975364319292357e-09</v>
+        <v>-4.0866817256624e-09</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-9.975364319292357e-09</v>
+        <v>-4.0866817256624e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.975364319292357e-09</v>
+        <v>-4.0866817256624e-09</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -6461,7 +6280,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02999999002463568</v>
+        <v>0.02999999591331827</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
@@ -6480,15 +6299,15 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.05000000997536432</v>
+        <v>0.05000000408668173</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.05000000997536432</v>
+        <v>0.05000000408668173</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05000000997536432</v>
+        <v>0.05000000408668173</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -6501,7 +6320,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1301655956246374</v>
+        <v>-0.1482161274128829</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -6520,15 +6339,15 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.1301655956246374</v>
+        <v>0.1482161274128829</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.1301655956246374</v>
+        <v>0.1482161274128829</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1301655956246374</v>
+        <v>0.1482161274128829</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -6541,7 +6360,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.03416412908632467</v>
+        <v>0.0299962223873968</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -6559,16 +6378,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.03416412908632467</v>
+        <v>0.0299962223873968</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0.03416412908632467</v>
+        <v>0.0299962223873968</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03416412908632467</v>
+        <v>0.0299962223873968</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -6581,7 +6400,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.5395584074505652</v>
+        <v>-0.57931475229415</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -6600,15 +6419,15 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.5394584074505652</v>
+        <v>0.57921475229415</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.5394584074505652</v>
+        <v>0.57921475229415</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5394584074505652</v>
+        <v>0.57921475229415</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -6621,7 +6440,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.605487237063405</v>
+        <v>5.905933264278247</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -6653,7 +6472,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>163.0920617807786</v>
+        <v>190.2712995487436</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -6685,7 +6504,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.03437008016121631</v>
+        <v>0.03103953816621339</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -6717,7 +6536,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.326009071516924e-05</v>
+        <v>4.702093498522415e-05</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -6736,15 +6555,15 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.007146739909284831</v>
+        <v>0.007152979065014776</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.007146739909284831</v>
+        <v>0.007152979065014776</v>
       </c>
       <c r="M24" t="n">
-        <v>0.007146739909284831</v>
+        <v>0.007152979065014776</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -6757,7 +6576,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.191509007190641e-05</v>
+        <v>1.450759516399133e-05</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
@@ -6776,15 +6595,15 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.007178084909928093</v>
+        <v>0.007185492404836008</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.007178084909928093</v>
+        <v>0.007185492404836008</v>
       </c>
       <c r="M25" t="n">
-        <v>0.007178084909928093</v>
+        <v>0.007185492404836008</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -6797,7 +6616,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.826630830291486e-06</v>
+        <v>2.679583388112769e-06</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -6816,15 +6635,15 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.007197173369169708</v>
+        <v>0.007197320416611887</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0.007197173369169708</v>
+        <v>0.007197320416611887</v>
       </c>
       <c r="M26" t="n">
-        <v>0.007197173369169708</v>
+        <v>0.007197320416611887</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -6837,7 +6656,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.181709548775771</v>
+        <v>4.522872254052008</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -6869,7 +6688,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.385007216173159</v>
+        <v>0.3596702631069514</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -6901,7 +6720,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-13.05653267986326</v>
+        <v>-0.7365326411904274</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -6933,7 +6752,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5.440485503569021</v>
+        <v>2.571516961762562</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -6965,7 +6784,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.009987835178577e-06</v>
+        <v>-1.004551826244132e-06</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -6997,7 +6816,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5395584074505652</v>
+        <v>-0.57931475229415</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -7029,7 +6848,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>171.0246568338559</v>
+        <v>102.3793920419568</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -7061,7 +6880,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>121.0246568464731</v>
+        <v>52.37940784031489</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -7093,7 +6912,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>171.0246568464731</v>
+        <v>102.3794078403149</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -7125,7 +6944,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6.677006654063078e-17</v>
+        <v>1.060388543299999e-16</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -7157,7 +6976,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.112396518263171</v>
+        <v>0.1472207713764126</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -7189,7 +7008,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.305569024969542e-15</v>
+        <v>3.030457717975491e-15</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -7221,7 +7040,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.003385495155179471</v>
+        <v>0.001817246788802192</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -7253,7 +7072,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01628575244430116</v>
+        <v>0.01345603621896405</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
@@ -7285,7 +7104,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1338198671999475</v>
+        <v>0.1659353775819366</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -7399,18 +7218,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nominal Trim Cm tolerance</t>
+          <t>Lift &gt;= Weight</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.009987835178577e-06</v>
+        <v>1.314067408448119</v>
       </c>
       <c r="C2" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1e-06</v>
-      </c>
+        <v>1.314067416149759</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1e-06</v>
       </c>
@@ -7423,18 +7240,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.987835178576707e-09</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.009987835178577e-06</v>
-      </c>
+        <v>-7.701639548329808e-09</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.987835178576707e-09</v>
+        <v>-7.701639548329808e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.987835178576707e-09</v>
+        <v>-5.860916611794357e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -7443,16 +7258,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vv minimum</t>
+          <t>Nominal Trim Cm tolerance</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02999999002463568</v>
+        <v>-1.004551826244132e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>-1e-06</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="E3" t="n">
         <v>1e-06</v>
       </c>
@@ -7465,16 +7282,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-9.975364319292357e-09</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>-4.551826244131708e-09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.004551826244132e-06</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-9.975364319292357e-09</v>
+        <v>-4.551826244131708e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.975364319292357e-09</v>
+        <v>-4.551826244131708e-09</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -7483,16 +7302,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Static margin maximum</t>
+          <t>Vv minimum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2000000098107236</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.02999999591331827</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>1e-06</v>
       </c>
@@ -7504,17 +7323,17 @@
           <t>ineq</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>-9.810723539116495e-09</v>
-      </c>
+      <c r="H4" t="n">
+        <v>-4.0866817256624e-09</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.810723539116495e-09</v>
+        <v>-4.0866817256624e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.810723539116495e-09</v>
+        <v>-4.0866817256624e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -7523,16 +7342,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lift &gt;= Weight</t>
+          <t>Static margin maximum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.381895478466654</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.381895488457083</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>0.09999999438017741</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.1</v>
+      </c>
       <c r="E5" t="n">
         <v>1e-06</v>
       </c>
@@ -7544,17 +7363,17 @@
           <t>ineq</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>-9.990429816753021e-09</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>5.619822593394552e-09</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-9.990429816753021e-09</v>
+        <v>5.619822593394552e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.229511855420815e-09</v>
+        <v>5.619822593394552e-09</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -7567,7 +7386,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -7587,22 +7406,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.536262932741319e-18</v>
+        <v>5.443335099852945e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>-5.443335099852945e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>2.536262932741319e-18</v>
+        <v>5.443335099852945e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009999999999999974</v>
+        <v>0.0009999999999999946</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009999999999999974</v>
+        <v>0.0009999999999999946</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -7615,7 +7434,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -7635,22 +7454,22 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="I7" t="n">
-        <v>3.011763798644184e-19</v>
+        <v>-6.292884784522545e-19</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="K7" t="n">
-        <v>3.011763798644184e-19</v>
+        <v>6.292884784522545e-19</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009999999999999998</v>
+        <v>0.0009999999999999994</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009999999999999998</v>
+        <v>0.0009999999999999994</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -7667,7 +7486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7689,7 +7508,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -7709,7 +7528,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.9996636160172002</v>
       </c>
     </row>
     <row r="5">
@@ -7719,7 +7538,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9973159716987698</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -7735,67 +7554,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[13]</t>
+          <t>iterations.alpha_du[1]</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.6847829902381042</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[14]</t>
+          <t>iterations.alpha_du[2]</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.9874371023721598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[15]</t>
+          <t>iterations.alpha_du[3]</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.2321570989082681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[1]</t>
+          <t>iterations.alpha_du[4]</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8695588035970125</v>
+        <v>0.4654507073226779</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[2]</t>
+          <t>iterations.alpha_du[5]</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7453311880063755</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[3]</t>
+          <t>iterations.alpha_du[6]</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.9999120038967072</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[4]</t>
+          <t>iterations.alpha_du[7]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7805,7 +7624,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[5]</t>
+          <t>iterations.alpha_du[8]</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -7815,7 +7634,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[6]</t>
+          <t>iterations.alpha_du[9]</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7825,17 +7644,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[7]</t>
+          <t>iterations.alpha_pr[0]</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[8]</t>
+          <t>iterations.alpha_pr[10]</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -7845,7 +7664,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[9]</t>
+          <t>iterations.alpha_pr[11]</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7855,987 +7674,989 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[0]</t>
+          <t>iterations.alpha_pr[12]</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[10]</t>
+          <t>iterations.alpha_pr[1]</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0.1617228598894004</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[11]</t>
+          <t>iterations.alpha_pr[2]</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0.3905858655626279</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[12]</t>
+          <t>iterations.alpha_pr[3]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.990561915582554</v>
+        <v>0.1103043814562606</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[13]</t>
+          <t>iterations.alpha_pr[4]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0.6897797272268273</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[14]</t>
+          <t>iterations.alpha_pr[5]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0.7251411927248902</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[15]</t>
+          <t>iterations.alpha_pr[6]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0.8857405524990868</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[1]</t>
+          <t>iterations.alpha_pr[7]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1841698804006667</v>
+        <v>0.8523810244065889</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[2]</t>
+          <t>iterations.alpha_pr[8]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1744191010923265</v>
+        <v>0.798994431395973</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[3]</t>
+          <t>iterations.alpha_pr[9]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2747435512240049</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[4]</t>
+          <t>iterations.d_norm[0]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8138735300488935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[5]</t>
+          <t>iterations.d_norm[10]</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9073522984905922</v>
+        <v>0.07374570341615129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[6]</t>
+          <t>iterations.d_norm[11]</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8195713998759652</v>
+        <v>0.001059309326154644</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[7]</t>
+          <t>iterations.d_norm[12]</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.756715670987304</v>
+        <v>0.000199535353898185</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[8]</t>
+          <t>iterations.d_norm[1]</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8497056588344294</v>
+        <v>0.2993376542532629</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[9]</t>
+          <t>iterations.d_norm[2]</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9762557900019193</v>
+        <v>0.3560925407607093</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iterations.d_norm[0]</t>
+          <t>iterations.d_norm[3]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>96.67721813817909</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iterations.d_norm[10]</t>
+          <t>iterations.d_norm[4]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.04433152731960267</v>
+        <v>18.35646437219289</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iterations.d_norm[11]</t>
+          <t>iterations.d_norm[5]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.005889165940314859</v>
+        <v>4.88112524025567</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iterations.d_norm[12]</t>
+          <t>iterations.d_norm[6]</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.04385908849175971</v>
+        <v>4.263908672901895</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iterations.d_norm[13]</t>
+          <t>iterations.d_norm[7]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2112783470201302</v>
+        <v>1.132744489894867</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iterations.d_norm[14]</t>
+          <t>iterations.d_norm[8]</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1135833105427513</v>
+        <v>0.4697613894334244</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iterations.d_norm[15]</t>
+          <t>iterations.d_norm[9]</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.05281005041817935</v>
+        <v>0.5470645740644593</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>iterations.d_norm[1]</t>
+          <t>iterations.inf_du[0]</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.078634897574489</v>
+        <v>0.9853449153935951</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iterations.d_norm[2]</t>
+          <t>iterations.inf_du[10]</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4.193052402585394</v>
+        <v>0.003138683724341007</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iterations.d_norm[3]</t>
+          <t>iterations.inf_du[11]</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16.19596884554542</v>
+        <v>1.166780672079426e-09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iterations.d_norm[4]</t>
+          <t>iterations.inf_du[12]</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.882658903545234</v>
+        <v>1.401772031783821e-10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iterations.d_norm[5]</t>
+          <t>iterations.inf_du[1]</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6450909206167239</v>
+        <v>2.676560704601611</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iterations.d_norm[6]</t>
+          <t>iterations.inf_du[2]</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.34780476720436</v>
+        <v>11.47426744118759</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iterations.d_norm[7]</t>
+          <t>iterations.inf_du[3]</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3.327814778762712</v>
+        <v>17.13203696477353</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iterations.d_norm[8]</t>
+          <t>iterations.inf_du[4]</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.236876107552781</v>
+        <v>12.89445931790572</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iterations.d_norm[9]</t>
+          <t>iterations.inf_du[5]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3071213350370104</v>
+        <v>0.8669773392669988</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iterations.inf_du[0]</t>
+          <t>iterations.inf_du[6]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9545759034129052</v>
+        <v>0.6050650372946569</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iterations.inf_du[10]</t>
+          <t>iterations.inf_du[7]</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0001452643769042083</v>
+        <v>0.3161282450582608</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iterations.inf_du[11]</t>
+          <t>iterations.inf_du[8]</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01061171300692143</v>
+        <v>0.900147679623549</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iterations.inf_du[12]</t>
+          <t>iterations.inf_du[9]</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.003653837950373884</v>
+        <v>0.0009599686266426044</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iterations.inf_du[13]</t>
+          <t>iterations.inf_pr[0]</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6.430315565353339e-06</v>
+        <v>0.09451374970420925</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iterations.inf_du[14]</t>
+          <t>iterations.inf_pr[10]</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.114267019237559e-07</v>
+        <v>5.03542992547068e-06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>iterations.inf_du[15]</t>
+          <t>iterations.inf_pr[11]</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4.674262754633673e-09</v>
+        <v>1.075363798008766e-09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iterations.inf_du[1]</t>
+          <t>iterations.inf_pr[12]</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>16.5271815113038</v>
+        <v>4.018474442091247e-11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iterations.inf_du[2]</t>
+          <t>iterations.inf_pr[1]</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>38.43302884143124</v>
+        <v>0.0792921482767136</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iterations.inf_du[3]</t>
+          <t>iterations.inf_pr[2]</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>60.40652897372787</v>
+        <v>0.0503784205899377</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>iterations.inf_du[4]</t>
+          <t>iterations.inf_pr[3]</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6.273314933237373</v>
+        <v>0.1979352779221735</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iterations.inf_du[5]</t>
+          <t>iterations.inf_pr[4]</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.275006790258558</v>
+        <v>0.06880734480866657</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iterations.inf_du[6]</t>
+          <t>iterations.inf_pr[5]</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.290709283206298</v>
+        <v>0.02791432869876864</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iterations.inf_du[7]</t>
+          <t>iterations.inf_pr[6]</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2.956557412044539</v>
+        <v>0.01342583811829989</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iterations.inf_du[8]</t>
+          <t>iterations.inf_pr[7]</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.706440096871027</v>
+        <v>0.008053542700974248</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iterations.inf_du[9]</t>
+          <t>iterations.inf_pr[8]</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0417606889005171</v>
+        <v>0.002054668548739258</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[0]</t>
+          <t>iterations.inf_pr[9]</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.09696628842104291</v>
+        <v>0.0003117194555493086</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[10]</t>
+          <t>iterations.mu[0]</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.857549047912244e-06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[11]</t>
+          <t>iterations.mu[10]</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4.727152697059367e-09</v>
+        <v>8.060972617830917e-07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[12]</t>
+          <t>iterations.mu[11]</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>7.644981564469688e-09</v>
+        <v>1.018406499547601e-07</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[13]</t>
+          <t>iterations.mu[12]</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3.96880836528446e-09</v>
+        <v>2.156009637953364e-09</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[14]</t>
+          <t>iterations.mu[1]</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6.317296815869233e-11</v>
+        <v>6.356493767471419e-06</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[15]</t>
+          <t>iterations.mu[2]</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3.61002061577409e-11</v>
+        <v>0.05827285322202955</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[1]</t>
+          <t>iterations.mu[3]</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.08056408675789051</v>
+        <v>0.03373382487231333</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[2]</t>
+          <t>iterations.mu[4]</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.06724205920869081</v>
+        <v>0.03821317552353903</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[3]</t>
+          <t>iterations.mu[5]</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.04725390342973679</v>
+        <v>0.01087314713537807</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[4]</t>
+          <t>iterations.mu[6]</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.04365719331379392</v>
+        <v>0.001736282508296501</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[5]</t>
+          <t>iterations.mu[7]</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.001928854673058922</v>
+        <v>0.0004433477610378459</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[6]</t>
+          <t>iterations.mu[8]</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.008694077208617479</v>
+        <v>0.0001260113916752002</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[7]</t>
+          <t>iterations.mu[9]</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.01270562742753967</v>
+        <v>4.10059921209524e-06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[8]</t>
+          <t>iterations.obj[0]</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.002809957848590727</v>
+        <v>2.11092482469256</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[9]</t>
+          <t>iterations.obj[10]</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.000184637957667988</v>
+        <v>1.772381096799994</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iterations.mu[0]</t>
+          <t>iterations.obj[11]</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>1.772376549443898</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iterations.mu[10]</t>
+          <t>iterations.obj[12]</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.90217338042289e-06</v>
+        <v>1.772375861260131</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iterations.mu[11]</t>
+          <t>iterations.obj[1]</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4.21420113508245e-07</v>
+        <v>2.09662413151326</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>iterations.mu[12]</t>
+          <t>iterations.obj[2]</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4.13890221288537e-08</v>
+        <v>2.05124748020444</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>iterations.mu[13]</t>
+          <t>iterations.obj[3]</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.658123934185443e-09</v>
+        <v>1.814113989824313</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iterations.mu[14]</t>
+          <t>iterations.obj[4]</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7.155658304627041e-11</v>
+        <v>1.802996476571388</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>iterations.mu[15]</t>
+          <t>iterations.obj[5]</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9.999999999999999e-12</v>
+        <v>1.810146991244163</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iterations.mu[1]</t>
+          <t>iterations.obj[6]</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.1980754861799579</v>
+        <v>1.791550815976863</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iterations.mu[2]</t>
+          <t>iterations.obj[7]</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9.529436303557169e-07</v>
+        <v>1.776302148631285</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iterations.mu[3]</t>
+          <t>iterations.obj[8]</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.06531265460594078</v>
+        <v>1.773603446662081</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iterations.mu[4]</t>
+          <t>iterations.obj[9]</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.07239469536400245</v>
+        <v>1.772431565134674</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iterations.mu[5]</t>
+          <t>iterations.regularization_size[0]</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.00815004317151272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iterations.mu[6]</t>
+          <t>iterations.regularization_size[10]</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.002634337937762354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iterations.mu[7]</t>
+          <t>iterations.regularization_size[11]</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0008211406080667111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iterations.mu[8]</t>
+          <t>iterations.regularization_size[12]</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0003185986999670291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>iterations.mu[9]</t>
+          <t>iterations.regularization_size[1]</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4.224445327306245e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iterations.obj[0]</t>
+          <t>iterations.regularization_size[2]</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.891556931836755</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>iterations.obj[10]</t>
+          <t>iterations.regularization_size[3]</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.791866130647261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>iterations.obj[11]</t>
+          <t>iterations.regularization_size[4]</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1.791856049859151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iterations.obj[12]</t>
+          <t>iterations.regularization_size[5]</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.791852928964671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iterations.obj[13]</t>
+          <t>iterations.regularization_size[6]</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1.791852639517245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iterations.obj[14]</t>
+          <t>iterations.regularization_size[7]</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1.791852611769461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iterations.obj[15]</t>
+          <t>iterations.regularization_size[8]</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.79185260855713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iterations.obj[1]</t>
+          <t>iterations.regularization_size[9]</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.555382562575581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iterations.obj[2]</t>
+          <t>n_call_callback_fun</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.601570595398571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iterations.obj[3]</t>
+          <t>n_call_nlp_f</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.634083941494519</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iterations.obj[4]</t>
+          <t>n_call_nlp_g</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.887549754148789</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>iterations.obj[5]</t>
+          <t>n_call_nlp_grad</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.873910259886061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>iterations.obj[6]</t>
+          <t>n_call_nlp_grad_f</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.826779056485769</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>iterations.obj[7]</t>
+          <t>n_call_nlp_hess_l</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.801915776259836</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iterations.obj[8]</t>
+          <t>n_call_nlp_jac_g</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1.795358394615814</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iterations.obj[9]</t>
+          <t>n_call_total</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.79215914772873</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[0]</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
+          <t>return_status</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Solve_Succeeded</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[10]</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="B116" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[11]</t>
+          <t>t_proc_callback_fun</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -8845,27 +8666,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[12]</t>
+          <t>t_proc_nlp_f</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[13]</t>
+          <t>t_proc_nlp_g</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>0.4630000000000002</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[14]</t>
+          <t>t_proc_nlp_grad</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -8875,47 +8696,47 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[15]</t>
+          <t>t_proc_nlp_grad_f</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>0.4740000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[1]</t>
+          <t>t_proc_nlp_hess_l</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>5.056000000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[2]</t>
+          <t>t_proc_nlp_jac_g</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[3]</t>
+          <t>t_proc_total</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>7.982</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[4]</t>
+          <t>t_wall_callback_fun</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -8925,27 +8746,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[5]</t>
+          <t>t_wall_nlp_f</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>0.232565</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[6]</t>
+          <t>t_wall_nlp_g</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>0.46363</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[7]</t>
+          <t>t_wall_nlp_grad</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -8955,292 +8776,50 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[8]</t>
+          <t>t_wall_nlp_grad_f</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>0.4707680000000001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[9]</t>
+          <t>t_wall_nlp_hess_l</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>5.056382</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>n_call_callback_fun</t>
+          <t>t_wall_nlp_jac_g</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>1.735678</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>n_call_nlp_f</t>
+          <t>t_wall_total</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>17</v>
+        <v>7.983066</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>n_call_nlp_g</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>n_call_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>n_call_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>n_call_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>n_call_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>n_call_total</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>return_status</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Solve_Succeeded</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="B140" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>t_proc_callback_fun</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_f</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_g</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0.5750000000000002</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0.608</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>7.518000000000001</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>2.427</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>t_proc_total</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>11.442</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>t_wall_callback_fun</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_f</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0.279849</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_g</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>0.5752290000000001</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>0.608633</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>7.518521999999999</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>2.427948</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>t_wall_total</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>11.441171</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
           <t>unified_return_status</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>SOLVER_RET_SUCCESS</t>
         </is>
@@ -9257,7 +8836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9302,10 +8881,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7484904106847665</v>
+        <v>0.7287422796956008</v>
       </c>
       <c r="E2" t="n">
-        <v>41.77187381988302</v>
+        <v>41.1166895027264</v>
       </c>
     </row>
     <row r="3">
@@ -9323,133 +8902,112 @@
         <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.563464011603296</v>
+        <v>0.5358073052598403</v>
       </c>
       <c r="E3" t="n">
-        <v>31.44589063366207</v>
+        <v>30.2310202351148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J_ballast</t>
+          <t>J_trim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>w_ballast</t>
+          <t>w_trim_effort</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.971588330453208e-07</v>
+        <v>1.083697776233297e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.216470434837432e-05</v>
+        <v>0.0006114379009104792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J_trim</t>
+          <t>J_wing_deflection</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>w_trim_effort</t>
+          <t>w_wing_deflection</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0006187130069220122</v>
+        <v>0.3280847114488961</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03452923549444306</v>
+        <v>18.51101217411261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J_wing_deflection</t>
+          <t>J_htail_deflection</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>w_wing_deflection</t>
+          <t>w_htail_deflection</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3301844120382679</v>
+        <v>0.1659353775819366</v>
       </c>
       <c r="E6" t="n">
-        <v>18.4269850355686</v>
+        <v>9.362313108008546</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J_htail_deflection</t>
+          <t>J_roll_tau</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>w_htail_deflection</t>
+          <t>w_roll_tau</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1338198671999475</v>
+        <v>0.01379535029609484</v>
       </c>
       <c r="E7" t="n">
-        <v>7.46824077833637</v>
+        <v>0.7783535421367435</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J_roll_tau</t>
+          <t>J_total</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>w_roll_tau</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.2</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.0152755911827628</v>
+        <v>1.772375861260131</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8525026617598482</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>J_total</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
-        <v>1.79185260855713</v>
-      </c>
-      <c r="E9" t="n">
         <v>100</v>
       </c>
     </row>
@@ -9464,7 +9022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9521,7 +9079,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.181709548775771</v>
+        <v>4.522872254052008</v>
       </c>
       <c r="C2" t="n">
         <v>-4</v>
@@ -9554,7 +9112,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.677006654063078e-17</v>
+        <v>1.060388543299999e-16</v>
       </c>
       <c r="C3" t="n">
         <v>-30</v>
@@ -9587,7 +9145,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.112396518263171</v>
+        <v>-0.1472207713764126</v>
       </c>
       <c r="C4" t="n">
         <v>-30</v>
@@ -9620,7 +9178,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.305569024969542e-15</v>
+        <v>3.030457717975491e-15</v>
       </c>
       <c r="C5" t="n">
         <v>-30</v>
@@ -9653,7 +9211,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.70000000699319</v>
+        <v>0.7000000053932461</v>
       </c>
       <c r="C6" t="n">
         <v>0.3</v>
@@ -9690,7 +9248,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2290084178524724</v>
+        <v>0.198625050198878</v>
       </c>
       <c r="C7" t="n">
         <v>0.1</v>
@@ -9723,7 +9281,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.499999994540779</v>
+        <v>0.5000000042301929</v>
       </c>
       <c r="C8" t="n">
         <v>0.5</v>
@@ -9760,7 +9318,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6712501614845966</v>
+        <v>0.6588701626881606</v>
       </c>
       <c r="C9" t="n">
         <v>0.35</v>
@@ -9793,7 +9351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4071438111075289</v>
+        <v>0.3364009054741012</v>
       </c>
       <c r="C10" t="n">
         <v>0.2</v>
@@ -9826,7 +9384,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1169334036779487</v>
+        <v>0.1089005104594736</v>
       </c>
       <c r="C11" t="n">
         <v>0.1</v>
@@ -9851,76 +9409,6 @@
         <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ballast_mass_kg</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>5e-06</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>lower</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>[WARN] ballast_mass_kg hit lower bound (value=0, lower=0, tol=5e-06).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ballast_slider_eta</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.02358254083198405</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41c01f7-dirty</t>
+          <t>7ebfbdb-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8.251428584143424</v>
+        <v>11.5714285892593</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.921516959065938</v>
+        <v>2.694648090102857</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.571516961762562</v>
+        <v>3.344648092799479</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.7365326411904274</v>
+        <v>-4.056532646306307</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.762159557447057</v>
+        <v>3.270978423292568</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.05309394686325974</v>
+        <v>0.04483488846230822</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>102.3793920419568</v>
+        <v>122.7866075300728</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52.37940784031489</v>
+        <v>72.78660892279186</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>102.3794078403149</v>
+        <v>122.7866089227919</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>102.3794078403149</v>
+        <v>122.7866089227919</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.251428584143424</v>
+        <v>11.5714285892593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.921516959065938</v>
+        <v>2.694648090102857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.571516961762562</v>
+        <v>3.344648092799479</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.7365326411904274</v>
+        <v>-4.056532646306307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.05309394686325974</v>
+        <v>0.04483488846230822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>102.3793920419568</v>
+        <v>122.7866075300728</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>52.37940784031489</v>
+        <v>72.78660892279186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>102.3794078403149</v>
+        <v>122.7866089227919</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>102.3794078403149</v>
+        <v>122.7866089227919</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7365326411904274</v>
+        <v>-4.056532646306307</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.571516961762562</v>
+        <v>3.344648092799479</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>102.3793920419568</v>
+        <v>122.7866075300728</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>52.37940784031489</v>
+        <v>72.78660892279186</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>102.3794078403149</v>
+        <v>122.7866089227919</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.233</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="119">
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4630000000000002</v>
+        <v>0.3760000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4740000000000001</v>
+        <v>0.4010000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5.056000000000001</v>
+        <v>4.352</v>
       </c>
     </row>
     <row r="123">
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.734</v>
+        <v>1.581</v>
       </c>
     </row>
     <row r="124">
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>7.982</v>
+        <v>6.927</v>
       </c>
     </row>
     <row r="125">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.232565</v>
+        <v>0.185183</v>
       </c>
     </row>
     <row r="127">
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.46363</v>
+        <v>0.3781220000000001</v>
       </c>
     </row>
     <row r="128">
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4707680000000001</v>
+        <v>0.401359</v>
       </c>
     </row>
     <row r="130">
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>5.056382</v>
+        <v>4.347157</v>
       </c>
     </row>
     <row r="131">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.735678</v>
+        <v>1.583032</v>
       </c>
     </row>
     <row r="132">
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>7.983066</v>
+        <v>6.926352</v>
       </c>
     </row>
     <row r="133">

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9f2c90c-dirty</t>
+          <t>93578c8-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.5580000000000003</v>
+        <v>1.034</v>
       </c>
     </row>
     <row r="223">
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1.159</v>
+        <v>2.062</v>
       </c>
     </row>
     <row r="224">
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.9230000000000005</v>
+        <v>1.855</v>
       </c>
     </row>
     <row r="226">
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>10.534</v>
+        <v>18.065</v>
       </c>
     </row>
     <row r="227">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>3.543000000000001</v>
+        <v>6.021</v>
       </c>
     </row>
     <row r="228">
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>16.781</v>
+        <v>29.133</v>
       </c>
     </row>
     <row r="229">
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.562148</v>
+        <v>1.029228</v>
       </c>
     </row>
     <row r="231">
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.150602</v>
+        <v>2.063758</v>
       </c>
     </row>
     <row r="232">
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.926215</v>
+        <v>1.856062</v>
       </c>
     </row>
     <row r="234">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>10.539897</v>
+        <v>18.067515</v>
       </c>
     </row>
     <row r="235">
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>3.535993000000001</v>
+        <v>6.022767000000001</v>
       </c>
     </row>
     <row r="236">
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>16.780467</v>
+        <v>29.133203</v>
       </c>
     </row>
     <row r="237">

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93578c8-dirty</t>
+          <t>914634d-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1.034</v>
+        <v>0.6740000000000003</v>
       </c>
     </row>
     <row r="223">
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2.062</v>
+        <v>1.323000000000001</v>
       </c>
     </row>
     <row r="224">
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1.855</v>
+        <v>1.045</v>
       </c>
     </row>
     <row r="226">
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>18.065</v>
+        <v>11.885</v>
       </c>
     </row>
     <row r="227">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>6.021</v>
+        <v>3.960999999999999</v>
       </c>
     </row>
     <row r="228">
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>29.133</v>
+        <v>18.971</v>
       </c>
     </row>
     <row r="229">
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1.029228</v>
+        <v>0.666415</v>
       </c>
     </row>
     <row r="231">
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2.063758</v>
+        <v>1.323642</v>
       </c>
     </row>
     <row r="232">
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.856062</v>
+        <v>1.0483</v>
       </c>
     </row>
     <row r="234">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>18.067515</v>
+        <v>11.886728</v>
       </c>
     </row>
     <row r="235">
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>6.022767000000001</v>
+        <v>3.961224</v>
       </c>
     </row>
     <row r="236">
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>29.133203</v>
+        <v>18.970762</v>
       </c>
     </row>
     <row r="237">

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>914634d-dirty</t>
+          <t>aadd597-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.166267395045595</v>
+        <v>2.166267395059844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.563971623321324</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4639716232510613</v>
+        <v>0.463971623321324</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.563971623321324</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.808035465986087</v>
+        <v>3.808035466072172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.86535588595925e-15</v>
+        <v>-2.5522288122537e-16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1140304863710548</v>
+        <v>-0.1140304864151476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.367107440935978e-14</v>
+        <v>6.587616550414456e-15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.808035465986087</v>
+        <v>3.808035466072172</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.86535588595925e-15</v>
+        <v>-2.5522288122537e-16</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1140304863710548</v>
+        <v>-0.1140304864151476</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.367107440935978e-14</v>
+        <v>6.587616550414456e-15</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1175251467514151</v>
+        <v>0.117525146753172</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1175251467514151</v>
+        <v>0.117525146753172</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117.5251467514151</v>
+        <v>117.525146753172</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2590985971642668</v>
+        <v>0.2590985971681401</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.113736149419482</v>
+        <v>0.1137361494300794</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0158435610015062</v>
+        <v>0.01584356100175216</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.113736149419482</v>
+        <v>0.1137361494300794</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01584356100150619</v>
+        <v>0.01584356100175216</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1175251467514151</v>
+        <v>0.117525146753172</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0161599176490243</v>
+        <v>0.01615991765162661</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537648173</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9.696954368839226</v>
+        <v>9.696954368854737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.824999996252064</v>
+        <v>1.824999996252063</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.824999996252064</v>
+        <v>1.824999996252063</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8.767123305675957</v>
+        <v>8.767123305675961</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.514895921886005</v>
+        <v>7.514895921886137</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.129104669753629</v>
+        <v>2.129104669753592</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.704104673501566</v>
+        <v>2.704104673501529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.252227383789952</v>
+        <v>-1.252227383789823</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.355322739199893</v>
+        <v>0.3553227391827451</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9.195080003956393</v>
+        <v>9.195080003512478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>73262.37412186408</v>
+        <v>73262.37412649603</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1000000099235376</v>
+        <v>0.1000000098654832</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6473213460307183</v>
+        <v>0.6473213459669306</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.02999999002391656</v>
+        <v>0.02999999002416101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5.239711081987844</v>
+        <v>5.239711082357698</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.740771950578257</v>
+        <v>2.740771950771719</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.03717044124832115</v>
+        <v>0.03717044124948815</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.57077861162896</v>
+        <v>25.57077861325071</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-24.40325581035889</v>
+        <v>-24.40325580872998</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.59674418964111</v>
+        <v>25.59674419127002</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25.59674418964111</v>
+        <v>25.59674419127002</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.8272426172822788</v>
+        <v>-0.8272426172712272</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8272426172822788</v>
+        <v>-0.8272426172712272</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>229.0672432793575</v>
+        <v>229.0672432883348</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.02287411769127456</v>
+        <v>0.02287411769199271</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.008152368697787939</v>
+        <v>0.008152368697903957</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.03000000029983491</v>
+        <v>0.03000000029983498</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.02173964964349098</v>
+        <v>0.02173964964380031</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.2717456205436372</v>
+        <v>0.2717456205475038</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3807849832629087</v>
+        <v>0.3807849832629095</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5764608398210722</v>
+        <v>0.5764608398297</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.513874929839503</v>
+        <v>1.513874929862158</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4661115090952813</v>
+        <v>0.4661115090956274</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.002045221041526817</v>
+        <v>0.002045221041065397</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.01462208659341158</v>
+        <v>0.01462208659223752</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.01118976298470754</v>
+        <v>0.01118976298308151</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.1398720373088443</v>
+        <v>0.1398720372885188</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.1827760824176448</v>
+        <v>0.1827760824029689</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.1441152099552681</v>
+        <v>0.144115209957425</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7884795868748498</v>
+        <v>0.788479586949961</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0537820897593865</v>
+        <v>0.05378208975937</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.310723987774028</v>
+        <v>1.310723987777075</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.1174456015503173</v>
+        <v>0.1174456015613583</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.01255907900492259</v>
+        <v>0.01255907900531688</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.004807540212569393</v>
+        <v>0.004807540213177311</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537648173</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0552234488668002</v>
+        <v>0.05522344886762574</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.724083649561253e-06</v>
+        <v>1.724083650894573e-06</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.310723987774028</v>
+        <v>1.310723987777075</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.1174456015503173</v>
+        <v>0.1174456015613583</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.01255907900492259</v>
+        <v>0.01255907900531688</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.166267395045595</v>
+        <v>2.166267395059844</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537648173</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>30.94325083315806</v>
+        <v>30.94325083290559</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0552234488668002</v>
+        <v>0.05522344886762574</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2.549244335814687</v>
+        <v>2.549244335836028</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.724083649561253e-06</v>
+        <v>1.724083650894573e-06</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>7.958775788733897e-05</v>
+        <v>7.958775794836467e-05</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.310723987774028</v>
+        <v>1.310723987777075</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>60.50610329877767</v>
+        <v>60.50610329852036</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.1174456015503173</v>
+        <v>0.1174456015613583</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5.421565307169542</v>
+        <v>5.421565307643556</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.01255907900492259</v>
+        <v>0.01255907900531688</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.579756637322155</v>
+        <v>0.5797566373365434</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.166267395045595</v>
+        <v>2.166267395059844</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.808035465986087</v>
+        <v>3.808035466072172</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.86535588595925e-15</v>
+        <v>-2.5522288122537e-16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.1140304863710548</v>
+        <v>-0.1140304864151476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.367107440935978e-14</v>
+        <v>6.587616550414456e-15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537648173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.355322739199893</v>
+        <v>0.3553227391827451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.8272426172822788</v>
+        <v>-0.8272426172712272</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.808035465986087</v>
+        <v>3.808035466072172</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.86535588595925e-15</v>
+        <v>-2.5522288122537e-16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.1140304863710548</v>
+        <v>-0.1140304864151476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1.367107440935978e-14</v>
+        <v>6.587616550414456e-15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.355322739199893</v>
+        <v>0.3553227391827451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.824999996252064</v>
+        <v>1.824999996252063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.824999996252064</v>
+        <v>1.824999996252063</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.767123305675957</v>
+        <v>8.767123305675961</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.514895921886005</v>
+        <v>7.514895921886137</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.129104669753629</v>
+        <v>2.129104669753592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.704104673501566</v>
+        <v>2.704104673501529</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1.252227383789952</v>
+        <v>-1.252227383789823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.8272426172822788</v>
+        <v>-0.8272426172712272</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.03717044124832115</v>
+        <v>0.03717044124948815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25.57077861162896</v>
+        <v>25.57077861325071</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-24.40325581035889</v>
+        <v>-24.40325580872998</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.59674418964111</v>
+        <v>25.59674419127002</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>25.59674418964111</v>
+        <v>25.59674419127002</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7615699665258173</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1646396705960972</v>
+        <v>0.1646396706065065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1253846284246913</v>
+        <v>0.125384628432619</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.625677175910666</v>
+        <v>4.62567717561822</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.563971623321324</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4639716232510613</v>
+        <v>0.463971623321324</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.563971623321324</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3655521648352896</v>
+        <v>0.3655521648059379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09138804120882239</v>
+        <v>0.09138804120148446</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03340709630394168</v>
+        <v>0.03340709629857689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1187676990826549</v>
+        <v>0.1187676990756998</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05938384954132745</v>
+        <v>0.05938384953784991</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.007052883172694033</v>
+        <v>0.007052883171867995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3435,28 +3435,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02482615642808889</v>
+        <v>0.02482615642965856</v>
       </c>
       <c r="C2" t="n">
-        <v>24.82615642808889</v>
+        <v>24.82615642965856</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08231983529804861</v>
+        <v>0.08231983530325322</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04006130921326834</v>
+        <v>0.04006130921326841</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001163800584297664</v>
+        <v>0.001163800584371253</v>
       </c>
       <c r="H2" t="n">
-        <v>5.789663706248288e-05</v>
+        <v>5.789663707345507e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001221548264421579</v>
+        <v>0.00122154826450613</v>
       </c>
     </row>
     <row r="3">
@@ -3472,7 +3472,7 @@
         <v>11.98624513657535</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0654599176490243</v>
+        <v>0.06545991765162661</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3497,28 +3497,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008705566426030745</v>
+        <v>0.008705566426160887</v>
       </c>
       <c r="C4" t="n">
-        <v>8.705566426030746</v>
+        <v>8.705566426160887</v>
       </c>
       <c r="D4" t="n">
-        <v>0.113736149419482</v>
+        <v>0.1137361494300794</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0158435610015062</v>
+        <v>0.01584356100175216</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001854183660230625</v>
+        <v>0.0001854183660275195</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001472501819614589</v>
+        <v>0.0001472501820051632</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003229004953556597</v>
+        <v>0.0003229004954038383</v>
       </c>
     </row>
     <row r="5">
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007441430255442309</v>
+        <v>0.007441430256369403</v>
       </c>
       <c r="C5" t="n">
-        <v>7.441430255442309</v>
+        <v>7.441430256369403</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1819858116255307</v>
+        <v>0.181985811660662</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3543,13 +3543,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.860357563860577e-08</v>
+        <v>1.860357564092351e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000197246886120207</v>
+        <v>0.000197246886193927</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000197246886120207</v>
+        <v>0.000197246886193927</v>
       </c>
     </row>
     <row r="6">
@@ -3565,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09115991764902431</v>
+        <v>0.09115991765162662</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3590,28 +3590,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005772676558666242</v>
+        <v>0.005772676558666255</v>
       </c>
       <c r="C7" t="n">
-        <v>5.772676558666242</v>
+        <v>5.772676558666255</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0411599176490243</v>
+        <v>0.04115991765162661</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03906130921326833</v>
+        <v>0.03906130921326841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002706032389035091</v>
+        <v>0.0002706032389035109</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8039614245832e-08</v>
+        <v>1.803961424583204e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002706032389035091</v>
+        <v>0.0002706032389035109</v>
       </c>
     </row>
     <row r="8">
@@ -3627,7 +3627,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0161599176490243</v>
+        <v>0.01615991765162661</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004008851556473002</v>
+        <v>0.004008851555829226</v>
       </c>
       <c r="C9" t="n">
-        <v>4.008851556473002</v>
+        <v>4.008851555829226</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4456940150092968</v>
+        <v>0.4456940150810271</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         <v>-0.0025</v>
       </c>
       <c r="G9" t="n">
-        <v>4.464436997710072e-05</v>
+        <v>4.464436996276246e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.79309184731944e-06</v>
+        <v>2.793091846422845e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>4.743144854708545e-05</v>
+        <v>4.743144853185156e-05</v>
       </c>
     </row>
     <row r="10">
@@ -3689,7 +3689,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0411599176490243</v>
+        <v>0.04115991765162661</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0411599176490243</v>
+        <v>0.04115991765162661</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3751,13 +3751,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04939190117882916</v>
+        <v>0.04939190118195193</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3000000029983491</v>
+        <v>0.3000000029983498</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05989809474122934</v>
+        <v>0.05989809474122946</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3782,13 +3782,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04939190117882916</v>
+        <v>0.04939190118195193</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3000000029983491</v>
+        <v>-0.3000000029983498</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05989809474122934</v>
+        <v>0.05989809474122946</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04433748857101012</v>
+        <v>0.04433748857361243</v>
       </c>
       <c r="E14" t="n">
         <v>0.03743439716312056</v>
@@ -3844,7 +3844,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1162874885710101</v>
+        <v>0.1162874885736124</v>
       </c>
       <c r="E15" t="n">
         <v>0.03743439716312056</v>
@@ -3875,7 +3875,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04433748857101012</v>
+        <v>0.04433748857361243</v>
       </c>
       <c r="E16" t="n">
         <v>-0.03743439716312056</v>
@@ -3906,7 +3906,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1162874885710101</v>
+        <v>0.1162874885736124</v>
       </c>
       <c r="E17" t="n">
         <v>-0.03743439716312056</v>
@@ -3937,7 +3937,7 @@
         <v>1.795290858725762</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4408716232510613</v>
+        <v>0.440871623321324</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3962,28 +3962,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001312500013117777</v>
+        <v>0.00131250001311778</v>
       </c>
       <c r="C19" t="n">
-        <v>1.312500013117777</v>
+        <v>1.31250001311778</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02307995882451215</v>
+        <v>0.0230799588258133</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02059565460663416</v>
+        <v>0.0205956546066342</v>
       </c>
       <c r="G19" t="n">
-        <v>1.538086168460938e-05</v>
+        <v>1.538086168460948e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>4.399757986484086e-07</v>
+        <v>4.399757987101623e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>1.582083378638275e-05</v>
+        <v>1.582083378644461e-05</v>
       </c>
     </row>
     <row r="20">
@@ -3993,28 +3993,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.001312500013117777</v>
+        <v>0.00131250001311778</v>
       </c>
       <c r="C20" t="n">
-        <v>1.312500013117777</v>
+        <v>1.31250001311778</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02307995882451215</v>
+        <v>0.0230799588258133</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02646565460663417</v>
+        <v>0.0264656546066342</v>
       </c>
       <c r="G20" t="n">
-        <v>1.538086168460938e-05</v>
+        <v>1.538086168460948e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>4.399757986484086e-07</v>
+        <v>4.399757987101623e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>1.582083378638275e-05</v>
+        <v>1.582083378644461e-05</v>
       </c>
     </row>
     <row r="21">
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1999999972024428</v>
+        <v>0.1999999972401424</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4061,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0561599176490243</v>
+        <v>0.05615991765162661</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3910599944048856</v>
+        <v>0.3910599944802849</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4117,28 +4117,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0008463459807232839</v>
+        <v>0.0008463459806241594</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8463459807232839</v>
+        <v>0.8463459806241594</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4392931766757979</v>
+        <v>0.4392931767483002</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06338384954132745</v>
+        <v>0.06338384953784991</v>
       </c>
       <c r="G24" t="n">
-        <v>9.954979804389555e-07</v>
+        <v>9.954979802058433e-07</v>
       </c>
       <c r="H24" t="n">
-        <v>1.243579026191766e-06</v>
+        <v>1.243579025900469e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>2.493505647238957e-07</v>
+        <v>2.493505646655619e-07</v>
       </c>
     </row>
     <row r="25">
@@ -4154,7 +4154,7 @@
         <v>0.7628808864265929</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4457716232510613</v>
+        <v>0.445771623321324</v>
       </c>
       <c r="E25" t="n">
         <v>0.01469135802469136</v>
@@ -4185,7 +4185,7 @@
         <v>0.7628808864265929</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4457716232510613</v>
+        <v>0.445771623321324</v>
       </c>
       <c r="E26" t="n">
         <v>-0.01469135802469136</v>
@@ -4216,7 +4216,7 @@
         <v>0.6789473684210525</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4351716232510613</v>
+        <v>0.435171623321324</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0006397162884617567</v>
+        <v>0.0006397162884103913</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6397162884617567</v>
+        <v>0.6397162884103913</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4274164067675323</v>
+        <v>0.4274164068407302</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4256,13 +4256,13 @@
         <v>-0.003935</v>
       </c>
       <c r="G28" t="n">
-        <v>7.123688786214454e-06</v>
+        <v>7.123688784498483e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>5.331870004287557e-09</v>
+        <v>5.33187000385944e-09</v>
       </c>
       <c r="I28" t="n">
-        <v>7.129018854351195e-06</v>
+        <v>7.129018852634795e-06</v>
       </c>
     </row>
     <row r="29">
@@ -4272,13 +4272,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0006397162884617567</v>
+        <v>0.0006397162884103913</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6397162884617567</v>
+        <v>0.6397162884103913</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4274164067675323</v>
+        <v>0.4274164068407302</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4287,13 +4287,13 @@
         <v>-0.001065</v>
       </c>
       <c r="G29" t="n">
-        <v>7.123688786214454e-06</v>
+        <v>7.123688784498483e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>5.331870004287557e-09</v>
+        <v>5.33187000385944e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>7.129018854351195e-06</v>
+        <v>7.129018852634795e-06</v>
       </c>
     </row>
     <row r="30">
@@ -4309,7 +4309,7 @@
         <v>0.5959941141696471</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0411599176490243</v>
+        <v>0.0411599176516266</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -4334,28 +4334,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002078434733946461</v>
+        <v>0.0002078434733824747</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2078434733946461</v>
+        <v>0.2078434733824747</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4274164067675323</v>
+        <v>0.4274164068407302</v>
       </c>
       <c r="E31" t="n">
         <v>0.001565</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06338384954132745</v>
+        <v>0.06338384953784991</v>
       </c>
       <c r="G31" t="n">
-        <v>2.443162487227882e-07</v>
+        <v>2.443162486798666e-07</v>
       </c>
       <c r="H31" t="n">
-        <v>2.460479849548519e-07</v>
+        <v>2.460479849118289e-07</v>
       </c>
       <c r="I31" t="n">
-        <v>1.732321657847081e-09</v>
+        <v>1.732321657745636e-09</v>
       </c>
     </row>
     <row r="32">
@@ -4365,28 +4365,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0002078434733946461</v>
+        <v>0.0002078434733824747</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2078434733946461</v>
+        <v>0.2078434733824747</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4274164067675323</v>
+        <v>0.4274164068407302</v>
       </c>
       <c r="E32" t="n">
         <v>-0.001565</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06338384954132745</v>
+        <v>0.06338384953784991</v>
       </c>
       <c r="G32" t="n">
-        <v>2.443162487227882e-07</v>
+        <v>2.443162486798666e-07</v>
       </c>
       <c r="H32" t="n">
-        <v>2.460479849548519e-07</v>
+        <v>2.460479849118289e-07</v>
       </c>
       <c r="I32" t="n">
-        <v>1.732321657847081e-09</v>
+        <v>1.732321657745636e-09</v>
       </c>
     </row>
     <row r="33">
@@ -4396,28 +4396,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0003960000039578208</v>
+        <v>-0.0003960000039578216</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3960000039578208</v>
+        <v>-0.3960000039578216</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0411599176490243</v>
+        <v>0.04115991765162661</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03906130921326833</v>
+        <v>0.03906130921326841</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.856302855657383e-05</v>
+        <v>-1.856302855657396e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.056000010554189e-09</v>
+        <v>-1.056000010554191e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.856302855657383e-05</v>
+        <v>-1.856302855657396e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03664271540162221</v>
+        <v>0.03664271539979523</v>
       </c>
     </row>
     <row r="3">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7061559045866079</v>
+        <v>0.7061559045134552</v>
       </c>
     </row>
     <row r="4">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.282843122620439e-08</v>
+        <v>-2.284473156894689e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001794660944298698</v>
+        <v>-0.001794660944229309</v>
       </c>
     </row>
     <row r="6">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07160127584992376</v>
+        <v>0.07160127583716314</v>
       </c>
     </row>
     <row r="7">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-7.763231804625015e-05</v>
+        <v>-7.76323183238059e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.355322739199893</v>
+        <v>0.3553227391827451</v>
       </c>
     </row>
     <row r="9">
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.648463391351588</v>
+        <v>5.648463390620061</v>
       </c>
     </row>
     <row r="10">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.191039274239208e-05</v>
+        <v>-2.191051678402466e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01250308513706111</v>
+        <v>-0.01250308513717213</v>
       </c>
     </row>
     <row r="12">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9323336277551886</v>
+        <v>0.9323336274281169</v>
       </c>
     </row>
     <row r="13">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0002424221027252926</v>
+        <v>-0.0002424221045016494</v>
       </c>
     </row>
     <row r="14">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-6.004384935559393e-17</v>
+        <v>-1.954949201517465e-17</v>
       </c>
     </row>
     <row r="15">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.544401326368661e-12</v>
+        <v>4.517539521240818e-22</v>
       </c>
     </row>
     <row r="16">
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2408579823093662</v>
+        <v>-0.2408579822914199</v>
       </c>
     </row>
     <row r="17">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.4000315992502382</v>
+        <v>-0.4000315992275166</v>
       </c>
     </row>
     <row r="18">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.596730176084865e-14</v>
+        <v>1.256727680381765e-17</v>
       </c>
     </row>
     <row r="19">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1024021430446388</v>
+        <v>0.1024021430455406</v>
       </c>
     </row>
     <row r="20">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>-1.233238910570726e-18</v>
       </c>
     </row>
     <row r="21">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.029689396391938e-11</v>
+        <v>-1.934827174273248e-19</v>
       </c>
     </row>
     <row r="22">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1986060691007141</v>
+        <v>-0.1986060691019765</v>
       </c>
     </row>
     <row r="23">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7794457260989065</v>
+        <v>-0.7794457260438862</v>
       </c>
     </row>
     <row r="24">
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.081083517758276e-13</v>
+        <v>7.51057012892061e-19</v>
       </c>
     </row>
     <row r="25">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01591371476332364</v>
+        <v>0.01591371475994741</v>
       </c>
     </row>
     <row r="26">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.009957488131532e-06</v>
+        <v>-1.009943506936824e-06</v>
       </c>
     </row>
     <row r="27">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5648463951878975</v>
+        <v>-0.5648463947868269</v>
       </c>
     </row>
     <row r="28">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-5.783212416952033e-06</v>
+        <v>-5.783190067811703e-06</v>
       </c>
     </row>
     <row r="29">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.003253733018465601</v>
+        <v>-0.003253733017144216</v>
       </c>
     </row>
     <row r="30">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-11.47472238741731</v>
+        <v>-11.47472238827099</v>
       </c>
     </row>
     <row r="31">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001267192478528347</v>
+        <v>-0.0001267192463559272</v>
       </c>
     </row>
     <row r="32">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>8.073342737495452e-18</v>
       </c>
     </row>
     <row r="33">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.060861634138313e-12</v>
+        <v>-1.306851650478998e-20</v>
       </c>
     </row>
     <row r="34">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02574590957155478</v>
+        <v>0.02574590957319787</v>
       </c>
     </row>
     <row r="35">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.08493058475733455</v>
+        <v>-0.08493058475885355</v>
       </c>
     </row>
     <row r="36">
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8.165262820429911e-15</v>
+        <v>-5.239670694945015e-18</v>
       </c>
     </row>
     <row r="37">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.04854440594545696</v>
+        <v>-0.04854440595543232</v>
       </c>
     </row>
     <row r="38">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1188952361523956</v>
+        <v>0.118895236153985</v>
       </c>
     </row>
     <row r="39">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0359982932048754</v>
+        <v>0.03599829320587388</v>
       </c>
     </row>
     <row r="40">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.08289694294752024</v>
+        <v>0.08289694294811105</v>
       </c>
     </row>
     <row r="41">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.04206278273478523</v>
+        <v>-0.04206278273348475</v>
       </c>
     </row>
     <row r="42">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.04206278273478523</v>
+        <v>0.04206278273348475</v>
       </c>
     </row>
     <row r="43">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1188952361523956</v>
+        <v>-0.118895236153985</v>
       </c>
     </row>
     <row r="44">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.152921679642144</v>
+        <v>1.1529216796594</v>
       </c>
     </row>
     <row r="45">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-3.58208960670591e-16</v>
+        <v>-3.047430655777885e-18</v>
       </c>
     </row>
     <row r="46">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.58208960670591e-16</v>
+        <v>3.047430655777885e-18</v>
       </c>
     </row>
     <row r="47">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-3.599213739303475e-16</v>
+        <v>-1.715755223053363e-18</v>
       </c>
     </row>
     <row r="48">
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-1.948252898396324e-16</v>
+        <v>-6.343256618606443e-17</v>
       </c>
     </row>
     <row r="49">
@@ -4925,11 +4925,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.000340437824685027,
+	L=0.0003404378247374978,
 	Y=0.0,
-	D=0.0012461336137824343,
+	D=0.0012461336138990264,
 	l_b=0.0,
-	m_b=-3.601981611802251e-05,
+	m_b=-3.601981613290454e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-3.58208960670591e-16</v>
+        <v>-3.047430655777885e-18</v>
       </c>
     </row>
     <row r="51">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-5.395284945353823e-07</v>
+        <v>-5.395210257219728e-07</v>
       </c>
     </row>
     <row r="52">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-3.769214468381244e-17</v>
+        <v>1.994986692518442e-17</v>
       </c>
     </row>
     <row r="53">
@@ -4975,29 +4975,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.9168592898139383,
-	Y=-2.498001805406602e-16,
-	D=0.06055915724284599,
-	l_b=-3.608224830031759e-16,
-	m_b=0.07213813865433602,
-	n_b=-2.0816681711721685e-17,
-	span_effective=0.7500878943334834, oswalds_efficiency=0.8072554931486365,
+	L=0.9168592898654198,
+	Y=0.0,
+	D=0.06055915724584764,
+	l_b=-0.0,
+	m_b=0.07213813866633308,
+	n_b=-0.0,
+	span_effective=0.7500878943334851, oswalds_efficiency=0.8072554931504061,
 ), AeroComponentResults(
-	L=0.23572195200352128,
+	L=0.2357219519692426,
 	Y=0.0,
-	D=0.018196401858493014,
+	D=0.018196401856206714,
 	l_b=-0.0,
-	m_b=-0.07218097051784401,
+	m_b=-0.07218097052232664,
 	n_b=-0.0,
-	span_effective=0.3655521648352896, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.3655521648059379, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=-2.710505431213761e-20,
-	Y=5.4974890701027866e-17,
-	D=0.002895250232398816,
-	l_b=2.6135223325848924e-18,
-	m_b=7.831215113148152e-05,
-	n_b=-1.6875462972090752e-17,
-	span_effective=0.1187676990826549, oswalds_efficiency=0.8232692748986458,
+	Y=-6.343256618606443e-17,
+	D=0.002895250232157671,
+	l_b=-3.0474306557778854e-18,
+	m_b=7.831215110074344e-05,
+	n_b=1.9949866925184424e-17,
+	span_effective=0.11876769907569983, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1302001181128997</v>
+        <v>0.13020011811498</v>
       </c>
     </row>
     <row r="55">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1951422597862184</v>
+        <v>0.1951422598080768</v>
       </c>
     </row>
     <row r="56">
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.03664271540162221</v>
+        <v>0.03664271539979523</v>
       </c>
     </row>
     <row r="57">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7061559045866079</v>
+        <v>0.7061559045134552</v>
       </c>
     </row>
     <row r="58">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-2.282843122620439e-08</v>
+        <v>-2.284473156894689e-08</v>
       </c>
     </row>
     <row r="59">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.001794660944298698</v>
+        <v>-0.001794660944229309</v>
       </c>
     </row>
     <row r="60">
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.07160127584992376</v>
+        <v>0.07160127583716314</v>
       </c>
     </row>
     <row r="61">
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-7.763231804625015e-05</v>
+        <v>-7.76323183238059e-05</v>
       </c>
     </row>
     <row r="62">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.355322739199893</v>
+        <v>0.3553227391827451</v>
       </c>
     </row>
     <row r="63">
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5.648463391351588</v>
+        <v>5.648463390620061</v>
       </c>
     </row>
     <row r="64">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-2.191039274239208e-05</v>
+        <v>-2.191051678402466e-05</v>
       </c>
     </row>
     <row r="65">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.01250308513706111</v>
+        <v>-0.01250308513717213</v>
       </c>
     </row>
     <row r="66">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9323336277551886</v>
+        <v>0.9323336274281169</v>
       </c>
     </row>
     <row r="67">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.0002424221027252926</v>
+        <v>-0.0002424221045016494</v>
       </c>
     </row>
     <row r="68">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-6.004384935559393e-17</v>
+        <v>-1.954949201517465e-17</v>
       </c>
     </row>
     <row r="69">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5.544401326368661e-12</v>
+        <v>4.517539521240818e-22</v>
       </c>
     </row>
     <row r="70">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.2408579823093662</v>
+        <v>-0.2408579822914199</v>
       </c>
     </row>
     <row r="71">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.4000315992502382</v>
+        <v>-0.4000315992275166</v>
       </c>
     </row>
     <row r="72">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4.596730176084865e-14</v>
+        <v>1.256727680381765e-17</v>
       </c>
     </row>
     <row r="73">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1024021430446388</v>
+        <v>0.1024021430455406</v>
       </c>
     </row>
     <row r="74">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>-1.233238910570726e-18</v>
       </c>
     </row>
     <row r="75">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.029689396391938e-11</v>
+        <v>-1.934827174273248e-19</v>
       </c>
     </row>
     <row r="76">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1986060691007141</v>
+        <v>-0.1986060691019765</v>
       </c>
     </row>
     <row r="77">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7794457260989065</v>
+        <v>-0.7794457260438862</v>
       </c>
     </row>
     <row r="78">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.081083517758276e-13</v>
+        <v>7.51057012892061e-19</v>
       </c>
     </row>
     <row r="79">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.01591371476332364</v>
+        <v>0.01591371475994741</v>
       </c>
     </row>
     <row r="80">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.009957488131532e-06</v>
+        <v>-1.009943506936824e-06</v>
       </c>
     </row>
     <row r="81">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.5648463951878975</v>
+        <v>-0.5648463947868269</v>
       </c>
     </row>
     <row r="82">
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-5.783212416952033e-06</v>
+        <v>-5.783190067811703e-06</v>
       </c>
     </row>
     <row r="83">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.003253733018465601</v>
+        <v>-0.003253733017144216</v>
       </c>
     </row>
     <row r="84">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-11.47472238741731</v>
+        <v>-11.47472238827099</v>
       </c>
     </row>
     <row r="85">
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.0001267192478528347</v>
+        <v>-0.0001267192463559272</v>
       </c>
     </row>
     <row r="86">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>8.073342737495452e-18</v>
       </c>
     </row>
     <row r="87">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.060861634138313e-12</v>
+        <v>-1.306851650478998e-20</v>
       </c>
     </row>
     <row r="88">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.02574590957155478</v>
+        <v>0.02574590957319787</v>
       </c>
     </row>
     <row r="89">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.08493058475733455</v>
+        <v>-0.08493058475885355</v>
       </c>
     </row>
     <row r="90">
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8.165262820429911e-15</v>
+        <v>-5.239670694945015e-18</v>
       </c>
     </row>
     <row r="91">
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.04854440594545696</v>
+        <v>-0.04854440595543232</v>
       </c>
     </row>
     <row r="92">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1188952361523956</v>
+        <v>0.118895236153985</v>
       </c>
     </row>
     <row r="93">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0359982932048754</v>
+        <v>0.03599829320587388</v>
       </c>
     </row>
     <row r="94">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.08289694294752024</v>
+        <v>0.08289694294811105</v>
       </c>
     </row>
     <row r="95">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.04206278273478523</v>
+        <v>-0.04206278273348475</v>
       </c>
     </row>
     <row r="96">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.04206278273478523</v>
+        <v>0.04206278273348475</v>
       </c>
     </row>
     <row r="97">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.1188952361523956</v>
+        <v>-0.118895236153985</v>
       </c>
     </row>
     <row r="98">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.152921679642144</v>
+        <v>1.1529216796594</v>
       </c>
     </row>
     <row r="99">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-3.58208960670591e-16</v>
+        <v>-3.047430655777885e-18</v>
       </c>
     </row>
     <row r="100">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3.58208960670591e-16</v>
+        <v>3.047430655777885e-18</v>
       </c>
     </row>
     <row r="101">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-3.599213739303475e-16</v>
+        <v>-1.715755223053363e-18</v>
       </c>
     </row>
     <row r="102">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-1.948252898396324e-16</v>
+        <v>-6.343256618606443e-17</v>
       </c>
     </row>
     <row r="103">
@@ -5501,11 +5501,11 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.000340437824685027,
+	L=0.0003404378247374978,
 	Y=0.0,
-	D=0.0012461336137824343,
+	D=0.0012461336138990264,
 	l_b=0.0,
-	m_b=-3.601981611802251e-05,
+	m_b=-3.601981613290454e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-3.58208960670591e-16</v>
+        <v>-3.047430655777885e-18</v>
       </c>
     </row>
     <row r="105">
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-5.395284945353823e-07</v>
+        <v>-5.395210257219728e-07</v>
       </c>
     </row>
     <row r="106">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-3.769214468381244e-17</v>
+        <v>1.994986692518442e-17</v>
       </c>
     </row>
     <row r="107">
@@ -5551,29 +5551,29 @@
       <c r="B107" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.9168592898139383,
-	Y=-2.498001805406602e-16,
-	D=0.06055915724284599,
-	l_b=-3.608224830031759e-16,
-	m_b=0.07213813865433602,
-	n_b=-2.0816681711721685e-17,
-	span_effective=0.7500878943334834, oswalds_efficiency=0.8072554931486365,
+	L=0.9168592898654198,
+	Y=0.0,
+	D=0.06055915724584764,
+	l_b=-0.0,
+	m_b=0.07213813866633308,
+	n_b=-0.0,
+	span_effective=0.7500878943334851, oswalds_efficiency=0.8072554931504061,
 ), AeroComponentResults(
-	L=0.23572195200352128,
+	L=0.2357219519692426,
 	Y=0.0,
-	D=0.018196401858493014,
+	D=0.018196401856206714,
 	l_b=-0.0,
-	m_b=-0.07218097051784401,
+	m_b=-0.07218097052232664,
 	n_b=-0.0,
-	span_effective=0.3655521648352896, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.3655521648059379, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
 	L=-2.710505431213761e-20,
-	Y=5.4974890701027866e-17,
-	D=0.002895250232398816,
-	l_b=2.6135223325848924e-18,
-	m_b=7.831215113148152e-05,
-	n_b=-1.6875462972090752e-17,
-	span_effective=0.1187676990826549, oswalds_efficiency=0.8232692748986458,
+	Y=-6.343256618606443e-17,
+	D=0.002895250232157671,
+	l_b=-3.0474306557778854e-18,
+	m_b=7.831215110074344e-05,
+	n_b=1.9949866925184424e-17,
+	span_effective=0.11876769907569983, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.1302001181128997</v>
+        <v>0.13020011811498</v>
       </c>
     </row>
     <row r="109">
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.1951422597862184</v>
+        <v>0.1951422598080768</v>
       </c>
     </row>
   </sheetData>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.152921679642144</v>
+        <v>1.1529216796594</v>
       </c>
       <c r="C2" t="n">
-        <v>1.152921689631382</v>
+        <v>1.152921689648617</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -5709,16 +5709,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.989237215179969e-09</v>
+        <v>-9.989217009120921e-09</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.989237215179969e-09</v>
+        <v>-9.989217009120921e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.664280761665419e-09</v>
+        <v>-8.664263235576213e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1188952361523956</v>
+        <v>0.118895236153985</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -5749,16 +5749,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.1178952361523956</v>
+        <v>0.117895236153985</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.1178952361523956</v>
+        <v>0.117895236153985</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1178952361523956</v>
+        <v>0.117895236153985</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.009957488131532e-06</v>
+        <v>-1.009943506936824e-06</v>
       </c>
       <c r="C4" t="n">
         <v>-1e-06</v>
@@ -5791,18 +5791,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-9.957488131531999e-09</v>
+        <v>-9.9435069368239e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.009957488131532e-06</v>
+        <v>2.009943506936824e-06</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.957488131531999e-09</v>
+        <v>-9.9435069368239e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.957488131531999e-09</v>
+        <v>-9.9435069368239e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>-1.233238910570726e-18</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -5835,22 +5835,22 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>-1.233238910570726e-18</v>
       </c>
       <c r="I5" t="n">
-        <v>1.449605514745473e-16</v>
+        <v>1.233238910570726e-18</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>-1.233238910570726e-18</v>
       </c>
       <c r="K5" t="n">
-        <v>1.449605514745473e-16</v>
+        <v>1.233238910570726e-18</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000999999999999855</v>
+        <v>0.0009999999999999987</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000999999999999855</v>
+        <v>0.0009999999999999987</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -5883,22 +5883,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>1.525331490701723e-17</v>
+        <v>-8.073342737495452e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>1.525331490701723e-17</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009999999999999848</v>
+        <v>0.000999999999999992</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009999999999999848</v>
+        <v>0.000999999999999992</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.355322739199893</v>
+        <v>0.3553227391827451</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -5930,15 +5930,15 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.844677260800107</v>
+        <v>0.8446772608172548</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.844677260800107</v>
+        <v>0.8446772608172548</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7038977173334225</v>
+        <v>0.7038977173477123</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.696954368839226</v>
+        <v>9.696954368854737</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -5969,16 +5969,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.696954368839226</v>
+        <v>3.696954368854737</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>3.696954368839226</v>
+        <v>3.696954368854737</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3812490219320038</v>
+        <v>0.3812490219329935</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.195080003956393</v>
+        <v>9.195080003512478</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7.195080003956393</v>
+        <v>7.195080003512478</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>7.195080003956393</v>
+        <v>7.195080003512478</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7824923764513789</v>
+        <v>0.7824923764408782</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.195080003956393</v>
+        <v>9.195080003512478</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -6050,15 +6050,15 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>10.80491999604361</v>
+        <v>10.80491999648752</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>10.80491999604361</v>
+        <v>10.80491999648752</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5402459998021804</v>
+        <v>0.540245999824376</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73262.37412186408</v>
+        <v>73262.37412649603</v>
       </c>
       <c r="C11" t="n">
         <v>20000</v>
@@ -6089,16 +6089,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>53262.37412186408</v>
+        <v>53262.37412649603</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>53262.37412186408</v>
+        <v>53262.37412649603</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7270085737771458</v>
+        <v>0.7270085737944054</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1000000099235376</v>
+        <v>0.1000000098654832</v>
       </c>
       <c r="C12" t="n">
         <v>0.05</v>
@@ -6129,16 +6129,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.05000000992353755</v>
+        <v>0.05000000986548321</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.05000000992353755</v>
+        <v>0.05000000986548321</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05000000992353755</v>
+        <v>0.05000000986548321</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1000000099235376</v>
+        <v>0.1000000098654832</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
@@ -6170,15 +6170,15 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>-9.923537547251726e-09</v>
+        <v>-9.86548320813796e-09</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-9.923537547251726e-09</v>
+        <v>-9.86548320813796e-09</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.923537547251726e-09</v>
+        <v>-9.86548320813796e-09</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6473213460307183</v>
+        <v>0.6473213459669306</v>
       </c>
       <c r="C14" t="n">
         <v>0.5</v>
@@ -6209,16 +6209,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.1473213460307183</v>
+        <v>0.1473213459669306</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.1473213460307183</v>
+        <v>0.1473213459669306</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1473213460307183</v>
+        <v>0.1473213459669306</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6473213460307183</v>
+        <v>0.6473213459669306</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
@@ -6250,15 +6250,15 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.3526786539692817</v>
+        <v>0.3526786540330694</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.3526786539692817</v>
+        <v>0.3526786540330694</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3526786539692817</v>
+        <v>0.3526786540330694</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02999999002391656</v>
+        <v>0.02999999002416101</v>
       </c>
       <c r="C16" t="n">
         <v>0.03</v>
@@ -6289,16 +6289,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.976083438500982e-09</v>
+        <v>-9.975838984738195e-09</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-9.976083438500982e-09</v>
+        <v>-9.975838984738195e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.976083438500982e-09</v>
+        <v>-9.975838984738195e-09</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02999999002391656</v>
+        <v>0.02999999002416101</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
@@ -6330,15 +6330,15 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.05000000997608344</v>
+        <v>0.05000000997583899</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.05000000997608344</v>
+        <v>0.05000000997583899</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05000000997608344</v>
+        <v>0.05000000997583899</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1986060691007141</v>
+        <v>-0.1986060691019765</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -6370,15 +6370,15 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.1986060691007141</v>
+        <v>0.1986060691019765</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.1986060691007141</v>
+        <v>0.1986060691019765</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1986060691007141</v>
+        <v>0.1986060691019765</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02574590957155478</v>
+        <v>0.02574590957319787</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -6409,16 +6409,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.02574590957155478</v>
+        <v>0.02574590957319787</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0.02574590957155478</v>
+        <v>0.02574590957319787</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02574590957155478</v>
+        <v>0.02574590957319787</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.7794457260989065</v>
+        <v>-0.7794457260438862</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -6450,15 +6450,15 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.7793457260989065</v>
+        <v>0.7793457260438862</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.7793457260989065</v>
+        <v>0.7793457260438862</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7793457260989065</v>
+        <v>0.7793457260438862</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.239711081987844</v>
+        <v>5.239711082357698</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>229.0672432793575</v>
+        <v>229.0672432883348</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02287411769127456</v>
+        <v>0.02287411769199271</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.461428953049963e-05</v>
+        <v>3.461428953487664e-05</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -6586,15 +6586,15 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.0071653857104695</v>
+        <v>0.007165385710465123</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.0071653857104695</v>
+        <v>0.007165385710465123</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0071653857104695</v>
+        <v>0.007165385710465123</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.861538575660353e-05</v>
+        <v>1.861538575211941e-05</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
@@ -6626,15 +6626,15 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.007181384614243396</v>
+        <v>0.007181384614247881</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.007181384614243396</v>
+        <v>0.007181384614247881</v>
       </c>
       <c r="M25" t="n">
-        <v>0.007181384614243396</v>
+        <v>0.007181384614247881</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.475942302203299e-06</v>
+        <v>3.475942301592643e-06</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -6666,15 +6666,15 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.007196524057697796</v>
+        <v>0.007196524057698407</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0.007196524057697796</v>
+        <v>0.007196524057698407</v>
       </c>
       <c r="M26" t="n">
-        <v>0.007196524057697796</v>
+        <v>0.007196524057698407</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.808035465986087</v>
+        <v>3.808035466072172</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.355322739199893</v>
+        <v>0.3553227391827451</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.252227383789952</v>
+        <v>-1.252227383789823</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.704104673501566</v>
+        <v>2.704104673501529</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.009957488131532e-06</v>
+        <v>-1.009943506936824e-06</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7794457260989065</v>
+        <v>-0.7794457260438862</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25.57077861162896</v>
+        <v>25.57077861325071</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-24.40325581035889</v>
+        <v>-24.40325580872998</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25.59674418964111</v>
+        <v>25.59674419127002</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7.86535588595925e-15</v>
+        <v>2.5522288122537e-16</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1140304863710548</v>
+        <v>0.1140304864151476</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.367107440935978e-14</v>
+        <v>6.587616550414456e-15</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.002045221041526817</v>
+        <v>0.002045221041065397</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01462208659341158</v>
+        <v>0.01462208659223752</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1174456015503173</v>
+        <v>0.1174456015613583</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02999999002391656</v>
+        <v>0.02999999002416101</v>
       </c>
       <c r="C2" t="n">
         <v>0.03</v>
@@ -7271,16 +7271,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.976083438500982e-09</v>
+        <v>-9.975838984738195e-09</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.976083438500982e-09</v>
+        <v>-9.975838984738195e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.976083438500982e-09</v>
+        <v>-9.975838984738195e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.009957488131532e-06</v>
+        <v>-1.009943506936824e-06</v>
       </c>
       <c r="C3" t="n">
         <v>-1e-06</v>
@@ -7313,18 +7313,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-9.957488131531999e-09</v>
+        <v>-9.9435069368239e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>2.009957488131532e-06</v>
+        <v>2.009943506936824e-06</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-9.957488131531999e-09</v>
+        <v>-9.9435069368239e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.957488131531999e-09</v>
+        <v>-9.9435069368239e-09</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1000000099235376</v>
+        <v>0.1000000098654832</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
@@ -7356,15 +7356,15 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>-9.923537547251726e-09</v>
+        <v>-9.86548320813796e-09</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.923537547251726e-09</v>
+        <v>-9.86548320813796e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.923537547251726e-09</v>
+        <v>-9.86548320813796e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.152921679642144</v>
+        <v>1.1529216796594</v>
       </c>
       <c r="C5" t="n">
-        <v>1.152921689631382</v>
+        <v>1.152921689648617</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -7395,16 +7395,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-9.989237215179969e-09</v>
+        <v>-9.989217009120921e-09</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-9.989237215179969e-09</v>
+        <v>-9.989217009120921e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>-8.664280761665419e-09</v>
+        <v>-8.664263235576213e-09</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -7413,11 +7413,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nominal Trim Cl</t>
+          <t>Nominal Trim Cn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -7437,22 +7437,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>1.449605514745473e-16</v>
+        <v>-8.073342737495452e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.449605514745473e-16</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>1.449605514745473e-16</v>
+        <v>8.073342737495452e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000999999999999855</v>
+        <v>0.000999999999999992</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000999999999999855</v>
+        <v>0.000999999999999992</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -7461,11 +7461,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nominal Trim Cn</t>
+          <t>Nominal Trim Cl</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>-1.233238910570726e-18</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -7485,22 +7485,22 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>-1.233238910570726e-18</v>
       </c>
       <c r="I7" t="n">
-        <v>1.525331490701723e-17</v>
+        <v>1.233238910570726e-18</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.525331490701723e-17</v>
+        <v>-1.233238910570726e-18</v>
       </c>
       <c r="K7" t="n">
-        <v>1.525331490701723e-17</v>
+        <v>1.233238910570726e-18</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009999999999999848</v>
+        <v>0.0009999999999999987</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009999999999999848</v>
+        <v>0.0009999999999999987</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -7517,7 +7517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B237"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.9915896389666687</v>
       </c>
     </row>
     <row r="8">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8647406397960675</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.739172497752381</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.874563613478903</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.1519418837766429</v>
       </c>
     </row>
     <row r="14">
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3865202083119469</v>
+        <v>0.3356497692647426</v>
       </c>
     </row>
     <row r="15">
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0.7792275026343395</v>
       </c>
     </row>
     <row r="18">
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9946446422596058</v>
+        <v>0.9977728756399165</v>
       </c>
     </row>
     <row r="20">
@@ -7725,77 +7725,77 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[2]</t>
+          <t>iterations.alpha_du[26]</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9020873379329158</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[3]</t>
+          <t>iterations.alpha_du[27]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.948906384805002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[4]</t>
+          <t>iterations.alpha_du[28]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.463792338627697</v>
+        <v>0.838854478511513</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[5]</t>
+          <t>iterations.alpha_du[29]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1815435060805274</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[6]</t>
+          <t>iterations.alpha_du[2]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0.9160287574850122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[7]</t>
+          <t>iterations.alpha_du[30]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9992100981448369</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[8]</t>
+          <t>iterations.alpha_du[3]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9999594613150793</v>
+        <v>0.9513060667676593</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[9]</t>
+          <t>iterations.alpha_du[4]</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7805,37 +7805,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[0]</t>
+          <t>iterations.alpha_du[5]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.1412261858571584</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[10]</t>
+          <t>iterations.alpha_du[6]</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1619005956094198</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[11]</t>
+          <t>iterations.alpha_du[7]</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[12]</t>
+          <t>iterations.alpha_du[8]</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -7845,47 +7845,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[13]</t>
+          <t>iterations.alpha_du[9]</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8878402044848255</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[14]</t>
+          <t>iterations.alpha_pr[0]</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3257990770328598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[15]</t>
+          <t>iterations.alpha_pr[10]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4161302876215399</v>
+        <v>0.5264622235972604</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[16]</t>
+          <t>iterations.alpha_pr[11]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0.6385799047818183</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[17]</t>
+          <t>iterations.alpha_pr[12]</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7895,7 +7895,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[18]</t>
+          <t>iterations.alpha_pr[13]</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -7905,1992 +7905,2392 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[19]</t>
+          <t>iterations.alpha_pr[14]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7656170201276495</v>
+        <v>0.5352135312162907</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[1]</t>
+          <t>iterations.alpha_pr[15]</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1401002009618226</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[20]</t>
+          <t>iterations.alpha_pr[16]</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9168610008989824</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[21]</t>
+          <t>iterations.alpha_pr[17]</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0.6677065173333778</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[22]</t>
+          <t>iterations.alpha_pr[18]</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9949757691631804</v>
+        <v>0.3577208896171598</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[23]</t>
+          <t>iterations.alpha_pr[19]</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0.3237051210420037</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[24]</t>
+          <t>iterations.alpha_pr[1]</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0.2647173673845499</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[25]</t>
+          <t>iterations.alpha_pr[20]</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0.007516782706813263</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[2]</t>
+          <t>iterations.alpha_pr[21]</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1464279252303919</v>
+        <v>0.3233212126246934</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[3]</t>
+          <t>iterations.alpha_pr[22]</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5368769739913642</v>
+        <v>0.9974357923196122</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[4]</t>
+          <t>iterations.alpha_pr[23]</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6751715257450052</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[5]</t>
+          <t>iterations.alpha_pr[24]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1448663932167525</v>
+        <v>0.8095316698838487</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[6]</t>
+          <t>iterations.alpha_pr[25]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7802533433928667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[7]</t>
+          <t>iterations.alpha_pr[26]</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7330680577570385</v>
+        <v>0.981236105188696</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[8]</t>
+          <t>iterations.alpha_pr[27]</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7417342044128407</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[9]</t>
+          <t>iterations.alpha_pr[28]</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9474932149843019</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iterations.d_norm[0]</t>
+          <t>iterations.alpha_pr[29]</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>0.9942761693575054</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iterations.d_norm[10]</t>
+          <t>iterations.alpha_pr[2]</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7272992216110895</v>
+        <v>0.08616289672338637</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>iterations.d_norm[11]</t>
+          <t>iterations.alpha_pr[30]</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2739568265665264</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iterations.d_norm[12]</t>
+          <t>iterations.alpha_pr[3]</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2633163140030746</v>
+        <v>0.6361610053707666</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iterations.d_norm[13]</t>
+          <t>iterations.alpha_pr[4]</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4382502076826575</v>
+        <v>0.577962749278744</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iterations.d_norm[14]</t>
+          <t>iterations.alpha_pr[5]</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>14.44066179802158</v>
+        <v>0.2710494739702024</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>iterations.d_norm[15]</t>
+          <t>iterations.alpha_pr[6]</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9013898182058694</v>
+        <v>0.6825501703277903</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iterations.d_norm[16]</t>
+          <t>iterations.alpha_pr[7]</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8.003324255876034</v>
+        <v>0.9260873418951333</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iterations.d_norm[17]</t>
+          <t>iterations.alpha_pr[8]</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7.03165024861942</v>
+        <v>0.3967995100558559</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iterations.d_norm[18]</t>
+          <t>iterations.alpha_pr[9]</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3.097451281786942</v>
+        <v>0.9372847378610333</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iterations.d_norm[19]</t>
+          <t>iterations.d_norm[0]</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.647323773261252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iterations.d_norm[1]</t>
+          <t>iterations.d_norm[10]</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6.544560899193607</v>
+        <v>0.1086654195236866</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iterations.d_norm[20]</t>
+          <t>iterations.d_norm[11]</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.241831134209767</v>
+        <v>0.1440875031124218</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iterations.d_norm[21]</t>
+          <t>iterations.d_norm[12]</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6615890427732305</v>
+        <v>0.09668686015530797</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iterations.d_norm[22]</t>
+          <t>iterations.d_norm[13]</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.1563961020153719</v>
+        <v>0.2325380870126869</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iterations.d_norm[23]</t>
+          <t>iterations.d_norm[14]</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.002989321407090501</v>
+        <v>0.03819067886898201</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iterations.d_norm[24]</t>
+          <t>iterations.d_norm[15]</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0002360239725177757</v>
+        <v>0.02254886858153141</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iterations.d_norm[25]</t>
+          <t>iterations.d_norm[16]</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5.088316656510057e-05</v>
+        <v>0.01212767997049278</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iterations.d_norm[2]</t>
+          <t>iterations.d_norm[17]</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>81.81867905008225</v>
+        <v>0.03190710167249801</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>iterations.d_norm[3]</t>
+          <t>iterations.d_norm[18]</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>61.48813652530714</v>
+        <v>0.1484090136839736</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>iterations.d_norm[4]</t>
+          <t>iterations.d_norm[19]</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>48.39264542410496</v>
+        <v>1.638129340349624</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>iterations.d_norm[5]</t>
+          <t>iterations.d_norm[1]</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3.181439782758623</v>
+        <v>5.819378187228672</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iterations.d_norm[6]</t>
+          <t>iterations.d_norm[20]</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>21.75223589452557</v>
+        <v>0.1422218610139849</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iterations.d_norm[7]</t>
+          <t>iterations.d_norm[21]</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5188976666221637</v>
+        <v>0.3121056951925072</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iterations.d_norm[8]</t>
+          <t>iterations.d_norm[22]</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7.122965755593777</v>
+        <v>7.321260040467346</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iterations.d_norm[9]</t>
+          <t>iterations.d_norm[23]</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.05413856381084572</v>
+        <v>0.5403918726666523</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iterations.inf_du[0]</t>
+          <t>iterations.d_norm[24]</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.9633332197286194</v>
+        <v>1.188525369254684</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iterations.inf_du[10]</t>
+          <t>iterations.d_norm[25]</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>38495.33802394902</v>
+        <v>1.331145073188553</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iterations.inf_du[11]</t>
+          <t>iterations.d_norm[26]</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>24707.45015458806</v>
+        <v>0.2782396055888623</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iterations.inf_du[12]</t>
+          <t>iterations.d_norm[27]</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.020968097989733</v>
+        <v>0.03582691607013199</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iterations.inf_du[13]</t>
+          <t>iterations.d_norm[28]</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>812.1136499909117</v>
+        <v>0.0004899823574266031</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>iterations.inf_du[14]</t>
+          <t>iterations.d_norm[29]</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>66078.31855878994</v>
+        <v>6.24650615362903e-05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>iterations.inf_du[15]</t>
+          <t>iterations.d_norm[2]</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>27198.59928900213</v>
+        <v>3.868648159852013</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iterations.inf_du[16]</t>
+          <t>iterations.d_norm[30]</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.3109831117427504</v>
+        <v>1.472312263591023e-06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>iterations.inf_du[17]</t>
+          <t>iterations.d_norm[3]</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2363.943369544606</v>
+        <v>18.15173138511456</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iterations.inf_du[18]</t>
+          <t>iterations.d_norm[4]</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.002544961337451301</v>
+        <v>0.8219633501928776</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iterations.inf_du[19]</t>
+          <t>iterations.d_norm[5]</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>475.9557344194075</v>
+        <v>31.82519451321187</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iterations.inf_du[1]</t>
+          <t>iterations.d_norm[6]</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>9.464709932236097</v>
+        <v>4.33599343217309</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iterations.inf_du[20]</t>
+          <t>iterations.d_norm[7]</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>87.82788586130289</v>
+        <v>0.5048000300535735</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iterations.inf_du[21]</t>
+          <t>iterations.d_norm[8]</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0001288671521373352</v>
+        <v>11.38020551448038</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iterations.inf_du[22]</t>
+          <t>iterations.d_norm[9]</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2502824035766622</v>
+        <v>19.28461116964666</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iterations.inf_du[23]</t>
+          <t>iterations.inf_du[0]</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>8.207994284248343e-10</v>
+        <v>0.9643852149363595</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iterations.inf_du[24]</t>
+          <t>iterations.inf_du[10]</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0001111095312859023</v>
+        <v>936.4752608663757</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>iterations.inf_du[25]</t>
+          <t>iterations.inf_du[11]</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4.65155691742325e-12</v>
+        <v>2377.907630176199</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iterations.inf_du[2]</t>
+          <t>iterations.inf_du[12]</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>208.3854641376601</v>
+        <v>0.2398620509777067</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>iterations.inf_du[3]</t>
+          <t>iterations.inf_du[13]</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>213.4741954569942</v>
+        <v>20.48511363072703</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>iterations.inf_du[4]</t>
+          <t>iterations.inf_du[14]</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>80.1586588514628</v>
+        <v>1319.906498985677</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iterations.inf_du[5]</t>
+          <t>iterations.inf_du[15]</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>310.5835988783788</v>
+        <v>0.2976572468424143</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iterations.inf_du[6]</t>
+          <t>iterations.inf_du[16]</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>345.374597795389</v>
+        <v>0.1817100217450815</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iterations.inf_du[7]</t>
+          <t>iterations.inf_du[17]</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>655.2209185176371</v>
+        <v>3.004363385041981</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iterations.inf_du[8]</t>
+          <t>iterations.inf_du[18]</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1106.728282449934</v>
+        <v>1.887235107777015</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iterations.inf_du[9]</t>
+          <t>iterations.inf_du[19]</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>114.9964621143954</v>
+        <v>0.5728416516769963</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[0]</t>
+          <t>iterations.inf_du[1]</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8861184565702587</v>
+        <v>4.385184986688515</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[10]</t>
+          <t>iterations.inf_du[20]</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.009649388412203308</v>
+        <v>314.6250228390973</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[11]</t>
+          <t>iterations.inf_du[21]</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.01039042229394127</v>
+        <v>14864.7015278235</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[12]</t>
+          <t>iterations.inf_du[22]</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.04670358719448053</v>
+        <v>4735.304590523092</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[13]</t>
+          <t>iterations.inf_du[23]</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0974497384973354</v>
+        <v>0.003987142050200232</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[14]</t>
+          <t>iterations.inf_du[24]</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.1620860614498945</v>
+        <v>418.1783175258879</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[15]</t>
+          <t>iterations.inf_du[25]</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.2001657942891946</v>
+        <v>0.0007161779393745071</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[16]</t>
+          <t>iterations.inf_du[26]</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.04297182202392769</v>
+        <v>2.512662104403574</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[17]</t>
+          <t>iterations.inf_du[27]</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.05053154240334301</v>
+        <v>1.117611012624309e-07</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[18]</t>
+          <t>iterations.inf_du[28]</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.01125616892811365</v>
+        <v>0.04704460009361702</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[19]</t>
+          <t>iterations.inf_du[29]</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.007463193096880261</v>
+        <v>0.000271910555938928</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[1]</t>
+          <t>iterations.inf_du[2]</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.8168497003491089</v>
+        <v>292.3197001431356</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[20]</t>
+          <t>iterations.inf_du[30]</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.001856685890126997</v>
+        <v>7.567058091240142e-12</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[21]</t>
+          <t>iterations.inf_du[3]</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.0006904362382709195</v>
+        <v>170.2231907590095</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[22]</t>
+          <t>iterations.inf_du[4]</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.577611996061989e-05</v>
+        <v>164.0131482492552</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[23]</t>
+          <t>iterations.inf_du[5]</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.423904549824329e-08</v>
+        <v>107.2751261901154</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[24]</t>
+          <t>iterations.inf_du[6]</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6.074785119380977e-11</v>
+        <v>124.494242259492</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[25]</t>
+          <t>iterations.inf_du[7]</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3.746170040841434e-11</v>
+        <v>53.13699455407038</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[2]</t>
+          <t>iterations.inf_du[8]</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7005603088453061</v>
+        <v>221.914503169496</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[3]</t>
+          <t>iterations.inf_du[9]</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4220481002273573</v>
+        <v>26.22223610027095</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[4]</t>
+          <t>iterations.inf_pr[0]</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3262356295733824</v>
+        <v>0.1869513138379173</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[5]</t>
+          <t>iterations.inf_pr[10]</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.2943100706231767</v>
+        <v>0.1327510096575359</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[6]</t>
+          <t>iterations.inf_pr[11]</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.06211117101512542</v>
+        <v>0.04804546535764587</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[7]</t>
+          <t>iterations.inf_pr[12]</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.05955175669180157</v>
+        <v>0.004732558335996784</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[8]</t>
+          <t>iterations.inf_pr[13]</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.01652432770266365</v>
+        <v>0.02255478775061619</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[9]</t>
+          <t>iterations.inf_pr[14]</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.00186700075901669</v>
+        <v>0.009973245485426219</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>iterations.mu[0]</t>
+          <t>iterations.inf_pr[15]</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>0.001335287702742605</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iterations.mu[10]</t>
+          <t>iterations.inf_pr[16]</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.1307314082100396</v>
+        <v>9.898035470889965e-05</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iterations.mu[11]</t>
+          <t>iterations.inf_pr[17]</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.04275072900144484</v>
+        <v>0.0004116054308336212</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iterations.mu[12]</t>
+          <t>iterations.inf_pr[18]</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.01019127528443889</v>
+        <v>0.002692133728223238</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iterations.mu[13]</t>
+          <t>iterations.inf_pr[19]</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.02311242893127176</v>
+        <v>0.1796432092113367</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iterations.mu[14]</t>
+          <t>iterations.inf_pr[1]</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.1479398276913833</v>
+        <v>0.3425800567557786</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iterations.mu[15]</t>
+          <t>iterations.inf_pr[20]</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.09549542011102975</v>
+        <v>0.1782970288171697</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>iterations.mu[16]</t>
+          <t>iterations.inf_pr[21]</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.02865791805345809</v>
+        <v>0.1265310207929602</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>iterations.mu[17]</t>
+          <t>iterations.inf_pr[22]</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.009626189088045399</v>
+        <v>0.07078826672577421</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>iterations.mu[18]</t>
+          <t>iterations.inf_pr[23]</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.003098236162411289</v>
+        <v>0.001320468132742655</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iterations.mu[19]</t>
+          <t>iterations.inf_pr[24]</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.001047265250633167</v>
+        <v>0.004478933000273751</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iterations.mu[1]</t>
+          <t>iterations.inf_pr[25]</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.323142876219158</v>
+        <v>0.001983413284889934</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iterations.mu[20]</t>
+          <t>iterations.inf_pr[26]</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.0004610347446208043</v>
+        <v>0.0001309371203124243</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iterations.mu[21]</t>
+          <t>iterations.inf_pr[27]</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>5.186775438492818e-05</v>
+        <v>1.553062562109631e-06</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iterations.mu[22]</t>
+          <t>iterations.inf_pr[28]</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.554537297469826e-06</v>
+        <v>2.87975865376211e-10</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iterations.mu[23]</t>
+          <t>iterations.inf_pr[29]</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1.224047284573878e-07</v>
+        <v>2.649616637206975e-11</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>iterations.mu[24]</t>
+          <t>iterations.inf_pr[2]</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.60964624962432e-08</v>
+        <v>0.3394708311039736</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>iterations.mu[25]</t>
+          <t>iterations.inf_pr[30]</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>9.999999999999999e-12</v>
+        <v>3.962548345004535e-11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>iterations.mu[2]</t>
+          <t>iterations.inf_pr[3]</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1.889234020690886</v>
+        <v>0.1615249379295201</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iterations.mu[3]</t>
+          <t>iterations.inf_pr[4]</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3.219690973602247</v>
+        <v>0.1335973114494272</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iterations.mu[4]</t>
+          <t>iterations.inf_pr[5]</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2.221379114377282</v>
+        <v>0.215826619262784</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iterations.mu[5]</t>
+          <t>iterations.inf_pr[6]</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>11.80419775350624</v>
+        <v>0.03807516317657722</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iterations.mu[6]</t>
+          <t>iterations.inf_pr[7]</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1.571961546633907</v>
+        <v>0.0027929942133883</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iterations.mu[7]</t>
+          <t>iterations.inf_pr[8]</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.9866807945624391</v>
+        <v>0.01425125745722688</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iterations.mu[8]</t>
+          <t>iterations.inf_pr[9]</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.4240794036675688</v>
+        <v>0.2750468482898789</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>iterations.mu[9]</t>
+          <t>iterations.mu[0]</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.04335954149334025</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>iterations.obj[0]</t>
+          <t>iterations.mu[10]</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3.53074955862377</v>
+        <v>0.0152803741284103</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>iterations.obj[10]</t>
+          <t>iterations.mu[11]</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2.637440975102415</v>
+        <v>0.02552528093217498</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>iterations.obj[11]</t>
+          <t>iterations.mu[12]</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2.613193824985048</v>
+        <v>0.008084810365726705</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>iterations.obj[12]</t>
+          <t>iterations.mu[13]</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2.513503348577655</v>
+        <v>0.005999856582086264</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>iterations.obj[13]</t>
+          <t>iterations.mu[14]</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2.311783831322646</v>
+        <v>0.003131766525215177</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>iterations.obj[14]</t>
+          <t>iterations.mu[15]</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2.447641798908395</v>
+        <v>0.0002957511062581752</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>iterations.obj[15]</t>
+          <t>iterations.mu[16]</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2.259497200302917</v>
+        <v>1.295775959363564e-05</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>iterations.obj[16]</t>
+          <t>iterations.mu[17]</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2.256869156523058</v>
+        <v>3.888340515372698e-06</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>iterations.obj[17]</t>
+          <t>iterations.mu[18]</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2.206202350443796</v>
+        <v>4.196911857014151e-06</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>iterations.obj[18]</t>
+          <t>iterations.mu[19]</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2.189610407568541</v>
+        <v>9.999999999999999e-12</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>iterations.obj[19]</t>
+          <t>iterations.mu[1]</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2.173954280128013</v>
+        <v>0.6128839576018941</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>iterations.obj[1]</t>
+          <t>iterations.mu[20]</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>3.699184324232579</v>
+        <v>0.0003299750878501219</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>iterations.obj[20]</t>
+          <t>iterations.mu[21]</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2.168585306506681</v>
+        <v>0.02219504246574262</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>iterations.obj[21]</t>
+          <t>iterations.mu[22]</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2.166567380190733</v>
+        <v>0.0004508692989470423</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>iterations.obj[22]</t>
+          <t>iterations.mu[23]</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2.166274544054903</v>
+        <v>0.003050785046103949</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>iterations.obj[23]</t>
+          <t>iterations.mu[24]</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>2.166268210231566</v>
+        <v>0.0008070253231940831</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>iterations.obj[24]</t>
+          <t>iterations.mu[25]</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2.166267507886781</v>
+        <v>0.0001504562657857676</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>iterations.obj[25]</t>
+          <t>iterations.mu[26]</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2.166267395045595</v>
+        <v>1.520990727649117e-05</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>iterations.obj[2]</t>
+          <t>iterations.mu[27]</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>3.266075032891778</v>
+        <v>3.310553679758609e-07</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>iterations.obj[3]</t>
+          <t>iterations.mu[28]</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3.224871879537706</v>
+        <v>7.023967751110071e-09</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>iterations.obj[4]</t>
+          <t>iterations.mu[29]</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2.560006291478433</v>
+        <v>7.00113021073999e-10</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>iterations.obj[5]</t>
+          <t>iterations.mu[2]</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2.711566168545242</v>
+        <v>2.300524641232216</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>iterations.obj[6]</t>
+          <t>iterations.mu[30]</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2.612352506233407</v>
+        <v>9.999999999999999e-12</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>iterations.obj[7]</t>
+          <t>iterations.mu[3]</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2.754337879639674</v>
+        <v>2.300524641232216</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>iterations.obj[8]</t>
+          <t>iterations.mu[4]</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2.692884497541928</v>
+        <v>2.300524641232216</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>iterations.obj[9]</t>
+          <t>iterations.mu[5]</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>2.673821712625985</v>
+        <v>2.300524641232216</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[0]</t>
+          <t>iterations.mu[6]</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>2.300524641232216</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[10]</t>
+          <t>iterations.mu[7]</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.1721898648756668</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[11]</t>
+          <t>iterations.mu[8]</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.09876543209876543</v>
+        <v>0.05866814190598076</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[12]</t>
+          <t>iterations.mu[9]</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2.106995884773662</v>
+        <v>0.02050320539881186</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[13]</t>
+          <t>iterations.obj[0]</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.7023319615912207</v>
+        <v>2.592759875600154</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[14]</t>
+          <t>iterations.obj[10]</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>2.409733414699749</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[15]</t>
+          <t>iterations.obj[11]</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.2341106538637402</v>
+        <v>2.412103586058501</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[16]</t>
+          <t>iterations.obj[12]</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>2.392095216806003</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[17]</t>
+          <t>iterations.obj[13]</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>2.340684474053823</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[18]</t>
+          <t>iterations.obj[14]</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>2.333035211076758</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[19]</t>
+          <t>iterations.obj[15]</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>2.335856768636569</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[1]</t>
+          <t>iterations.obj[16]</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>2.332276218122759</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[20]</t>
+          <t>iterations.obj[17]</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>2.326476761569768</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[21]</t>
+          <t>iterations.obj[18]</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>2.31226676542363</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[22]</t>
+          <t>iterations.obj[19]</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>2.165263867204074</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[23]</t>
+          <t>iterations.obj[1]</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>3.111973695535434</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[24]</t>
+          <t>iterations.obj[20]</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>2.164373974507242</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[25]</t>
+          <t>iterations.obj[21]</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0</v>
+        <v>2.198933436505788</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[2]</t>
+          <t>iterations.obj[22]</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>2.18071495343769</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[3]</t>
+          <t>iterations.obj[23]</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>2.18499470766311</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[4]</t>
+          <t>iterations.obj[24]</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>2.171855929387564</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[5]</t>
+          <t>iterations.obj[25]</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>2.167142817688195</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[6]</t>
+          <t>iterations.obj[26]</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>2.166338780967626</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[7]</t>
+          <t>iterations.obj[27]</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.166269210165879</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[8]</t>
+          <t>iterations.obj[28]</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>2.166267539166262</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>iterations.regularization_size[9]</t>
+          <t>iterations.obj[29]</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.1111111111111111</v>
+        <v>2.166267399767584</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>n_call_callback_fun</t>
+          <t>iterations.obj[2]</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>3.413738813076199</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>n_call_nlp_f</t>
+          <t>iterations.obj[30]</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>37</v>
+        <v>2.166267395059844</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>n_call_nlp_g</t>
+          <t>iterations.obj[3]</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>37</v>
+        <v>3.24386425100924</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>n_call_nlp_grad</t>
+          <t>iterations.obj[4]</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>3.235527797243469</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>n_call_nlp_grad_f</t>
+          <t>iterations.obj[5]</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>27</v>
+        <v>2.758915791756197</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>n_call_nlp_hess_l</t>
+          <t>iterations.obj[6]</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>25</v>
+        <v>2.787457002764151</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>n_call_nlp_jac_g</t>
+          <t>iterations.obj[7]</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>27</v>
+        <v>2.794397841397392</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>n_call_total</t>
+          <t>iterations.obj[8]</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>2.723876332694718</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>return_status</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Solve_Succeeded</t>
-        </is>
+          <t>iterations.obj[9]</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2.412223518695485</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="B220" t="b">
-        <v>1</v>
+          <t>iterations.regularization_size[0]</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>t_proc_callback_fun</t>
+          <t>iterations.regularization_size[10]</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>21.33333333333333</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>t_proc_nlp_f</t>
+          <t>iterations.regularization_size[11]</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.6740000000000003</v>
+        <v>7.111111111111111</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>t_proc_nlp_g</t>
+          <t>iterations.regularization_size[12]</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1.323000000000001</v>
+        <v>2.37037037037037</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>t_proc_nlp_grad</t>
+          <t>iterations.regularization_size[13]</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>0.7901234567901234</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>t_proc_nlp_grad_f</t>
+          <t>iterations.regularization_size[14]</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1.045</v>
+        <v>2.106995884773662</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>t_proc_nlp_hess_l</t>
+          <t>iterations.regularization_size[15]</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>11.885</v>
+        <v>5.618655692729766</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>t_proc_nlp_jac_g</t>
+          <t>iterations.regularization_size[16]</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>3.960999999999999</v>
+        <v>14.98308184727937</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>t_proc_total</t>
+          <t>iterations.regularization_size[17]</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>18.971</v>
+        <v>4.994360615759791</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>t_wall_callback_fun</t>
+          <t>iterations.regularization_size[18]</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0</v>
+        <v>1.66478687191993</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>t_wall_nlp_f</t>
+          <t>iterations.regularization_size[19]</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.666415</v>
+        <v>0.5549289573066434</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>t_wall_nlp_g</t>
+          <t>iterations.regularization_size[1]</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.323642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>t_wall_nlp_grad</t>
+          <t>iterations.regularization_size[20]</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0</v>
+        <v>1.479810552817716</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>t_wall_nlp_grad_f</t>
+          <t>iterations.regularization_size[21]</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0483</v>
+        <v>0.4932701842725719</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>t_wall_nlp_hess_l</t>
+          <t>iterations.regularization_size[22]</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>11.886728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>t_wall_nlp_jac_g</t>
+          <t>iterations.regularization_size[23]</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>3.961224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>t_wall_total</t>
+          <t>iterations.regularization_size[24]</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>18.970762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
+          <t>iterations.regularization_size[25]</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[26]</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[27]</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[28]</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[29]</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[2]</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[30]</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[3]</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[4]</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[5]</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[6]</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[7]</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[8]</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>iterations.regularization_size[9]</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>n_call_callback_fun</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>n_call_nlp_f</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>n_call_nlp_g</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>n_call_nlp_grad</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>n_call_nlp_grad_f</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>n_call_nlp_hess_l</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>n_call_nlp_jac_g</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>n_call_total</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>return_status</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Solve_Succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="B260" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>t_proc_callback_fun</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>t_proc_nlp_f</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0.7070000000000004</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>t_proc_nlp_g</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>1.467</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>t_proc_nlp_grad</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>t_proc_nlp_grad_f</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>1.176</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>t_proc_nlp_hess_l</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>13.257</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>t_proc_nlp_jac_g</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>4.387</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>t_proc_total</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>21.093</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>t_wall_callback_fun</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>t_wall_nlp_f</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0.7082569999999998</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>t_wall_nlp_g</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>1.467031</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>t_wall_nlp_grad</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>t_wall_nlp_grad_f</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>1.17512</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>t_wall_nlp_hess_l</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>13.256074</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>t_wall_nlp_jac_g</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>4.390722</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>t_wall_total</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>21.093465</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
           <t>unified_return_status</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>SOLVER_RET_SUCCESS</t>
         </is>
@@ -9952,10 +10352,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537648173</v>
       </c>
       <c r="E2" t="n">
-        <v>30.94325083315806</v>
+        <v>30.94325083290559</v>
       </c>
     </row>
     <row r="3">
@@ -9973,10 +10373,10 @@
         <v>0.04698862362078716</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0552234488668002</v>
+        <v>0.05522344886762574</v>
       </c>
       <c r="E3" t="n">
-        <v>2.549244335814687</v>
+        <v>2.549244335836028</v>
       </c>
     </row>
     <row r="4">
@@ -9994,10 +10394,10 @@
         <v>0.01325917124942102</v>
       </c>
       <c r="D4" t="n">
-        <v>1.724083649561253e-06</v>
+        <v>1.724083650894573e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>7.958775788733897e-05</v>
+        <v>7.958775794836467e-05</v>
       </c>
     </row>
     <row r="5">
@@ -10015,10 +10415,10 @@
         <v>2.151606933843013</v>
       </c>
       <c r="D5" t="n">
-        <v>1.310723987774028</v>
+        <v>1.310723987777075</v>
       </c>
       <c r="E5" t="n">
-        <v>60.50610329877767</v>
+        <v>60.50610329852036</v>
       </c>
     </row>
     <row r="6">
@@ -10036,10 +10436,10 @@
         <v>0.0783091834800308</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1174456015503173</v>
+        <v>0.1174456015613583</v>
       </c>
       <c r="E6" t="n">
-        <v>5.421565307169542</v>
+        <v>5.421565307643556</v>
       </c>
     </row>
     <row r="7">
@@ -10057,10 +10457,10 @@
         <v>0.2470733791131532</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01255907900492259</v>
+        <v>0.01255907900531688</v>
       </c>
       <c r="E7" t="n">
-        <v>0.579756637322155</v>
+        <v>0.5797566373365434</v>
       </c>
     </row>
     <row r="8">
@@ -10076,7 +10476,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>2.166267395045595</v>
+        <v>2.166267395059844</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
@@ -10150,7 +10550,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.808035465986087</v>
+        <v>3.808035466072172</v>
       </c>
       <c r="C2" t="n">
         <v>-4</v>
@@ -10183,7 +10583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.86535588595925e-15</v>
+        <v>-2.5522288122537e-16</v>
       </c>
       <c r="C3" t="n">
         <v>-30</v>
@@ -10216,7 +10616,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1140304863710548</v>
+        <v>-0.1140304864151476</v>
       </c>
       <c r="C4" t="n">
         <v>-30</v>
@@ -10249,7 +10649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.367107440935978e-14</v>
+        <v>6.587616550414456e-15</v>
       </c>
       <c r="C5" t="n">
         <v>-30</v>
@@ -10282,7 +10682,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7500000074958727</v>
+        <v>0.7500000074958744</v>
       </c>
       <c r="C6" t="n">
         <v>0.3</v>
@@ -10319,7 +10719,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1646396705960972</v>
+        <v>0.1646396706065064</v>
       </c>
       <c r="C7" t="n">
         <v>0.1</v>
@@ -10352,7 +10752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3999999944048857</v>
+        <v>0.3999999944802849</v>
       </c>
       <c r="C8" t="n">
         <v>0.4</v>
@@ -10389,7 +10789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.563971623321324</v>
       </c>
       <c r="C9" t="n">
         <v>0.35</v>
@@ -10422,7 +10822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3655521648352896</v>
+        <v>0.3655521648059379</v>
       </c>
       <c r="C10" t="n">
         <v>0.2</v>
@@ -10455,7 +10855,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1187676990826549</v>
+        <v>0.1187676990756998</v>
       </c>
       <c r="C11" t="n">
         <v>0.1</v>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>aadd597-dirty</t>
+          <t>4809b98-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.166267395059844</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.563971623321324</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.463971623321324</v>
+        <v>0.4639716234248189</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.563971623321324</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.808035466072172</v>
+        <v>3.808035466104309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.5522288122537e-16</v>
+        <v>-1.419485665407633e-16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1140304864151476</v>
+        <v>-0.1140304862776677</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.587616550414456e-15</v>
+        <v>2.329054801675277e-16</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.808035466072172</v>
+        <v>3.808035466104309</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.5522288122537e-16</v>
+        <v>-1.419485665407633e-16</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1140304864151476</v>
+        <v>-0.1140304862776677</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.587616550414456e-15</v>
+        <v>2.329054801675277e-16</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.117525146753172</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.117525146753172</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117.525146753172</v>
+        <v>117.5251467546148</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2590985971681401</v>
+        <v>0.259098597171321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1137361494300794</v>
+        <v>0.1137361494450511</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01584356100175216</v>
+        <v>0.01584356100153953</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1137361494300794</v>
+        <v>0.1137361494450511</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01584356100175216</v>
+        <v>0.01584356100153953</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.117525146753172</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.01615991765162661</v>
+        <v>0.01615991765255458</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6703135537648173</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9.696954368854737</v>
+        <v>9.696954368874374</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.514895921886137</v>
+        <v>7.514895921886133</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.129104669753592</v>
+        <v>2.129104669753593</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.704104673501529</v>
+        <v>2.704104673501531</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.252227383789823</v>
+        <v>-1.252227383789828</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3553227391827451</v>
+        <v>0.3553227391790962</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9.195080003512478</v>
+        <v>9.195080003418058</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>73262.37412649603</v>
+        <v>73262.37412814774</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1000000098654832</v>
+        <v>0.1000000099082708</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6473213459669306</v>
+        <v>0.6473213460623958</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.02999999002416101</v>
+        <v>0.02999999002416147</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5.239711082357698</v>
+        <v>5.239711082509094</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.740771950771719</v>
+        <v>2.74077195085091</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.03717044124948815</v>
+        <v>0.03717044124999266</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.57077861325071</v>
+        <v>25.57077861391034</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-24.40325580872998</v>
+        <v>-24.40325580806729</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.59674419127002</v>
+        <v>25.59674419193271</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25.59674419127002</v>
+        <v>25.59674419193271</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.8272426172712272</v>
+        <v>-0.8272426172673978</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8272426172712272</v>
+        <v>-0.8272426172673978</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>229.0672432883348</v>
+        <v>229.0672432918443</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.02287411769199271</v>
+        <v>0.02287411769230318</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.008152368697903957</v>
+        <v>0.008152368698001877</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.02173964964380031</v>
+        <v>0.02173964964406143</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.2717456205475038</v>
+        <v>0.2717456205507678</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5764608398297</v>
+        <v>0.5764608398367767</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.513874929862158</v>
+        <v>1.513874929880742</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4661115090956274</v>
+        <v>0.4661115090957508</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.002045221041065397</v>
+        <v>0.002045221040870147</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.01462208659223752</v>
+        <v>0.0146220865917117</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.01118976298308151</v>
+        <v>0.01118976298241564</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.1398720372885188</v>
+        <v>0.1398720372801955</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.1827760824029689</v>
+        <v>0.1827760823963963</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.144115209957425</v>
+        <v>0.1441152099591942</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.788479586949961</v>
+        <v>0.7884795869879944</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.05378208975937</v>
+        <v>0.05378208975936261</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.310723987777075</v>
+        <v>1.310723987779651</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.1174456015613583</v>
+        <v>0.1174456015663288</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.01255907900531688</v>
+        <v>0.01255907900548735</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.004807540213177311</v>
+        <v>0.004807540213394086</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6703135537648173</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.05522344886762574</v>
+        <v>0.05522344886830369</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.724083650894573e-06</v>
+        <v>1.72408364673732e-06</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.310723987777075</v>
+        <v>1.310723987779651</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.1174456015613583</v>
+        <v>0.1174456015663288</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.01255907900531688</v>
+        <v>0.01255907900548735</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.166267395059844</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6703135537648173</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>30.94325083290559</v>
+        <v>30.94325083274244</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.05522344886762574</v>
+        <v>0.05522344886830369</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2.549244335836028</v>
+        <v>2.549244335859048</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.724083650894573e-06</v>
+        <v>1.72408364673732e-06</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>7.958775794836467e-05</v>
+        <v>7.958775775619772e-05</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.310723987777075</v>
+        <v>1.310723987779651</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>60.50610329852036</v>
+        <v>60.50610329844281</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.1174456015613583</v>
+        <v>0.1174456015663288</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5.421565307643556</v>
+        <v>5.421565307855405</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.01255907900531688</v>
+        <v>0.01255907900548735</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5797566373365434</v>
+        <v>0.5797566373425304</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.166267395059844</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.808035466072172</v>
+        <v>3.808035466104309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-2.5522288122537e-16</v>
+        <v>-1.419485665407633e-16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.1140304864151476</v>
+        <v>-0.1140304862776677</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.587616550414456e-15</v>
+        <v>2.329054801675277e-16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6703135537648173</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.3553227391827451</v>
+        <v>0.3553227391790962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.8272426172712272</v>
+        <v>-0.8272426172673978</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.808035466072172</v>
+        <v>3.808035466104309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-2.5522288122537e-16</v>
+        <v>-1.419485665407633e-16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.1140304864151476</v>
+        <v>-0.1140304862776677</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.587616550414456e-15</v>
+        <v>2.329054801675277e-16</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.3553227391827451</v>
+        <v>0.3553227391790962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.514895921886137</v>
+        <v>7.514895921886133</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.129104669753592</v>
+        <v>2.129104669753593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.704104673501529</v>
+        <v>2.704104673501531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1.252227383789823</v>
+        <v>-1.252227383789828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.8272426172712272</v>
+        <v>-0.8272426172673978</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.03717044124948815</v>
+        <v>0.03717044124999266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25.57077861325071</v>
+        <v>25.57077861391034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-24.40325580872998</v>
+        <v>-24.40325580806729</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.59674419127002</v>
+        <v>25.59674419193271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>25.59674419127002</v>
+        <v>25.59674419193271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1646396706065065</v>
+        <v>0.1646396706102183</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.125384628432619</v>
+        <v>0.1253846284354458</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.62567717561822</v>
+        <v>4.625677175513933</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.563971623321324</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.463971623321324</v>
+        <v>0.4639716234248189</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.563971623321324</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3655521648059379</v>
+        <v>0.3655521647927926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09138804120148446</v>
+        <v>0.09138804119819814</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03340709629857689</v>
+        <v>0.03340709629617424</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1187676990756998</v>
+        <v>0.1187676990613332</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05938384953784991</v>
+        <v>0.05938384953066662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.007052883171867995</v>
+        <v>0.007052883170161708</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02482615642965856</v>
+        <v>0.02482615643021828</v>
       </c>
       <c r="C2" t="n">
-        <v>24.82615642965856</v>
+        <v>24.82615643021828</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08231983530325322</v>
+        <v>0.08231983530510915</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3450,13 +3450,13 @@
         <v>0.04006130921326841</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001163800584371253</v>
+        <v>0.001163800584397492</v>
       </c>
       <c r="H2" t="n">
-        <v>5.789663707345507e-05</v>
+        <v>5.789663707736762e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00122154826450613</v>
+        <v>0.001221548264536278</v>
       </c>
     </row>
     <row r="3">
@@ -3472,7 +3472,7 @@
         <v>11.98624513657535</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06545991765162661</v>
+        <v>0.06545991765255457</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3497,28 +3497,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008705566426160887</v>
+        <v>0.008705566426267762</v>
       </c>
       <c r="C4" t="n">
-        <v>8.705566426160887</v>
+        <v>8.705566426267762</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1137361494300794</v>
+        <v>0.1137361494450511</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01584356100175216</v>
+        <v>0.01584356100153953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001854183660275195</v>
+        <v>0.000185418366028859</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001472501820051632</v>
+        <v>0.0001472501820757719</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003229004954038383</v>
+        <v>0.0003229004954760323</v>
       </c>
     </row>
     <row r="5">
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007441430256369403</v>
+        <v>0.007441430257734986</v>
       </c>
       <c r="C5" t="n">
-        <v>7.441430256369403</v>
+        <v>7.441430257734986</v>
       </c>
       <c r="D5" t="n">
-        <v>0.181985811660662</v>
+        <v>0.1819858117124095</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3543,13 +3543,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.860357564092351e-08</v>
+        <v>1.860357564433746e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000197246886193927</v>
+        <v>0.0001972468863025144</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000197246886193927</v>
+        <v>0.0001972468863025144</v>
       </c>
     </row>
     <row r="6">
@@ -3565,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09115991765162662</v>
+        <v>0.09115991765255457</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3596,7 +3596,7 @@
         <v>5.772676558666255</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04115991765162661</v>
+        <v>0.04115991765255458</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01615991765162661</v>
+        <v>0.01615991765255458</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004008851555829226</v>
+        <v>0.004008851555540909</v>
       </c>
       <c r="C9" t="n">
-        <v>4.008851555829226</v>
+        <v>4.008851555540909</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4456940150810271</v>
+        <v>0.4456940151851793</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         <v>-0.0025</v>
       </c>
       <c r="G9" t="n">
-        <v>4.464436996276246e-05</v>
+        <v>4.464436995634101e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.793091846422845e-06</v>
+        <v>2.793091846021303e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>4.743144853185156e-05</v>
+        <v>4.743144852502899e-05</v>
       </c>
     </row>
     <row r="10">
@@ -3689,7 +3689,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04115991765162661</v>
+        <v>0.04115991765255458</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04115991765162661</v>
+        <v>0.04115991765255458</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04939190118195193</v>
+        <v>0.04939190118306549</v>
       </c>
       <c r="E12" t="n">
         <v>0.3000000029983498</v>
@@ -3782,7 +3782,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04939190118195193</v>
+        <v>0.04939190118306549</v>
       </c>
       <c r="E13" t="n">
         <v>-0.3000000029983498</v>
@@ -3813,7 +3813,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04433748857361243</v>
+        <v>0.0443374885745404</v>
       </c>
       <c r="E14" t="n">
         <v>0.03743439716312056</v>
@@ -3844,7 +3844,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1162874885736124</v>
+        <v>0.1162874885745404</v>
       </c>
       <c r="E15" t="n">
         <v>0.03743439716312056</v>
@@ -3875,7 +3875,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04433748857361243</v>
+        <v>0.0443374885745404</v>
       </c>
       <c r="E16" t="n">
         <v>-0.03743439716312056</v>
@@ -3906,7 +3906,7 @@
         <v>3.85444018731375</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1162874885736124</v>
+        <v>0.1162874885745404</v>
       </c>
       <c r="E17" t="n">
         <v>-0.03743439716312056</v>
@@ -3937,7 +3937,7 @@
         <v>1.795290858725762</v>
       </c>
       <c r="D18" t="n">
-        <v>0.440871623321324</v>
+        <v>0.4408716234248189</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
         <v>1.31250001311778</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0230799588258133</v>
+        <v>0.02307995882627729</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -3980,10 +3980,10 @@
         <v>1.538086168460948e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>4.399757987101623e-07</v>
+        <v>4.399757987321829e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>1.582083378644461e-05</v>
+        <v>1.582083378646663e-05</v>
       </c>
     </row>
     <row r="20">
@@ -3999,7 +3999,7 @@
         <v>1.31250001311778</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0230799588258133</v>
+        <v>0.02307995882627729</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4011,10 +4011,10 @@
         <v>1.538086168460948e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>4.399757987101623e-07</v>
+        <v>4.399757987321829e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>1.582083378644461e-05</v>
+        <v>1.582083378646663e-05</v>
       </c>
     </row>
     <row r="21">
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1999999972401424</v>
+        <v>0.1999999972930401</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4061,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.05615991765162661</v>
+        <v>0.05615991765255458</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3910599944802849</v>
+        <v>0.3910599945860802</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4117,28 +4117,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0008463459806241594</v>
+        <v>0.000846345980419405</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8463459806241594</v>
+        <v>0.846345980419405</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4392931767483002</v>
+        <v>0.439293176851673</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06338384953784991</v>
+        <v>0.06338384953066661</v>
       </c>
       <c r="G24" t="n">
-        <v>9.954979802058433e-07</v>
+        <v>9.954979797243199e-07</v>
       </c>
       <c r="H24" t="n">
-        <v>1.243579025900469e-06</v>
+        <v>1.243579025298757e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>2.493505646655619e-07</v>
+        <v>2.493505645450659e-07</v>
       </c>
     </row>
     <row r="25">
@@ -4154,7 +4154,7 @@
         <v>0.7628808864265929</v>
       </c>
       <c r="D25" t="n">
-        <v>0.445771623321324</v>
+        <v>0.4457716234248189</v>
       </c>
       <c r="E25" t="n">
         <v>0.01469135802469136</v>
@@ -4185,7 +4185,7 @@
         <v>0.7628808864265929</v>
       </c>
       <c r="D26" t="n">
-        <v>0.445771623321324</v>
+        <v>0.4457716234248189</v>
       </c>
       <c r="E26" t="n">
         <v>-0.01469135802469136</v>
@@ -4216,7 +4216,7 @@
         <v>0.6789473684210525</v>
       </c>
       <c r="D27" t="n">
-        <v>0.435171623321324</v>
+        <v>0.4351716234248189</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0006397162884103913</v>
+        <v>0.000639716288387387</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6397162884103913</v>
+        <v>0.639716288387387</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4274164068407302</v>
+        <v>0.4274164069455397</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4256,13 +4256,13 @@
         <v>-0.003935</v>
       </c>
       <c r="G28" t="n">
-        <v>7.123688784498483e-06</v>
+        <v>7.123688783729976e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>5.33187000385944e-09</v>
+        <v>5.331870003667704e-09</v>
       </c>
       <c r="I28" t="n">
-        <v>7.129018852634795e-06</v>
+        <v>7.129018851866098e-06</v>
       </c>
     </row>
     <row r="29">
@@ -4272,13 +4272,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0006397162884103913</v>
+        <v>0.000639716288387387</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6397162884103913</v>
+        <v>0.639716288387387</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4274164068407302</v>
+        <v>0.4274164069455397</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4287,13 +4287,13 @@
         <v>-0.001065</v>
       </c>
       <c r="G29" t="n">
-        <v>7.123688784498483e-06</v>
+        <v>7.123688783729976e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>5.33187000385944e-09</v>
+        <v>5.331870003667704e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>7.129018852634795e-06</v>
+        <v>7.129018851866098e-06</v>
       </c>
     </row>
     <row r="30">
@@ -4309,7 +4309,7 @@
         <v>0.5959941141696471</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0411599176516266</v>
+        <v>0.04115991765255458</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -4334,28 +4334,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002078434733824747</v>
+        <v>0.0002078434733573332</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2078434733824747</v>
+        <v>0.2078434733573332</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4274164068407302</v>
+        <v>0.4274164069455397</v>
       </c>
       <c r="E31" t="n">
         <v>0.001565</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06338384953784991</v>
+        <v>0.06338384953066661</v>
       </c>
       <c r="G31" t="n">
-        <v>2.443162486798666e-07</v>
+        <v>2.443162485912064e-07</v>
       </c>
       <c r="H31" t="n">
-        <v>2.460479849118289e-07</v>
+        <v>2.460479848229592e-07</v>
       </c>
       <c r="I31" t="n">
-        <v>1.732321657745636e-09</v>
+        <v>1.732321657536088e-09</v>
       </c>
     </row>
     <row r="32">
@@ -4365,28 +4365,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0002078434733824747</v>
+        <v>0.0002078434733573332</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2078434733824747</v>
+        <v>0.2078434733573332</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4274164068407302</v>
+        <v>0.4274164069455397</v>
       </c>
       <c r="E32" t="n">
         <v>-0.001565</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06338384953784991</v>
+        <v>0.06338384953066661</v>
       </c>
       <c r="G32" t="n">
-        <v>2.443162486798666e-07</v>
+        <v>2.443162485912064e-07</v>
       </c>
       <c r="H32" t="n">
-        <v>2.460479849118289e-07</v>
+        <v>2.460479848229592e-07</v>
       </c>
       <c r="I32" t="n">
-        <v>1.732321657745636e-09</v>
+        <v>1.732321657536088e-09</v>
       </c>
     </row>
     <row r="33">
@@ -4402,7 +4402,7 @@
         <v>-0.3960000039578216</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04115991765162661</v>
+        <v>0.04115991765255458</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03664271539979523</v>
+        <v>0.03664271539934473</v>
       </c>
     </row>
     <row r="3">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7061559045134552</v>
+        <v>0.7061559045126601</v>
       </c>
     </row>
     <row r="4">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.284473156894689e-08</v>
+        <v>-2.283598504357287e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001794660944229309</v>
+        <v>-0.001794660944028081</v>
       </c>
     </row>
     <row r="6">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07160127583716314</v>
+        <v>0.07160127585222054</v>
       </c>
     </row>
     <row r="7">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-7.76323183238059e-05</v>
+        <v>-7.763231817808913e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3553227391827451</v>
+        <v>0.3553227391790962</v>
       </c>
     </row>
     <row r="9">
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.648463390620061</v>
+        <v>5.648463390578714</v>
       </c>
     </row>
     <row r="10">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.191051678402466e-05</v>
+        <v>-2.191043727015762e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01250308513717213</v>
+        <v>-0.01250308513689458</v>
       </c>
     </row>
     <row r="12">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9323336274281169</v>
+        <v>0.9323336276652604</v>
       </c>
     </row>
     <row r="13">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0002424221045016494</v>
+        <v>-0.0002424221038355157</v>
       </c>
     </row>
     <row r="14">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.954949201517465e-17</v>
+        <v>-2.085279147733796e-17</v>
       </c>
     </row>
     <row r="15">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.517539521240818e-22</v>
+        <v>4.818707410206858e-22</v>
       </c>
     </row>
     <row r="16">
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2408579822914199</v>
+        <v>-0.2408579822849669</v>
       </c>
     </row>
     <row r="17">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.4000315992275166</v>
+        <v>-0.4000315992141975</v>
       </c>
     </row>
     <row r="18">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.256727680381765e-17</v>
+        <v>1.340509524672916e-17</v>
       </c>
     </row>
     <row r="19">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1024021430455406</v>
+        <v>0.1024021430446468</v>
       </c>
     </row>
     <row r="20">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
     </row>
     <row r="21">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.934827174273248e-19</v>
+        <v>1.935385882339244e-19</v>
       </c>
     </row>
     <row r="22">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1986060691019765</v>
+        <v>-0.1986060691330394</v>
       </c>
     </row>
     <row r="23">
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7794457260438862</v>
+        <v>-0.779445726021365</v>
       </c>
     </row>
     <row r="24">
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7.51057012892061e-19</v>
+        <v>2.28667207055287e-18</v>
       </c>
     </row>
     <row r="25">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01591371475994741</v>
+        <v>0.01591371475306178</v>
       </c>
     </row>
     <row r="26">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.009943506936824e-06</v>
+        <v>-1.009953632655828e-06</v>
       </c>
     </row>
     <row r="27">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5648463947868269</v>
+        <v>-0.5648463950243764</v>
       </c>
     </row>
     <row r="28">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-5.783190067811703e-06</v>
+        <v>-5.783127554474369e-06</v>
       </c>
     </row>
     <row r="29">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.003253733017144216</v>
+        <v>-0.003253733017750465</v>
       </c>
     </row>
     <row r="30">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-11.47472238827099</v>
+        <v>-11.47472239298415</v>
       </c>
     </row>
     <row r="31">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0001267192463559272</v>
+        <v>-0.0001267192462976988</v>
       </c>
     </row>
     <row r="32">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
     </row>
     <row r="33">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.306851650478998e-20</v>
+        <v>1.269203898795724e-20</v>
       </c>
     </row>
     <row r="34">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02574590957319787</v>
+        <v>0.02574590957015981</v>
       </c>
     </row>
     <row r="35">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.08493058475885355</v>
+        <v>-0.08493058476554616</v>
       </c>
     </row>
     <row r="36">
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-5.239670694945015e-18</v>
+        <v>-5.229038944214264e-18</v>
       </c>
     </row>
     <row r="37">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.04854440595543232</v>
+        <v>-0.04854440597030987</v>
       </c>
     </row>
     <row r="38">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.118895236153985</v>
+        <v>0.1188952361552037</v>
       </c>
     </row>
     <row r="39">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.03599829320587388</v>
+        <v>0.03599829320672956</v>
       </c>
     </row>
     <row r="40">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.08289694294811105</v>
+        <v>0.08289694294847418</v>
       </c>
     </row>
     <row r="41">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.04206278273348475</v>
+        <v>-0.04206278273311121</v>
       </c>
     </row>
     <row r="42">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.04206278273348475</v>
+        <v>0.04206278273311121</v>
       </c>
     </row>
     <row r="43">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.118895236153985</v>
+        <v>-0.1188952361552037</v>
       </c>
     </row>
     <row r="44">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1529216796594</v>
+        <v>1.152921679673553</v>
       </c>
     </row>
     <row r="45">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-3.047430655777885e-18</v>
+        <v>-3.184814904083324e-18</v>
       </c>
     </row>
     <row r="46">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.047430655777885e-18</v>
+        <v>3.184814904083324e-18</v>
       </c>
     </row>
     <row r="47">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.715755223053363e-18</v>
+        <v>-1.830138903257797e-18</v>
       </c>
     </row>
     <row r="48">
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-6.343256618606443e-17</v>
+        <v>-6.76614039154329e-17</v>
       </c>
     </row>
     <row r="49">
@@ -4925,11 +4925,11 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0003404378247374978,
+	L=0.0003404378248003771,
 	Y=0.0,
-	D=0.0012461336138990264,
+	D=0.0012461336140693828,
 	l_b=0.0,
-	m_b=-3.601981613290454e-05,
+	m_b=-3.601981615357263e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-3.047430655777885e-18</v>
+        <v>-3.184814904083324e-18</v>
       </c>
     </row>
     <row r="51">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-5.395210257219728e-07</v>
+        <v>-5.395264349976748e-07</v>
       </c>
     </row>
     <row r="52">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.994986692518442e-17</v>
+        <v>2.029162170539768e-17</v>
       </c>
     </row>
     <row r="53">
@@ -4975,29 +4975,29 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.9168592898654198,
+	L=0.9168592898841235,
 	Y=0.0,
-	D=0.06055915724584764,
+	D=0.06055915724693969,
 	l_b=-0.0,
-	m_b=0.07213813866633308,
+	m_b=0.07213813868092246,
 	n_b=-0.0,
-	span_effective=0.7500878943334851, oswalds_efficiency=0.8072554931504061,
+	span_effective=0.7500878943334851, oswalds_efficiency=0.8072554931510372,
 ), AeroComponentResults(
-	L=0.2357219519692426,
+	L=0.23572195196462953,
 	Y=0.0,
-	D=0.018196401856206714,
+	D=0.01819640185580553,
 	l_b=-0.0,
-	m_b=-0.07218097052232664,
+	m_b=-0.07218097054225309,
 	n_b=-0.0,
-	span_effective=0.3655521648059379, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.36555216479279257, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-2.710505431213761e-20,
-	Y=-6.343256618606443e-17,
-	D=0.002895250232157671,
-	l_b=-3.0474306557778854e-18,
-	m_b=7.831215110074344e-05,
-	n_b=1.9949866925184424e-17,
-	span_effective=0.11876769907569983, oswalds_efficiency=0.8232692748986458,
+	L=-0.0,
+	Y=-6.76614039154329e-17,
+	D=0.0028952502316595603,
+	l_b=-3.1848149040833245e-18,
+	m_b=7.831215104919995e-05,
+	n_b=2.0291621705397675e-17,
+	span_effective=0.11876769906133323, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.13020011811498</v>
+        <v>0.1302001181373674</v>
       </c>
     </row>
     <row r="55">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1951422598080768</v>
+        <v>0.1951422598156234</v>
       </c>
     </row>
     <row r="56">
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.03664271539979523</v>
+        <v>0.03664271539934473</v>
       </c>
     </row>
     <row r="57">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7061559045134552</v>
+        <v>0.7061559045126601</v>
       </c>
     </row>
     <row r="58">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-2.284473156894689e-08</v>
+        <v>-2.283598504357287e-08</v>
       </c>
     </row>
     <row r="59">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.001794660944229309</v>
+        <v>-0.001794660944028081</v>
       </c>
     </row>
     <row r="60">
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.07160127583716314</v>
+        <v>0.07160127585222054</v>
       </c>
     </row>
     <row r="61">
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-7.76323183238059e-05</v>
+        <v>-7.763231817808913e-05</v>
       </c>
     </row>
     <row r="62">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3553227391827451</v>
+        <v>0.3553227391790962</v>
       </c>
     </row>
     <row r="63">
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5.648463390620061</v>
+        <v>5.648463390578714</v>
       </c>
     </row>
     <row r="64">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-2.191051678402466e-05</v>
+        <v>-2.191043727015762e-05</v>
       </c>
     </row>
     <row r="65">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.01250308513717213</v>
+        <v>-0.01250308513689458</v>
       </c>
     </row>
     <row r="66">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9323336274281169</v>
+        <v>0.9323336276652604</v>
       </c>
     </row>
     <row r="67">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.0002424221045016494</v>
+        <v>-0.0002424221038355157</v>
       </c>
     </row>
     <row r="68">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.954949201517465e-17</v>
+        <v>-2.085279147733796e-17</v>
       </c>
     </row>
     <row r="69">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4.517539521240818e-22</v>
+        <v>4.818707410206858e-22</v>
       </c>
     </row>
     <row r="70">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.2408579822914199</v>
+        <v>-0.2408579822849669</v>
       </c>
     </row>
     <row r="71">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.4000315992275166</v>
+        <v>-0.4000315992141975</v>
       </c>
     </row>
     <row r="72">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.256727680381765e-17</v>
+        <v>1.340509524672916e-17</v>
       </c>
     </row>
     <row r="73">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1024021430455406</v>
+        <v>0.1024021430446468</v>
       </c>
     </row>
     <row r="74">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
     </row>
     <row r="75">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.934827174273248e-19</v>
+        <v>1.935385882339244e-19</v>
       </c>
     </row>
     <row r="76">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1986060691019765</v>
+        <v>-0.1986060691330394</v>
       </c>
     </row>
     <row r="77">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7794457260438862</v>
+        <v>-0.779445726021365</v>
       </c>
     </row>
     <row r="78">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7.51057012892061e-19</v>
+        <v>2.28667207055287e-18</v>
       </c>
     </row>
     <row r="79">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.01591371475994741</v>
+        <v>0.01591371475306178</v>
       </c>
     </row>
     <row r="80">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.009943506936824e-06</v>
+        <v>-1.009953632655828e-06</v>
       </c>
     </row>
     <row r="81">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.5648463947868269</v>
+        <v>-0.5648463950243764</v>
       </c>
     </row>
     <row r="82">
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-5.783190067811703e-06</v>
+        <v>-5.783127554474369e-06</v>
       </c>
     </row>
     <row r="83">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.003253733017144216</v>
+        <v>-0.003253733017750465</v>
       </c>
     </row>
     <row r="84">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-11.47472238827099</v>
+        <v>-11.47472239298415</v>
       </c>
     </row>
     <row r="85">
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.0001267192463559272</v>
+        <v>-0.0001267192462976988</v>
       </c>
     </row>
     <row r="86">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
     </row>
     <row r="87">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-1.306851650478998e-20</v>
+        <v>1.269203898795724e-20</v>
       </c>
     </row>
     <row r="88">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.02574590957319787</v>
+        <v>0.02574590957015981</v>
       </c>
     </row>
     <row r="89">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.08493058475885355</v>
+        <v>-0.08493058476554616</v>
       </c>
     </row>
     <row r="90">
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-5.239670694945015e-18</v>
+        <v>-5.229038944214264e-18</v>
       </c>
     </row>
     <row r="91">
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.04854440595543232</v>
+        <v>-0.04854440597030987</v>
       </c>
     </row>
     <row r="92">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.118895236153985</v>
+        <v>0.1188952361552037</v>
       </c>
     </row>
     <row r="93">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.03599829320587388</v>
+        <v>0.03599829320672956</v>
       </c>
     </row>
     <row r="94">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.08289694294811105</v>
+        <v>0.08289694294847418</v>
       </c>
     </row>
     <row r="95">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.04206278273348475</v>
+        <v>-0.04206278273311121</v>
       </c>
     </row>
     <row r="96">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.04206278273348475</v>
+        <v>0.04206278273311121</v>
       </c>
     </row>
     <row r="97">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.118895236153985</v>
+        <v>-0.1188952361552037</v>
       </c>
     </row>
     <row r="98">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.1529216796594</v>
+        <v>1.152921679673553</v>
       </c>
     </row>
     <row r="99">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-3.047430655777885e-18</v>
+        <v>-3.184814904083324e-18</v>
       </c>
     </row>
     <row r="100">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3.047430655777885e-18</v>
+        <v>3.184814904083324e-18</v>
       </c>
     </row>
     <row r="101">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-1.715755223053363e-18</v>
+        <v>-1.830138903257797e-18</v>
       </c>
     </row>
     <row r="102">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-6.343256618606443e-17</v>
+        <v>-6.76614039154329e-17</v>
       </c>
     </row>
     <row r="103">
@@ -5501,11 +5501,11 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.0003404378247374978,
+	L=0.0003404378248003771,
 	Y=0.0,
-	D=0.0012461336138990264,
+	D=0.0012461336140693828,
 	l_b=0.0,
-	m_b=-3.601981613290454e-05,
+	m_b=-3.601981615357263e-05,
 	n_b=-0.0,
 	span_effective=0.004055451774444796, oswalds_efficiency=0.95,
 )]</t>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-3.047430655777885e-18</v>
+        <v>-3.184814904083324e-18</v>
       </c>
     </row>
     <row r="105">
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-5.395210257219728e-07</v>
+        <v>-5.395264349976748e-07</v>
       </c>
     </row>
     <row r="106">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.994986692518442e-17</v>
+        <v>2.029162170539768e-17</v>
       </c>
     </row>
     <row r="107">
@@ -5551,29 +5551,29 @@
       <c r="B107" t="inlineStr">
         <is>
           <t>[AeroComponentResults(
-	L=0.9168592898654198,
+	L=0.9168592898841235,
 	Y=0.0,
-	D=0.06055915724584764,
+	D=0.06055915724693969,
 	l_b=-0.0,
-	m_b=0.07213813866633308,
+	m_b=0.07213813868092246,
 	n_b=-0.0,
-	span_effective=0.7500878943334851, oswalds_efficiency=0.8072554931504061,
+	span_effective=0.7500878943334851, oswalds_efficiency=0.8072554931510372,
 ), AeroComponentResults(
-	L=0.2357219519692426,
+	L=0.23572195196462953,
 	Y=0.0,
-	D=0.018196401856206714,
+	D=0.01819640185580553,
 	l_b=-0.0,
-	m_b=-0.07218097052232664,
+	m_b=-0.07218097054225309,
 	n_b=-0.0,
-	span_effective=0.3655521648059379, oswalds_efficiency=0.8106853777008906,
+	span_effective=0.36555216479279257, oswalds_efficiency=0.8106853777008906,
 ), AeroComponentResults(
-	L=-2.710505431213761e-20,
-	Y=-6.343256618606443e-17,
-	D=0.002895250232157671,
-	l_b=-3.0474306557778854e-18,
-	m_b=7.831215110074344e-05,
-	n_b=1.9949866925184424e-17,
-	span_effective=0.11876769907569983, oswalds_efficiency=0.8232692748986458,
+	L=-0.0,
+	Y=-6.76614039154329e-17,
+	D=0.0028952502316595603,
+	l_b=-3.1848149040833245e-18,
+	m_b=7.831215104919995e-05,
+	n_b=2.0291621705397675e-17,
+	span_effective=0.11876769906133323, oswalds_efficiency=0.8232692748986458,
 )]</t>
         </is>
       </c>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.13020011811498</v>
+        <v>0.1302001181373674</v>
       </c>
     </row>
     <row r="109">
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.1951422598080768</v>
+        <v>0.1951422598156234</v>
       </c>
     </row>
   </sheetData>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.1529216796594</v>
+        <v>1.152921679673553</v>
       </c>
       <c r="C2" t="n">
-        <v>1.152921689648617</v>
+        <v>1.152921689662771</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -5709,16 +5709,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.989217009120921e-09</v>
+        <v>-9.989217897299341e-09</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.989217009120921e-09</v>
+        <v>-9.989217897299341e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.664263235576213e-09</v>
+        <v>-8.664264005841697e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.118895236153985</v>
+        <v>0.1188952361552037</v>
       </c>
       <c r="C3" t="n">
         <v>0.001</v>
@@ -5749,16 +5749,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.117895236153985</v>
+        <v>0.1178952361552037</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.117895236153985</v>
+        <v>0.1178952361552037</v>
       </c>
       <c r="M3" t="n">
-        <v>0.117895236153985</v>
+        <v>0.1178952361552037</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.009943506936824e-06</v>
+        <v>-1.009953632655828e-06</v>
       </c>
       <c r="C4" t="n">
         <v>-1e-06</v>
@@ -5791,18 +5791,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-9.9435069368239e-09</v>
+        <v>-9.953632655827594e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.009943506936824e-06</v>
+        <v>2.009953632655828e-06</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.9435069368239e-09</v>
+        <v>-9.953632655827594e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.9435069368239e-09</v>
+        <v>-9.953632655827594e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -5835,16 +5835,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
       <c r="I5" t="n">
-        <v>1.233238910570726e-18</v>
+        <v>1.288835778804625e-18</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
       <c r="K5" t="n">
-        <v>1.233238910570726e-18</v>
+        <v>1.288835778804625e-18</v>
       </c>
       <c r="L5" t="n">
         <v>0.0009999999999999987</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -5883,22 +5883,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.073342737495452e-18</v>
+        <v>-8.211644585798137e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000999999999999992</v>
+        <v>0.0009999999999999918</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000999999999999992</v>
+        <v>0.0009999999999999918</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3553227391827451</v>
+        <v>0.3553227391790962</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -5930,15 +5930,15 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.8446772608172548</v>
+        <v>0.8446772608209038</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.8446772608172548</v>
+        <v>0.8446772608209038</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7038977173477123</v>
+        <v>0.7038977173507531</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.696954368854737</v>
+        <v>9.696954368874374</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -5969,16 +5969,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.696954368854737</v>
+        <v>3.696954368874374</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>3.696954368854737</v>
+        <v>3.696954368874374</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3812490219329935</v>
+        <v>0.3812490219342466</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.195080003512478</v>
+        <v>9.195080003418058</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7.195080003512478</v>
+        <v>7.195080003418058</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>7.195080003512478</v>
+        <v>7.195080003418058</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7824923764408782</v>
+        <v>0.7824923764386448</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.195080003512478</v>
+        <v>9.195080003418058</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
@@ -6050,15 +6050,15 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>10.80491999648752</v>
+        <v>10.80491999658194</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>10.80491999648752</v>
+        <v>10.80491999658194</v>
       </c>
       <c r="M10" t="n">
-        <v>0.540245999824376</v>
+        <v>0.5402459998290972</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73262.37412649603</v>
+        <v>73262.37412814774</v>
       </c>
       <c r="C11" t="n">
         <v>20000</v>
@@ -6089,16 +6089,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>53262.37412649603</v>
+        <v>53262.37412814774</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>53262.37412649603</v>
+        <v>53262.37412814774</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7270085737944054</v>
+        <v>0.7270085738005601</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1000000098654832</v>
+        <v>0.1000000099082708</v>
       </c>
       <c r="C12" t="n">
         <v>0.05</v>
@@ -6129,16 +6129,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.05000000986548321</v>
+        <v>0.05000000990827082</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.05000000986548321</v>
+        <v>0.05000000990827082</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05000000986548321</v>
+        <v>0.05000000990827082</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1000000098654832</v>
+        <v>0.1000000099082708</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
@@ -6170,15 +6170,15 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>-9.86548320813796e-09</v>
+        <v>-9.908270814928954e-09</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-9.86548320813796e-09</v>
+        <v>-9.908270814928954e-09</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.86548320813796e-09</v>
+        <v>-9.908270814928954e-09</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6473213459669306</v>
+        <v>0.6473213460623958</v>
       </c>
       <c r="C14" t="n">
         <v>0.5</v>
@@ -6209,16 +6209,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.1473213459669306</v>
+        <v>0.1473213460623958</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.1473213459669306</v>
+        <v>0.1473213460623958</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1473213459669306</v>
+        <v>0.1473213460623958</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6473213459669306</v>
+        <v>0.6473213460623958</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
@@ -6250,15 +6250,15 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.3526786540330694</v>
+        <v>0.3526786539376042</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.3526786540330694</v>
+        <v>0.3526786539376042</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3526786540330694</v>
+        <v>0.3526786539376042</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02999999002416101</v>
+        <v>0.02999999002416147</v>
       </c>
       <c r="C16" t="n">
         <v>0.03</v>
@@ -6289,16 +6289,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.975838984738195e-09</v>
+        <v>-9.975838526771197e-09</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-9.975838984738195e-09</v>
+        <v>-9.975838526771197e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.975838984738195e-09</v>
+        <v>-9.975838526771197e-09</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02999999002416101</v>
+        <v>0.02999999002416147</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
@@ -6330,15 +6330,15 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.05000000997583899</v>
+        <v>0.05000000997583853</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.05000000997583899</v>
+        <v>0.05000000997583853</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05000000997583899</v>
+        <v>0.05000000997583853</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1986060691019765</v>
+        <v>-0.1986060691330394</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
@@ -6370,15 +6370,15 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.1986060691019765</v>
+        <v>0.1986060691330394</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.1986060691019765</v>
+        <v>0.1986060691330394</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1986060691019765</v>
+        <v>0.1986060691330394</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02574590957319787</v>
+        <v>0.02574590957015981</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -6409,16 +6409,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.02574590957319787</v>
+        <v>0.02574590957015981</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0.02574590957319787</v>
+        <v>0.02574590957015981</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02574590957319787</v>
+        <v>0.02574590957015981</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.7794457260438862</v>
+        <v>-0.779445726021365</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
@@ -6450,15 +6450,15 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.7793457260438862</v>
+        <v>0.779345726021365</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.7793457260438862</v>
+        <v>0.779345726021365</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7793457260438862</v>
+        <v>0.779345726021365</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.239711082357698</v>
+        <v>5.239711082509094</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>229.0672432883348</v>
+        <v>229.0672432918443</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02287411769199271</v>
+        <v>0.02287411769230318</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.461428953487664e-05</v>
+        <v>3.461428953643742e-05</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
@@ -6586,15 +6586,15 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.007165385710465123</v>
+        <v>0.007165385710463563</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.007165385710465123</v>
+        <v>0.007165385710463563</v>
       </c>
       <c r="M24" t="n">
-        <v>0.007165385710465123</v>
+        <v>0.007165385710463563</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.861538575211941e-05</v>
+        <v>1.861538575011118e-05</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
@@ -6626,15 +6626,15 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.007181384614247881</v>
+        <v>0.007181384614249889</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.007181384614247881</v>
+        <v>0.007181384614249889</v>
       </c>
       <c r="M25" t="n">
-        <v>0.007181384614247881</v>
+        <v>0.007181384614249889</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.475942301592643e-06</v>
+        <v>3.475942300331253e-06</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
@@ -6666,15 +6666,15 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.007196524057698407</v>
+        <v>0.007196524057699669</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0.007196524057698407</v>
+        <v>0.007196524057699669</v>
       </c>
       <c r="M26" t="n">
-        <v>0.007196524057698407</v>
+        <v>0.007196524057699669</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.808035466072172</v>
+        <v>3.808035466104309</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3553227391827451</v>
+        <v>0.3553227391790962</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.252227383789823</v>
+        <v>-1.252227383789828</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.704104673501529</v>
+        <v>2.704104673501531</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.009943506936824e-06</v>
+        <v>-1.009953632655828e-06</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7794457260438862</v>
+        <v>-0.779445726021365</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25.57077861325071</v>
+        <v>25.57077861391034</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-24.40325580872998</v>
+        <v>-24.40325580806729</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25.59674419127002</v>
+        <v>25.59674419193271</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.5522288122537e-16</v>
+        <v>1.419485665407633e-16</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1140304864151476</v>
+        <v>0.1140304862776677</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6.587616550414456e-15</v>
+        <v>2.329054801675277e-16</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.002045221041065397</v>
+        <v>0.002045221040870147</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01462208659223752</v>
+        <v>0.0146220865917117</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1174456015613583</v>
+        <v>0.1174456015663288</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02999999002416101</v>
+        <v>0.02999999002416147</v>
       </c>
       <c r="C2" t="n">
         <v>0.03</v>
@@ -7271,16 +7271,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-9.975838984738195e-09</v>
+        <v>-9.975838526771197e-09</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-9.975838984738195e-09</v>
+        <v>-9.975838526771197e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.975838984738195e-09</v>
+        <v>-9.975838526771197e-09</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.009943506936824e-06</v>
+        <v>-1.009953632655828e-06</v>
       </c>
       <c r="C3" t="n">
         <v>-1e-06</v>
@@ -7313,18 +7313,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-9.9435069368239e-09</v>
+        <v>-9.953632655827594e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>2.009943506936824e-06</v>
+        <v>2.009953632655828e-06</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-9.9435069368239e-09</v>
+        <v>-9.953632655827594e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.9435069368239e-09</v>
+        <v>-9.953632655827594e-09</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1000000098654832</v>
+        <v>0.1000000099082708</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
@@ -7356,15 +7356,15 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>-9.86548320813796e-09</v>
+        <v>-9.908270814928954e-09</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-9.86548320813796e-09</v>
+        <v>-9.908270814928954e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.86548320813796e-09</v>
+        <v>-9.908270814928954e-09</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.1529216796594</v>
+        <v>1.152921679673553</v>
       </c>
       <c r="C5" t="n">
-        <v>1.152921689648617</v>
+        <v>1.152921689662771</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -7395,16 +7395,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-9.989217009120921e-09</v>
+        <v>-9.989217897299341e-09</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-9.989217009120921e-09</v>
+        <v>-9.989217897299341e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>-8.664263235576213e-09</v>
+        <v>-8.664264005841697e-09</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -7437,22 +7437,22 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.073342737495452e-18</v>
+        <v>-8.211644585798137e-18</v>
       </c>
       <c r="J6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="K6" t="n">
-        <v>8.073342737495452e-18</v>
+        <v>8.211644585798137e-18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000999999999999992</v>
+        <v>0.0009999999999999918</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000999999999999992</v>
+        <v>0.0009999999999999918</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -7485,16 +7485,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
       <c r="I7" t="n">
-        <v>1.233238910570726e-18</v>
+        <v>1.288835778804625e-18</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.233238910570726e-18</v>
+        <v>-1.288835778804625e-18</v>
       </c>
       <c r="K7" t="n">
-        <v>1.233238910570726e-18</v>
+        <v>1.288835778804625e-18</v>
       </c>
       <c r="L7" t="n">
         <v>0.0009999999999999987</v>
@@ -7517,7 +7517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9915896389666687</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.932694231753585</v>
       </c>
     </row>
     <row r="10">
@@ -7635,127 +7635,127 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[18]</t>
+          <t>iterations.alpha_du[1]</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.6965559459495476</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[19]</t>
+          <t>iterations.alpha_du[2]</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1519418837766429</v>
+        <v>0.9884543453305623</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[1]</t>
+          <t>iterations.alpha_du[3]</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3356497692647426</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[20]</t>
+          <t>iterations.alpha_du[4]</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0.4337988954054068</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[21]</t>
+          <t>iterations.alpha_du[5]</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0.9171737931179601</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[22]</t>
+          <t>iterations.alpha_du[6]</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7792275026343395</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[23]</t>
+          <t>iterations.alpha_du[7]</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.7535307323460199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[24]</t>
+          <t>iterations.alpha_du[8]</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9977728756399165</v>
+        <v>0.1100488034382017</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[25]</t>
+          <t>iterations.alpha_du[9]</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0.8155400279028017</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[26]</t>
+          <t>iterations.alpha_pr[0]</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[27]</t>
+          <t>iterations.alpha_pr[10]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0.9943855075117993</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[28]</t>
+          <t>iterations.alpha_pr[11]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.838854478511513</v>
+        <v>0.841832255279194</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[29]</t>
+          <t>iterations.alpha_pr[12]</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -7765,17 +7765,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[2]</t>
+          <t>iterations.alpha_pr[13]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9160287574850122</v>
+        <v>0.9888295062739901</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[30]</t>
+          <t>iterations.alpha_pr[14]</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -7785,2512 +7785,1472 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[3]</t>
+          <t>iterations.alpha_pr[15]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9513060667676593</v>
+        <v>0.9999821889542652</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[4]</t>
+          <t>iterations.alpha_pr[16]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.9962878005580073</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[5]</t>
+          <t>iterations.alpha_pr[17]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1412261858571584</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[6]</t>
+          <t>iterations.alpha_pr[1]</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0.1614192686406677</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[7]</t>
+          <t>iterations.alpha_pr[2]</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0.4443957254711802</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[8]</t>
+          <t>iterations.alpha_pr[3]</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0.7826452891460988</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iterations.alpha_du[9]</t>
+          <t>iterations.alpha_pr[4]</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0.4551035933255529</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[0]</t>
+          <t>iterations.alpha_pr[5]</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>0.4041315775353848</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[10]</t>
+          <t>iterations.alpha_pr[6]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5264622235972604</v>
+        <v>0.9151365956339617</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[11]</t>
+          <t>iterations.alpha_pr[7]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6385799047818183</v>
+        <v>0.5882352531802419</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[12]</t>
+          <t>iterations.alpha_pr[8]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>0.3463058263005206</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[13]</t>
+          <t>iterations.alpha_pr[9]</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0.6517486195994501</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[14]</t>
+          <t>iterations.d_norm[0]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5352135312162907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[15]</t>
+          <t>iterations.d_norm[10]</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>10.31844688772525</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[16]</t>
+          <t>iterations.d_norm[11]</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>4.864290072354748</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[17]</t>
+          <t>iterations.d_norm[12]</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6677065173333778</v>
+        <v>0.9612842060863653</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[18]</t>
+          <t>iterations.d_norm[13]</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3577208896171598</v>
+        <v>0.1039241252086953</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[19]</t>
+          <t>iterations.d_norm[14]</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3237051210420037</v>
+        <v>0.01500665259396397</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[1]</t>
+          <t>iterations.d_norm[15]</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2647173673845499</v>
+        <v>0.0002436488986577044</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[20]</t>
+          <t>iterations.d_norm[16]</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.007516782706813263</v>
+        <v>1.046672777291918e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[21]</t>
+          <t>iterations.d_norm[17]</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3233212126246934</v>
+        <v>2.728696655209738e-07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[22]</t>
+          <t>iterations.d_norm[1]</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9974357923196122</v>
+        <v>0.6121193524663514</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[23]</t>
+          <t>iterations.d_norm[2]</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>0.4156361898606424</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[24]</t>
+          <t>iterations.d_norm[3]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8095316698838487</v>
+        <v>0.6561841369070964</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[25]</t>
+          <t>iterations.d_norm[4]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2.842527470577552</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[26]</t>
+          <t>iterations.d_norm[5]</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.981236105188696</v>
+        <v>21.81031607080584</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[27]</t>
+          <t>iterations.d_norm[6]</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>1.858430314974523</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[28]</t>
+          <t>iterations.d_norm[7]</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>5.675909053840105</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[29]</t>
+          <t>iterations.d_norm[8]</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9942761693575054</v>
+        <v>171.7980799816368</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[2]</t>
+          <t>iterations.d_norm[9]</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.08616289672338637</v>
+        <v>18.87930196632806</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[30]</t>
+          <t>iterations.inf_du[0]</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>1.033754587220863</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[3]</t>
+          <t>iterations.inf_du[10]</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6361610053707666</v>
+        <v>0.5890167879793466</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[4]</t>
+          <t>iterations.inf_du[11]</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.577962749278744</v>
+        <v>78.01112192725111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[5]</t>
+          <t>iterations.inf_du[12]</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2710494739702024</v>
+        <v>0.0006359810018952694</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[6]</t>
+          <t>iterations.inf_du[13]</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6825501703277903</v>
+        <v>1.33667731884114</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[7]</t>
+          <t>iterations.inf_du[14]</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9260873418951333</v>
+        <v>1.741366584262494e-08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[8]</t>
+          <t>iterations.inf_du[15]</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3967995100558559</v>
+        <v>0.01103706350350814</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iterations.alpha_pr[9]</t>
+          <t>iterations.inf_du[16]</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9372847378610333</v>
+        <v>4.125905529873256e-05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iterations.d_norm[0]</t>
+          <t>iterations.inf_du[17]</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>5.209929709870664e-13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iterations.d_norm[10]</t>
+          <t>iterations.inf_du[1]</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.1086654195236866</v>
+        <v>2.742738651327326</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iterations.d_norm[11]</t>
+          <t>iterations.inf_du[2]</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.1440875031124218</v>
+        <v>9.339322837869133</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iterations.d_norm[12]</t>
+          <t>iterations.inf_du[3]</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.09668686015530797</v>
+        <v>4.585850070983724</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iterations.d_norm[13]</t>
+          <t>iterations.inf_du[4]</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.2325380870126869</v>
+        <v>3.138970807541185</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iterations.d_norm[14]</t>
+          <t>iterations.inf_du[5]</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.03819067886898201</v>
+        <v>56.38519144510536</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iterations.d_norm[15]</t>
+          <t>iterations.inf_du[6]</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.02254886858153141</v>
+        <v>6.548295623653814</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iterations.d_norm[16]</t>
+          <t>iterations.inf_du[7]</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.01212767997049278</v>
+        <v>4.4510780414534</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iterations.d_norm[17]</t>
+          <t>iterations.inf_du[8]</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.03190710167249801</v>
+        <v>6.738474343207599</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>iterations.d_norm[18]</t>
+          <t>iterations.inf_du[9]</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.1484090136839736</v>
+        <v>16.83054331918839</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>iterations.d_norm[19]</t>
+          <t>iterations.inf_pr[0]</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.638129340349624</v>
+        <v>0.08384087778595477</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>iterations.d_norm[1]</t>
+          <t>iterations.inf_pr[10]</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>5.819378187228672</v>
+        <v>0.2562503632304267</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iterations.d_norm[20]</t>
+          <t>iterations.inf_pr[11]</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.1422218610139849</v>
+        <v>0.06982453479918149</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iterations.d_norm[21]</t>
+          <t>iterations.inf_pr[12]</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.3121056951925072</v>
+        <v>0.0013614012035017</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iterations.d_norm[22]</t>
+          <t>iterations.inf_pr[13]</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7.321260040467346</v>
+        <v>3.59144341430806e-05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iterations.d_norm[23]</t>
+          <t>iterations.inf_pr[14]</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5403918726666523</v>
+        <v>3.007760511763991e-07</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iterations.d_norm[24]</t>
+          <t>iterations.inf_pr[15]</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.188525369254684</v>
+        <v>8.261658024366625e-11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iterations.d_norm[25]</t>
+          <t>iterations.inf_pr[16]</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.331145073188553</v>
+        <v>1.312391861851836e-11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iterations.d_norm[26]</t>
+          <t>iterations.inf_pr[17]</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.2782396055888623</v>
+        <v>1.652353254222305e-11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iterations.d_norm[27]</t>
+          <t>iterations.inf_pr[1]</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.03582691607013199</v>
+        <v>0.07037152529113752</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iterations.d_norm[28]</t>
+          <t>iterations.inf_pr[2]</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0004899823574266031</v>
+        <v>0.04190251174957116</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>iterations.d_norm[29]</t>
+          <t>iterations.inf_pr[3]</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6.24650615362903e-05</v>
+        <v>0.03505638183937876</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>iterations.d_norm[2]</t>
+          <t>iterations.inf_pr[4]</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3.868648159852013</v>
+        <v>0.3496389055686357</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iterations.d_norm[30]</t>
+          <t>iterations.inf_pr[5]</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1.472312263591023e-06</v>
+        <v>0.2180480692093347</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>iterations.d_norm[3]</t>
+          <t>iterations.inf_pr[6]</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>18.15173138511456</v>
+        <v>0.06925674157566242</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iterations.d_norm[4]</t>
+          <t>iterations.inf_pr[7]</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8219633501928776</v>
+        <v>0.02984172573939503</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iterations.d_norm[5]</t>
+          <t>iterations.inf_pr[8]</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>31.82519451321187</v>
+        <v>3.583446759258218</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iterations.d_norm[6]</t>
+          <t>iterations.inf_pr[9]</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4.33599343217309</v>
+        <v>1.905390813819645</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iterations.d_norm[7]</t>
+          <t>iterations.mu[0]</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5048000300535735</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iterations.d_norm[8]</t>
+          <t>iterations.mu[10]</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11.38020551448038</v>
+        <v>0.001301919318458811</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iterations.d_norm[9]</t>
+          <t>iterations.mu[11]</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>19.28461116964666</v>
+        <v>0.0008665881431428498</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iterations.inf_du[0]</t>
+          <t>iterations.mu[12]</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.9643852149363595</v>
+        <v>0.0001224022201689183</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iterations.inf_du[10]</t>
+          <t>iterations.mu[13]</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>936.4752608663757</v>
+        <v>8.366583500343537e-06</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>iterations.inf_du[11]</t>
+          <t>iterations.mu[14]</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2377.907630176199</v>
+        <v>1.796963865333e-07</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iterations.inf_du[12]</t>
+          <t>iterations.mu[15]</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.2398620509777067</v>
+        <v>9.999999999999999e-12</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>iterations.inf_du[13]</t>
+          <t>iterations.mu[16]</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>20.48511363072703</v>
+        <v>1.488202842664764e-10</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>iterations.inf_du[14]</t>
+          <t>iterations.mu[17]</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1319.906498985677</v>
+        <v>9.999999999999999e-12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iterations.inf_du[15]</t>
+          <t>iterations.mu[1]</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.2976572468424143</v>
+        <v>6.364299347732312e-06</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iterations.inf_du[16]</t>
+          <t>iterations.mu[2]</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.1817100217450815</v>
+        <v>0.05597590423514164</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iterations.inf_du[17]</t>
+          <t>iterations.mu[3]</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3.004363385041981</v>
+        <v>0.03637145070812217</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iterations.inf_du[18]</t>
+          <t>iterations.mu[4]</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.887235107777015</v>
+        <v>0.3044742791888753</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iterations.inf_du[19]</t>
+          <t>iterations.mu[5]</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5728416516769963</v>
+        <v>0.1364617180787321</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iterations.inf_du[1]</t>
+          <t>iterations.mu[6]</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4.385184986688515</v>
+        <v>0.02955829263583381</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iterations.inf_du[20]</t>
+          <t>iterations.mu[7]</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>314.6250228390973</v>
+        <v>0.0009537597817588035</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iterations.inf_du[21]</t>
+          <t>iterations.mu[8]</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>14864.7015278235</v>
+        <v>0.001736880832662201</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>iterations.inf_du[22]</t>
+          <t>iterations.mu[9]</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>4735.304590523092</v>
+        <v>0.003848623394942297</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>iterations.inf_du[23]</t>
+          <t>iterations.obj[0]</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.003987142050200232</v>
+        <v>2.882185475353177</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>iterations.inf_du[24]</t>
+          <t>iterations.obj[10]</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>418.1783175258879</v>
+        <v>2.171590628284926</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iterations.inf_du[25]</t>
+          <t>iterations.obj[11]</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0007161779393745071</v>
+        <v>2.167130649794932</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iterations.inf_du[26]</t>
+          <t>iterations.obj[12]</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.512662104403574</v>
+        <v>2.166929031082759</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iterations.inf_du[27]</t>
+          <t>iterations.obj[13]</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.117611012624309e-07</v>
+        <v>2.166303372698453</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iterations.inf_du[28]</t>
+          <t>iterations.obj[14]</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.04704460009361702</v>
+        <v>2.166268349230476</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iterations.inf_du[29]</t>
+          <t>iterations.obj[15]</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.000271910555938928</v>
+        <v>2.166267417385915</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iterations.inf_du[2]</t>
+          <t>iterations.obj[16]</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>292.3197001431356</v>
+        <v>2.166267395972951</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iterations.inf_du[30]</t>
+          <t>iterations.obj[17]</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7.567058091240142e-12</v>
+        <v>2.166267395066876</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iterations.inf_du[3]</t>
+          <t>iterations.obj[1]</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>170.2231907590095</v>
+        <v>2.845012842193742</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iterations.inf_du[4]</t>
+          <t>iterations.obj[2]</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>164.0131482492552</v>
+        <v>2.784730775090921</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>iterations.inf_du[5]</t>
+          <t>iterations.obj[3]</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>107.2751261901154</v>
+        <v>2.672522516780621</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>iterations.inf_du[6]</t>
+          <t>iterations.obj[4]</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>124.494242259492</v>
+        <v>2.668633015240638</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>iterations.inf_du[7]</t>
+          <t>iterations.obj[5]</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>53.13699455407038</v>
+        <v>2.49985547606864</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iterations.inf_du[8]</t>
+          <t>iterations.obj[6]</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>221.914503169496</v>
+        <v>2.26570338670916</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iterations.inf_du[9]</t>
+          <t>iterations.obj[7]</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>26.22223610027095</v>
+        <v>2.224602782138617</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[0]</t>
+          <t>iterations.obj[8]</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.1869513138379173</v>
+        <v>2.018489522748726</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[10]</t>
+          <t>iterations.obj[9]</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.1327510096575359</v>
+        <v>2.108705187337625</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[11]</t>
+          <t>iterations.regularization_size[0]</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.04804546535764587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[12]</t>
+          <t>iterations.regularization_size[10]</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.004732558335996784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[13]</t>
+          <t>iterations.regularization_size[11]</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.02255478775061619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[14]</t>
+          <t>iterations.regularization_size[12]</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.009973245485426219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[15]</t>
+          <t>iterations.regularization_size[13]</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.001335287702742605</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[16]</t>
+          <t>iterations.regularization_size[14]</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>9.898035470889965e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[17]</t>
+          <t>iterations.regularization_size[15]</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0004116054308336212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[18]</t>
+          <t>iterations.regularization_size[16]</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.002692133728223238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[19]</t>
+          <t>iterations.regularization_size[17]</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.1796432092113367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[1]</t>
+          <t>iterations.regularization_size[1]</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.3425800567557786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[20]</t>
+          <t>iterations.regularization_size[2]</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.1782970288171697</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[21]</t>
+          <t>iterations.regularization_size[3]</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.1265310207929602</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[22]</t>
+          <t>iterations.regularization_size[4]</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.07078826672577421</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[23]</t>
+          <t>iterations.regularization_size[5]</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.001320468132742655</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[24]</t>
+          <t>iterations.regularization_size[6]</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.004478933000273751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[25]</t>
+          <t>iterations.regularization_size[7]</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.001983413284889934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[26]</t>
+          <t>iterations.regularization_size[8]</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.0001309371203124243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[27]</t>
+          <t>iterations.regularization_size[9]</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1.553062562109631e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[28]</t>
+          <t>n_call_callback_fun</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2.87975865376211e-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[29]</t>
+          <t>n_call_nlp_f</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2.649616637206975e-11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[2]</t>
+          <t>n_call_nlp_g</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.3394708311039736</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[30]</t>
+          <t>n_call_nlp_grad</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3.962548345004535e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[3]</t>
+          <t>n_call_nlp_grad_f</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.1615249379295201</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[4]</t>
+          <t>n_call_nlp_hess_l</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.1335973114494272</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[5]</t>
+          <t>n_call_nlp_jac_g</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.215826619262784</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[6]</t>
+          <t>n_call_total</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.03807516317657722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[7]</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>0.0027929942133883</v>
+          <t>return_status</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Solve_Succeeded</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[8]</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>0.01425125745722688</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="B156" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iterations.inf_pr[9]</t>
+          <t>t_proc_callback_fun</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.2750468482898789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>iterations.mu[0]</t>
+          <t>t_proc_nlp_f</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>iterations.mu[10]</t>
+          <t>t_proc_nlp_g</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0152803741284103</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>iterations.mu[11]</t>
+          <t>t_proc_nlp_grad</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.02552528093217498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>iterations.mu[12]</t>
+          <t>t_proc_nlp_grad_f</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.008084810365726705</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>iterations.mu[13]</t>
+          <t>t_proc_nlp_hess_l</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.005999856582086264</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>iterations.mu[14]</t>
+          <t>t_proc_nlp_jac_g</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.003131766525215177</v>
+        <v>4.122</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>iterations.mu[15]</t>
+          <t>t_proc_total</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.0002957511062581752</v>
+        <v>19.929</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>iterations.mu[16]</t>
+          <t>t_wall_callback_fun</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1.295775959363564e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>iterations.mu[17]</t>
+          <t>t_wall_nlp_f</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3.888340515372698e-06</v>
+        <v>0.5325909999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>iterations.mu[18]</t>
+          <t>t_wall_nlp_g</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>4.196911857014151e-06</v>
+        <v>1.089186</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>iterations.mu[19]</t>
+          <t>t_wall_nlp_grad</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>9.999999999999999e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>iterations.mu[1]</t>
+          <t>t_wall_nlp_grad_f</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.6128839576018941</v>
+        <v>1.201571</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>iterations.mu[20]</t>
+          <t>t_wall_nlp_hess_l</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0003299750878501219</v>
+        <v>12.93198</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>iterations.mu[21]</t>
+          <t>t_wall_nlp_jac_g</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.02219504246574262</v>
+        <v>4.118498</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>iterations.mu[22]</t>
+          <t>t_wall_total</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.0004508692989470423</v>
+        <v>19.928558</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>iterations.mu[23]</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0.003050785046103949</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>iterations.mu[24]</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0.0008070253231940831</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>iterations.mu[25]</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0.0001504562657857676</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>iterations.mu[26]</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>1.520990727649117e-05</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>iterations.mu[27]</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>3.310553679758609e-07</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>iterations.mu[28]</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>7.023967751110071e-09</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>iterations.mu[29]</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>7.00113021073999e-10</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>iterations.mu[2]</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>2.300524641232216</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>iterations.mu[30]</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>9.999999999999999e-12</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>iterations.mu[3]</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>2.300524641232216</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>iterations.mu[4]</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>2.300524641232216</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>iterations.mu[5]</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>2.300524641232216</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>iterations.mu[6]</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>2.300524641232216</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>iterations.mu[7]</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>0.1721898648756668</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>iterations.mu[8]</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>0.05866814190598076</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>iterations.mu[9]</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>0.02050320539881186</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>iterations.obj[0]</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>2.592759875600154</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>iterations.obj[10]</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>2.409733414699749</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>iterations.obj[11]</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>2.412103586058501</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>iterations.obj[12]</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>2.392095216806003</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>iterations.obj[13]</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>2.340684474053823</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>iterations.obj[14]</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>2.333035211076758</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>iterations.obj[15]</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>2.335856768636569</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>iterations.obj[16]</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>2.332276218122759</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>iterations.obj[17]</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>2.326476761569768</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>iterations.obj[18]</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>2.31226676542363</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>iterations.obj[19]</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>2.165263867204074</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>iterations.obj[1]</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>3.111973695535434</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>iterations.obj[20]</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>2.164373974507242</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>iterations.obj[21]</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>2.198933436505788</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>iterations.obj[22]</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>2.18071495343769</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>iterations.obj[23]</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>2.18499470766311</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>iterations.obj[24]</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>2.171855929387564</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>iterations.obj[25]</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>2.167142817688195</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>iterations.obj[26]</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>2.166338780967626</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>iterations.obj[27]</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>2.166269210165879</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>iterations.obj[28]</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>2.166267539166262</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>iterations.obj[29]</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>2.166267399767584</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>iterations.obj[2]</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>3.413738813076199</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>iterations.obj[30]</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>2.166267395059844</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>iterations.obj[3]</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>3.24386425100924</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>iterations.obj[4]</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>3.235527797243469</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>iterations.obj[5]</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>2.758915791756197</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>iterations.obj[6]</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>2.787457002764151</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>iterations.obj[7]</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>2.794397841397392</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>iterations.obj[8]</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>2.723876332694718</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>iterations.obj[9]</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>2.412223518695485</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[0]</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[10]</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>21.33333333333333</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[11]</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>7.111111111111111</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[12]</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>2.37037037037037</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[13]</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>0.7901234567901234</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[14]</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>2.106995884773662</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[15]</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>5.618655692729766</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[16]</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>14.98308184727937</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[17]</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>4.994360615759791</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[18]</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>1.66478687191993</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[19]</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>0.5549289573066434</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[1]</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[20]</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>1.479810552817716</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[21]</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>0.4932701842725719</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[22]</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[23]</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[24]</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[25]</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[26]</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[27]</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[28]</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[29]</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[2]</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[30]</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[3]</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[4]</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[5]</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[6]</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[7]</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[8]</t>
-        </is>
-      </c>
-      <c r="B249" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>iterations.regularization_size[9]</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>n_call_callback_fun</t>
-        </is>
-      </c>
-      <c r="B251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>n_call_nlp_f</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>n_call_nlp_g</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>n_call_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>n_call_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>n_call_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B256" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>n_call_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B257" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>n_call_total</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>return_status</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Solve_Succeeded</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="B260" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>t_proc_callback_fun</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_f</t>
-        </is>
-      </c>
-      <c r="B262" t="n">
-        <v>0.7070000000000004</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_g</t>
-        </is>
-      </c>
-      <c r="B263" t="n">
-        <v>1.467</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>1.176</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>13.257</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>t_proc_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>4.387</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>t_proc_total</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>21.093</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>t_wall_callback_fun</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_f</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>0.7082569999999998</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_g</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>1.467031</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_grad</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_grad_f</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>1.17512</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_hess_l</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>13.256074</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>t_wall_nlp_jac_g</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>4.390722</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>t_wall_total</t>
-        </is>
-      </c>
-      <c r="B276" t="n">
-        <v>21.093465</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
           <t>unified_return_status</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>SOLVER_RET_SUCCESS</t>
         </is>
@@ -10352,10 +9312,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6703135537648173</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="E2" t="n">
-        <v>30.94325083290559</v>
+        <v>30.94325083274244</v>
       </c>
     </row>
     <row r="3">
@@ -10373,10 +9333,10 @@
         <v>0.04698862362078716</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05522344886762574</v>
+        <v>0.05522344886830369</v>
       </c>
       <c r="E3" t="n">
-        <v>2.549244335836028</v>
+        <v>2.549244335859048</v>
       </c>
     </row>
     <row r="4">
@@ -10394,10 +9354,10 @@
         <v>0.01325917124942102</v>
       </c>
       <c r="D4" t="n">
-        <v>1.724083650894573e-06</v>
+        <v>1.72408364673732e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>7.958775794836467e-05</v>
+        <v>7.958775775619772e-05</v>
       </c>
     </row>
     <row r="5">
@@ -10415,10 +9375,10 @@
         <v>2.151606933843013</v>
       </c>
       <c r="D5" t="n">
-        <v>1.310723987777075</v>
+        <v>1.310723987779651</v>
       </c>
       <c r="E5" t="n">
-        <v>60.50610329852036</v>
+        <v>60.50610329844281</v>
       </c>
     </row>
     <row r="6">
@@ -10436,10 +9396,10 @@
         <v>0.0783091834800308</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1174456015613583</v>
+        <v>0.1174456015663288</v>
       </c>
       <c r="E6" t="n">
-        <v>5.421565307643556</v>
+        <v>5.421565307855405</v>
       </c>
     </row>
     <row r="7">
@@ -10457,10 +9417,10 @@
         <v>0.2470733791131532</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01255907900531688</v>
+        <v>0.01255907900548735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5797566373365434</v>
+        <v>0.5797566373425304</v>
       </c>
     </row>
     <row r="8">
@@ -10476,7 +9436,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>2.166267395059844</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
@@ -10550,7 +9510,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.808035466072172</v>
+        <v>3.808035466104309</v>
       </c>
       <c r="C2" t="n">
         <v>-4</v>
@@ -10583,7 +9543,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.5522288122537e-16</v>
+        <v>-1.419485665407633e-16</v>
       </c>
       <c r="C3" t="n">
         <v>-30</v>
@@ -10616,7 +9576,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1140304864151476</v>
+        <v>-0.1140304862776677</v>
       </c>
       <c r="C4" t="n">
         <v>-30</v>
@@ -10649,7 +9609,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.587616550414456e-15</v>
+        <v>2.329054801675277e-16</v>
       </c>
       <c r="C5" t="n">
         <v>-30</v>
@@ -10719,7 +9679,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1646396706065064</v>
+        <v>0.1646396706102183</v>
       </c>
       <c r="C7" t="n">
         <v>0.1</v>
@@ -10752,7 +9712,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3999999944802849</v>
+        <v>0.3999999945860802</v>
       </c>
       <c r="C8" t="n">
         <v>0.4</v>
@@ -10789,7 +9749,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.563971623321324</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="C9" t="n">
         <v>0.35</v>
@@ -10822,7 +9782,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3655521648059379</v>
+        <v>0.3655521647927926</v>
       </c>
       <c r="C10" t="n">
         <v>0.2</v>
@@ -10855,7 +9815,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1187676990756998</v>
+        <v>0.1187676990613332</v>
       </c>
       <c r="C11" t="n">
         <v>0.1</v>

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4809b98-dirty</t>
+          <t>becd544-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.534</v>
+        <v>0.3080000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1.09</v>
+        <v>0.6020000000000002</v>
       </c>
     </row>
     <row r="160">
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.2</v>
+        <v>0.6970000000000002</v>
       </c>
     </row>
     <row r="162">
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>12.93</v>
+        <v>7.460999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>4.122</v>
+        <v>2.568</v>
       </c>
     </row>
     <row r="164">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>19.929</v>
+        <v>11.659</v>
       </c>
     </row>
     <row r="165">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.5325909999999999</v>
+        <v>0.3095909999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1.089186</v>
+        <v>0.59902</v>
       </c>
     </row>
     <row r="168">
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1.201571</v>
+        <v>0.697962</v>
       </c>
     </row>
     <row r="170">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>12.93198</v>
+        <v>7.460197000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>4.118498</v>
+        <v>2.564164</v>
       </c>
     </row>
     <row r="172">
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>19.928558</v>
+        <v>11.658973</v>
       </c>
     </row>
     <row r="173">

--- a/02_Glider_Design/C_results/nausicaa_results.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>becd544-dirty</t>
+          <t>65ef22b-dirty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.3080000000000001</v>
+        <v>0.4770000000000002</v>
       </c>
     </row>
     <row r="159">
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.6020000000000002</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="160">
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.6970000000000002</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="162">
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7.460999999999999</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="163">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2.568</v>
+        <v>3.974</v>
       </c>
     </row>
     <row r="164">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>11.659</v>
+        <v>17.849</v>
       </c>
     </row>
     <row r="165">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.3095909999999999</v>
+        <v>0.4823419999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.59902</v>
+        <v>1.004327</v>
       </c>
     </row>
     <row r="168">
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.697962</v>
+        <v>1.079192</v>
       </c>
     </row>
     <row r="170">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7.460197000000001</v>
+        <v>11.269779</v>
       </c>
     </row>
     <row r="171">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2.564164</v>
+        <v>3.97445</v>
       </c>
     </row>
     <row r="172">
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>11.658973</v>
+        <v>17.848511</v>
       </c>
     </row>
     <row r="173">
